--- a/UAE_EU_Outreach AH Structures.xlsx
+++ b/UAE_EU_Outreach AH Structures.xlsx
@@ -451,12 +451,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -482,7 +482,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="44" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Mercon Steel Structures B.V.</t>
@@ -490,12 +490,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Dutch multidisciplinary steel construction contractor based in Gorinchem. Fabricates modules, platforms, drilling packages, substructures and derricks for offshore and onshore oil &amp; gas and renewable energy clients, with yards at Gorinchem and Kinderdijk, plus maintenance/repair services.</t>
+          <t>Multidisciplinary steel construction contractor fabricating modules, platforms, drilling packages, substructures and derricks for offshore/onshore oil &amp; gas and renewables, yards at Gorinchem and Kinderdijk.</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>J. van der Kamp, General Director. No verified individual email found; contact via mercon.com website contact form.</t>
+          <t>J. van der Kamp, General Director. General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -504,7 +504,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1">
+    <row r="3" ht="44" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Heerema Marine Contractors (HMC)</t>
@@ -512,12 +512,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Major Dutch offshore construction contractor headquartered in Leiden, operating some of the largest heavy-lift and pipelay crane vessels in the offshore industry; active in oil &amp; gas and offshore wind installation and decommissioning.</t>
+          <t>Major offshore construction contractor operating some of the largest heavy-lift and pipelay crane vessels in the industry; active in oil &amp; gas and offshore wind installation/decommissioning.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>General contact only (recruitment@hmc-heerema.com is recruitment-specific, not a business contact); reach out via heerema.com/get-in-touch for business inquiries.</t>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -526,289 +526,6581 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="44" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>EEW Group (EEW Special Pipe Constructions GmbH)</t>
+          <t>Heerema Fabrication Group - Vlissingen Yard</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Germany-headquartered global manufacturer of monopiles, jackets, pin piles and structural pipes for offshore wind farms; has produced 2,200+ monopiles, primarily for European wind projects, with plants including Rostock.</t>
+          <t>Yard specially equipped for EPC(I) of offshore structures and construction of jackets of all sizes, part of the Heerema group.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Frank Benfer, General Manager Sales - Structural Pipes (Monopiles). General company email: info@eew-group.com.</t>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Erndtebrück, Germany - Priority A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+          <t>Vlissingen, Netherlands - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Cuxhaven Steel Construction GmbH (CSC, BARD Group subsidiary)</t>
+          <t>Smulders HSM (HSM Offshore Energy)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Steel fabricator based in Cuxhaven, a major German offshore industry hub, producing foundation structures for offshore wind since 2007; part of the BARD Group.</t>
+          <t>Leading position in fabrication/integration of high-voltage substations and offshore wind foundation structures; track record of 3.6+ GW connected across Europe.</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Bertram Liebler, Managing Director. No verified email found; contact via company/LinkedIn listing.</t>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Netherlands - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SIF Netherlands B.V.</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>75-year-old pioneer in offshore foundations based in Maasvlakte, Rotterdam; monopiles are its flagship product for offshore wind turbine installation.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam Offshore Group</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Offers conversions, ship repair, port/voyage maintenance, heavy-lift floating cranes, and steel construction work for offshore wind mobilization/demobilization.</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>VDS Rotterdam B.V.</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Extensive experience in offshore fabrication across various countries and seas worldwide.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Offshore &amp; Marine Supply Rotterdam (OMS)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Marine and offshore supply company serving the Rotterdam port area.</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Damen Shipyards Group</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Global Dutch shipbuilding/engineering conglomerate producing warships, yachts, fishing vessels, barges, merchant vessels and dredgers (mixed commercial/naval).</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Gorinchem, Netherlands - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Royal IHC (incl. IHC Dredge Equipment)</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Multinational shipbuilder and equipment manufacturer for dredging and offshore vessels/equipment.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Kinderdijk, Netherlands - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Royal Huisman</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilder specializing in newbuild sailing and unique motor superyachts.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Vollenhove, Netherlands - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Huisman Equipment</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Worldwide supplier of heavy-lift cranes and step-changing offshore equipment for oil &amp; gas, renewable energy and civil markets.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Schiedam, Netherlands - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Barge Master</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Developer of motion-compensated gangway and offshore access systems (with Bosch Rexroth) for offshore wind and marine operations.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Damen Shiprepair Rotterdam</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Repair shipyard in the port of Rotterdam.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Saltwater</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Offshore engineering and naval architecture firm covering ship design &amp; conversion, maritime engineering and on-site services.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>H2Offshore Engineering B.V.</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Dutch engineering company specialised in transportation, installation and removal engineering for offshore oil, gas and wind farm projects.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Hendrik Veder Group</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Rigging and lifting equipment supplier for marine/offshore, with operations in Netherlands, Norway, UK and Poland.</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Enersea</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Offshore wind structures specialist; engineers experienced in monopile, transition piece and secondary steel design.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>EEW Special Pipe Constructions GmbH (EEW Group)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Global manufacturer of monopiles, jackets and pin piles for offshore wind; 2,200+ monopiles produced, plants in Erndtebrück and Rostock.</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Frank Benfer, General Manager Sales - Structural Pipes (Monopiles). General email: info@eew-group.com.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Erndtebrück / Rostock, Germany - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Cuxhaven Steel Construction GmbH (CSC, BARD Group)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Steel fabricator producing offshore wind foundation structures since 2007 in the Cuxhaven offshore industry hub.</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Bertram Liebler, Managing Director. General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>Cuxhaven, Germany - Priority B</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>DEME Germany (DEME Group)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Marine engineering/dredging contractor active in Germany for ~50 years, involved in installation of multiple German offshore wind farms.</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Bremen, Germany - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Deutsche Windtechnik</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Leading independent technical maintenance/service provider for offshore wind turbines.</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Bremen, Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Meyer Werft</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Major shipbuilder (founded 1795) constructing large cruise ships and specialised vessels.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Papenburg, Germany - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Lürssen</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>World's largest yacht builder with some naval-adjacent work; multiple shipbuilding sites in northern Germany.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Bremen-Vegesack, Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Fassmer</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilder of custom special-purpose vessels, lifeboats and deck equipment.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Berne, Germany - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Nordic Yards Wismar</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard (formerly Wismar shipyard) producing specialised vessels; owned by Genting Hong Kong.</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Wismar, Germany - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Neptun Werft GmbH</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard founded 1850, delivered 1,500+ new ships, now part of Meyer group producing river cruise vessels.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Rostock-Warnemünde, Germany - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>German Naval Yards Kiel</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilder specialising in design/construction of naval vessels (frigates, corvettes) - defense-primary.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Kiel, Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BVT Bremen GmbH &amp; Co. KG</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Provides offshore wind energy services from Bremen.</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Bremen, Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="44" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Skyborn Renewables (Germany)</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Offshore wind developer/operator with offices in Hamburg, Bremen, Rostock and Leer.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg, Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Adwen GmbH (now Siemens Gamesa Renewable Energy Deutschland GmbH)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Former offshore wind turbine/service company headquartered in Bremerhaven, now part of Siemens Gamesa.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Bremerhaven, Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="44" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>WeserWind Offshore Construction (Georgsmarienhütte)</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Designs and manufactures heavy-duty steel offshore foundation structures in Bremerhaven.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Bremerhaven, Germany - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="44" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Deutsche WindGuard</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Operates a wind-tunnel test centre in Bremerhaven offering aerodynamic testing for rotor blades.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Bremerhaven, Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Bladt Industries A/S</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Danish steel fabricator headquartered in Aalborg, specializing in offshore wind foundations (monopiles, jackets) and complex steel structures; formed offshore-structure joint ventures with EEW Group.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Anders Søe-Jensen, CEO. No verified company email found; contact via bladt.dk/contact.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Steel fabricator specialising in offshore wind foundations (monopiles, jackets); offshore-structure joint ventures with EEW Group.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Anders Søe-Jensen, CEO. General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Aalborg, Denmark - Priority A</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>MT Højgaard Holding A/S</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Danish construction and civil engineering group headquartered near Copenhagen (Søborg), active in bridges, buildings and offshore wind turbine foundation installation.</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>No named individual contact found; general inquiries via company website.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Construction/civil engineering group active in bridges, buildings and offshore wind turbine foundation installation.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Søborg, Denmark - Priority B</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Odense Maritime Technology (OMT)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Naval architecture and ship-design advisory firm with heritage from the former Odense Steel Shipyard (est. 1917).</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Odense, Denmark - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Fayard A/S</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard (founded 1916) specialising in shipbuilding and repair.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Munkebo, Denmark - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="44" customHeight="1">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Ørskov Yard</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilder founded 1958.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Frederikshavn, Denmark - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="44" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Semco Maritime</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Offshore wind EPC firm offering full-scope engineering from FEED to detailed design; designed/built 20+ offshore substations.</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Esbjerg, Denmark - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="44" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Esvagt</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Offshore support vessel operator serving offshore wind and oil &amp; gas (standby, emergency response, rescue).</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Esbjerg, Denmark - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CS Wind Offshore A/S</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>450,000 m2 offshore wind tower manufacturing facility with workshops for painting, blasting, rolling and welding.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Aalborg, Denmark - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="44" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Titan Wind Energy (Europe) A/S</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Wind turbine tower manufacturer with production facilities in Denmark and Germany.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Denmark - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Welcon A/S</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Steel tower manufacturer for offshore wind, known for engineering quality; partnered with Marmen (Canada) on offshore tower fabrication.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Denmark - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="44" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>A2SEA</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Historic offshore wind farm installation/service vessel operator based in Fredericia.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Fredericia, Denmark - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="44" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Vestas Wind Systems A/S</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Major wind turbine OEM designing/manufacturing/installing/servicing offshore turbines, towers and blades.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Aarhus, Denmark - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="44" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Eiffage Métal</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>French steel construction specialist (part of the Eiffage Group), headquartered near Paris, with 50 years of experience building sea-based structures; a major fabricator of jackets and foundations for fixed offshore wind and expanding into floating wind in the Mediterranean.</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Arnaud De Villepin, Director Energy &amp; Industry. No verified individual email found; contact via eiffagemetal.com.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Steel construction specialist (Eiffage Group) with 50 years of sea-based structure experience; major fabricator of jackets/foundations for fixed offshore wind, expanding into floating wind.</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Arnaud De Villepin, Director Energy &amp; Industry. General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Vélizy-Villacoublay, France - Priority A</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Setec Offshore Wind (Setec Group)</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>French engineering firm (division of Setec Group, HQ Paris) specializing in offshore structure and substation design - geotechnical, structural, electrical, mechanical and installation-method engineering for offshore wind.</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Engineering firm specialising in offshore structure and substation design (geotechnical, structural, electrical, mechanical, installation methods).</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Pascal Ochoa, Managing Director. General email: offshorewind@setec.com.</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Paris, France - Priority A</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Chantiers de l'Atlantique</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Europe's largest shipyard, building commercial, naval and passenger ships; sites also in Brest, Toulon, La Réunion, La Martinique.</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Nazaire, France - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="44" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Damen Shiprepair Brest</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Repair yard with three dry docks (largest 420x80m); large workshops for steelwork, mechanical work, LNG equipment and pipefitting.</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Brest, France - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="44" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>BW Ideol</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Floating offshore wind foundation designer/developer, partnering with NGE on a floating-foundation manufacturing facility in southern France.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>France - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>NGE (via Fos3F joint venture)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>French construction group entering floating offshore wind via a 50% stake in BW Ideol's Fos-sur-Mer serial production line.</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>France - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="44" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>VALOREM Group / VALEMO</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Offshore wind developer active since 2014, with an engineering office and O&amp;M subsidiary (VALEMO).</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>France - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="44" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Saipem (France)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Global offshore engineering/construction major with an offshore competency centre in France; designs/builds fixed and mobile platforms, subsea pipelines.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Quentin-en-Yvelines, France - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="44" customHeight="1">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Haizea Wind Group</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Spanish manufacturer (Basque Country) founded 2017, specializing in design, fabrication and assembly of large metal structures and cast components for onshore and offshore wind towers and foundations.</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer of large metal structures/cast components for onshore and offshore wind towers and foundations; Bilbao factory has largest berthing capacity in Europe.</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Borja Zarraga Suarez, CEO. General email: info@haizeawindgroup.com.</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Zierbena, Spain - Priority A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Zierbena / Bilbao, Spain - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="44" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>WindWaves (Offshore WindWaves S.L., Grupo Amper)</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Spanish company (formerly Nervión Naval Offshore) specializing in the design, engineering and manufacture of fixed and floating support structures for offshore wind turbines.</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Formerly Nervión Naval Offshore; designs/engineers/manufactures fixed and floating support structures for offshore wind, expanding infrastructure in Ferrol.</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Diego Río, Director de Operaciones Offshore Wind España. General email: comunicacion@windwaves.com.</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Spain (Grupo Amper) - Priority B</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Ferrol, Spain - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="44" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Windar Renovables</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer of offshore wind foundations, strategic partnership with Navantia for a one-stop offshore service.</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Avilés, Spain - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="44" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Navantia, S.A.</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>State-owned shipbuilder for civil and military naval construction, also producing structures for offshore wind/hydrogen; sites in Ferrol, Cádiz, Cartagena, Madrid.</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Ferrol / Cádiz / Cartagena, Spain - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Iberian Offshore</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Engineering provider with fixed-bottom offshore wind experience, including foundation and monopile design.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Spain - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="44" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>IberBlue Wind</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Joint venture (Simply Blue Group, Proes Consultores/Grupo Amper, FF New Energy Venture) for floating offshore wind farm design/development.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Spain - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="44" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Proes Consultores (Grupo Amper)</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Engineering division of Grupo Amper providing offshore wind structural/foundation design services.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Spain - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="44" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Acebrón Group</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer of mechanically welded foundation components for offshore wind power.</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Spain - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="44" customHeight="1">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Vigo Marine Services S.L. (VMS)</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Supplies and provides technical assistance for shaft and rudder line equipment; Vigo is a major European Atlantic ship-repair hub.</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Vigo, Spain - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Remazel Engineering S.p.A. (Fincantieri subsidiary)</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Designs/manufactures critical handling, lifting, anchoring and launch/recovery systems for offshore oil &amp; gas, offshore/floating wind and subsea sectors.</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Chiuduno, Italy - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="44" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>COSMI S.p.A.</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Italian company based in Ravenna with 40+ years of experience in heavy steel structures construction, supplying wind turbine components and other critical elements of the offshore/onshore energy supply chain.</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>No named individual contact found; general inquiries via gruppocosmi.com/contact-us or phone +39 0544 605111.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>40+ years of heavy steel structures construction, supplying wind turbine components and offshore/onshore energy supply-chain elements.</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Ravenna, Italy - Priority B</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Remazel Engineering S.p.A. (Fincantieri subsidiary)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Italian engineering company headquartered in Chiuduno, specializing in the design and manufacture of critical equipment (handling, lifting, anchoring, launch and recovery systems) for offshore oil &amp; gas, offshore/floating wind, and subsea/underwater sectors; owned by Fincantieri.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>No named individual contact found; general email: info@remazel.com.</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Chiuduno, Italy - Priority A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="66" ht="44" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Fincantieri S.p.A.</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Major shipbuilder (7,000+ vessels over 230 years) expanding into offshore engineering via acquisitions.</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Trieste, Italy - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="44" customHeight="1">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>CI.MAR Shipyard (Cimolai-Mariotti)</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Joint venture between Genoa shipbuilder T. Mariotti and steel manufacturer Cimolai.</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>San Giorgio di Nogaro, Italy - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="44" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Genova Industrie Navali (Mariotti + San Giorgio del Porto)</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Group uniting two historic Genoa shipyards - ultra-luxury cruise ship construction and ship repair/conversion.</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="44" customHeight="1">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Saipem S.p.A.</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Global leader in design/construction of offshore plants (fixed/mobile platforms, subsea pipelines); Sardinia (Arbatax) facility fabricates HVAC offshore substations.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>San Donato Milanese, Italy - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="44" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Ship Projects Engineering &amp; Contracting (S.P.E.C)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Naval architects and marine engineers designing/building offshore and other vessel types since 1994.</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Italy - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="44" customHeight="1">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Intermarine</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilder (founded 1970) specialising in fibre-reinforced plastic hull vessels.</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="44" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Acier Steel S.R.L.</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard-area operator/workshop in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="44" customHeight="1">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Amico &amp; Co. S.R.L.</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard-area operator/workshop in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="44" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Cantieri Navali Genovesi S.R.L.</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="44" customHeight="1">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Enrico Polipodio S.R.L.</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Marine/ship service workshop operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="44" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Ente Bacini S.R.L.</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Dry-dock/ship repair operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>GB Shipyard S.R.L.</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="44" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Genoa Sea Service S.R.L.</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Marine services operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="44" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Lagomarsino Anielli S.R.L.</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Ship repair/workshop operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="44" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Luigi Amico S.R.L.</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Ship repair/workshop operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="44" customHeight="1">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Naval Diesel S.R.L.</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Marine engine/diesel repair workshop in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="44" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Navalsider Porto S.R.L.</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Steel/ship repair workshop operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="44" customHeight="1">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Officina Diesel S.R.L.</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Marine engine workshop operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="44" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Ortec Santamaria S.R.L.</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Ship repair/workshop operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="44" customHeight="1">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Otam S.R.L.</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Ship repair/workshop operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="44" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Piaggio &amp; Figli S.R.L.</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Ship repair/workshop operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="44" customHeight="1">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Ranieri Tonissi S.p.A.</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Ship repair/workshop operator in the Port of Genoa.</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="44" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>TK Tuzla Shipyard</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Largest ship repair facility in Tuzla Bay, offering repair and conversion services.</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="44" customHeight="1">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Çeksan Shipyard</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>65+ year shipbuilding/repair yard, 85+ delivered vessel projects (chemical tankers, ferries, heavy-duty barges, specialised marine vessels).</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="44" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Gemak Group (incl. Gemak Neta Steel &amp; Pipe Fabrication Yard)</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Group of shipyards (Tuzla, TGE, Neta, Altinova) covering shipbuilding and steel/pipe fabrication.</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla / Altınova, Turkey - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="44" customHeight="1">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Anadolu Shipyard</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard located in Tuzla, Istanbul.</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="44" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Sedef Shipyard</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard established 1990 in Tuzla, Istanbul.</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="44" customHeight="1">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Argem Shipyard</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard established 1999 in Tuzla, Istanbul.</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="44" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Art Shipyard</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard established 1975 in Tuzla, Istanbul.</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="44" customHeight="1">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SeAh Wind</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>UK corporation (est. Feb 2021) building the world's largest monopile manufacturing plant in Teesside.</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Teesside, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="44" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Smulders Group (Wallsend yard)</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Fabricates jacket foundations and transition pieces for offshore wind turbines from its Wallsend yard, North East England.</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Wallsend, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="44" customHeight="1">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>MTE</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Produces fabricated products for offshore wind farms - material prep, fabrication, welding and assembly for carbon/stainless/duplex steel.</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="44" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>ESC Steel Structures</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Specialises in heavy offshore structure fabrication for general marine, offshore renewables and oil &amp; gas industries.</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="44" customHeight="1">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>WEC Fabrication</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>45+ years delivering fabrication/construction services to Offshore, Oil &amp; Gas and Renewable Energy sectors.</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="44" customHeight="1">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Durata Group</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>UK manufacturer qualified to produce aluminium handrails/ladders for offshore wind turbine transition pieces.</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="44" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Harland &amp; Wolff</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding/fabrication company (HQ London) with sites in Belfast, Arnish, Appledore and Methil; ship repair, shipbuilding and offshore construction (mixed commercial/defense).</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Belfast, UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="44" customHeight="1">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Cammell Laird</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Storied British shipbuilder; built RRS Sir David Attenborough, holds ongoing Royal Navy/RFA dry-dock and refit work (defense-heavy).</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Birkenhead, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="44" customHeight="1">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>A&amp;P Group</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Refit/maintenance yards (Falmouth, Tyne) serving Royal Fleet Auxiliary and offshore energy/defence fabrication work (mixed).</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Falmouth / Tyne, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="44" customHeight="1">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Subsea 7 S.A.</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Major offshore engineering, construction and project management services provider.</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Sutton, Greater London, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="44" customHeight="1">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Acteon Group Ltd</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Global services organisation focused on seabed-to-surface subsea services and structural integrity.</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="44" customHeight="1">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Orcina Ltd</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Structural and hydrodynamic consultancy for the offshore oil &amp; gas sector, established 1986.</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="44" customHeight="1">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>RES Group</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>30+ years offshore experience providing long-term operations &amp; maintenance (O&amp;M) packages for offshore wind.</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="44" customHeight="1">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>CWind</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Supports 12+ GW of power generation across UK/European wind farms with maintenance and repair solutions.</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="44" customHeight="1">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Briggs Marine</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Supports all phases of UK offshore wind farms from planning/development through O&amp;M.</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Burntisland, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="44" customHeight="1">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>BiFab (Burntisland Fabrications, now Harland &amp; Wolff)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Steel fabrication for renewable, oil &amp; gas (and defense-adjacent) sectors; yards at Methil and Arnish.</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Methil / Arnish, UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="44" customHeight="1">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Global Energy Group</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Manufacture, assembly and factory acceptance testing services; assembles turbines and manufactures offshore wind infrastructure products.</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Inverness, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="44" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Custom Steel Design</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Steel fabrication company covering Cardiff, Newport, Bridgend, Swansea and surrounding South Wales.</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Barry, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="44" customHeight="1">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Cardiff Steels</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Steel supplier serving Cardiff, Swansea, Newport and Bristol.</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Cardiff, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="44" customHeight="1">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>AB Metal Fabricators Ltd</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Steel fabricator providing services in Cardiff, Newport and South Wales.</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Caerphilly, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="44" customHeight="1">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>CJN Engineering</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Fabrication in mild steel, stainless steel and aluminium - design through installation, based in Newport.</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Newport, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="44" customHeight="1">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Walden Steels Ltd</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Bespoke steelwork fabricator in Newport, Gwent.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Newport, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="44" customHeight="1">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>UK Steel Centre</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer of bespoke stainless steel/sheet metal products and structural steel supply/fabrication for South Wales.</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>South Wales, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="44" customHeight="1">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Ulstein Group ASA</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Group of ~30 companies covering shipbuilding, ship design, diesel engines, propulsion and hydraulic deck machinery; founded 1917.</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Ulsteinvik, Norway - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="44" customHeight="1">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Umoe Mandal AS</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilder specialising in high-speed naval vessels, mine countermeasure vessels and fast patrol boats (defense-primary).</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Mandal, Norway - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="44" customHeight="1">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Grenland Framnæs (formerly Hitec Framnæs)</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Design/engineering company for oil &amp; gas, marine and process industries.</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Sandefjord / Stavanger, Norway - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="44" customHeight="1">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>STX Norway Design Florø AS</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Naval architecture/marine engineering firm supplying complete design/construction/drawing packages for newbuilds.</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Florø, Norway - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="44" customHeight="1">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Aas Mek. Verksted A/S</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard building modern live fish carriers (aquaculture-focused marine fabrication).</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Norway - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="44" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Jotne Group</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Structural engineering, design, fabrication and construction company (~250 employees, multiple Norwegian facilities).</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Norway - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="44" customHeight="1">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>eSubsea AS</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Subsea engineering specialist - structural, piping and finite element analysis (FEA) design and consultancy.</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Norway (near Oslo) - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="44" customHeight="1">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Havport AS</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Engineering firm specialising in naval architecture, offshore structural engineering and subsea solutions for maritime/oil &amp; gas.</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Norway - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="44" customHeight="1">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Naval Dynamics AS</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Independent marine engineering company for offshore and shipping industry concept development.</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Norway - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="44" customHeight="1">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GeoProvider</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Marine geoscience/geotechnics consultancy for offshore wind, E&amp;P and seabed minerals site surveys.</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Norway - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="44" customHeight="1">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>ShipCAD AS</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Independent engineering company providing engineering services to shipyards, ship-owners and offshore yards.</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland, Norway - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="44" customHeight="1">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Aibel</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Offshore substations/topsides EPC provider.</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Haugesund, Norway - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="44" customHeight="1">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Smulders Projects Belgium</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>International steel construction company (1,000+ employees across BE/NL/UK/PL), member of the Offshore Wind Foundations Alliance.</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Hoboken, Belgium - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="44" customHeight="1">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>ENGIE Fabricom (Equans)</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Part of a consortium for EPC of offshore substations in Belgian wind farms; design coordination/integration at Hoboken yard.</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Hoboken, Belgium - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="44" customHeight="1">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Jan De Nul</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Belgian marine construction/dredging company active in offshore renewable energy since 2012.</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Hofstade-Aalst, Belgium - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="44" customHeight="1">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>DEME Group</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Major dredging/marine engineering group, involved in offshore installation across Europe.</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Zwijndrecht, Belgium - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="44" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>ArcelorMittal Belgium</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Develops steel solutions for wind turbines (up to 285 tons of steel per turbine); primarily a raw-material producer.</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Ghent, Belgium - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="44" customHeight="1">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Gdańsk Shipyard (Stocznia Gdańska)</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Large historic shipyard in northern Poland.</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Gdańsk, Poland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="44" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>CRIST S.A.</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard (Port of Gdynia, founded 1990) producing offshore-industry ships including wind turbine installation vessels.</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Gdynia, Poland - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="44" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Szczecin Shipyard (Stocznia Szczecińska Nowa)</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard specialising in container ships, chemical tankers, multi-purpose vessels and ConRo ships.</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Szczecin, Poland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="44" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Marine Projects Ltd.</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Established 1989; complete ship construction plus technical/engineering documentation for the shipbuilding industry.</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Poland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="44" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Damen Engineering Gdansk</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Competence centre (est. 2013) for engineering-to-order, one-offs and prototype vessels.</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Gdańsk, Poland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="44" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Naviretech</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Construction of new floating units, ship modernization and repair of offshore/land structures.</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Poland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="44" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Remontowa Group</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>One of the largest shipbuilding-sector companies in Poland.</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Gdańsk, Poland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="44" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>ICD Poland (Vard group)</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding operation developing in Pomerania as part of the Vard group.</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Poland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="44" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Kongsberg Maritime Poland</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Polish subsidiary of Kongsberg Maritime equipment/systems supplier.</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Poland - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="44" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Shoreline Engineering</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Precision fabrication and emergency repairs, custom metal structures/components for marine vessels.</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Cork, Ireland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="44" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>IMC Marine and Offshore Engineering (IMC Industrial Group)</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Multi-disciplinary engineering services, project management, procurement and fabrication for marine/offshore clients.</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Ireland - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="44" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Irish Sea Contractors</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Nearshore fibre-optic/power cable installation, marine civil engineering and diving services.</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Ireland - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="44" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Marine Technology Limited (MTL)</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Design and manufacture services including high-precision fabrication and prototype development.</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Ireland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="44" customHeight="1">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Doran Consulting</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Marine and river engineering consultancy active since 1993.</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Ireland - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="44" customHeight="1">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Boghammar Marin</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Swedish shipbuilder of fast craft/patrol boats.</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Sweden - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="44" customHeight="1">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>FKAB Marine Design</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Ship design house.</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Sweden - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="44" customHeight="1">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Saab Kockums</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Naval shipbuilder (submarines/surface combatants) - defense-primary.</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Malmö, Sweden - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="44" customHeight="1">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Wallenius Marine</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Ship design and shipowning group.</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="44" customHeight="1">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Swede Ship Marine (Djupvik Shipyard)</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Specialized shipyard group (Djupvik, Swede Ship Composite, Swede Ship Yachtservice) on Sweden's west coast; building ships since the 1890s.</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Sweden - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="44" customHeight="1">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Delta Marine Scandinavia</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Constructs customized steel/aluminium port vessels; prefabricates ship parts.</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Sweden - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="44" customHeight="1">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Nimbus Boats AB</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Leisure boat manufacturer.</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Sweden - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="44" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Scanjet Marine</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Marine tank-cleaning equipment manufacturer, Gothenburg.</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Gothenburg, Sweden - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="44" customHeight="1">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>SSAB</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Primary Swedish supplier of high-strength steel plate/coil for marine hulls and offshore platforms; raw-material producer.</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Sweden - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="44" customHeight="1">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Meyer Turku Oy</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilder specialising in cruise ships and cruiseferries.</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Turku, Finland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="44" customHeight="1">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Wärtsilä</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Major marine engine, propulsion systems and lifecycle solutions provider.</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki, Finland - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="44" customHeight="1">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Aker Arctic Technology</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Arctic/ice-class ship and structure engineering specialist.</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki, Finland - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="44" customHeight="1">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Marine Alutech Oy Ab</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Designer/manufacturer of aluminium and composite boats (5-27m) for navies, coast guards, government agencies and ports.</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Finland - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="44" customHeight="1">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>ABB Marine &amp; Ports (Finland)</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Marine electrical systems and ports equipment supplier.</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Finland - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="44" customHeight="1">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Kongsberg Maritime Finland</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Finnish subsidiary of Kongsberg Maritime equipment/systems supplier.</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Finland - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="44" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Lisnave Estaleiros Navais S.A.</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Major ship repair yard.</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Setúbal, Portugal - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="44" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Arsenal do Alfeite, S.A.</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>State naval shipyard - defense-primary.</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Almada, Portugal - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="44" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>West Sea - Viana Shipyard</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding/repair yard on Portugal's Atlantic coast.</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Viana do Castelo, Portugal - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="44" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>ENVC S.A.</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Public shipbuilding/repair company (since 1944), Atlantic coast; has faced financial difficulty.</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Viana do Castelo, Portugal - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="44" customHeight="1">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Naval Rocha</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Vessel repair/maintenance yard in Lisbon.</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon, Portugal - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="44" customHeight="1">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Odisseia Teórica LDA</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Repair, maintenance and shipbuilding company (founded 2017), onshore and offshore.</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Portugal - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="44" customHeight="1">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Metalúrgica Fonseca &amp; Flora</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Produces zinc/aluminium sacrificial anodes and machined parts for shipbuilding, repair and maintenance.</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Portugal - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="44" customHeight="1">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>TF Metals (Tribunas &amp; Figueiredo, Lda)</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Metalworking company established 1997.</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Águeda, Portugal - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="44" customHeight="1">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Iberomecânica, Lda.</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Precision metalworking company.</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Santo Tirso, Portugal - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="44" customHeight="1">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Neorion</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>One of the oldest Greek heavy industries (founded 1861), historic shipyard on Syros.</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Ermoupolis, Greece - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="44" customHeight="1">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Skaramangas Shipyards</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Large shipyard (founded 1937), historically linked to Greek Navy work (mixed).</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Skaramagas, Greece - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="44" customHeight="1">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Elefsis Shipyards</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Greek shipbuilding company founded 1968.</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Athens, Greece - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="44" customHeight="1">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Chalkis Shipyards S.A.</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Large shipyard founded 1971.</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Aulis, Evia, Greece - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="44" customHeight="1">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Motomarine S.A.</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Greek shipbuilder founded 1962.</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Koropi, Greece - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="44" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Technava</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Founded 1968; supply, installation and service of shipboard equipment for all vessel types.</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Greece - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="44" customHeight="1">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Spanopoulos Group</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Leading marine construction contractor across the Mediterranean, North Africa and Red Sea.</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Greece - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="44" customHeight="1">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Group Navale</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Naval architecture and marine engineering services provider.</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Greece - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="44" customHeight="1">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>3. Maj (Treći Maj Brodogradilište d.d.)</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Largest shipyard in Croatia (Rijeka); builds oil tankers, bulk carriers, container ships.</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Rijeka, Croatia - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="44" customHeight="1">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Brodosplit d.d.</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Largest shipyard in Croatia by some measures, located on the Split peninsula.</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Split, Croatia - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="44" customHeight="1">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Viktor Lenac Shipyard</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard founded 1896 on the northern Adriatic coast.</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Rijeka, Croatia - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="44" customHeight="1">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Kraljevica Shipyard</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilder on Croatia's Adriatic coast.</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Kraljevica, Croatia - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="44" customHeight="1">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>IHC Engineering Croatia (IEC)</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Subsidiary of Royal IHC.</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Croatia - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="44" customHeight="1">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Brodoplan Ltd.</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilder (est. 1995) known for patrol boats and specialised maritime vessels (defense-leaning).</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Croatia - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="44" customHeight="1">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Brodarski Institut</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Marine engineering and research institute (established 1948).</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Croatia - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="44" customHeight="1">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Damen Shipyards Galati</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>Major shipyard, part of the Damen Group.</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>Galați, Romania - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="44" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Vard Braila</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard part of the Vard group.</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>Brăila, Romania - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="44" customHeight="1">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Santierul Naval Constanta</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard on the Black Sea coast.</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>Constanța, Romania - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="44" customHeight="1">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Vard Tulcea</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard, top-revenue Romanian shipbuilder in 2019.</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>Tulcea, Romania - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="44" customHeight="1">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Damen Shiprepair Mangalia</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Ship repair yard, part of the Damen Group.</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Mangalia, Romania - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="44" customHeight="1">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Marine Engineering Galati (MEGA)</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Damen Schelde Naval Shipbuilding engineering company (100+ employees) providing detailed engineering for hulls, piping and outfitting.</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>Galați, Romania - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="44" customHeight="1">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>NAVALINK Srl.</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>20+ years in marine newbuilds across Europe and vessel dry-docking services around Constanța.</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Constanța, Romania - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="44" customHeight="1">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>BLRT Grupp AS</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding group (50+ companies) headquartered in Tallinn, active across the Baltic/Nordic region.</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn, Estonia - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="44" customHeight="1">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Baltic Workboats AS</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilder specialising in aluminium/steel workboats - patrol vessels, pilot boats, ferries.</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>Estonia - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="44" customHeight="1">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Riga Shipyard (JSC)</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>One of the largest shipyards in the Baltic region.</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>Riga, Latvia - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="44" customHeight="1">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>BLRT Western Shipyard</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard in Klaipėda, part of the BLRT Grupp.</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Klaipėda, Lithuania - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="44" customHeight="1">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Navalis Group</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding/offshore construction services operating across Estonia, Latvia, Lithuania, Netherlands, Germany and Finland.</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Baltic region - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="44" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Bourgas Shipyards JSC</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding and ship repair company.</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>Burgas, Bulgaria - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="44" customHeight="1">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Rousse Shipyard West JSC</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Specialises in construction of new river and sea-going vessels.</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>Ruse, Bulgaria - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="44" customHeight="1">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>NOVAGLASS LTD</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding and ship repair services provider.</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>Sofia, Bulgaria - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="44" customHeight="1">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>PBM Bulgaria</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Operates a workshop at Odessos Shipyard.</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>Varna, Bulgaria - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="44" customHeight="1">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Baier Marine CME Ltd.</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Marine/shipbuilding services company.</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Cyprus - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="44" customHeight="1">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Shipyard Famagusta Ltd.</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding/repair yard.</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Famagusta, Cyprus - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="44" customHeight="1">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Nexans</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Designs/manufactures high-voltage inter-array and export cables for offshore wind.</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Courbevoie, France - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="44" customHeight="1">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Hellenic Cables</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Provides export and inter-array cable packages for offshore wind farms.</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Greece - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="44" customHeight="1">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Ali &amp; Sons Marine Engineering Factory (ASMEF) / Emarat Aloula Industries</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>One of the largest marine engineering/fabrication facilities in the UAE - 280,000 m2 yard, 545m unrestricted waterfront.</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Mussafah, Abu Dhabi, UAE - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="44" customHeight="1">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi Ship Building (ADSB)</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Established 1996; construction, repair and refit of naval and commercial vessels (mixed defense/commercial).</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="44" customHeight="1">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi MAR (ADM)</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding group, one of the leading shipbuilders in the Persian Gulf.</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="44" customHeight="1">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>ADSO Group of Companies</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Marine contracting company providing comprehensive marine contracting services.</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="44" customHeight="1">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>OceanSi</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Delivers industrial heavy machinery, offshore marine cranes, ROV launch &amp; recovery systems and custom industrial fabrication.</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="44" customHeight="1">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Drilltech UAE</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Designs/manufactures offshore contracted items and aluminum work (oil &amp; gas-leaning).</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="44" customHeight="1">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Al Bawardi Marine Services (ABMS)</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Maritime company providing marine services supporting oil &amp; gas and other maritime sectors.</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="44" customHeight="1">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Latest Mechanical Equipment LLC</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical equipment/fabrication services provider.</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="44" customHeight="1">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Front Line Mechanical Equipment Maintenance LLC</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Mechanical equipment maintenance/fabrication provider.</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="44" customHeight="1">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>APT Global Marine and Offshore Engineering</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Marine engineering and steel-structure fabrication company established 2003, headquartered in Dubai, specializing in shipbuilding, offshore engineering and marine services for the marine, offshore, dredging, oil &amp; gas and renewable-energy sectors; facilities in UAE, India, Qatar, Belgium, Netherlands, Taiwan and USA.</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Marine engineering/steel-structure fabrication company (est. 2003) with facilities in UAE, India, Qatar, Belgium, Netherlands, Taiwan and USA.</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
         <is>
           <t>Beau Yarnold, Managing Director. General email: info@aptglobalmarine.com.</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Dubai / Ras Al Khaimah, UAE - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="44" customHeight="1">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Grandweld Shipyards (Stanford Marine Group)</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Fully integrated shipyard (est. 1984) in Dubai Maritime City - shipbuilding, ship repair and marine engineering solutions.</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Cameron, Head of Sales - Ship Repair, Cameron@grandweld.com. Marawan F., Sales Manager - Ship Building, marawan.f@grandweld.com.</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE - Priority A</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Grandweld Shipyards (Stanford Marine Group)</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Fully integrated shipyard in Dubai Maritime City established 1984, providing shipbuilding, ship repair and marine engineering solutions; part of the Stanford Marine Group.</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Cameron, Head of Sales - Ship Repair, Cameron@grandweld.com. (Also: Marawan F., Sales Manager - Ship Building, marawan.f@grandweld.com.)</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="219" ht="44" customHeight="1">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>McDermott Dubai (McDermott International)</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Global offshore oil &amp; gas EPC major with a Jebel Ali facility (oil &amp; gas-primary).</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="44" customHeight="1">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>SAS International Marine Services LLC</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Marine services company based in Jebel Ali Free Zone.</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="44" customHeight="1">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Schottel Middle East FZE</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Middle East arm of Schottel, supplier of marine propulsion systems.</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="44" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Seaworks ME</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Marine services company in Jebel Ali Free Zone.</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="44" customHeight="1">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Van Oord Gulf FZE</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Gulf arm of Dutch marine contractor Van Oord - dredging and marine construction.</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="44" customHeight="1">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Valbruna Gulf FZE</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Steel distribution company in Jebel Ali Free Zone (raw-material supplier).</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="44" customHeight="1">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Union Dredgers &amp; Marine Contracting (UDMC)</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Marine construction contractor (since 2007) - construction, dredging and offshore pipeline installation.</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="44" customHeight="1">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Tecmark Contracting LLC</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Construction contractor active in JAFZA projects.</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="44" customHeight="1">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Albwardy Damen</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding/ship-repair yards in Dubai, Sharjah and Fujairah, building Damen and non-Damen designs up to 120m.</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Dubai / Sharjah / Fujairah, UAE - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="44" customHeight="1">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>VU Marine</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding company operating across UAE and the Gulf, including boat building in Dubai.</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="44" customHeight="1">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Ocean Connect FZE</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Marine services company - ship repair, dry docking and vessel support across UAE ports.</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="44" customHeight="1">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Inventure Metal Products Industries LLC</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Automated cutting and fabrication capabilities, Dubai Silicon Oasis.</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="44" customHeight="1">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Laser Beam Industry LLC</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Automated cutting/fabrication company in Al Quoz.</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="44" customHeight="1">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Al Baraq Steel</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Steel erection company respected for structural steel contracting across the UAE.</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Ajman / Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="44" customHeight="1">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Standard Steel Fabrication Co LLC</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Established 2009; fabrication assistance to various industrial sectors in the UAE.</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="44" customHeight="1">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Kingston (Middle East Metals)</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Engineering, fabrication and construction across a wide spectrum of industries; sites in Sharjah, Dubai and Abu Dhabi.</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah / Dubai / Abu Dhabi, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="44" customHeight="1">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Yarmouk Steel</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>40+ years in steel fabrication, recognized among Dubai's top steel companies.</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="44" customHeight="1">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Middle East Metals</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Custom industrial steel fabrication and heavy steel structures specialist.</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="44" customHeight="1">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Rukn Al Mizan Metal</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Fabrication and structural steelwork company.</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="44" customHeight="1">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Al Nawras Steel Middle East FZC</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Steel structure fabrication specialist operating from Hamriya Free Zone.</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="44" customHeight="1">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Ghosh Metal Industries LLC</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Fabrication facility with in-house production support.</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="44" customHeight="1">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>SABER-1</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Heavy-lift specialist; completed load-out and float-off operation for jack-up barge Vahana Arjun.</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="44" customHeight="1">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>Phoenix Engineering &amp; Marine Co. LLC (Phoenix Engineering Group)</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>UAE-based onshore/offshore contractor headquartered in Sharjah, providing ship repair and new construction, structural steel work, insulation &amp; cladding, refractory linings and machine tool automation services.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>No named individual contact found; general email: pemco@eim.ae.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Onshore/offshore contractor - ship repair/new construction, structural steel work, insulation &amp; cladding, refractory linings.</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Sharjah, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="44" customHeight="1">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>OSA Engineering Works Est LLC</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Structural steel fabrication company based in Al Sajaa.</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="44" customHeight="1">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Techno Marine Ship Repairing LLC</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>ISO-certified marine repair company - marine repairs, maintenance, fabrication, engine reconditioning, Class survey prep.</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Fujairah, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="44" customHeight="1">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>NICO International</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Marine and industrial repair services across UAE/Middle East - repair, maintenance, refurbishment, fabrication, engineering.</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Dubai / Fujairah / Abu Dhabi, UAE - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="44" customHeight="1">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>AIMAR Marine Services</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Marine services operating across multiple UAE ports including Ajman Port and Umm Al Quwain Port.</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Ajman / Umm Al Quwain, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="44" customHeight="1">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>BMT</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Marine and offshore engineering consultancy providing naval architecture, structural and specialist design services.</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>London, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="44" customHeight="1">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Ramboll UK (Offshore Wind)</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Engineering consultancy with a major offshore wind foundation/structural design practice.</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="44" customHeight="1">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Xodus Group</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Energy consultancy providing engineering, subsea and offshore wind advisory services.</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="44" customHeight="1">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Genesis (TechnipFMC)</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Oil &amp; gas and offshore engineering consultancy (part of TechnipFMC).</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>London, UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="44" customHeight="1">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Wood Group (Wood plc)</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Global engineering and consultancy company serving energy, including offshore oil &amp; gas and renewables.</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen, UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="44" customHeight="1">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Global Maritime</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Marine warranty surveying and offshore engineering consultancy for marine operations.</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>London, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="44" customHeight="1">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>ODE Offshore Design Engineering</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Independent offshore engineering consultancy for oil &amp; gas and renewables projects.</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="44" customHeight="1">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>JDR Cable Systems</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer of subsea power and umbilical cables for offshore wind and oil &amp; gas.</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Hartlepool, UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="44" customHeight="1">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Houlder</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Marine and offshore engineering consultancy specialising in ship design and offshore renewables.</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>London, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="44" customHeight="1">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Frazer-Nash Consultancy</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Systems and engineering consultancy with a marine/offshore structural engineering practice.</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="44" customHeight="1">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Aker Solutions</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Engineering and construction services provider for offshore oil &amp; gas and renewable energy projects.</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Norway - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="44" customHeight="1">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Kvaerner</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>EPC contractor for offshore platforms, substructures and onshore facilities.</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Norway - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="44" customHeight="1">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>TechnipFMC Norway</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Norwegian arm of the global subsea/offshore engineering and technology group.</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Norway - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="44" customHeight="1">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>DNV</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Classification society and technical advisor providing naval architecture, structural engineering and standards for offshore/marine structures.</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>Høvik, Norway - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="44" customHeight="1">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Reinertsen</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Norwegian engineering company delivering structural, mechanical and offshore engineering services.</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Trondheim, Norway - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="44" customHeight="1">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Multiconsult</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Norwegian multidisciplinary consultancy with marine/offshore structural engineering capability.</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Norway - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="44" customHeight="1">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Ørsted A/S</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>World's largest offshore wind developer/operator, headquartered in Denmark.</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Fredericia, Denmark - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="44" customHeight="1">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>RWE Offshore Wind GmbH</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Major German utility's offshore wind development/operations arm.</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg, Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="44" customHeight="1">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Vattenfall Offshore Wind</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Swedish state-owned utility's offshore wind development/operations arm.</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="44" customHeight="1">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Iberdrola (Offshore Wind)</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Major Spanish utility with a large offshore wind development portfolio.</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Bilbao, Spain - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="44" customHeight="1">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>EDF Renewables (Offshore Wind)</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>French utility's renewable energy arm, active in offshore wind.</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Paris, France - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="44" customHeight="1">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>SSE Renewables</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>UK/Irish utility's renewable energy arm with a large offshore wind portfolio.</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Glasgow, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="44" customHeight="1">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>ScottishPower Renewables</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>UK renewable energy developer (Iberdrola subsidiary) active in offshore wind.</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Glasgow, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="44" customHeight="1">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Ocean Winds</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Joint venture (EDP Renewables/Engie) offshore wind developer active across Europe.</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Madrid, Spain - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="44" customHeight="1">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Equinor</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Norwegian energy major with a significant offshore wind (and oil &amp; gas) portfolio.</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Stavanger, Norway - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="44" customHeight="1">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>EnBW</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>German utility with an offshore wind development/operations portfolio.</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="44" customHeight="1">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Shell (Offshore Wind)</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>Global energy major with a growing offshore wind development portfolio.</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>The Hague, Netherlands - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="44" customHeight="1">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>TotalEnergies (Offshore Wind)</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>French energy major with an offshore wind development portfolio.</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Paris, France - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="44" customHeight="1">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>BP (Offshore Wind)</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>UK-based energy major with an offshore wind development portfolio.</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>London, UK - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="44" customHeight="1">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Northland Power (Europe)</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Canadian-headquartered developer with major European offshore wind assets.</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands/Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="44" customHeight="1">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Eneco</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Dutch energy company active in offshore wind development.</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="44" customHeight="1">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Van Oord</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>150-year-old Dutch marine contractor designing/building offshore wind farms in Europe, Asia and the USA.</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="44" customHeight="1">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Boskalis</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Dutch dredging and marine services group active in offshore energy installation.</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Papendrecht, Netherlands - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="44" customHeight="1">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Seaway7 (Subsea7)</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>Offshore wind installation specialist (part of Subsea7), delivering foundations and cable installation.</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Norway - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="44" customHeight="1">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>GVA Consultants</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>Swedish/Norwegian structural and marine engineering/design consultancy.</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Gothenburg, Sweden - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="44" customHeight="1">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Semco Maritime (Germany operations)</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>German arm of the Danish offshore wind EPC firm Semco Maritime.</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Germany - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="44" customHeight="1">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Gmmostech</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding and repair services provider in the Dubai/Sharjah/Ajman/Umm Al Quwain area.</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="44" customHeight="1">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Adams Marine</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding and repair services provider in the UAE.</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="44" customHeight="1">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Triangle Marine Services</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Shipbuilding and repair services provider in the UAE.</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="44" customHeight="1">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Hamriyah Free Zone Fabrication Cluster (general)</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Cluster of steel and marine fabrication companies operating from Hamriyah Free Zone, Sharjah.</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah, UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="44" customHeight="1">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Emirates Technical Associates (ETA)</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>Engineering and industrial fabrication services provider in the UAE.</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>UAE - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="44" customHeight="1">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Malta Shipyards (Palumbo Malta)</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>Ship repair and conversion yard (part of the Palumbo Group), a major Mediterranean drydock facility.</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>Marsa, Malta - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="44" customHeight="1">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia marine/steel fabrication sector (no single dominant firm identified)</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia's registered shipbuilders are mostly small workshops; no single dominant marine structural fabricator was confirmed in this pass - flagged for a deeper follow-up search if needed.</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="44" customHeight="1">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Siemens Gamesa Renewable Energy</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>Major wind turbine OEM with offshore turbine, tower and foundation-adjacent manufacturing across Europe.</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>Zamudio, Spain - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="44" customHeight="1">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>GE Renewable Energy (Offshore Wind)</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>Global turbine OEM with European offshore wind manufacturing operations (Haliade-X).</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Nazaire, France - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="44" customHeight="1">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>GRI Renewable Industries</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>Spanish manufacturer of steel and concrete wind towers, 22 facilities across nine countries.</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Bilbao, Spain - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="44" customHeight="1">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>CS Wind Corporation (Portugal facility)</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>Global wind tower manufacturer with a production facility in Portugal.</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Portugal - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="44" customHeight="1">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>LM Wind Power</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>Rotor blade manufacturer for onshore/offshore wind turbines.</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>Kolding, Denmark - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="44" customHeight="1">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>Flender International GmbH</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturer of gearboxes/drivetrain components for wind turbines.</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>Bocholt, Germany - Priority C</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="44" customHeight="1">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>Wood Thilsted</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>Specialist offshore wind foundation design and structural engineering consultancy.</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>London, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="44" customHeight="1">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>Atkins (Offshore Wind, part of SNC-Lavalin)</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>Major engineering consultancy with an offshore wind structural design practice.</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Epsom, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="44" customHeight="1">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>Xerxes Offshore Engineering</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>Offshore engineering consultancy supporting fixed and floating structure design.</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="44" customHeight="1">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>K2 Management</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>Independent offshore/onshore wind engineering and consultancy firm.</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>London, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="44" customHeight="1">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Natural Power</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>Renewable energy engineering and consultancy firm active in offshore wind.</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>Scotland, UK - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="44" customHeight="1">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Longitude Engineering</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>Independent engineering consultancy specialising in offshore wind foundation design (part of Xodus/Baker Hughes group).</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>London, UK - Priority A</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="44" customHeight="1">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>Temporary Works Design BV</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Dutch engineering firm specialising in temporary works and installation engineering for offshore projects.</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands - Priority B</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="44" customHeight="1">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>GustoMSC (part of NOV)</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Dutch designer of offshore vessels and jack-up rigs for wind installation and oil &amp; gas.</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>Schiedam, Netherlands - Priority A</t>
         </is>
       </c>
     </row>

--- a/UAE_EU_Outreach AH Structures.xlsx
+++ b/UAE_EU_Outreach AH Structures.xlsx
@@ -10,7 +10,7 @@
     <sheet name="UAE &amp; EU Outreach" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'UAE &amp; EU Outreach'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'UAE &amp; EU Outreach'!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,13 +451,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D302"/>
+  <dimension ref="A1:G302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -473,12 +476,27 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Contact (Name, Designation, Email)</t>
+          <t>Contact Name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Location &amp; Priority</t>
+          <t>Designation</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Priority</t>
         </is>
       </c>
     </row>
@@ -495,12 +513,23 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>J. van der Kamp, General Director. General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+          <t>J. van der Kamp</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Gorinchem, Netherlands - Priority A</t>
+          <t>General Director</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Gorinchem, Netherlands</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -515,14 +544,17 @@
           <t>Major offshore construction contractor operating some of the largest heavy-lift and pipelay crane vessels in the industry; active in oil &amp; gas and offshore wind installation/decommissioning.</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Leiden, Netherlands - Priority A</t>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Leiden, Netherlands</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -537,14 +569,17 @@
           <t>Yard specially equipped for EPC(I) of offshore structures and construction of jackets of all sizes, part of the Heerema group.</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Vlissingen, Netherlands - Priority A</t>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Vlissingen, Netherlands</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -559,14 +594,17 @@
           <t>Leading position in fabrication/integration of high-voltage substations and offshore wind foundation structures; track record of 3.6+ GW connected across Europe.</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands - Priority A</t>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -581,14 +619,17 @@
           <t>75-year-old pioneer in offshore foundations based in Maasvlakte, Rotterdam; monopiles are its flagship product for offshore wind turbine installation.</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Rotterdam, Netherlands - Priority A</t>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -603,14 +644,17 @@
           <t>Offers conversions, ship repair, port/voyage maintenance, heavy-lift floating cranes, and steel construction work for offshore wind mobilization/demobilization.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Rotterdam, Netherlands - Priority B</t>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -625,14 +669,17 @@
           <t>Extensive experience in offshore fabrication across various countries and seas worldwide.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Rotterdam, Netherlands - Priority B</t>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -647,14 +694,17 @@
           <t>Marine and offshore supply company serving the Rotterdam port area.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Rotterdam, Netherlands - Priority C</t>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -669,14 +719,17 @@
           <t>Global Dutch shipbuilding/engineering conglomerate producing warships, yachts, fishing vessels, barges, merchant vessels and dredgers (mixed commercial/naval).</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Gorinchem, Netherlands - Priority B</t>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Gorinchem, Netherlands</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -691,14 +744,17 @@
           <t>Multinational shipbuilder and equipment manufacturer for dredging and offshore vessels/equipment.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Kinderdijk, Netherlands - Priority B</t>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Kinderdijk, Netherlands</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -713,14 +769,17 @@
           <t>Shipbuilder specializing in newbuild sailing and unique motor superyachts.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Vollenhove, Netherlands - Priority C</t>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Vollenhove, Netherlands</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -735,14 +794,17 @@
           <t>Worldwide supplier of heavy-lift cranes and step-changing offshore equipment for oil &amp; gas, renewable energy and civil markets.</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Schiedam, Netherlands - Priority A</t>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr"/>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Schiedam, Netherlands</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -757,14 +819,17 @@
           <t>Developer of motion-compensated gangway and offshore access systems (with Bosch Rexroth) for offshore wind and marine operations.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands - Priority B</t>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -779,14 +844,17 @@
           <t>Repair shipyard in the port of Rotterdam.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Rotterdam, Netherlands - Priority B</t>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr"/>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -801,14 +869,17 @@
           <t>Offshore engineering and naval architecture firm covering ship design &amp; conversion, maritime engineering and on-site services.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands - Priority A</t>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr"/>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -823,14 +894,17 @@
           <t>Dutch engineering company specialised in transportation, installation and removal engineering for offshore oil, gas and wind farm projects.</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands - Priority A</t>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -845,14 +919,17 @@
           <t>Rigging and lifting equipment supplier for marine/offshore, with operations in Netherlands, Norway, UK and Poland.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands - Priority B</t>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -867,14 +944,17 @@
           <t>Offshore wind structures specialist; engineers experienced in monopile, transition piece and secondary steel design.</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands - Priority A</t>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr"/>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -891,12 +971,27 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Frank Benfer, General Manager Sales - Structural Pipes (Monopiles). General email: info@eew-group.com.</t>
+          <t>Frank Benfer</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Erndtebrück / Rostock, Germany - Priority A</t>
+          <t>General Manager Sales - Structural Pipes (Monopiles)</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>info@eew-group.com</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Erndtebrück / Rostock, Germany</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -913,12 +1008,23 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Bertram Liebler, Managing Director. General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+          <t>Bertram Liebler</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Cuxhaven, Germany - Priority B</t>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Cuxhaven, Germany</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -933,14 +1039,17 @@
           <t>Marine engineering/dredging contractor active in Germany for ~50 years, involved in installation of multiple German offshore wind farms.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Bremen, Germany - Priority B</t>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Bremen, Germany</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -955,14 +1064,17 @@
           <t>Leading independent technical maintenance/service provider for offshore wind turbines.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Bremen, Germany - Priority C</t>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr"/>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Bremen, Germany</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -977,14 +1089,17 @@
           <t>Major shipbuilder (founded 1795) constructing large cruise ships and specialised vessels.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Papenburg, Germany - Priority B</t>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Papenburg, Germany</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -999,14 +1114,17 @@
           <t>World's largest yacht builder with some naval-adjacent work; multiple shipbuilding sites in northern Germany.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Bremen-Vegesack, Germany - Priority C</t>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Bremen-Vegesack, Germany</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1021,14 +1139,17 @@
           <t>Shipbuilder of custom special-purpose vessels, lifeboats and deck equipment.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Berne, Germany - Priority B</t>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Berne, Germany</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1043,14 +1164,17 @@
           <t>Shipyard (formerly Wismar shipyard) producing specialised vessels; owned by Genting Hong Kong.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Wismar, Germany - Priority B</t>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Wismar, Germany</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1065,14 +1189,17 @@
           <t>Shipyard founded 1850, delivered 1,500+ new ships, now part of Meyer group producing river cruise vessels.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Rostock-Warnemünde, Germany - Priority B</t>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Rostock-Warnemünde, Germany</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1087,14 +1214,17 @@
           <t>Shipbuilder specialising in design/construction of naval vessels (frigates, corvettes) - defense-primary.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Kiel, Germany - Priority C</t>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Kiel, Germany</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1109,14 +1239,17 @@
           <t>Provides offshore wind energy services from Bremen.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Bremen, Germany - Priority C</t>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Bremen, Germany</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1131,14 +1264,17 @@
           <t>Offshore wind developer/operator with offices in Hamburg, Bremen, Rostock and Leer.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Hamburg, Germany - Priority C</t>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg, Germany</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1153,14 +1289,17 @@
           <t>Former offshore wind turbine/service company headquartered in Bremerhaven, now part of Siemens Gamesa.</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Bremerhaven, Germany - Priority C</t>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Bremerhaven, Germany</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1175,14 +1314,17 @@
           <t>Designs and manufactures heavy-duty steel offshore foundation structures in Bremerhaven.</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Bremerhaven, Germany - Priority A</t>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Bremerhaven, Germany</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1197,14 +1339,17 @@
           <t>Operates a wind-tunnel test centre in Bremerhaven offering aerodynamic testing for rotor blades.</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Bremerhaven, Germany - Priority C</t>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Bremerhaven, Germany</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1366,23 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Anders Søe-Jensen, CEO. General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+          <t>Anders Søe-Jensen</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Aalborg, Denmark - Priority A</t>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Aalborg, Denmark</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1241,14 +1397,17 @@
           <t>Construction/civil engineering group active in bridges, buildings and offshore wind turbine foundation installation.</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Søborg, Denmark - Priority B</t>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Søborg, Denmark</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1263,14 +1422,17 @@
           <t>Naval architecture and ship-design advisory firm with heritage from the former Odense Steel Shipyard (est. 1917).</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Odense, Denmark - Priority B</t>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Odense, Denmark</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1285,14 +1447,17 @@
           <t>Shipyard (founded 1916) specialising in shipbuilding and repair.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Munkebo, Denmark - Priority B</t>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Munkebo, Denmark</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1307,14 +1472,17 @@
           <t>Shipbuilder founded 1958.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Frederikshavn, Denmark - Priority B</t>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Frederikshavn, Denmark</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1329,14 +1497,17 @@
           <t>Offshore wind EPC firm offering full-scope engineering from FEED to detailed design; designed/built 20+ offshore substations.</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Esbjerg, Denmark - Priority A</t>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Esbjerg, Denmark</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1351,14 +1522,17 @@
           <t>Offshore support vessel operator serving offshore wind and oil &amp; gas (standby, emergency response, rescue).</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Esbjerg, Denmark - Priority C</t>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Esbjerg, Denmark</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1373,14 +1547,17 @@
           <t>450,000 m2 offshore wind tower manufacturing facility with workshops for painting, blasting, rolling and welding.</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Aalborg, Denmark - Priority A</t>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Aalborg, Denmark</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1395,14 +1572,17 @@
           <t>Wind turbine tower manufacturer with production facilities in Denmark and Germany.</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Denmark - Priority A</t>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1417,14 +1597,17 @@
           <t>Steel tower manufacturer for offshore wind, known for engineering quality; partnered with Marmen (Canada) on offshore tower fabrication.</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Denmark - Priority A</t>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1439,14 +1622,17 @@
           <t>Historic offshore wind farm installation/service vessel operator based in Fredericia.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Fredericia, Denmark - Priority C</t>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Fredericia, Denmark</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1461,14 +1647,17 @@
           <t>Major wind turbine OEM designing/manufacturing/installing/servicing offshore turbines, towers and blades.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Aarhus, Denmark - Priority B</t>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Aarhus, Denmark</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1674,23 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Arnaud De Villepin, Director Energy &amp; Industry. General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
+          <t>Arnaud De Villepin</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Vélizy-Villacoublay, France - Priority A</t>
+          <t>Director Energy &amp; Industry</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Vélizy-Villacoublay, France</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1707,27 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Pascal Ochoa, Managing Director. General email: offshorewind@setec.com.</t>
+          <t>Pascal Ochoa</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Paris, France - Priority A</t>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>offshorewind@setec.com</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1527,14 +1742,17 @@
           <t>Europe's largest shipyard, building commercial, naval and passenger ships; sites also in Brest, Toulon, La Réunion, La Martinique.</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Saint-Nazaire, France - Priority B</t>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Nazaire, France</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1549,14 +1767,17 @@
           <t>Repair yard with three dry docks (largest 420x80m); large workshops for steelwork, mechanical work, LNG equipment and pipefitting.</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Brest, France - Priority B</t>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Brest, France</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1571,14 +1792,17 @@
           <t>Floating offshore wind foundation designer/developer, partnering with NGE on a floating-foundation manufacturing facility in southern France.</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>France - Priority A</t>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1593,14 +1817,17 @@
           <t>French construction group entering floating offshore wind via a 50% stake in BW Ideol's Fos-sur-Mer serial production line.</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>France - Priority B</t>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1615,14 +1842,17 @@
           <t>Offshore wind developer active since 2014, with an engineering office and O&amp;M subsidiary (VALEMO).</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>France - Priority C</t>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1637,14 +1867,17 @@
           <t>Global offshore engineering/construction major with an offshore competency centre in France; designs/builds fixed and mobile platforms, subsea pipelines.</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>Saint-Quentin-en-Yvelines, France - Priority A</t>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Quentin-en-Yvelines, France</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1661,12 +1894,27 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Borja Zarraga Suarez, CEO. General email: info@haizeawindgroup.com.</t>
+          <t>Borja Zarraga Suarez</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Zierbena / Bilbao, Spain - Priority A</t>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>info@haizeawindgroup.com</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Zierbena / Bilbao, Spain</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1931,27 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Diego Río, Director de Operaciones Offshore Wind España. General email: comunicacion@windwaves.com.</t>
+          <t>Diego Río</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Ferrol, Spain - Priority A</t>
+          <t>Director de Operaciones Offshore Wind España</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>comunicacion@windwaves.com</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Ferrol, Spain</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1703,14 +1966,17 @@
           <t>Manufacturer of offshore wind foundations, strategic partnership with Navantia for a one-stop offshore service.</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Avilés, Spain - Priority A</t>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr"/>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Avilés, Spain</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1725,14 +1991,17 @@
           <t>State-owned shipbuilder for civil and military naval construction, also producing structures for offshore wind/hydrogen; sites in Ferrol, Cádiz, Cartagena, Madrid.</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>Ferrol / Cádiz / Cartagena, Spain - Priority B</t>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr"/>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Ferrol / Cádiz / Cartagena, Spain</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1747,14 +2016,17 @@
           <t>Engineering provider with fixed-bottom offshore wind experience, including foundation and monopile design.</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>Spain - Priority A</t>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr"/>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1769,14 +2041,17 @@
           <t>Joint venture (Simply Blue Group, Proes Consultores/Grupo Amper, FF New Energy Venture) for floating offshore wind farm design/development.</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>Spain - Priority A</t>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr"/>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1791,14 +2066,17 @@
           <t>Engineering division of Grupo Amper providing offshore wind structural/foundation design services.</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Spain - Priority A</t>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1813,14 +2091,17 @@
           <t>Manufacturer of mechanically welded foundation components for offshore wind power.</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>Spain - Priority B</t>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1835,14 +2116,17 @@
           <t>Supplies and provides technical assistance for shaft and rudder line equipment; Vigo is a major European Atlantic ship-repair hub.</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Vigo, Spain - Priority C</t>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>Vigo, Spain</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1857,14 +2141,17 @@
           <t>Designs/manufactures critical handling, lifting, anchoring and launch/recovery systems for offshore oil &amp; gas, offshore/floating wind and subsea sectors.</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Chiuduno, Italy - Priority A</t>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Chiuduno, Italy</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1879,14 +2166,17 @@
           <t>40+ years of heavy steel structures construction, supplying wind turbine components and offshore/onshore energy supply-chain elements.</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Ravenna, Italy - Priority B</t>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>Ravenna, Italy</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1901,14 +2191,17 @@
           <t>Major shipbuilder (7,000+ vessels over 230 years) expanding into offshore engineering via acquisitions.</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Trieste, Italy - Priority B</t>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Trieste, Italy</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1923,14 +2216,17 @@
           <t>Joint venture between Genoa shipbuilder T. Mariotti and steel manufacturer Cimolai.</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>San Giorgio di Nogaro, Italy - Priority B</t>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr"/>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>San Giorgio di Nogaro, Italy</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1945,14 +2241,17 @@
           <t>Group uniting two historic Genoa shipyards - ultra-luxury cruise ship construction and ship repair/conversion.</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority B</t>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1967,14 +2266,17 @@
           <t>Global leader in design/construction of offshore plants (fixed/mobile platforms, subsea pipelines); Sardinia (Arbatax) facility fabricates HVAC offshore substations.</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>San Donato Milanese, Italy - Priority A</t>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>San Donato Milanese, Italy</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1989,14 +2291,17 @@
           <t>Naval architects and marine engineers designing/building offshore and other vessel types since 1994.</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Italy - Priority B</t>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2011,14 +2316,17 @@
           <t>Shipbuilder (founded 1970) specialising in fibre-reinforced plastic hull vessels.</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Italy - Priority C</t>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2033,14 +2341,17 @@
           <t>Shipyard-area operator/workshop in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2055,14 +2366,17 @@
           <t>Shipyard-area operator/workshop in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2077,14 +2391,17 @@
           <t>Shipyard operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr"/>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2099,14 +2416,17 @@
           <t>Marine/ship service workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2121,14 +2441,17 @@
           <t>Dry-dock/ship repair operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr"/>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2143,14 +2466,17 @@
           <t>Shipyard operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr"/>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2165,14 +2491,17 @@
           <t>Marine services operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2187,14 +2516,17 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr"/>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2209,14 +2541,17 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr"/>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2231,14 +2566,17 @@
           <t>Marine engine/diesel repair workshop in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2253,14 +2591,17 @@
           <t>Steel/ship repair workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr"/>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2275,14 +2616,17 @@
           <t>Marine engine workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="inlineStr"/>
+      <c r="E83" s="2" t="inlineStr"/>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2297,14 +2641,17 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr"/>
+      <c r="E84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2319,14 +2666,17 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="inlineStr"/>
+      <c r="E85" s="2" t="inlineStr"/>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2341,14 +2691,17 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr"/>
+      <c r="E86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2363,14 +2716,17 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Genoa, Italy - Priority C</t>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr"/>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Genoa, Italy</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2385,14 +2741,17 @@
           <t>Largest ship repair facility in Tuzla Bay, offering repair and conversion services.</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Tuzla, Turkey - Priority B</t>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr"/>
+      <c r="E88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2407,14 +2766,17 @@
           <t>65+ year shipbuilding/repair yard, 85+ delivered vessel projects (chemical tankers, ferries, heavy-duty barges, specialised marine vessels).</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Tuzla, Turkey - Priority B</t>
+      <c r="C89" s="2" t="inlineStr"/>
+      <c r="D89" s="2" t="inlineStr"/>
+      <c r="E89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2429,14 +2791,17 @@
           <t>Group of shipyards (Tuzla, TGE, Neta, Altinova) covering shipbuilding and steel/pipe fabrication.</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Tuzla / Altınova, Turkey - Priority B</t>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr"/>
+      <c r="E90" s="2" t="inlineStr"/>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla / Altınova, Turkey</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2451,14 +2816,17 @@
           <t>Shipyard located in Tuzla, Istanbul.</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Tuzla, Turkey - Priority B</t>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr"/>
+      <c r="E91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2473,14 +2841,17 @@
           <t>Shipyard established 1990 in Tuzla, Istanbul.</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Tuzla, Turkey - Priority B</t>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2495,14 +2866,17 @@
           <t>Shipyard established 1999 in Tuzla, Istanbul.</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Tuzla, Turkey - Priority C</t>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="inlineStr"/>
+      <c r="E93" s="2" t="inlineStr"/>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2517,14 +2891,17 @@
           <t>Shipyard established 1975 in Tuzla, Istanbul.</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Tuzla, Turkey - Priority C</t>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr"/>
+      <c r="E94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Tuzla, Turkey</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2539,14 +2916,17 @@
           <t>UK corporation (est. Feb 2021) building the world's largest monopile manufacturing plant in Teesside.</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Teesside, UK - Priority A</t>
+      <c r="C95" s="2" t="inlineStr"/>
+      <c r="D95" s="2" t="inlineStr"/>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Teesside, UK</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2561,14 +2941,17 @@
           <t>Fabricates jacket foundations and transition pieces for offshore wind turbines from its Wallsend yard, North East England.</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Wallsend, UK - Priority A</t>
+      <c r="C96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Wallsend, UK</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2583,14 +2966,17 @@
           <t>Produces fabricated products for offshore wind farms - material prep, fabrication, welding and assembly for carbon/stainless/duplex steel.</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority B</t>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2605,14 +2991,17 @@
           <t>Specialises in heavy offshore structure fabrication for general marine, offshore renewables and oil &amp; gas industries.</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority A</t>
+      <c r="C98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2627,14 +3016,17 @@
           <t>45+ years delivering fabrication/construction services to Offshore, Oil &amp; Gas and Renewable Energy sectors.</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority B</t>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="inlineStr"/>
+      <c r="E99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2649,14 +3041,17 @@
           <t>UK manufacturer qualified to produce aluminium handrails/ladders for offshore wind turbine transition pieces.</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority B</t>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="inlineStr"/>
+      <c r="E100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2671,14 +3066,17 @@
           <t>Shipbuilding/fabrication company (HQ London) with sites in Belfast, Arnish, Appledore and Methil; ship repair, shipbuilding and offshore construction (mixed commercial/defense).</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Belfast, UK - Priority B</t>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="2" t="inlineStr"/>
+      <c r="E101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Belfast, UK</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2693,14 +3091,17 @@
           <t>Storied British shipbuilder; built RRS Sir David Attenborough, holds ongoing Royal Navy/RFA dry-dock and refit work (defense-heavy).</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Birkenhead, UK - Priority C</t>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="2" t="inlineStr"/>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Birkenhead, UK</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2715,14 +3116,17 @@
           <t>Refit/maintenance yards (Falmouth, Tyne) serving Royal Fleet Auxiliary and offshore energy/defence fabrication work (mixed).</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Falmouth / Tyne, UK - Priority C</t>
+      <c r="C103" s="2" t="inlineStr"/>
+      <c r="D103" s="2" t="inlineStr"/>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Falmouth / Tyne, UK</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2737,14 +3141,17 @@
           <t>Major offshore engineering, construction and project management services provider.</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>Sutton, Greater London, UK - Priority A</t>
+      <c r="C104" s="2" t="inlineStr"/>
+      <c r="D104" s="2" t="inlineStr"/>
+      <c r="E104" s="2" t="inlineStr"/>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Sutton, Greater London, UK</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2759,14 +3166,17 @@
           <t>Global services organisation focused on seabed-to-surface subsea services and structural integrity.</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority A</t>
+      <c r="C105" s="2" t="inlineStr"/>
+      <c r="D105" s="2" t="inlineStr"/>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2781,14 +3191,17 @@
           <t>Structural and hydrodynamic consultancy for the offshore oil &amp; gas sector, established 1986.</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority A</t>
+      <c r="C106" s="2" t="inlineStr"/>
+      <c r="D106" s="2" t="inlineStr"/>
+      <c r="E106" s="2" t="inlineStr"/>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2803,14 +3216,17 @@
           <t>30+ years offshore experience providing long-term operations &amp; maintenance (O&amp;M) packages for offshore wind.</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority C</t>
+      <c r="C107" s="2" t="inlineStr"/>
+      <c r="D107" s="2" t="inlineStr"/>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2825,14 +3241,17 @@
           <t>Supports 12+ GW of power generation across UK/European wind farms with maintenance and repair solutions.</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority C</t>
+      <c r="C108" s="2" t="inlineStr"/>
+      <c r="D108" s="2" t="inlineStr"/>
+      <c r="E108" s="2" t="inlineStr"/>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2847,14 +3266,17 @@
           <t>Supports all phases of UK offshore wind farms from planning/development through O&amp;M.</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>Burntisland, UK - Priority C</t>
+      <c r="C109" s="2" t="inlineStr"/>
+      <c r="D109" s="2" t="inlineStr"/>
+      <c r="E109" s="2" t="inlineStr"/>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Burntisland, UK</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2869,14 +3291,17 @@
           <t>Steel fabrication for renewable, oil &amp; gas (and defense-adjacent) sectors; yards at Methil and Arnish.</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>Methil / Arnish, UK - Priority B</t>
+      <c r="C110" s="2" t="inlineStr"/>
+      <c r="D110" s="2" t="inlineStr"/>
+      <c r="E110" s="2" t="inlineStr"/>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Methil / Arnish, UK</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -2891,14 +3316,17 @@
           <t>Manufacture, assembly and factory acceptance testing services; assembles turbines and manufactures offshore wind infrastructure products.</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>Inverness, UK - Priority A</t>
+      <c r="C111" s="2" t="inlineStr"/>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr"/>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Inverness, UK</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -2913,14 +3341,17 @@
           <t>Steel fabrication company covering Cardiff, Newport, Bridgend, Swansea and surrounding South Wales.</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
-        <is>
-          <t>Barry, UK - Priority C</t>
+      <c r="C112" s="2" t="inlineStr"/>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Barry, UK</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2935,14 +3366,17 @@
           <t>Steel supplier serving Cardiff, Swansea, Newport and Bristol.</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
-        <is>
-          <t>Cardiff, UK - Priority C</t>
+      <c r="C113" s="2" t="inlineStr"/>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="inlineStr"/>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Cardiff, UK</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2957,14 +3391,17 @@
           <t>Steel fabricator providing services in Cardiff, Newport and South Wales.</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>Caerphilly, UK - Priority C</t>
+      <c r="C114" s="2" t="inlineStr"/>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Caerphilly, UK</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -2979,14 +3416,17 @@
           <t>Fabrication in mild steel, stainless steel and aluminium - design through installation, based in Newport.</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Newport, UK - Priority C</t>
+      <c r="C115" s="2" t="inlineStr"/>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Newport, UK</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3001,14 +3441,17 @@
           <t>Bespoke steelwork fabricator in Newport, Gwent.</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>Newport, UK - Priority C</t>
+      <c r="C116" s="2" t="inlineStr"/>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Newport, UK</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3023,14 +3466,17 @@
           <t>Manufacturer of bespoke stainless steel/sheet metal products and structural steel supply/fabrication for South Wales.</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
-        <is>
-          <t>South Wales, UK - Priority C</t>
+      <c r="C117" s="2" t="inlineStr"/>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr"/>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>South Wales, UK</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3045,14 +3491,17 @@
           <t>Group of ~30 companies covering shipbuilding, ship design, diesel engines, propulsion and hydraulic deck machinery; founded 1917.</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
-        <is>
-          <t>Ulsteinvik, Norway - Priority B</t>
+      <c r="C118" s="2" t="inlineStr"/>
+      <c r="D118" s="2" t="inlineStr"/>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Ulsteinvik, Norway</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3067,14 +3516,17 @@
           <t>Shipbuilder specialising in high-speed naval vessels, mine countermeasure vessels and fast patrol boats (defense-primary).</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
-        <is>
-          <t>Mandal, Norway - Priority C</t>
+      <c r="C119" s="2" t="inlineStr"/>
+      <c r="D119" s="2" t="inlineStr"/>
+      <c r="E119" s="2" t="inlineStr"/>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Mandal, Norway</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3089,14 +3541,17 @@
           <t>Design/engineering company for oil &amp; gas, marine and process industries.</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
-        <is>
-          <t>Sandefjord / Stavanger, Norway - Priority A</t>
+      <c r="C120" s="2" t="inlineStr"/>
+      <c r="D120" s="2" t="inlineStr"/>
+      <c r="E120" s="2" t="inlineStr"/>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Sandefjord / Stavanger, Norway</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3111,14 +3566,17 @@
           <t>Naval architecture/marine engineering firm supplying complete design/construction/drawing packages for newbuilds.</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>Florø, Norway - Priority B</t>
+      <c r="C121" s="2" t="inlineStr"/>
+      <c r="D121" s="2" t="inlineStr"/>
+      <c r="E121" s="2" t="inlineStr"/>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Florø, Norway</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3133,14 +3591,17 @@
           <t>Shipyard building modern live fish carriers (aquaculture-focused marine fabrication).</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Norway - Priority C</t>
+      <c r="C122" s="2" t="inlineStr"/>
+      <c r="D122" s="2" t="inlineStr"/>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3155,14 +3616,17 @@
           <t>Structural engineering, design, fabrication and construction company (~250 employees, multiple Norwegian facilities).</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>Oslo, Norway - Priority A</t>
+      <c r="C123" s="2" t="inlineStr"/>
+      <c r="D123" s="2" t="inlineStr"/>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Norway</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3177,14 +3641,17 @@
           <t>Subsea engineering specialist - structural, piping and finite element analysis (FEA) design and consultancy.</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>Norway (near Oslo) - Priority A</t>
+      <c r="C124" s="2" t="inlineStr"/>
+      <c r="D124" s="2" t="inlineStr"/>
+      <c r="E124" s="2" t="inlineStr"/>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Norway (near Oslo)</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3199,14 +3666,17 @@
           <t>Engineering firm specialising in naval architecture, offshore structural engineering and subsea solutions for maritime/oil &amp; gas.</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
-        <is>
-          <t>Norway - Priority A</t>
+      <c r="C125" s="2" t="inlineStr"/>
+      <c r="D125" s="2" t="inlineStr"/>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3221,14 +3691,17 @@
           <t>Independent marine engineering company for offshore and shipping industry concept development.</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
-        <is>
-          <t>Norway - Priority B</t>
+      <c r="C126" s="2" t="inlineStr"/>
+      <c r="D126" s="2" t="inlineStr"/>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3243,14 +3716,17 @@
           <t>Marine geoscience/geotechnics consultancy for offshore wind, E&amp;P and seabed minerals site surveys.</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Norway - Priority C</t>
+      <c r="C127" s="2" t="inlineStr"/>
+      <c r="D127" s="2" t="inlineStr"/>
+      <c r="E127" s="2" t="inlineStr"/>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3265,14 +3741,17 @@
           <t>Independent engineering company providing engineering services to shipyards, ship-owners and offshore yards.</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Rogaland, Norway - Priority B</t>
+      <c r="C128" s="2" t="inlineStr"/>
+      <c r="D128" s="2" t="inlineStr"/>
+      <c r="E128" s="2" t="inlineStr"/>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Rogaland, Norway</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3287,14 +3766,17 @@
           <t>Offshore substations/topsides EPC provider.</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Haugesund, Norway - Priority A</t>
+      <c r="C129" s="2" t="inlineStr"/>
+      <c r="D129" s="2" t="inlineStr"/>
+      <c r="E129" s="2" t="inlineStr"/>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Haugesund, Norway</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3309,14 +3791,17 @@
           <t>International steel construction company (1,000+ employees across BE/NL/UK/PL), member of the Offshore Wind Foundations Alliance.</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Hoboken, Belgium - Priority A</t>
+      <c r="C130" s="2" t="inlineStr"/>
+      <c r="D130" s="2" t="inlineStr"/>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Hoboken, Belgium</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3331,14 +3816,17 @@
           <t>Part of a consortium for EPC of offshore substations in Belgian wind farms; design coordination/integration at Hoboken yard.</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Hoboken, Belgium - Priority A</t>
+      <c r="C131" s="2" t="inlineStr"/>
+      <c r="D131" s="2" t="inlineStr"/>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Hoboken, Belgium</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3353,14 +3841,17 @@
           <t>Belgian marine construction/dredging company active in offshore renewable energy since 2012.</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Hofstade-Aalst, Belgium - Priority B</t>
+      <c r="C132" s="2" t="inlineStr"/>
+      <c r="D132" s="2" t="inlineStr"/>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Hofstade-Aalst, Belgium</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3375,14 +3866,17 @@
           <t>Major dredging/marine engineering group, involved in offshore installation across Europe.</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Zwijndrecht, Belgium - Priority B</t>
+      <c r="C133" s="2" t="inlineStr"/>
+      <c r="D133" s="2" t="inlineStr"/>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Zwijndrecht, Belgium</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3397,14 +3891,17 @@
           <t>Develops steel solutions for wind turbines (up to 285 tons of steel per turbine); primarily a raw-material producer.</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Ghent, Belgium - Priority C</t>
+      <c r="C134" s="2" t="inlineStr"/>
+      <c r="D134" s="2" t="inlineStr"/>
+      <c r="E134" s="2" t="inlineStr"/>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Ghent, Belgium</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3419,14 +3916,17 @@
           <t>Large historic shipyard in northern Poland.</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Gdańsk, Poland - Priority B</t>
+      <c r="C135" s="2" t="inlineStr"/>
+      <c r="D135" s="2" t="inlineStr"/>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Gdańsk, Poland</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3441,14 +3941,17 @@
           <t>Shipyard (Port of Gdynia, founded 1990) producing offshore-industry ships including wind turbine installation vessels.</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Gdynia, Poland - Priority A</t>
+      <c r="C136" s="2" t="inlineStr"/>
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr"/>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Gdynia, Poland</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3463,14 +3966,17 @@
           <t>Shipyard specialising in container ships, chemical tankers, multi-purpose vessels and ConRo ships.</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Szczecin, Poland - Priority B</t>
+      <c r="C137" s="2" t="inlineStr"/>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr"/>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Szczecin, Poland</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3485,14 +3991,17 @@
           <t>Established 1989; complete ship construction plus technical/engineering documentation for the shipbuilding industry.</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Poland - Priority B</t>
+      <c r="C138" s="2" t="inlineStr"/>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3507,14 +4016,17 @@
           <t>Competence centre (est. 2013) for engineering-to-order, one-offs and prototype vessels.</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Gdańsk, Poland - Priority B</t>
+      <c r="C139" s="2" t="inlineStr"/>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="inlineStr"/>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Gdańsk, Poland</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3529,14 +4041,17 @@
           <t>Construction of new floating units, ship modernization and repair of offshore/land structures.</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Poland - Priority B</t>
+      <c r="C140" s="2" t="inlineStr"/>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr"/>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3551,14 +4066,17 @@
           <t>One of the largest shipbuilding-sector companies in Poland.</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Gdańsk, Poland - Priority B</t>
+      <c r="C141" s="2" t="inlineStr"/>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Gdańsk, Poland</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3573,14 +4091,17 @@
           <t>Shipbuilding operation developing in Pomerania as part of the Vard group.</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>Poland - Priority B</t>
+      <c r="C142" s="2" t="inlineStr"/>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3595,14 +4116,17 @@
           <t>Polish subsidiary of Kongsberg Maritime equipment/systems supplier.</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
-        <is>
-          <t>Poland - Priority C</t>
+      <c r="C143" s="2" t="inlineStr"/>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3617,14 +4141,17 @@
           <t>Precision fabrication and emergency repairs, custom metal structures/components for marine vessels.</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
-        <is>
-          <t>Cork, Ireland - Priority B</t>
+      <c r="C144" s="2" t="inlineStr"/>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Cork, Ireland</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3639,14 +4166,17 @@
           <t>Multi-disciplinary engineering services, project management, procurement and fabrication for marine/offshore clients.</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
-        <is>
-          <t>Ireland - Priority A</t>
+      <c r="C145" s="2" t="inlineStr"/>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr"/>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3661,14 +4191,17 @@
           <t>Nearshore fibre-optic/power cable installation, marine civil engineering and diving services.</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
-        <is>
-          <t>Ireland - Priority C</t>
+      <c r="C146" s="2" t="inlineStr"/>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr"/>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3683,14 +4216,17 @@
           <t>Design and manufacture services including high-precision fabrication and prototype development.</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>Ireland - Priority B</t>
+      <c r="C147" s="2" t="inlineStr"/>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr"/>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3705,14 +4241,17 @@
           <t>Marine and river engineering consultancy active since 1993.</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>Ireland - Priority C</t>
+      <c r="C148" s="2" t="inlineStr"/>
+      <c r="D148" s="2" t="inlineStr"/>
+      <c r="E148" s="2" t="inlineStr"/>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3727,14 +4266,17 @@
           <t>Swedish shipbuilder of fast craft/patrol boats.</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Sweden - Priority C</t>
+      <c r="C149" s="2" t="inlineStr"/>
+      <c r="D149" s="2" t="inlineStr"/>
+      <c r="E149" s="2" t="inlineStr"/>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3749,14 +4291,17 @@
           <t>Ship design house.</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Sweden - Priority B</t>
+      <c r="C150" s="2" t="inlineStr"/>
+      <c r="D150" s="2" t="inlineStr"/>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3771,14 +4316,17 @@
           <t>Naval shipbuilder (submarines/surface combatants) - defense-primary.</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
-        <is>
-          <t>Malmö, Sweden - Priority C</t>
+      <c r="C151" s="2" t="inlineStr"/>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="2" t="inlineStr"/>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Malmö, Sweden</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3793,14 +4341,17 @@
           <t>Ship design and shipowning group.</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
-        <is>
-          <t>Stockholm, Sweden - Priority C</t>
+      <c r="C152" s="2" t="inlineStr"/>
+      <c r="D152" s="2" t="inlineStr"/>
+      <c r="E152" s="2" t="inlineStr"/>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3815,14 +4366,17 @@
           <t>Specialized shipyard group (Djupvik, Swede Ship Composite, Swede Ship Yachtservice) on Sweden's west coast; building ships since the 1890s.</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>Sweden - Priority B</t>
+      <c r="C153" s="2" t="inlineStr"/>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3837,14 +4391,17 @@
           <t>Constructs customized steel/aluminium port vessels; prefabricates ship parts.</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Sweden - Priority B</t>
+      <c r="C154" s="2" t="inlineStr"/>
+      <c r="D154" s="2" t="inlineStr"/>
+      <c r="E154" s="2" t="inlineStr"/>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3859,14 +4416,17 @@
           <t>Leisure boat manufacturer.</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>Sweden - Priority C</t>
+      <c r="C155" s="2" t="inlineStr"/>
+      <c r="D155" s="2" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3881,14 +4441,17 @@
           <t>Marine tank-cleaning equipment manufacturer, Gothenburg.</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>Gothenburg, Sweden - Priority C</t>
+      <c r="C156" s="2" t="inlineStr"/>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="inlineStr"/>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Gothenburg, Sweden</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3903,14 +4466,17 @@
           <t>Primary Swedish supplier of high-strength steel plate/coil for marine hulls and offshore platforms; raw-material producer.</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
-        <is>
-          <t>Sweden - Priority C</t>
+      <c r="C157" s="2" t="inlineStr"/>
+      <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" s="2" t="inlineStr"/>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -3925,14 +4491,17 @@
           <t>Shipbuilder specialising in cruise ships and cruiseferries.</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>Turku, Finland - Priority B</t>
+      <c r="C158" s="2" t="inlineStr"/>
+      <c r="D158" s="2" t="inlineStr"/>
+      <c r="E158" s="2" t="inlineStr"/>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Turku, Finland</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3947,14 +4516,17 @@
           <t>Major marine engine, propulsion systems and lifecycle solutions provider.</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Helsinki, Finland - Priority B</t>
+      <c r="C159" s="2" t="inlineStr"/>
+      <c r="D159" s="2" t="inlineStr"/>
+      <c r="E159" s="2" t="inlineStr"/>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -3969,14 +4541,17 @@
           <t>Arctic/ice-class ship and structure engineering specialist.</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>Helsinki, Finland - Priority A</t>
+      <c r="C160" s="2" t="inlineStr"/>
+      <c r="D160" s="2" t="inlineStr"/>
+      <c r="E160" s="2" t="inlineStr"/>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -3991,14 +4566,17 @@
           <t>Designer/manufacturer of aluminium and composite boats (5-27m) for navies, coast guards, government agencies and ports.</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
-        <is>
-          <t>Finland - Priority C</t>
+      <c r="C161" s="2" t="inlineStr"/>
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="2" t="inlineStr"/>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4013,14 +4591,17 @@
           <t>Marine electrical systems and ports equipment supplier.</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
-        <is>
-          <t>Finland - Priority C</t>
+      <c r="C162" s="2" t="inlineStr"/>
+      <c r="D162" s="2" t="inlineStr"/>
+      <c r="E162" s="2" t="inlineStr"/>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4035,14 +4616,17 @@
           <t>Finnish subsidiary of Kongsberg Maritime equipment/systems supplier.</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>Finland - Priority C</t>
+      <c r="C163" s="2" t="inlineStr"/>
+      <c r="D163" s="2" t="inlineStr"/>
+      <c r="E163" s="2" t="inlineStr"/>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4057,14 +4641,17 @@
           <t>Major ship repair yard.</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
-        <is>
-          <t>Setúbal, Portugal - Priority B</t>
+      <c r="C164" s="2" t="inlineStr"/>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr"/>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Setúbal, Portugal</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4079,14 +4666,17 @@
           <t>State naval shipyard - defense-primary.</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
-        <is>
-          <t>Almada, Portugal - Priority C</t>
+      <c r="C165" s="2" t="inlineStr"/>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="inlineStr"/>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Almada, Portugal</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4101,14 +4691,17 @@
           <t>Shipbuilding/repair yard on Portugal's Atlantic coast.</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
-        <is>
-          <t>Viana do Castelo, Portugal - Priority B</t>
+      <c r="C166" s="2" t="inlineStr"/>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="inlineStr"/>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Viana do Castelo, Portugal</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4123,14 +4716,17 @@
           <t>Public shipbuilding/repair company (since 1944), Atlantic coast; has faced financial difficulty.</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>Viana do Castelo, Portugal - Priority C</t>
+      <c r="C167" s="2" t="inlineStr"/>
+      <c r="D167" s="2" t="inlineStr"/>
+      <c r="E167" s="2" t="inlineStr"/>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Viana do Castelo, Portugal</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4145,14 +4741,17 @@
           <t>Vessel repair/maintenance yard in Lisbon.</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
-        <is>
-          <t>Lisbon, Portugal - Priority B</t>
+      <c r="C168" s="2" t="inlineStr"/>
+      <c r="D168" s="2" t="inlineStr"/>
+      <c r="E168" s="2" t="inlineStr"/>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Lisbon, Portugal</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4167,14 +4766,17 @@
           <t>Repair, maintenance and shipbuilding company (founded 2017), onshore and offshore.</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Portugal - Priority B</t>
+      <c r="C169" s="2" t="inlineStr"/>
+      <c r="D169" s="2" t="inlineStr"/>
+      <c r="E169" s="2" t="inlineStr"/>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4189,14 +4791,17 @@
           <t>Produces zinc/aluminium sacrificial anodes and machined parts for shipbuilding, repair and maintenance.</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
-        <is>
-          <t>Portugal - Priority C</t>
+      <c r="C170" s="2" t="inlineStr"/>
+      <c r="D170" s="2" t="inlineStr"/>
+      <c r="E170" s="2" t="inlineStr"/>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4211,14 +4816,17 @@
           <t>Metalworking company established 1997.</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Águeda, Portugal - Priority C</t>
+      <c r="C171" s="2" t="inlineStr"/>
+      <c r="D171" s="2" t="inlineStr"/>
+      <c r="E171" s="2" t="inlineStr"/>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Águeda, Portugal</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4233,14 +4841,17 @@
           <t>Precision metalworking company.</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
-        <is>
-          <t>Santo Tirso, Portugal - Priority C</t>
+      <c r="C172" s="2" t="inlineStr"/>
+      <c r="D172" s="2" t="inlineStr"/>
+      <c r="E172" s="2" t="inlineStr"/>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Santo Tirso, Portugal</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4255,14 +4866,17 @@
           <t>One of the oldest Greek heavy industries (founded 1861), historic shipyard on Syros.</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Ermoupolis, Greece - Priority C</t>
+      <c r="C173" s="2" t="inlineStr"/>
+      <c r="D173" s="2" t="inlineStr"/>
+      <c r="E173" s="2" t="inlineStr"/>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Ermoupolis, Greece</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4277,14 +4891,17 @@
           <t>Large shipyard (founded 1937), historically linked to Greek Navy work (mixed).</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
-        <is>
-          <t>Skaramagas, Greece - Priority C</t>
+      <c r="C174" s="2" t="inlineStr"/>
+      <c r="D174" s="2" t="inlineStr"/>
+      <c r="E174" s="2" t="inlineStr"/>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Skaramagas, Greece</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4299,14 +4916,17 @@
           <t>Greek shipbuilding company founded 1968.</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Athens, Greece - Priority B</t>
+      <c r="C175" s="2" t="inlineStr"/>
+      <c r="D175" s="2" t="inlineStr"/>
+      <c r="E175" s="2" t="inlineStr"/>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Athens, Greece</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4321,14 +4941,17 @@
           <t>Large shipyard founded 1971.</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
-        <is>
-          <t>Aulis, Evia, Greece - Priority B</t>
+      <c r="C176" s="2" t="inlineStr"/>
+      <c r="D176" s="2" t="inlineStr"/>
+      <c r="E176" s="2" t="inlineStr"/>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>Aulis, Evia, Greece</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4343,14 +4966,17 @@
           <t>Greek shipbuilder founded 1962.</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
-        <is>
-          <t>Koropi, Greece - Priority C</t>
+      <c r="C177" s="2" t="inlineStr"/>
+      <c r="D177" s="2" t="inlineStr"/>
+      <c r="E177" s="2" t="inlineStr"/>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Koropi, Greece</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4365,14 +4991,17 @@
           <t>Founded 1968; supply, installation and service of shipboard equipment for all vessel types.</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
-        <is>
-          <t>Greece - Priority C</t>
+      <c r="C178" s="2" t="inlineStr"/>
+      <c r="D178" s="2" t="inlineStr"/>
+      <c r="E178" s="2" t="inlineStr"/>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4387,14 +5016,17 @@
           <t>Leading marine construction contractor across the Mediterranean, North Africa and Red Sea.</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>Greece - Priority A</t>
+      <c r="C179" s="2" t="inlineStr"/>
+      <c r="D179" s="2" t="inlineStr"/>
+      <c r="E179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -4409,14 +5041,17 @@
           <t>Naval architecture and marine engineering services provider.</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>Greece - Priority A</t>
+      <c r="C180" s="2" t="inlineStr"/>
+      <c r="D180" s="2" t="inlineStr"/>
+      <c r="E180" s="2" t="inlineStr"/>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -4431,14 +5066,17 @@
           <t>Largest shipyard in Croatia (Rijeka); builds oil tankers, bulk carriers, container ships.</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t>Rijeka, Croatia - Priority B</t>
+      <c r="C181" s="2" t="inlineStr"/>
+      <c r="D181" s="2" t="inlineStr"/>
+      <c r="E181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Rijeka, Croatia</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4453,14 +5091,17 @@
           <t>Largest shipyard in Croatia by some measures, located on the Split peninsula.</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
-        <is>
-          <t>Split, Croatia - Priority B</t>
+      <c r="C182" s="2" t="inlineStr"/>
+      <c r="D182" s="2" t="inlineStr"/>
+      <c r="E182" s="2" t="inlineStr"/>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Split, Croatia</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4475,14 +5116,17 @@
           <t>Shipyard founded 1896 on the northern Adriatic coast.</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
-        <is>
-          <t>Rijeka, Croatia - Priority B</t>
+      <c r="C183" s="2" t="inlineStr"/>
+      <c r="D183" s="2" t="inlineStr"/>
+      <c r="E183" s="2" t="inlineStr"/>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Rijeka, Croatia</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4497,14 +5141,17 @@
           <t>Shipbuilder on Croatia's Adriatic coast.</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
-        <is>
-          <t>Kraljevica, Croatia - Priority B</t>
+      <c r="C184" s="2" t="inlineStr"/>
+      <c r="D184" s="2" t="inlineStr"/>
+      <c r="E184" s="2" t="inlineStr"/>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Kraljevica, Croatia</t>
+        </is>
+      </c>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4519,14 +5166,17 @@
           <t>Subsidiary of Royal IHC.</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
-        <is>
-          <t>Croatia - Priority B</t>
+      <c r="C185" s="2" t="inlineStr"/>
+      <c r="D185" s="2" t="inlineStr"/>
+      <c r="E185" s="2" t="inlineStr"/>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4541,14 +5191,17 @@
           <t>Shipbuilder (est. 1995) known for patrol boats and specialised maritime vessels (defense-leaning).</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
-        <is>
-          <t>Croatia - Priority C</t>
+      <c r="C186" s="2" t="inlineStr"/>
+      <c r="D186" s="2" t="inlineStr"/>
+      <c r="E186" s="2" t="inlineStr"/>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4563,14 +5216,17 @@
           <t>Marine engineering and research institute (established 1948).</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
-        <is>
-          <t>Croatia - Priority A</t>
+      <c r="C187" s="2" t="inlineStr"/>
+      <c r="D187" s="2" t="inlineStr"/>
+      <c r="E187" s="2" t="inlineStr"/>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -4585,14 +5241,17 @@
           <t>Major shipyard, part of the Damen Group.</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>Galați, Romania - Priority B</t>
+      <c r="C188" s="2" t="inlineStr"/>
+      <c r="D188" s="2" t="inlineStr"/>
+      <c r="E188" s="2" t="inlineStr"/>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Galați, Romania</t>
+        </is>
+      </c>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4607,14 +5266,17 @@
           <t>Shipyard part of the Vard group.</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D189" s="2" t="inlineStr">
-        <is>
-          <t>Brăila, Romania - Priority B</t>
+      <c r="C189" s="2" t="inlineStr"/>
+      <c r="D189" s="2" t="inlineStr"/>
+      <c r="E189" s="2" t="inlineStr"/>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Brăila, Romania</t>
+        </is>
+      </c>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4629,14 +5291,17 @@
           <t>Shipyard on the Black Sea coast.</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D190" s="2" t="inlineStr">
-        <is>
-          <t>Constanța, Romania - Priority B</t>
+      <c r="C190" s="2" t="inlineStr"/>
+      <c r="D190" s="2" t="inlineStr"/>
+      <c r="E190" s="2" t="inlineStr"/>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>Constanța, Romania</t>
+        </is>
+      </c>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4651,14 +5316,17 @@
           <t>Shipyard, top-revenue Romanian shipbuilder in 2019.</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D191" s="2" t="inlineStr">
-        <is>
-          <t>Tulcea, Romania - Priority B</t>
+      <c r="C191" s="2" t="inlineStr"/>
+      <c r="D191" s="2" t="inlineStr"/>
+      <c r="E191" s="2" t="inlineStr"/>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Tulcea, Romania</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4673,14 +5341,17 @@
           <t>Ship repair yard, part of the Damen Group.</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D192" s="2" t="inlineStr">
-        <is>
-          <t>Mangalia, Romania - Priority B</t>
+      <c r="C192" s="2" t="inlineStr"/>
+      <c r="D192" s="2" t="inlineStr"/>
+      <c r="E192" s="2" t="inlineStr"/>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Mangalia, Romania</t>
+        </is>
+      </c>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4695,14 +5366,17 @@
           <t>Damen Schelde Naval Shipbuilding engineering company (100+ employees) providing detailed engineering for hulls, piping and outfitting.</t>
         </is>
       </c>
-      <c r="C193" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D193" s="2" t="inlineStr">
-        <is>
-          <t>Galați, Romania - Priority A</t>
+      <c r="C193" s="2" t="inlineStr"/>
+      <c r="D193" s="2" t="inlineStr"/>
+      <c r="E193" s="2" t="inlineStr"/>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Galați, Romania</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -4717,14 +5391,17 @@
           <t>20+ years in marine newbuilds across Europe and vessel dry-docking services around Constanța.</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D194" s="2" t="inlineStr">
-        <is>
-          <t>Constanța, Romania - Priority B</t>
+      <c r="C194" s="2" t="inlineStr"/>
+      <c r="D194" s="2" t="inlineStr"/>
+      <c r="E194" s="2" t="inlineStr"/>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Constanța, Romania</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4739,14 +5416,17 @@
           <t>Shipbuilding group (50+ companies) headquartered in Tallinn, active across the Baltic/Nordic region.</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D195" s="2" t="inlineStr">
-        <is>
-          <t>Tallinn, Estonia - Priority B</t>
+      <c r="C195" s="2" t="inlineStr"/>
+      <c r="D195" s="2" t="inlineStr"/>
+      <c r="E195" s="2" t="inlineStr"/>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Tallinn, Estonia</t>
+        </is>
+      </c>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4761,14 +5441,17 @@
           <t>Shipbuilder specialising in aluminium/steel workboats - patrol vessels, pilot boats, ferries.</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D196" s="2" t="inlineStr">
-        <is>
-          <t>Estonia - Priority B</t>
+      <c r="C196" s="2" t="inlineStr"/>
+      <c r="D196" s="2" t="inlineStr"/>
+      <c r="E196" s="2" t="inlineStr"/>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4783,14 +5466,17 @@
           <t>One of the largest shipyards in the Baltic region.</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D197" s="2" t="inlineStr">
-        <is>
-          <t>Riga, Latvia - Priority B</t>
+      <c r="C197" s="2" t="inlineStr"/>
+      <c r="D197" s="2" t="inlineStr"/>
+      <c r="E197" s="2" t="inlineStr"/>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>Riga, Latvia</t>
+        </is>
+      </c>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4805,14 +5491,17 @@
           <t>Shipyard in Klaipėda, part of the BLRT Grupp.</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>Klaipėda, Lithuania - Priority B</t>
+      <c r="C198" s="2" t="inlineStr"/>
+      <c r="D198" s="2" t="inlineStr"/>
+      <c r="E198" s="2" t="inlineStr"/>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Klaipėda, Lithuania</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4827,14 +5516,17 @@
           <t>Shipbuilding/offshore construction services operating across Estonia, Latvia, Lithuania, Netherlands, Germany and Finland.</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D199" s="2" t="inlineStr">
-        <is>
-          <t>Baltic region - Priority C</t>
+      <c r="C199" s="2" t="inlineStr"/>
+      <c r="D199" s="2" t="inlineStr"/>
+      <c r="E199" s="2" t="inlineStr"/>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Baltic region</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4849,14 +5541,17 @@
           <t>Shipbuilding and ship repair company.</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t>Burgas, Bulgaria - Priority B</t>
+      <c r="C200" s="2" t="inlineStr"/>
+      <c r="D200" s="2" t="inlineStr"/>
+      <c r="E200" s="2" t="inlineStr"/>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Burgas, Bulgaria</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4871,14 +5566,17 @@
           <t>Specialises in construction of new river and sea-going vessels.</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
-        <is>
-          <t>Ruse, Bulgaria - Priority B</t>
+      <c r="C201" s="2" t="inlineStr"/>
+      <c r="D201" s="2" t="inlineStr"/>
+      <c r="E201" s="2" t="inlineStr"/>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Ruse, Bulgaria</t>
+        </is>
+      </c>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4893,14 +5591,17 @@
           <t>Shipbuilding and ship repair services provider.</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>Sofia, Bulgaria - Priority C</t>
+      <c r="C202" s="2" t="inlineStr"/>
+      <c r="D202" s="2" t="inlineStr"/>
+      <c r="E202" s="2" t="inlineStr"/>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>Sofia, Bulgaria</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4915,14 +5616,17 @@
           <t>Operates a workshop at Odessos Shipyard.</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
-        <is>
-          <t>Varna, Bulgaria - Priority B</t>
+      <c r="C203" s="2" t="inlineStr"/>
+      <c r="D203" s="2" t="inlineStr"/>
+      <c r="E203" s="2" t="inlineStr"/>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Varna, Bulgaria</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -4937,14 +5641,17 @@
           <t>Marine/shipbuilding services company.</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
-        <is>
-          <t>Cyprus - Priority C</t>
+      <c r="C204" s="2" t="inlineStr"/>
+      <c r="D204" s="2" t="inlineStr"/>
+      <c r="E204" s="2" t="inlineStr"/>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4959,14 +5666,17 @@
           <t>Shipbuilding/repair yard.</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
-        <is>
-          <t>Famagusta, Cyprus - Priority C</t>
+      <c r="C205" s="2" t="inlineStr"/>
+      <c r="D205" s="2" t="inlineStr"/>
+      <c r="E205" s="2" t="inlineStr"/>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Famagusta, Cyprus</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -4981,14 +5691,17 @@
           <t>Designs/manufactures high-voltage inter-array and export cables for offshore wind.</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
-        <is>
-          <t>Courbevoie, France - Priority B</t>
+      <c r="C206" s="2" t="inlineStr"/>
+      <c r="D206" s="2" t="inlineStr"/>
+      <c r="E206" s="2" t="inlineStr"/>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Courbevoie, France</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5003,14 +5716,17 @@
           <t>Provides export and inter-array cable packages for offshore wind farms.</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
-        <is>
-          <t>Greece - Priority B</t>
+      <c r="C207" s="2" t="inlineStr"/>
+      <c r="D207" s="2" t="inlineStr"/>
+      <c r="E207" s="2" t="inlineStr"/>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5025,14 +5741,17 @@
           <t>One of the largest marine engineering/fabrication facilities in the UAE - 280,000 m2 yard, 545m unrestricted waterfront.</t>
         </is>
       </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
-        <is>
-          <t>Mussafah, Abu Dhabi, UAE - Priority A</t>
+      <c r="C208" s="2" t="inlineStr"/>
+      <c r="D208" s="2" t="inlineStr"/>
+      <c r="E208" s="2" t="inlineStr"/>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Mussafah, Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5047,14 +5766,17 @@
           <t>Established 1996; construction, repair and refit of naval and commercial vessels (mixed defense/commercial).</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
-        <is>
-          <t>Abu Dhabi, UAE - Priority C</t>
+      <c r="C209" s="2" t="inlineStr"/>
+      <c r="D209" s="2" t="inlineStr"/>
+      <c r="E209" s="2" t="inlineStr"/>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5069,14 +5791,17 @@
           <t>Shipbuilding group, one of the leading shipbuilders in the Persian Gulf.</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D210" s="2" t="inlineStr">
-        <is>
-          <t>Abu Dhabi, UAE - Priority C</t>
+      <c r="C210" s="2" t="inlineStr"/>
+      <c r="D210" s="2" t="inlineStr"/>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5091,14 +5816,17 @@
           <t>Marine contracting company providing comprehensive marine contracting services.</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>Abu Dhabi, UAE - Priority B</t>
+      <c r="C211" s="2" t="inlineStr"/>
+      <c r="D211" s="2" t="inlineStr"/>
+      <c r="E211" s="2" t="inlineStr"/>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5113,14 +5841,17 @@
           <t>Delivers industrial heavy machinery, offshore marine cranes, ROV launch &amp; recovery systems and custom industrial fabrication.</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
-        <is>
-          <t>Abu Dhabi, UAE - Priority B</t>
+      <c r="C212" s="2" t="inlineStr"/>
+      <c r="D212" s="2" t="inlineStr"/>
+      <c r="E212" s="2" t="inlineStr"/>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5135,14 +5866,17 @@
           <t>Designs/manufactures offshore contracted items and aluminum work (oil &amp; gas-leaning).</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D213" s="2" t="inlineStr">
-        <is>
-          <t>Abu Dhabi, UAE - Priority C</t>
+      <c r="C213" s="2" t="inlineStr"/>
+      <c r="D213" s="2" t="inlineStr"/>
+      <c r="E213" s="2" t="inlineStr"/>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5157,14 +5891,17 @@
           <t>Maritime company providing marine services supporting oil &amp; gas and other maritime sectors.</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D214" s="2" t="inlineStr">
-        <is>
-          <t>Abu Dhabi, UAE - Priority C</t>
+      <c r="C214" s="2" t="inlineStr"/>
+      <c r="D214" s="2" t="inlineStr"/>
+      <c r="E214" s="2" t="inlineStr"/>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5179,14 +5916,17 @@
           <t>Mechanical equipment/fabrication services provider.</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D215" s="2" t="inlineStr">
-        <is>
-          <t>Abu Dhabi, UAE - Priority C</t>
+      <c r="C215" s="2" t="inlineStr"/>
+      <c r="D215" s="2" t="inlineStr"/>
+      <c r="E215" s="2" t="inlineStr"/>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5201,14 +5941,17 @@
           <t>Mechanical equipment maintenance/fabrication provider.</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D216" s="2" t="inlineStr">
-        <is>
-          <t>Abu Dhabi, UAE - Priority C</t>
+      <c r="C216" s="2" t="inlineStr"/>
+      <c r="D216" s="2" t="inlineStr"/>
+      <c r="E216" s="2" t="inlineStr"/>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5225,12 +5968,27 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Beau Yarnold, Managing Director. General email: info@aptglobalmarine.com.</t>
+          <t>Beau Yarnold</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Dubai / Ras Al Khaimah, UAE - Priority A</t>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>info@aptglobalmarine.com</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Dubai / Ras Al Khaimah, UAE</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5247,12 +6005,27 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Cameron, Head of Sales - Ship Repair, Cameron@grandweld.com. Marawan F., Sales Manager - Ship Building, marawan.f@grandweld.com.</t>
+          <t>Cameron; Marawan F.</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Dubai, UAE - Priority A</t>
+          <t>Head of Sales - Ship Repair; Sales Manager - Ship Building</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Cameron@grandweld.com; marawan.f@grandweld.com</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5267,14 +6040,17 @@
           <t>Global offshore oil &amp; gas EPC major with a Jebel Ali facility (oil &amp; gas-primary).</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D219" s="2" t="inlineStr">
-        <is>
-          <t>Jebel Ali, Dubai, UAE - Priority C</t>
+      <c r="C219" s="2" t="inlineStr"/>
+      <c r="D219" s="2" t="inlineStr"/>
+      <c r="E219" s="2" t="inlineStr"/>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5289,14 +6065,17 @@
           <t>Marine services company based in Jebel Ali Free Zone.</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D220" s="2" t="inlineStr">
-        <is>
-          <t>Jebel Ali, Dubai, UAE - Priority C</t>
+      <c r="C220" s="2" t="inlineStr"/>
+      <c r="D220" s="2" t="inlineStr"/>
+      <c r="E220" s="2" t="inlineStr"/>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5311,14 +6090,17 @@
           <t>Middle East arm of Schottel, supplier of marine propulsion systems.</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D221" s="2" t="inlineStr">
-        <is>
-          <t>Jebel Ali, Dubai, UAE - Priority B</t>
+      <c r="C221" s="2" t="inlineStr"/>
+      <c r="D221" s="2" t="inlineStr"/>
+      <c r="E221" s="2" t="inlineStr"/>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5333,14 +6115,17 @@
           <t>Marine services company in Jebel Ali Free Zone.</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D222" s="2" t="inlineStr">
-        <is>
-          <t>Jebel Ali, Dubai, UAE - Priority C</t>
+      <c r="C222" s="2" t="inlineStr"/>
+      <c r="D222" s="2" t="inlineStr"/>
+      <c r="E222" s="2" t="inlineStr"/>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5355,14 +6140,17 @@
           <t>Gulf arm of Dutch marine contractor Van Oord - dredging and marine construction.</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D223" s="2" t="inlineStr">
-        <is>
-          <t>Jebel Ali, Dubai, UAE - Priority B</t>
+      <c r="C223" s="2" t="inlineStr"/>
+      <c r="D223" s="2" t="inlineStr"/>
+      <c r="E223" s="2" t="inlineStr"/>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5377,14 +6165,17 @@
           <t>Steel distribution company in Jebel Ali Free Zone (raw-material supplier).</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D224" s="2" t="inlineStr">
-        <is>
-          <t>Jebel Ali, Dubai, UAE - Priority C</t>
+      <c r="C224" s="2" t="inlineStr"/>
+      <c r="D224" s="2" t="inlineStr"/>
+      <c r="E224" s="2" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Jebel Ali, Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5399,14 +6190,17 @@
           <t>Marine construction contractor (since 2007) - construction, dredging and offshore pipeline installation.</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D225" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority B</t>
+      <c r="C225" s="2" t="inlineStr"/>
+      <c r="D225" s="2" t="inlineStr"/>
+      <c r="E225" s="2" t="inlineStr"/>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5421,14 +6215,17 @@
           <t>Construction contractor active in JAFZA projects.</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D226" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority C</t>
+      <c r="C226" s="2" t="inlineStr"/>
+      <c r="D226" s="2" t="inlineStr"/>
+      <c r="E226" s="2" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5443,14 +6240,17 @@
           <t>Shipbuilding/ship-repair yards in Dubai, Sharjah and Fujairah, building Damen and non-Damen designs up to 120m.</t>
         </is>
       </c>
-      <c r="C227" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D227" s="2" t="inlineStr">
-        <is>
-          <t>Dubai / Sharjah / Fujairah, UAE - Priority A</t>
+      <c r="C227" s="2" t="inlineStr"/>
+      <c r="D227" s="2" t="inlineStr"/>
+      <c r="E227" s="2" t="inlineStr"/>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Dubai / Sharjah / Fujairah, UAE</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5465,14 +6265,17 @@
           <t>Shipbuilding company operating across UAE and the Gulf, including boat building in Dubai.</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D228" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority B</t>
+      <c r="C228" s="2" t="inlineStr"/>
+      <c r="D228" s="2" t="inlineStr"/>
+      <c r="E228" s="2" t="inlineStr"/>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5487,14 +6290,17 @@
           <t>Marine services company - ship repair, dry docking and vessel support across UAE ports.</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D229" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority C</t>
+      <c r="C229" s="2" t="inlineStr"/>
+      <c r="D229" s="2" t="inlineStr"/>
+      <c r="E229" s="2" t="inlineStr"/>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5509,14 +6315,17 @@
           <t>Automated cutting and fabrication capabilities, Dubai Silicon Oasis.</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D230" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority C</t>
+      <c r="C230" s="2" t="inlineStr"/>
+      <c r="D230" s="2" t="inlineStr"/>
+      <c r="E230" s="2" t="inlineStr"/>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5531,14 +6340,17 @@
           <t>Automated cutting/fabrication company in Al Quoz.</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D231" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority C</t>
+      <c r="C231" s="2" t="inlineStr"/>
+      <c r="D231" s="2" t="inlineStr"/>
+      <c r="E231" s="2" t="inlineStr"/>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5553,14 +6365,17 @@
           <t>Steel erection company respected for structural steel contracting across the UAE.</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D232" s="2" t="inlineStr">
-        <is>
-          <t>Ajman / Dubai, UAE - Priority C</t>
+      <c r="C232" s="2" t="inlineStr"/>
+      <c r="D232" s="2" t="inlineStr"/>
+      <c r="E232" s="2" t="inlineStr"/>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Ajman / Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5575,14 +6390,17 @@
           <t>Established 2009; fabrication assistance to various industrial sectors in the UAE.</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority C</t>
+      <c r="C233" s="2" t="inlineStr"/>
+      <c r="D233" s="2" t="inlineStr"/>
+      <c r="E233" s="2" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5597,14 +6415,17 @@
           <t>Engineering, fabrication and construction across a wide spectrum of industries; sites in Sharjah, Dubai and Abu Dhabi.</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
-        <is>
-          <t>Sharjah / Dubai / Abu Dhabi, UAE - Priority B</t>
+      <c r="C234" s="2" t="inlineStr"/>
+      <c r="D234" s="2" t="inlineStr"/>
+      <c r="E234" s="2" t="inlineStr"/>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah / Dubai / Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5619,14 +6440,17 @@
           <t>40+ years in steel fabrication, recognized among Dubai's top steel companies.</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority C</t>
+      <c r="C235" s="2" t="inlineStr"/>
+      <c r="D235" s="2" t="inlineStr"/>
+      <c r="E235" s="2" t="inlineStr"/>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5641,14 +6465,17 @@
           <t>Custom industrial steel fabrication and heavy steel structures specialist.</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority B</t>
+      <c r="C236" s="2" t="inlineStr"/>
+      <c r="D236" s="2" t="inlineStr"/>
+      <c r="E236" s="2" t="inlineStr"/>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5663,14 +6490,17 @@
           <t>Fabrication and structural steelwork company.</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority C</t>
+      <c r="C237" s="2" t="inlineStr"/>
+      <c r="D237" s="2" t="inlineStr"/>
+      <c r="E237" s="2" t="inlineStr"/>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5685,14 +6515,17 @@
           <t>Steel structure fabrication specialist operating from Hamriya Free Zone.</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
-        <is>
-          <t>Sharjah, UAE - Priority C</t>
+      <c r="C238" s="2" t="inlineStr"/>
+      <c r="D238" s="2" t="inlineStr"/>
+      <c r="E238" s="2" t="inlineStr"/>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah, UAE</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5707,14 +6540,17 @@
           <t>Fabrication facility with in-house production support.</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah, UAE - Priority B</t>
+      <c r="C239" s="2" t="inlineStr"/>
+      <c r="D239" s="2" t="inlineStr"/>
+      <c r="E239" s="2" t="inlineStr"/>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah, UAE</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5729,14 +6565,17 @@
           <t>Heavy-lift specialist; completed load-out and float-off operation for jack-up barge Vahana Arjun.</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
-        <is>
-          <t>Ras Al Khaimah, UAE - Priority C</t>
+      <c r="C240" s="2" t="inlineStr"/>
+      <c r="D240" s="2" t="inlineStr"/>
+      <c r="E240" s="2" t="inlineStr"/>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Ras Al Khaimah, UAE</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5751,14 +6590,17 @@
           <t>Onshore/offshore contractor - ship repair/new construction, structural steel work, insulation &amp; cladding, refractory linings.</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
-        <is>
-          <t>Sharjah, UAE - Priority B</t>
+      <c r="C241" s="2" t="inlineStr"/>
+      <c r="D241" s="2" t="inlineStr"/>
+      <c r="E241" s="2" t="inlineStr"/>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah, UAE</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5773,14 +6615,17 @@
           <t>Structural steel fabrication company based in Al Sajaa.</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
-        <is>
-          <t>Sharjah, UAE - Priority B</t>
+      <c r="C242" s="2" t="inlineStr"/>
+      <c r="D242" s="2" t="inlineStr"/>
+      <c r="E242" s="2" t="inlineStr"/>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah, UAE</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5795,14 +6640,17 @@
           <t>ISO-certified marine repair company - marine repairs, maintenance, fabrication, engine reconditioning, Class survey prep.</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
-        <is>
-          <t>Fujairah, UAE - Priority B</t>
+      <c r="C243" s="2" t="inlineStr"/>
+      <c r="D243" s="2" t="inlineStr"/>
+      <c r="E243" s="2" t="inlineStr"/>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Fujairah, UAE</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5817,14 +6665,17 @@
           <t>Marine and industrial repair services across UAE/Middle East - repair, maintenance, refurbishment, fabrication, engineering.</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
-        <is>
-          <t>Dubai / Fujairah / Abu Dhabi, UAE - Priority B</t>
+      <c r="C244" s="2" t="inlineStr"/>
+      <c r="D244" s="2" t="inlineStr"/>
+      <c r="E244" s="2" t="inlineStr"/>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Dubai / Fujairah / Abu Dhabi, UAE</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5839,14 +6690,17 @@
           <t>Marine services operating across multiple UAE ports including Ajman Port and Umm Al Quwain Port.</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
-        <is>
-          <t>Ajman / Umm Al Quwain, UAE - Priority C</t>
+      <c r="C245" s="2" t="inlineStr"/>
+      <c r="D245" s="2" t="inlineStr"/>
+      <c r="E245" s="2" t="inlineStr"/>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Ajman / Umm Al Quwain, UAE</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -5861,14 +6715,17 @@
           <t>Marine and offshore engineering consultancy providing naval architecture, structural and specialist design services.</t>
         </is>
       </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
-        <is>
-          <t>London, UK - Priority A</t>
+      <c r="C246" s="2" t="inlineStr"/>
+      <c r="D246" s="2" t="inlineStr"/>
+      <c r="E246" s="2" t="inlineStr"/>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5883,14 +6740,17 @@
           <t>Engineering consultancy with a major offshore wind foundation/structural design practice.</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority A</t>
+      <c r="C247" s="2" t="inlineStr"/>
+      <c r="D247" s="2" t="inlineStr"/>
+      <c r="E247" s="2" t="inlineStr"/>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5905,14 +6765,17 @@
           <t>Energy consultancy providing engineering, subsea and offshore wind advisory services.</t>
         </is>
       </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="inlineStr">
-        <is>
-          <t>Aberdeen, UK - Priority A</t>
+      <c r="C248" s="2" t="inlineStr"/>
+      <c r="D248" s="2" t="inlineStr"/>
+      <c r="E248" s="2" t="inlineStr"/>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen, UK</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5927,14 +6790,17 @@
           <t>Oil &amp; gas and offshore engineering consultancy (part of TechnipFMC).</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="inlineStr">
-        <is>
-          <t>London, UK - Priority B</t>
+      <c r="C249" s="2" t="inlineStr"/>
+      <c r="D249" s="2" t="inlineStr"/>
+      <c r="E249" s="2" t="inlineStr"/>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5949,14 +6815,17 @@
           <t>Global engineering and consultancy company serving energy, including offshore oil &amp; gas and renewables.</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="inlineStr">
-        <is>
-          <t>Aberdeen, UK - Priority B</t>
+      <c r="C250" s="2" t="inlineStr"/>
+      <c r="D250" s="2" t="inlineStr"/>
+      <c r="E250" s="2" t="inlineStr"/>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen, UK</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -5971,14 +6840,17 @@
           <t>Marine warranty surveying and offshore engineering consultancy for marine operations.</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="inlineStr">
-        <is>
-          <t>London, UK - Priority A</t>
+      <c r="C251" s="2" t="inlineStr"/>
+      <c r="D251" s="2" t="inlineStr"/>
+      <c r="E251" s="2" t="inlineStr"/>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -5993,14 +6865,17 @@
           <t>Independent offshore engineering consultancy for oil &amp; gas and renewables projects.</t>
         </is>
       </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="inlineStr">
-        <is>
-          <t>Aberdeen, UK - Priority A</t>
+      <c r="C252" s="2" t="inlineStr"/>
+      <c r="D252" s="2" t="inlineStr"/>
+      <c r="E252" s="2" t="inlineStr"/>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Aberdeen, UK</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6015,14 +6890,17 @@
           <t>Manufacturer of subsea power and umbilical cables for offshore wind and oil &amp; gas.</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="inlineStr">
-        <is>
-          <t>Hartlepool, UK - Priority B</t>
+      <c r="C253" s="2" t="inlineStr"/>
+      <c r="D253" s="2" t="inlineStr"/>
+      <c r="E253" s="2" t="inlineStr"/>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Hartlepool, UK</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6037,14 +6915,17 @@
           <t>Marine and offshore engineering consultancy specialising in ship design and offshore renewables.</t>
         </is>
       </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="inlineStr">
-        <is>
-          <t>London, UK - Priority A</t>
+      <c r="C254" s="2" t="inlineStr"/>
+      <c r="D254" s="2" t="inlineStr"/>
+      <c r="E254" s="2" t="inlineStr"/>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6059,14 +6940,17 @@
           <t>Systems and engineering consultancy with a marine/offshore structural engineering practice.</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority B</t>
+      <c r="C255" s="2" t="inlineStr"/>
+      <c r="D255" s="2" t="inlineStr"/>
+      <c r="E255" s="2" t="inlineStr"/>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6081,14 +6965,17 @@
           <t>Engineering and construction services provider for offshore oil &amp; gas and renewable energy projects.</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="inlineStr">
-        <is>
-          <t>Oslo, Norway - Priority B</t>
+      <c r="C256" s="2" t="inlineStr"/>
+      <c r="D256" s="2" t="inlineStr"/>
+      <c r="E256" s="2" t="inlineStr"/>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Norway</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6103,14 +6990,17 @@
           <t>EPC contractor for offshore platforms, substructures and onshore facilities.</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="inlineStr">
-        <is>
-          <t>Oslo, Norway - Priority B</t>
+      <c r="C257" s="2" t="inlineStr"/>
+      <c r="D257" s="2" t="inlineStr"/>
+      <c r="E257" s="2" t="inlineStr"/>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Norway</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6125,14 +7015,17 @@
           <t>Norwegian arm of the global subsea/offshore engineering and technology group.</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="inlineStr">
-        <is>
-          <t>Norway - Priority B</t>
+      <c r="C258" s="2" t="inlineStr"/>
+      <c r="D258" s="2" t="inlineStr"/>
+      <c r="E258" s="2" t="inlineStr"/>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6147,14 +7040,17 @@
           <t>Classification society and technical advisor providing naval architecture, structural engineering and standards for offshore/marine structures.</t>
         </is>
       </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="inlineStr">
-        <is>
-          <t>Høvik, Norway - Priority A</t>
+      <c r="C259" s="2" t="inlineStr"/>
+      <c r="D259" s="2" t="inlineStr"/>
+      <c r="E259" s="2" t="inlineStr"/>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Høvik, Norway</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6169,14 +7065,17 @@
           <t>Norwegian engineering company delivering structural, mechanical and offshore engineering services.</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="inlineStr">
-        <is>
-          <t>Trondheim, Norway - Priority B</t>
+      <c r="C260" s="2" t="inlineStr"/>
+      <c r="D260" s="2" t="inlineStr"/>
+      <c r="E260" s="2" t="inlineStr"/>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Trondheim, Norway</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6191,14 +7090,17 @@
           <t>Norwegian multidisciplinary consultancy with marine/offshore structural engineering capability.</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="inlineStr">
-        <is>
-          <t>Oslo, Norway - Priority B</t>
+      <c r="C261" s="2" t="inlineStr"/>
+      <c r="D261" s="2" t="inlineStr"/>
+      <c r="E261" s="2" t="inlineStr"/>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Norway</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6213,14 +7115,17 @@
           <t>World's largest offshore wind developer/operator, headquartered in Denmark.</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D262" s="2" t="inlineStr">
-        <is>
-          <t>Fredericia, Denmark - Priority C</t>
+      <c r="C262" s="2" t="inlineStr"/>
+      <c r="D262" s="2" t="inlineStr"/>
+      <c r="E262" s="2" t="inlineStr"/>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Fredericia, Denmark</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6235,14 +7140,17 @@
           <t>Major German utility's offshore wind development/operations arm.</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
-        <is>
-          <t>Hamburg, Germany - Priority C</t>
+      <c r="C263" s="2" t="inlineStr"/>
+      <c r="D263" s="2" t="inlineStr"/>
+      <c r="E263" s="2" t="inlineStr"/>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Hamburg, Germany</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6257,14 +7165,17 @@
           <t>Swedish state-owned utility's offshore wind development/operations arm.</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
-        <is>
-          <t>Stockholm, Sweden - Priority C</t>
+      <c r="C264" s="2" t="inlineStr"/>
+      <c r="D264" s="2" t="inlineStr"/>
+      <c r="E264" s="2" t="inlineStr"/>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Stockholm, Sweden</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6279,14 +7190,17 @@
           <t>Major Spanish utility with a large offshore wind development portfolio.</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
-        <is>
-          <t>Bilbao, Spain - Priority C</t>
+      <c r="C265" s="2" t="inlineStr"/>
+      <c r="D265" s="2" t="inlineStr"/>
+      <c r="E265" s="2" t="inlineStr"/>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Bilbao, Spain</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6301,14 +7215,17 @@
           <t>French utility's renewable energy arm, active in offshore wind.</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
-        <is>
-          <t>Paris, France - Priority C</t>
+      <c r="C266" s="2" t="inlineStr"/>
+      <c r="D266" s="2" t="inlineStr"/>
+      <c r="E266" s="2" t="inlineStr"/>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6323,14 +7240,17 @@
           <t>UK/Irish utility's renewable energy arm with a large offshore wind portfolio.</t>
         </is>
       </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D267" s="2" t="inlineStr">
-        <is>
-          <t>Glasgow, UK - Priority C</t>
+      <c r="C267" s="2" t="inlineStr"/>
+      <c r="D267" s="2" t="inlineStr"/>
+      <c r="E267" s="2" t="inlineStr"/>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Glasgow, UK</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6345,14 +7265,17 @@
           <t>UK renewable energy developer (Iberdrola subsidiary) active in offshore wind.</t>
         </is>
       </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
-        <is>
-          <t>Glasgow, UK - Priority C</t>
+      <c r="C268" s="2" t="inlineStr"/>
+      <c r="D268" s="2" t="inlineStr"/>
+      <c r="E268" s="2" t="inlineStr"/>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Glasgow, UK</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6367,14 +7290,17 @@
           <t>Joint venture (EDP Renewables/Engie) offshore wind developer active across Europe.</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t>Madrid, Spain - Priority C</t>
+      <c r="C269" s="2" t="inlineStr"/>
+      <c r="D269" s="2" t="inlineStr"/>
+      <c r="E269" s="2" t="inlineStr"/>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Madrid, Spain</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6389,14 +7315,17 @@
           <t>Norwegian energy major with a significant offshore wind (and oil &amp; gas) portfolio.</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
-        <is>
-          <t>Stavanger, Norway - Priority C</t>
+      <c r="C270" s="2" t="inlineStr"/>
+      <c r="D270" s="2" t="inlineStr"/>
+      <c r="E270" s="2" t="inlineStr"/>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Stavanger, Norway</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6411,14 +7340,17 @@
           <t>German utility with an offshore wind development/operations portfolio.</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
-        <is>
-          <t>Karlsruhe, Germany - Priority C</t>
+      <c r="C271" s="2" t="inlineStr"/>
+      <c r="D271" s="2" t="inlineStr"/>
+      <c r="E271" s="2" t="inlineStr"/>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Karlsruhe, Germany</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6433,14 +7365,17 @@
           <t>Global energy major with a growing offshore wind development portfolio.</t>
         </is>
       </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
-        <is>
-          <t>The Hague, Netherlands - Priority C</t>
+      <c r="C272" s="2" t="inlineStr"/>
+      <c r="D272" s="2" t="inlineStr"/>
+      <c r="E272" s="2" t="inlineStr"/>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>The Hague, Netherlands</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6455,14 +7390,17 @@
           <t>French energy major with an offshore wind development portfolio.</t>
         </is>
       </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
-        <is>
-          <t>Paris, France - Priority C</t>
+      <c r="C273" s="2" t="inlineStr"/>
+      <c r="D273" s="2" t="inlineStr"/>
+      <c r="E273" s="2" t="inlineStr"/>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Paris, France</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6477,14 +7415,17 @@
           <t>UK-based energy major with an offshore wind development portfolio.</t>
         </is>
       </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
-        <is>
-          <t>London, UK - Priority C</t>
+      <c r="C274" s="2" t="inlineStr"/>
+      <c r="D274" s="2" t="inlineStr"/>
+      <c r="E274" s="2" t="inlineStr"/>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6499,14 +7440,17 @@
           <t>Canadian-headquartered developer with major European offshore wind assets.</t>
         </is>
       </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands/Germany - Priority C</t>
+      <c r="C275" s="2" t="inlineStr"/>
+      <c r="D275" s="2" t="inlineStr"/>
+      <c r="E275" s="2" t="inlineStr"/>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands/Germany</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6521,14 +7465,17 @@
           <t>Dutch energy company active in offshore wind development.</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
-        <is>
-          <t>Rotterdam, Netherlands - Priority C</t>
+      <c r="C276" s="2" t="inlineStr"/>
+      <c r="D276" s="2" t="inlineStr"/>
+      <c r="E276" s="2" t="inlineStr"/>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6543,14 +7490,17 @@
           <t>150-year-old Dutch marine contractor designing/building offshore wind farms in Europe, Asia and the USA.</t>
         </is>
       </c>
-      <c r="C277" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D277" s="2" t="inlineStr">
-        <is>
-          <t>Rotterdam, Netherlands - Priority B</t>
+      <c r="C277" s="2" t="inlineStr"/>
+      <c r="D277" s="2" t="inlineStr"/>
+      <c r="E277" s="2" t="inlineStr"/>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>Rotterdam, Netherlands</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6565,14 +7515,17 @@
           <t>Dutch dredging and marine services group active in offshore energy installation.</t>
         </is>
       </c>
-      <c r="C278" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D278" s="2" t="inlineStr">
-        <is>
-          <t>Papendrecht, Netherlands - Priority B</t>
+      <c r="C278" s="2" t="inlineStr"/>
+      <c r="D278" s="2" t="inlineStr"/>
+      <c r="E278" s="2" t="inlineStr"/>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>Papendrecht, Netherlands</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6587,14 +7540,17 @@
           <t>Offshore wind installation specialist (part of Subsea7), delivering foundations and cable installation.</t>
         </is>
       </c>
-      <c r="C279" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="inlineStr">
-        <is>
-          <t>Oslo, Norway - Priority A</t>
+      <c r="C279" s="2" t="inlineStr"/>
+      <c r="D279" s="2" t="inlineStr"/>
+      <c r="E279" s="2" t="inlineStr"/>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>Oslo, Norway</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6609,14 +7565,17 @@
           <t>Swedish/Norwegian structural and marine engineering/design consultancy.</t>
         </is>
       </c>
-      <c r="C280" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D280" s="2" t="inlineStr">
-        <is>
-          <t>Gothenburg, Sweden - Priority A</t>
+      <c r="C280" s="2" t="inlineStr"/>
+      <c r="D280" s="2" t="inlineStr"/>
+      <c r="E280" s="2" t="inlineStr"/>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>Gothenburg, Sweden</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6631,14 +7590,17 @@
           <t>German arm of the Danish offshore wind EPC firm Semco Maritime.</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D281" s="2" t="inlineStr">
-        <is>
-          <t>Germany - Priority A</t>
+      <c r="C281" s="2" t="inlineStr"/>
+      <c r="D281" s="2" t="inlineStr"/>
+      <c r="E281" s="2" t="inlineStr"/>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6653,14 +7615,17 @@
           <t>Shipbuilding and repair services provider in the Dubai/Sharjah/Ajman/Umm Al Quwain area.</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D282" s="2" t="inlineStr">
-        <is>
-          <t>Dubai, UAE - Priority C</t>
+      <c r="C282" s="2" t="inlineStr"/>
+      <c r="D282" s="2" t="inlineStr"/>
+      <c r="E282" s="2" t="inlineStr"/>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, UAE</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6675,14 +7640,17 @@
           <t>Shipbuilding and repair services provider in the UAE.</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D283" s="2" t="inlineStr">
-        <is>
-          <t>UAE - Priority C</t>
+      <c r="C283" s="2" t="inlineStr"/>
+      <c r="D283" s="2" t="inlineStr"/>
+      <c r="E283" s="2" t="inlineStr"/>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6697,14 +7665,17 @@
           <t>Shipbuilding and repair services provider in the UAE.</t>
         </is>
       </c>
-      <c r="C284" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D284" s="2" t="inlineStr">
-        <is>
-          <t>UAE - Priority C</t>
+      <c r="C284" s="2" t="inlineStr"/>
+      <c r="D284" s="2" t="inlineStr"/>
+      <c r="E284" s="2" t="inlineStr"/>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6719,14 +7690,17 @@
           <t>Cluster of steel and marine fabrication companies operating from Hamriyah Free Zone, Sharjah.</t>
         </is>
       </c>
-      <c r="C285" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D285" s="2" t="inlineStr">
-        <is>
-          <t>Sharjah, UAE - Priority C</t>
+      <c r="C285" s="2" t="inlineStr"/>
+      <c r="D285" s="2" t="inlineStr"/>
+      <c r="E285" s="2" t="inlineStr"/>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>Sharjah, UAE</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6741,14 +7715,17 @@
           <t>Engineering and industrial fabrication services provider in the UAE.</t>
         </is>
       </c>
-      <c r="C286" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D286" s="2" t="inlineStr">
-        <is>
-          <t>UAE - Priority C</t>
+      <c r="C286" s="2" t="inlineStr"/>
+      <c r="D286" s="2" t="inlineStr"/>
+      <c r="E286" s="2" t="inlineStr"/>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6763,14 +7740,17 @@
           <t>Ship repair and conversion yard (part of the Palumbo Group), a major Mediterranean drydock facility.</t>
         </is>
       </c>
-      <c r="C287" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D287" s="2" t="inlineStr">
-        <is>
-          <t>Marsa, Malta - Priority B</t>
+      <c r="C287" s="2" t="inlineStr"/>
+      <c r="D287" s="2" t="inlineStr"/>
+      <c r="E287" s="2" t="inlineStr"/>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>Marsa, Malta</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6785,14 +7765,17 @@
           <t>Slovenia's registered shipbuilders are mostly small workshops; no single dominant marine structural fabricator was confirmed in this pass - flagged for a deeper follow-up search if needed.</t>
         </is>
       </c>
-      <c r="C288" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D288" s="2" t="inlineStr">
-        <is>
-          <t>Slovenia - Priority C</t>
+      <c r="C288" s="2" t="inlineStr"/>
+      <c r="D288" s="2" t="inlineStr"/>
+      <c r="E288" s="2" t="inlineStr"/>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6807,14 +7790,17 @@
           <t>Major wind turbine OEM with offshore turbine, tower and foundation-adjacent manufacturing across Europe.</t>
         </is>
       </c>
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D289" s="2" t="inlineStr">
-        <is>
-          <t>Zamudio, Spain - Priority B</t>
+      <c r="C289" s="2" t="inlineStr"/>
+      <c r="D289" s="2" t="inlineStr"/>
+      <c r="E289" s="2" t="inlineStr"/>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>Zamudio, Spain</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6829,14 +7815,17 @@
           <t>Global turbine OEM with European offshore wind manufacturing operations (Haliade-X).</t>
         </is>
       </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D290" s="2" t="inlineStr">
-        <is>
-          <t>Saint-Nazaire, France - Priority B</t>
+      <c r="C290" s="2" t="inlineStr"/>
+      <c r="D290" s="2" t="inlineStr"/>
+      <c r="E290" s="2" t="inlineStr"/>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>Saint-Nazaire, France</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -6851,14 +7840,17 @@
           <t>Spanish manufacturer of steel and concrete wind towers, 22 facilities across nine countries.</t>
         </is>
       </c>
-      <c r="C291" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D291" s="2" t="inlineStr">
-        <is>
-          <t>Bilbao, Spain - Priority A</t>
+      <c r="C291" s="2" t="inlineStr"/>
+      <c r="D291" s="2" t="inlineStr"/>
+      <c r="E291" s="2" t="inlineStr"/>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>Bilbao, Spain</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6873,14 +7865,17 @@
           <t>Global wind tower manufacturer with a production facility in Portugal.</t>
         </is>
       </c>
-      <c r="C292" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D292" s="2" t="inlineStr">
-        <is>
-          <t>Portugal - Priority A</t>
+      <c r="C292" s="2" t="inlineStr"/>
+      <c r="D292" s="2" t="inlineStr"/>
+      <c r="E292" s="2" t="inlineStr"/>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6895,14 +7890,17 @@
           <t>Rotor blade manufacturer for onshore/offshore wind turbines.</t>
         </is>
       </c>
-      <c r="C293" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D293" s="2" t="inlineStr">
-        <is>
-          <t>Kolding, Denmark - Priority C</t>
+      <c r="C293" s="2" t="inlineStr"/>
+      <c r="D293" s="2" t="inlineStr"/>
+      <c r="E293" s="2" t="inlineStr"/>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>Kolding, Denmark</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6917,14 +7915,17 @@
           <t>Manufacturer of gearboxes/drivetrain components for wind turbines.</t>
         </is>
       </c>
-      <c r="C294" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D294" s="2" t="inlineStr">
-        <is>
-          <t>Bocholt, Germany - Priority C</t>
+      <c r="C294" s="2" t="inlineStr"/>
+      <c r="D294" s="2" t="inlineStr"/>
+      <c r="E294" s="2" t="inlineStr"/>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>Bocholt, Germany</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -6939,14 +7940,17 @@
           <t>Specialist offshore wind foundation design and structural engineering consultancy.</t>
         </is>
       </c>
-      <c r="C295" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D295" s="2" t="inlineStr">
-        <is>
-          <t>London, UK - Priority A</t>
+      <c r="C295" s="2" t="inlineStr"/>
+      <c r="D295" s="2" t="inlineStr"/>
+      <c r="E295" s="2" t="inlineStr"/>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6961,14 +7965,17 @@
           <t>Major engineering consultancy with an offshore wind structural design practice.</t>
         </is>
       </c>
-      <c r="C296" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D296" s="2" t="inlineStr">
-        <is>
-          <t>Epsom, UK - Priority A</t>
+      <c r="C296" s="2" t="inlineStr"/>
+      <c r="D296" s="2" t="inlineStr"/>
+      <c r="E296" s="2" t="inlineStr"/>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>Epsom, UK</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -6983,14 +7990,17 @@
           <t>Offshore engineering consultancy supporting fixed and floating structure design.</t>
         </is>
       </c>
-      <c r="C297" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D297" s="2" t="inlineStr">
-        <is>
-          <t>UK - Priority B</t>
+      <c r="C297" s="2" t="inlineStr"/>
+      <c r="D297" s="2" t="inlineStr"/>
+      <c r="E297" s="2" t="inlineStr"/>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -7005,14 +8015,17 @@
           <t>Independent offshore/onshore wind engineering and consultancy firm.</t>
         </is>
       </c>
-      <c r="C298" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D298" s="2" t="inlineStr">
-        <is>
-          <t>London, UK - Priority A</t>
+      <c r="C298" s="2" t="inlineStr"/>
+      <c r="D298" s="2" t="inlineStr"/>
+      <c r="E298" s="2" t="inlineStr"/>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7027,14 +8040,17 @@
           <t>Renewable energy engineering and consultancy firm active in offshore wind.</t>
         </is>
       </c>
-      <c r="C299" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D299" s="2" t="inlineStr">
-        <is>
-          <t>Scotland, UK - Priority B</t>
+      <c r="C299" s="2" t="inlineStr"/>
+      <c r="D299" s="2" t="inlineStr"/>
+      <c r="E299" s="2" t="inlineStr"/>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>Scotland, UK</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -7049,14 +8065,17 @@
           <t>Independent engineering consultancy specialising in offshore wind foundation design (part of Xodus/Baker Hughes group).</t>
         </is>
       </c>
-      <c r="C300" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D300" s="2" t="inlineStr">
-        <is>
-          <t>London, UK - Priority A</t>
+      <c r="C300" s="2" t="inlineStr"/>
+      <c r="D300" s="2" t="inlineStr"/>
+      <c r="E300" s="2" t="inlineStr"/>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>London, UK</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -7071,14 +8090,17 @@
           <t>Dutch engineering firm specialising in temporary works and installation engineering for offshore projects.</t>
         </is>
       </c>
-      <c r="C301" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D301" s="2" t="inlineStr">
-        <is>
-          <t>Netherlands - Priority B</t>
+      <c r="C301" s="2" t="inlineStr"/>
+      <c r="D301" s="2" t="inlineStr"/>
+      <c r="E301" s="2" t="inlineStr"/>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -7093,19 +8115,22 @@
           <t>Dutch designer of offshore vessels and jack-up rigs for wind installation and oil &amp; gas.</t>
         </is>
       </c>
-      <c r="C302" s="2" t="inlineStr">
-        <is>
-          <t>General inquiries via company website/switchboard (no named individual or verified email surfaced in this pass).</t>
-        </is>
-      </c>
-      <c r="D302" s="2" t="inlineStr">
-        <is>
-          <t>Schiedam, Netherlands - Priority A</t>
+      <c r="C302" s="2" t="inlineStr"/>
+      <c r="D302" s="2" t="inlineStr"/>
+      <c r="E302" s="2" t="inlineStr"/>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Schiedam, Netherlands</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:G1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/UAE_EU_Outreach AH Structures.xlsx
+++ b/UAE_EU_Outreach AH Structures.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G302"/>
+  <dimension ref="A1:H302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -461,6 +461,7 @@
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="100" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -499,8 +500,13 @@
           <t>Priority</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="44" customHeight="1">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Email Draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="230" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Mercon Steel Structures B.V.</t>
@@ -532,8 +538,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Mercon Steel Structures B.V. while looking at companies working in structural steel fabrication, and your work as a multidisciplinary steel construction contractor fabricating modules caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="230" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Heerema Marine Contractors (HMC)</t>
@@ -557,8 +579,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Heerema Marine Contractors (HMC) while looking at companies working in offshore wind structural engineering, and your work as a major offshore construction contractor operating some of the largest heavy-lift and pipelay crane vessels caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="230" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Heerema Fabrication Group - Vlissingen Yard</t>
@@ -582,8 +620,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Heerema Fabrication Group - Vlissingen Yard while looking at companies working in marine and offshore engineering, and your work as a yard specially equipped for EPC of offshore structures and construction of jackets of all sizes caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="230" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Smulders HSM (HSM Offshore Energy)</t>
@@ -607,8 +661,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Smulders HSM (HSM Offshore Energy) while looking at companies working in offshore wind structural engineering, and your work as a leading position in fabrication/integration of high-voltage substations and offshore wind foundation structures caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="230" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SIF Netherlands B.V.</t>
@@ -632,8 +702,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across SIF Netherlands B.V. while looking at companies working in offshore wind structural engineering, and your 75-year-old pioneer in offshore foundations based in Maasvlakte, Rotterdam caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="230" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Rotterdam Offshore Group</t>
@@ -657,8 +743,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Rotterdam Offshore Group while looking at companies working in offshore wind structural engineering, and I noticed that Rotterdam Offshore Group offers conversions, ship repair, port/voyage maintenance, heavy-lift floating cranes, and steel construction work for offshore, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="230" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>VDS Rotterdam B.V.</t>
@@ -682,8 +784,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across VDS Rotterdam B.V. while looking at companies working in marine and offshore engineering, and your work as an extensive experience in offshore fabrication across various countries and seas worldwide caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="230" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Offshore &amp; Marine Supply Rotterdam (OMS)</t>
@@ -707,8 +825,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Offshore &amp; Marine Supply Rotterdam (OMS) while looking at companies working in marine and offshore engineering, and your work as a marine and offshore supply company serving the Rotterdam port area caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="230" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Damen Shipyards Group</t>
@@ -732,8 +866,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Damen Shipyards Group while looking at companies working in shipbuilding and marine fabrication, and your work as a global Dutch shipbuilding/engineering conglomerate producing warships, yachts, fishing vessels, barges, merchant vessels and dredgers caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="230" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Royal IHC (incl. IHC Dredge Equipment)</t>
@@ -757,8 +907,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Royal IHC (incl. IHC Dredge Equipment) while looking at companies working in shipbuilding and marine fabrication, and your work as a multinational shipbuilder and equipment manufacturer for dredging and offshore vessels/equipment caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="230" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Royal Huisman</t>
@@ -782,8 +948,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Royal Huisman while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilder specializing in newbuild sailing and unique motor superyachts caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="230" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Huisman Equipment</t>
@@ -807,8 +989,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Huisman Equipment while looking at companies working in heavy lift and marine transport engineering, and your work as a worldwide supplier of heavy-lift cranes and step-changing offshore equipment for oil &amp; gas caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="230" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Barge Master</t>
@@ -832,8 +1030,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Barge Master while looking at companies working in offshore wind structural engineering, and your work as a developer of motion-compensated gangway and offshore access systems for offshore wind and marine operations caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="230" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Damen Shiprepair Rotterdam</t>
@@ -857,8 +1071,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Damen Shiprepair Rotterdam while looking at companies working in shipbuilding and marine fabrication, and your work as a repair shipyard in the port of Rotterdam caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="230" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Saltwater</t>
@@ -882,8 +1112,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Saltwater while looking at companies working in naval architecture and marine engineering, and your work as an offshore engineering and naval architecture firm covering ship design &amp; conversion caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="230" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>H2Offshore Engineering B.V.</t>
@@ -907,8 +1153,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across H2Offshore Engineering B.V. while looking at companies working in offshore and structural engineering consultancy, and your work as a Dutch engineering company specialised in transportation caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="230" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Hendrik Veder Group</t>
@@ -932,8 +1194,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Hendrik Veder Group while looking at companies working in marine and offshore engineering, and your work as a rigging and lifting equipment supplier for marine/offshore, with operations in Netherlands, Norway, UK and Poland caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="230" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Enersea</t>
@@ -957,8 +1235,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Enersea while looking at companies working in offshore wind structural engineering, and your work as an offshore wind structures specialist caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="230" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>EEW Special Pipe Constructions GmbH (EEW Group)</t>
@@ -994,8 +1288,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Frank,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across EEW Special Pipe Constructions GmbH (EEW Group) while looking at companies working in offshore wind structural engineering, and your work as a global manufacturer of monopiles, jackets and pin piles for offshore wind caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="230" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Cuxhaven Steel Construction GmbH (CSC, BARD Group)</t>
@@ -1027,8 +1337,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Bertram,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Cuxhaven Steel Construction GmbH (CSC, BARD Group) while looking at companies working in offshore wind structural engineering, and your work as a steel fabricator producing offshore wind foundation structures since 2007 in the Cuxhaven offshore industry hub caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="230" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>DEME Germany (DEME Group)</t>
@@ -1052,8 +1378,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across DEME Germany (DEME Group) while looking at companies working in offshore wind structural engineering, and your work as a marine engineering/dredging contractor active in Germany for ~50 years caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="230" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Deutsche Windtechnik</t>
@@ -1077,8 +1419,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Deutsche Windtechnik while looking at companies working in offshore wind structural engineering, and your work as a leading independent technical maintenance/service provider for offshore wind turbines caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="230" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Meyer Werft</t>
@@ -1102,8 +1460,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Meyer Werft while looking at companies working in shipbuilding and marine fabrication, and your work as a major shipbuilder constructing large cruise ships and specialised vessels caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="230" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Lürssen</t>
@@ -1127,8 +1501,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="44" customHeight="1">
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Lürssen while looking at companies working in shipbuilding and marine fabrication, and your position as World's largest yacht builder with some naval-adjacent work caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="230" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Fassmer</t>
@@ -1152,8 +1542,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="44" customHeight="1">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Fassmer while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilder of custom special-purpose vessels, lifeboats and deck equipment caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="230" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Nordic Yards Wismar</t>
@@ -1177,8 +1583,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="44" customHeight="1">
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Nordic Yards Wismar while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard producing specialised vessels caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="230" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Neptun Werft GmbH</t>
@@ -1202,8 +1624,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="29" ht="44" customHeight="1">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Neptun Werft GmbH while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard founded 1850, delivered 1,500+ new ships, now part of Meyer group producing river cruise caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="230" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>German Naval Yards Kiel</t>
@@ -1227,8 +1665,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="44" customHeight="1">
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across German Naval Yards Kiel while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilder specialising in design/construction of naval vessels caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="230" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>BVT Bremen GmbH &amp; Co. KG</t>
@@ -1252,8 +1706,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="44" customHeight="1">
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BVT Bremen GmbH &amp; Co. KG while looking at companies working in offshore wind structural engineering, and I noticed that BVT Bremen GmbH &amp; Co. KG provides offshore wind energy services from Bremen, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="230" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Skyborn Renewables (Germany)</t>
@@ -1277,8 +1747,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="44" customHeight="1">
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Skyborn Renewables (Germany) while looking at companies working in offshore wind structural engineering, and your work as an offshore wind developer/operator with offices in Hamburg, Bremen, Rostock and Leer caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="230" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Adwen GmbH (now Siemens Gamesa Renewable Energy Deutschland GmbH)</t>
@@ -1302,8 +1788,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="44" customHeight="1">
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Adwen GmbH (now Siemens Gamesa Renewable Energy Deutschland GmbH) while looking at companies working in offshore wind structural engineering, and your work as a former offshore wind turbine/service company headquartered in Bremerhaven, now part of Siemens Gamesa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="230" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>WeserWind Offshore Construction (Georgsmarienhütte)</t>
@@ -1327,8 +1829,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="44" customHeight="1">
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across WeserWind Offshore Construction (Georgsmarienhütte) while looking at companies working in offshore foundation fabrication, and I noticed that WeserWind Offshore Construction (Georgsmarienhütte) designs and manufactures heavy-duty steel offshore foundation structures in Bremerhaven, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="230" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Deutsche WindGuard</t>
@@ -1352,8 +1870,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="44" customHeight="1">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Deutsche WindGuard while looking at companies working in marine and offshore engineering, and I noticed that Deutsche WindGuard operates a wind-tunnel test centre in Bremerhaven offering aerodynamic testing for rotor blades, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="230" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Bladt Industries A/S</t>
@@ -1385,8 +1919,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="36" ht="44" customHeight="1">
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Anders,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Bladt Industries A/S while looking at companies working in offshore wind structural engineering, and your work as a steel fabricator specialising in offshore wind foundations caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="230" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
           <t>MT Højgaard Holding A/S</t>
@@ -1410,8 +1960,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="44" customHeight="1">
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across MT Højgaard Holding A/S while looking at companies working in offshore wind structural engineering, and your work as a construction/civil engineering group active in bridges, buildings and offshore wind turbine foundation installation caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="230" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Odense Maritime Technology (OMT)</t>
@@ -1435,8 +2001,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="44" customHeight="1">
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Odense Maritime Technology (OMT) while looking at companies working in naval architecture and marine engineering, and your work as a naval architecture and ship-design advisory firm with heritage from the former Odense Steel Shipyard caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="230" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
           <t>Fayard A/S</t>
@@ -1460,8 +2042,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="44" customHeight="1">
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Fayard A/S while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard specialising in shipbuilding and repair caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="230" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Ørskov Yard</t>
@@ -1485,8 +2083,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="44" customHeight="1">
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ørskov Yard while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilder founded 1958 caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="230" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
           <t>Semco Maritime</t>
@@ -1510,8 +2124,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="44" customHeight="1">
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Semco Maritime while looking at companies working in offshore wind structural engineering, and your work as an offshore wind EPC firm offering full-scope engineering from FEED to detailed design caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="230" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>Esvagt</t>
@@ -1535,8 +2165,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Esvagt while looking at companies working in offshore wind structural engineering, and your work as an offshore support vessel operator serving offshore wind and oil &amp; gas caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="230" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
           <t>CS Wind Offshore A/S</t>
@@ -1560,8 +2206,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across CS Wind Offshore A/S while looking at companies working in offshore wind structural engineering, and your 450,000 m2 offshore wind tower manufacturing facility with workshops for painting, blasting, rolling and welding caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="230" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
           <t>Titan Wind Energy (Europe) A/S</t>
@@ -1585,8 +2247,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="44" customHeight="1">
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Titan Wind Energy (Europe) A/S while looking at companies working in offshore wind structural engineering, and your work as a wind turbine tower manufacturer with production facilities in Denmark and Germany caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="230" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
         <is>
           <t>Welcon A/S</t>
@@ -1610,8 +2288,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="44" customHeight="1">
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Welcon A/S while looking at companies working in offshore wind structural engineering, and your work as a steel tower manufacturer for offshore wind, known for engineering quality caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="230" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
         <is>
           <t>A2SEA</t>
@@ -1635,8 +2329,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="44" customHeight="1">
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across A2SEA while looking at companies working in offshore wind structural engineering, and your work as a historic offshore wind farm installation/service vessel operator based in Fredericia caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="230" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Vestas Wind Systems A/S</t>
@@ -1660,8 +2370,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="44" customHeight="1">
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Vestas Wind Systems A/S while looking at companies working in offshore wind structural engineering, and your work as a major wind turbine OEM designing/manufacturing/installing/servicing offshore turbines, towers and blades caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="230" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Eiffage Métal</t>
@@ -1693,8 +2419,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="44" customHeight="1">
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Arnaud,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Eiffage Métal while looking at companies working in offshore wind structural engineering, and your work as a steel construction specialist with 50 years of sea-based structure experience caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="230" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Setec Offshore Wind (Setec Group)</t>
@@ -1730,8 +2472,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="44" customHeight="1">
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Pascal,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Setec Offshore Wind (Setec Group) while looking at companies working in offshore and structural engineering consultancy, and your work as an engineering firm specialising in offshore structure and substation design caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="230" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Chantiers de l'Atlantique</t>
@@ -1755,8 +2513,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="44" customHeight="1">
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Chantiers de l'Atlantique while looking at companies working in shipbuilding and marine fabrication, and your position as Europe's largest shipyard, building commercial, naval and passenger ships caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="230" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Damen Shiprepair Brest</t>
@@ -1780,8 +2554,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="44" customHeight="1">
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Damen Shiprepair Brest while looking at companies working in shipbuilding and marine fabrication, and your work as a repair yard with three dry docks caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="230" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
         <is>
           <t>BW Ideol</t>
@@ -1805,8 +2595,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="52" ht="44" customHeight="1">
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BW Ideol while looking at companies working in offshore wind structural engineering, and your work as a floating offshore wind foundation designer/developer caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="230" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>NGE (via Fos3F joint venture)</t>
@@ -1830,8 +2636,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="53" ht="44" customHeight="1">
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across NGE (via Fos3F joint venture) while looking at companies working in offshore wind structural engineering, and your work as a French construction group entering floating offshore wind via a 50% stake in BW Ideol's Fos-sur-Mer caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="230" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
           <t>VALOREM Group / VALEMO</t>
@@ -1855,8 +2677,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="54" ht="44" customHeight="1">
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across VALOREM Group / VALEMO while looking at companies working in offshore wind structural engineering, and your work as an offshore wind developer active since 2014, with an engineering office and O&amp;M subsidiary caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="230" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Saipem (France)</t>
@@ -1880,8 +2718,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="44" customHeight="1">
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Saipem (France) while looking at companies working in subsea structural engineering, and your work as a global offshore engineering/construction major with an offshore competency centre in France caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="230" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Haizea Wind Group</t>
@@ -1917,8 +2771,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="56" ht="44" customHeight="1">
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Borja,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Haizea Wind Group while looking at companies working in offshore wind structural engineering, and your work as a manufacturer of large metal structures/cast components for onshore and offshore wind towers and foundations caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="230" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
           <t>WindWaves (Offshore WindWaves S.L., Grupo Amper)</t>
@@ -1954,8 +2824,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="57" ht="44" customHeight="1">
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Diego,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across WindWaves (Offshore WindWaves S.L., Grupo Amper) while looking at companies working in offshore wind structural engineering, and your work as a formerly Nervión Naval Offshore caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="230" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
           <t>Windar Renovables</t>
@@ -1979,8 +2865,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="58" ht="44" customHeight="1">
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Windar Renovables while looking at companies working in offshore wind structural engineering, and your work as a manufacturer of offshore wind foundations, strategic partnership with Navantia for a one-stop offshore service caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="230" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
           <t>Navantia, S.A.</t>
@@ -2004,8 +2906,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="59" ht="44" customHeight="1">
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Navantia, S.A. while looking at companies working in offshore wind structural engineering, and your work as a state-owned shipbuilder for civil and military naval construction, also producing structures for offshore wind/hydrogen caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="230" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Iberian Offshore</t>
@@ -2029,8 +2947,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="60" ht="44" customHeight="1">
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Iberian Offshore while looking at companies working in offshore wind structural engineering, and your work as an engineering provider with fixed-bottom offshore wind experience, including foundation and monopile design caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="230" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
           <t>IberBlue Wind</t>
@@ -2054,8 +2988,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="44" customHeight="1">
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across IberBlue Wind while looking at companies working in offshore wind structural engineering, and your work as a joint venture for floating offshore wind farm design/development caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="230" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Proes Consultores (Grupo Amper)</t>
@@ -2079,8 +3029,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="44" customHeight="1">
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Proes Consultores (Grupo Amper) while looking at companies working in offshore wind structural engineering, and your work as an engineering division of Grupo Amper providing offshore wind structural/foundation design services caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="230" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Acebrón Group</t>
@@ -2104,8 +3070,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="44" customHeight="1">
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Acebrón Group while looking at companies working in offshore wind structural engineering, and your work as a manufacturer of mechanically welded foundation components for offshore wind power caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="230" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Vigo Marine Services S.L. (VMS)</t>
@@ -2129,8 +3111,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="64" ht="44" customHeight="1">
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Vigo Marine Services S.L. (VMS) while looking at companies working in marine and offshore engineering, and I noticed that Vigo Marine Services S.L. (VMS) supplies and provides technical assistance for shaft and rudder line equipment, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="230" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Remazel Engineering S.p.A. (Fincantieri subsidiary)</t>
@@ -2154,8 +3152,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="44" customHeight="1">
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Remazel Engineering S.p.A. (Fincantieri subsidiary) while looking at companies working in subsea structural engineering, and your work as a designs/manufactures critical handling, lifting, anchoring and launch/recovery systems for offshore oil &amp; gas, offshore/floating wind caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="230" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
           <t>COSMI S.p.A.</t>
@@ -2179,8 +3193,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="66" ht="44" customHeight="1">
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across COSMI S.p.A. while looking at companies working in offshore wind structural engineering, and your 40+ years of heavy steel structures construction caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="230" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Fincantieri S.p.A.</t>
@@ -2204,8 +3234,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="44" customHeight="1">
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Fincantieri S.p.A. while looking at companies working in shipbuilding and marine fabrication, and your work as a major shipbuilder expanding into offshore engineering via acquisitions caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="230" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
           <t>CI.MAR Shipyard (Cimolai-Mariotti)</t>
@@ -2229,8 +3275,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="68" ht="44" customHeight="1">
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across CI.MAR Shipyard (Cimolai-Mariotti) while looking at companies working in shipbuilding and marine fabrication, and your work as a joint venture between Genoa shipbuilder T caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="230" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Genova Industrie Navali (Mariotti + San Giorgio del Porto)</t>
@@ -2254,8 +3316,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="69" ht="44" customHeight="1">
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Genova Industrie Navali (Mariotti + San Giorgio del Porto) while looking at companies working in shipbuilding and marine fabrication, and your work as a group uniting two historic Genoa shipyards, ultra-luxury cruise ship construction and ship repair/conversion caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="230" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Saipem S.p.A.</t>
@@ -2279,8 +3357,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="70" ht="44" customHeight="1">
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Saipem S.p.A. while looking at companies working in subsea structural engineering, and your work as a global leader in design/construction of offshore plants caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="230" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Ship Projects Engineering &amp; Contracting (S.P.E.C)</t>
@@ -2304,8 +3398,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="71" ht="44" customHeight="1">
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ship Projects Engineering &amp; Contracting (S.P.E.C) while looking at companies working in naval architecture and marine engineering, and your work as a naval architects and marine engineers designing/building offshore and other vessel types since 1994 caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="230" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Intermarine</t>
@@ -2329,8 +3439,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="72" ht="44" customHeight="1">
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Intermarine while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilder specialising in fibre-reinforced plastic hull vessels caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="230" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Acier Steel S.R.L.</t>
@@ -2354,8 +3480,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="73" ht="44" customHeight="1">
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Acier Steel S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard-area operator/workshop in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="230" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Amico &amp; Co. S.R.L.</t>
@@ -2379,8 +3521,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="74" ht="44" customHeight="1">
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Amico &amp; Co. S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard-area operator/workshop in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="230" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Cantieri Navali Genovesi S.R.L.</t>
@@ -2404,8 +3562,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="75" ht="44" customHeight="1">
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Cantieri Navali Genovesi S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="230" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Enrico Polipodio S.R.L.</t>
@@ -2429,8 +3603,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="76" ht="44" customHeight="1">
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Enrico Polipodio S.R.L. while looking at companies working in marine and offshore engineering, and your work as a marine/ship service workshop operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="230" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Ente Bacini S.R.L.</t>
@@ -2454,8 +3644,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="77" ht="44" customHeight="1">
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ente Bacini S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a dry-dock/ship repair operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="230" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
           <t>GB Shipyard S.R.L.</t>
@@ -2479,8 +3685,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="78" ht="44" customHeight="1">
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GB Shipyard S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="230" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Genoa Sea Service S.R.L.</t>
@@ -2504,8 +3726,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="79" ht="44" customHeight="1">
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Genoa Sea Service S.R.L. while looking at companies working in marine and offshore engineering, and your work as a marine services operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="230" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Lagomarsino Anielli S.R.L.</t>
@@ -2529,8 +3767,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="44" customHeight="1">
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Lagomarsino Anielli S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a ship repair/workshop operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="230" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Luigi Amico S.R.L.</t>
@@ -2554,8 +3808,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="81" ht="44" customHeight="1">
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Luigi Amico S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a ship repair/workshop operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="230" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Naval Diesel S.R.L.</t>
@@ -2579,8 +3849,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="82" ht="44" customHeight="1">
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Naval Diesel S.R.L. while looking at companies working in marine equipment and propulsion systems, and your work as a marine engine/diesel repair workshop in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="230" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Navalsider Porto S.R.L.</t>
@@ -2604,8 +3890,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="83" ht="44" customHeight="1">
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Navalsider Porto S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a steel/ship repair workshop operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="230" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Officina Diesel S.R.L.</t>
@@ -2629,8 +3931,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="84" ht="44" customHeight="1">
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Officina Diesel S.R.L. while looking at companies working in marine equipment and propulsion systems, and your work as a marine engine workshop operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="230" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Ortec Santamaria S.R.L.</t>
@@ -2654,8 +3972,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="85" ht="44" customHeight="1">
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ortec Santamaria S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a ship repair/workshop operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="230" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Otam S.R.L.</t>
@@ -2679,8 +4013,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="86" ht="44" customHeight="1">
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Otam S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a ship repair/workshop operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="230" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Piaggio &amp; Figli S.R.L.</t>
@@ -2704,8 +4054,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="87" ht="44" customHeight="1">
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Piaggio &amp; Figli S.R.L. while looking at companies working in shipbuilding and marine fabrication, and your work as a ship repair/workshop operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="230" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Ranieri Tonissi S.p.A.</t>
@@ -2729,8 +4095,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="88" ht="44" customHeight="1">
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ranieri Tonissi S.p.A. while looking at companies working in shipbuilding and marine fabrication, and your work as a ship repair/workshop operator in the Port of Genoa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="230" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
           <t>TK Tuzla Shipyard</t>
@@ -2754,8 +4136,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="89" ht="44" customHeight="1">
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across TK Tuzla Shipyard while looking at companies working in shipbuilding and marine fabrication, and your work as a largest ship repair facility in Tuzla Bay, offering repair and conversion services caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="230" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Çeksan Shipyard</t>
@@ -2779,8 +4177,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="90" ht="44" customHeight="1">
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Çeksan Shipyard while looking at companies working in shipbuilding and marine fabrication, and your 65+ year shipbuilding/repair yard, 85+ delivered vessel projects caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="230" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Gemak Group (incl. Gemak Neta Steel &amp; Pipe Fabrication Yard)</t>
@@ -2804,8 +4218,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="91" ht="44" customHeight="1">
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Gemak Group (incl. Gemak Neta Steel &amp; Pipe Fabrication Yard) while looking at companies working in shipbuilding and marine fabrication, and your work as a group of shipyards covering shipbuilding and steel/pipe fabrication caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="230" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Anadolu Shipyard</t>
@@ -2829,8 +4259,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="92" ht="44" customHeight="1">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Anadolu Shipyard while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard located in Tuzla, Istanbul caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="230" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Sedef Shipyard</t>
@@ -2854,8 +4300,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="93" ht="44" customHeight="1">
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Sedef Shipyard while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard established 1990 in Tuzla, Istanbul caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="230" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Argem Shipyard</t>
@@ -2879,8 +4341,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="94" ht="44" customHeight="1">
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Argem Shipyard while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard established 1999 in Tuzla, Istanbul caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="230" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Art Shipyard</t>
@@ -2904,8 +4382,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="95" ht="44" customHeight="1">
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Art Shipyard while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard established 1975 in Tuzla, Istanbul caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="230" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
           <t>SeAh Wind</t>
@@ -2929,8 +4423,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="96" ht="44" customHeight="1">
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across SeAh Wind while looking at companies working in offshore wind structural engineering, and your work as a UK corporation building the world's largest monopile manufacturing plant in Teesside caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="230" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Smulders Group (Wallsend yard)</t>
@@ -2954,8 +4464,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="97" ht="44" customHeight="1">
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Smulders Group (Wallsend yard) while looking at companies working in offshore wind structural engineering, and I noticed that Smulders Group (Wallsend yard) fabricates jacket foundations and transition pieces for offshore wind turbines from its Wallsend yard, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="230" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
           <t>MTE</t>
@@ -2979,8 +4505,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="98" ht="44" customHeight="1">
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across MTE while looking at companies working in offshore wind structural engineering, and I noticed that MTE produces fabricated products for offshore wind farms, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="230" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
           <t>ESC Steel Structures</t>
@@ -3004,8 +4546,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="99" ht="44" customHeight="1">
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ESC Steel Structures while looking at companies working in marine and offshore engineering, and I noticed that ESC Steel Structures specialises in heavy offshore structure fabrication for general marine, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="230" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
           <t>WEC Fabrication</t>
@@ -3029,8 +4587,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="100" ht="44" customHeight="1">
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across WEC Fabrication while looking at companies working in marine and offshore engineering, and your 45+ years delivering fabrication/construction services to Offshore, Oil &amp; Gas and Renewable Energy sectors caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="230" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Durata Group</t>
@@ -3054,8 +4628,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="101" ht="44" customHeight="1">
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Durata Group while looking at companies working in offshore wind structural engineering, and your work as a UK manufacturer qualified to produce aluminium handrails/ladders for offshore wind turbine transition pieces caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="230" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Harland &amp; Wolff</t>
@@ -3079,8 +4669,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="102" ht="44" customHeight="1">
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Harland &amp; Wolff while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding/fabrication company with sites in Belfast, Arnish, Appledore and Methil caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="230" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Cammell Laird</t>
@@ -3104,8 +4710,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="103" ht="44" customHeight="1">
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Cammell Laird while looking at companies working in shipbuilding and marine fabrication, and your work as a built RRS Sir David Attenborough, holds ongoing Royal Navy/RFA dry-dock and refit work caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="230" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
           <t>A&amp;P Group</t>
@@ -3129,8 +4751,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="104" ht="44" customHeight="1">
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across A&amp;P Group while looking at companies working in marine and offshore engineering, and your work as a refit/maintenance yards serving Royal Fleet Auxiliary and offshore energy/defence fabrication work caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="230" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Subsea 7 S.A.</t>
@@ -3154,8 +4792,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="105" ht="44" customHeight="1">
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Subsea 7 S.A. while looking at companies working in marine equipment and propulsion systems, and your work as a major offshore engineering, construction and project management services provider caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="230" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Acteon Group Ltd</t>
@@ -3179,8 +4833,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="106" ht="44" customHeight="1">
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Acteon Group Ltd while looking at companies working in subsea structural engineering, and your work as a global services organisation focused on seabed-to-surface subsea services and structural integrity caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="230" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Orcina Ltd</t>
@@ -3204,8 +4874,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="107" ht="44" customHeight="1">
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Orcina Ltd while looking at companies working in offshore and structural engineering consultancy, and your work as a structural and hydrodynamic consultancy for the offshore oil &amp; gas sector, established 1986 caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="230" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
           <t>RES Group</t>
@@ -3229,8 +4915,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="108" ht="44" customHeight="1">
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across RES Group while looking at companies working in offshore wind structural engineering, and your 30+ years offshore experience providing long-term operations &amp; maintenance packages for offshore wind caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="230" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
           <t>CWind</t>
@@ -3254,8 +4956,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="109" ht="44" customHeight="1">
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across CWind while looking at companies working in marine and offshore engineering, and I noticed that CWind supports 12+ GW of power generation across UK/European wind farms with maintenance and repair solutions, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="230" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Briggs Marine</t>
@@ -3279,8 +4997,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="110" ht="44" customHeight="1">
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Briggs Marine while looking at companies working in offshore wind structural engineering, and I noticed that Briggs Marine supports all phases of UK offshore wind farms from planning/development through O&amp;M, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="230" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
           <t>BiFab (Burntisland Fabrications, now Harland &amp; Wolff)</t>
@@ -3304,8 +5038,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="111" ht="44" customHeight="1">
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BiFab (Burntisland Fabrications, now Harland &amp; Wolff) while looking at companies working in structural steel fabrication, and your work as a steel fabrication for renewable, oil &amp; gas sectors caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="230" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Global Energy Group</t>
@@ -3329,8 +5079,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="112" ht="44" customHeight="1">
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Global Energy Group while looking at companies working in offshore wind structural engineering, and your work as a manufacture, assembly and factory acceptance testing services caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="230" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Custom Steel Design</t>
@@ -3354,8 +5120,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="113" ht="44" customHeight="1">
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Custom Steel Design while looking at companies working in structural steel fabrication, and your work as a steel fabrication company covering Cardiff, Newport, Bridgend, Swansea and surrounding South Wales caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="230" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Cardiff Steels</t>
@@ -3379,8 +5161,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="114" ht="44" customHeight="1">
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Cardiff Steels while looking at companies working in marine and offshore engineering, and your work as a steel supplier serving Cardiff, Swansea, Newport and Bristol caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="230" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
           <t>AB Metal Fabricators Ltd</t>
@@ -3404,8 +5202,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="115" ht="44" customHeight="1">
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across AB Metal Fabricators Ltd while looking at companies working in marine and offshore engineering, and your work as a steel fabricator providing services in Cardiff, Newport and South Wales caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="230" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
           <t>CJN Engineering</t>
@@ -3429,8 +5243,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="116" ht="44" customHeight="1">
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across CJN Engineering while looking at companies working in marine and offshore engineering, and your work as a fabrication in mild steel, stainless steel and aluminium, design through installation, based in Newport caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="230" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Walden Steels Ltd</t>
@@ -3454,8 +5284,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="117" ht="44" customHeight="1">
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Walden Steels Ltd while looking at companies working in marine and offshore engineering, and your work as a bespoke steelwork fabricator in Newport, Gwent caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="230" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
           <t>UK Steel Centre</t>
@@ -3479,8 +5325,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="118" ht="44" customHeight="1">
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across UK Steel Centre while looking at companies working in structural steel fabrication, and your work as a manufacturer of bespoke stainless steel/sheet metal products and structural steel supply/fabrication for South Wales caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="230" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Ulstein Group ASA</t>
@@ -3504,8 +5366,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="119" ht="44" customHeight="1">
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ulstein Group ASA while looking at companies working in shipbuilding and marine fabrication, and your work as a group of ~30 companies covering shipbuilding, ship design, diesel engines, propulsion and hydraulic deck machinery caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="230" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Umoe Mandal AS</t>
@@ -3529,8 +5407,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="120" ht="44" customHeight="1">
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Umoe Mandal AS while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilder specialising in high-speed naval vessels, mine countermeasure vessels and fast patrol boats caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="230" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Grenland Framnæs (formerly Hitec Framnæs)</t>
@@ -3554,8 +5448,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="121" ht="44" customHeight="1">
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Grenland Framnæs (formerly Hitec Framnæs) while looking at companies working in offshore and structural engineering consultancy, and your work as a design/engineering company for oil &amp; gas, marine and process industries caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="230" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
           <t>STX Norway Design Florø AS</t>
@@ -3579,8 +5489,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="122" ht="44" customHeight="1">
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across STX Norway Design Florø AS while looking at companies working in naval architecture and marine engineering, and your work as a naval architecture/marine engineering firm supplying complete design/construction/drawing packages for newbuilds caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="230" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Aas Mek. Verksted A/S</t>
@@ -3604,8 +5530,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="123" ht="44" customHeight="1">
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Aas Mek. Verksted A/S while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard building modern live fish carriers caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="230" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Jotne Group</t>
@@ -3629,8 +5571,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="124" ht="44" customHeight="1">
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Jotne Group while looking at companies working in marine equipment and propulsion systems, and your work as a structural engineering, design, fabrication and construction company caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="230" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
           <t>eSubsea AS</t>
@@ -3654,8 +5612,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="125" ht="44" customHeight="1">
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across eSubsea AS while looking at companies working in subsea structural engineering, and your work as a subsea engineering specialist, structural, piping and finite element analysis design and consultancy caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="230" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Havport AS</t>
@@ -3679,8 +5653,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="126" ht="44" customHeight="1">
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Havport AS while looking at companies working in subsea structural engineering, and your work as an engineering firm specialising in naval architecture caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="230" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Naval Dynamics AS</t>
@@ -3704,8 +5694,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="127" ht="44" customHeight="1">
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Naval Dynamics AS while looking at companies working in offshore and structural engineering consultancy, and your work as an independent marine engineering company for offshore and shipping industry concept development caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="230" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
           <t>GeoProvider</t>
@@ -3729,8 +5735,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="128" ht="44" customHeight="1">
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GeoProvider while looking at companies working in offshore wind structural engineering, and your work as a marine geoscience/geotechnics consultancy for offshore wind, E&amp;P and seabed minerals site surveys caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="230" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
           <t>ShipCAD AS</t>
@@ -3754,8 +5776,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="129" ht="44" customHeight="1">
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ShipCAD AS while looking at companies working in shipbuilding and marine fabrication, and your work as an independent engineering company providing engineering services to shipyards, ship-owners and offshore yards caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="230" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Aibel</t>
@@ -3779,8 +5817,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="130" ht="44" customHeight="1">
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Aibel while looking at companies working in offshore substation fabrication, and your work as an offshore substations/topsides EPC provider caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="230" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Smulders Projects Belgium</t>
@@ -3804,8 +5858,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="131" ht="44" customHeight="1">
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Smulders Projects Belgium while looking at companies working in offshore wind structural engineering, and your work as an international steel construction company, member of the Offshore Wind Foundations Alliance caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="230" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
           <t>ENGIE Fabricom (Equans)</t>
@@ -3829,8 +5899,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="132" ht="44" customHeight="1">
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ENGIE Fabricom (Equans) while looking at companies working in offshore substation fabrication, and your work as a part of a consortium for EPC of offshore substations in Belgian wind farms caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="230" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Jan De Nul</t>
@@ -3854,8 +5940,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="133" ht="44" customHeight="1">
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Jan De Nul while looking at companies working in marine construction and offshore engineering, and your work as a Belgian marine construction/dredging company active in offshore renewable energy since 2012 caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="230" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
           <t>DEME Group</t>
@@ -3879,8 +5981,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="134" ht="44" customHeight="1">
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across DEME Group while looking at companies working in marine construction and offshore engineering, and your work as a major dredging/marine engineering group, involved in offshore installation across Europe caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="230" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
           <t>ArcelorMittal Belgium</t>
@@ -3904,8 +6022,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="135" ht="44" customHeight="1">
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ArcelorMittal Belgium while looking at companies working in offshore wind structural engineering, and I noticed that ArcelorMittal Belgium develops steel solutions for wind turbines, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="230" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Gdańsk Shipyard (Stocznia Gdańska)</t>
@@ -3929,8 +6063,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="136" ht="44" customHeight="1">
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Gdańsk Shipyard (Stocznia Gdańska) while looking at companies working in shipbuilding and marine fabrication, and your work as a large historic shipyard in northern Poland caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="230" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
           <t>CRIST S.A.</t>
@@ -3954,8 +6104,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="137" ht="44" customHeight="1">
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across CRIST S.A. while looking at companies working in offshore wind structural engineering, and your work as a shipyard producing offshore-industry ships including wind turbine installation vessels caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="230" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Szczecin Shipyard (Stocznia Szczecińska Nowa)</t>
@@ -3979,8 +6145,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="138" ht="44" customHeight="1">
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Szczecin Shipyard (Stocznia Szczecińska Nowa) while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard specialising in container ships, chemical tankers, multi-purpose vessels and ConRo ships caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="230" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Marine Projects Ltd.</t>
@@ -4004,8 +6186,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="139" ht="44" customHeight="1">
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Marine Projects Ltd. while looking at companies working in shipbuilding and marine fabrication, and your work as a complete ship construction plus technical/engineering documentation for the shipbuilding industry caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="230" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Damen Engineering Gdansk</t>
@@ -4029,8 +6227,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="140" ht="44" customHeight="1">
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Damen Engineering Gdansk while looking at companies working in marine equipment and propulsion systems, and your work as a competence centre for engineering-to-order, one-offs and prototype vessels caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="230" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Naviretech</t>
@@ -4054,8 +6268,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="141" ht="44" customHeight="1">
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Naviretech while looking at companies working in marine and offshore engineering, and your work as a construction of new floating units, ship modernization and repair of offshore/land structures caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="230" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Remontowa Group</t>
@@ -4079,8 +6309,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="142" ht="44" customHeight="1">
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Remontowa Group while looking at companies working in shipbuilding and marine fabrication, and your position as one of the largest shipbuilding-sector companies in Poland caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="230" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
           <t>ICD Poland (Vard group)</t>
@@ -4104,8 +6350,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="143" ht="44" customHeight="1">
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ICD Poland (Vard group) while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding operation developing in Pomerania as part of the Vard group caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="230" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Kongsberg Maritime Poland</t>
@@ -4129,8 +6391,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="144" ht="44" customHeight="1">
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Kongsberg Maritime Poland while looking at companies working in marine and offshore engineering, and your work as a Polish subsidiary of Kongsberg Maritime equipment/systems supplier caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="230" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Shoreline Engineering</t>
@@ -4154,8 +6432,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="145" ht="44" customHeight="1">
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Shoreline Engineering while looking at companies working in marine and offshore engineering, and your work as a precision fabrication and emergency repairs, custom metal structures/components for marine vessels caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="230" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
           <t>IMC Marine and Offshore Engineering (IMC Industrial Group)</t>
@@ -4179,8 +6473,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="146" ht="44" customHeight="1">
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across IMC Marine and Offshore Engineering (IMC Industrial Group) while looking at companies working in offshore and structural engineering consultancy, and your work as a multi-disciplinary engineering services, project management, procurement and fabrication for marine/offshore clients caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="230" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Irish Sea Contractors</t>
@@ -4204,8 +6514,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="147" ht="44" customHeight="1">
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Irish Sea Contractors while looking at companies working in offshore cable and subsea infrastructure, and your work as a nearshore fibre-optic/power cable installation, marine civil engineering and diving services caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="230" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Marine Technology Limited (MTL)</t>
@@ -4229,8 +6555,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="148" ht="44" customHeight="1">
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Marine Technology Limited (MTL) while looking at companies working in marine and offshore engineering, and your work as a design and manufacture services including high-precision fabrication and prototype development caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="230" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Doran Consulting</t>
@@ -4254,8 +6596,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="149" ht="44" customHeight="1">
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Doran Consulting while looking at companies working in offshore and structural engineering consultancy, and your work as a marine and river engineering consultancy active since 1993 caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="230" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Boghammar Marin</t>
@@ -4279,8 +6637,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="150" ht="44" customHeight="1">
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Boghammar Marin while looking at companies working in shipbuilding and marine fabrication, and your work as a Swedish shipbuilder of fast craft/patrol boats caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="230" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
           <t>FKAB Marine Design</t>
@@ -4304,8 +6678,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="151" ht="44" customHeight="1">
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across FKAB Marine Design while looking at companies working in marine and offshore engineering, and your work as a ship design house caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="230" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Saab Kockums</t>
@@ -4329,8 +6719,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="152" ht="44" customHeight="1">
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Saab Kockums while looking at companies working in shipbuilding and marine fabrication, and your work as a naval shipbuilder caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="230" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Wallenius Marine</t>
@@ -4354,8 +6760,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="153" ht="44" customHeight="1">
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Wallenius Marine while looking at companies working in marine and offshore engineering, and your work as a ship design and shipowning group caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="230" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Swede Ship Marine (Djupvik Shipyard)</t>
@@ -4379,8 +6801,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="154" ht="44" customHeight="1">
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Swede Ship Marine (Djupvik Shipyard) while looking at companies working in shipbuilding and marine fabrication, and your work as a specialized shipyard group on Sweden's west coast caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="230" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Delta Marine Scandinavia</t>
@@ -4404,8 +6842,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="155" ht="44" customHeight="1">
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Delta Marine Scandinavia while looking at companies working in marine and offshore engineering, and I noticed that Delta Marine Scandinavia constructs customized steel/aluminium port vessels, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="230" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Nimbus Boats AB</t>
@@ -4429,8 +6883,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="156" ht="44" customHeight="1">
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Nimbus Boats AB while looking at companies working in marine and offshore engineering, and your work as a leisure boat manufacturer caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="230" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Scanjet Marine</t>
@@ -4454,8 +6924,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="157" ht="44" customHeight="1">
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Scanjet Marine while looking at companies working in marine and offshore engineering, and your work as a marine tank-cleaning equipment manufacturer, Gothenburg caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="230" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
           <t>SSAB</t>
@@ -4479,8 +6965,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="158" ht="44" customHeight="1">
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across SSAB while looking at companies working in marine and offshore engineering, and your work as a primary Swedish supplier of high-strength steel plate/coil for marine hulls and offshore platforms caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="230" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Meyer Turku Oy</t>
@@ -4504,8 +7006,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="159" ht="44" customHeight="1">
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Meyer Turku Oy while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilder specialising in cruise ships and cruiseferries caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="230" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Wärtsilä</t>
@@ -4529,8 +7047,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="160" ht="44" customHeight="1">
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Wärtsilä while looking at companies working in marine equipment and propulsion systems, and your work as a major marine engine, propulsion systems and lifecycle solutions provider caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="230" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Aker Arctic Technology</t>
@@ -4554,8 +7088,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="161" ht="44" customHeight="1">
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Aker Arctic Technology while looking at companies working in marine equipment and propulsion systems, and your work as an arctic/ice-class ship and structure engineering specialist caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="230" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Marine Alutech Oy Ab</t>
@@ -4579,8 +7129,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="162" ht="44" customHeight="1">
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Marine Alutech Oy Ab while looking at companies working in marine and offshore engineering, and your work as a designer/manufacturer of aluminium and composite boats for navies, coast guards, government agencies and ports caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="230" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
           <t>ABB Marine &amp; Ports (Finland)</t>
@@ -4604,8 +7170,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="163" ht="44" customHeight="1">
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ABB Marine &amp; Ports (Finland) while looking at companies working in marine and offshore engineering, and your work as a marine electrical systems and ports equipment supplier caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="230" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Kongsberg Maritime Finland</t>
@@ -4629,8 +7211,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="164" ht="44" customHeight="1">
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Kongsberg Maritime Finland while looking at companies working in marine and offshore engineering, and your work as a Finnish subsidiary of Kongsberg Maritime equipment/systems supplier caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="230" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Lisnave Estaleiros Navais S.A.</t>
@@ -4654,8 +7252,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="165" ht="44" customHeight="1">
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Lisnave Estaleiros Navais S.A. while looking at companies working in shipbuilding and marine fabrication, and your work as a major ship repair yard caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="230" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Arsenal do Alfeite, S.A.</t>
@@ -4679,8 +7293,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="166" ht="44" customHeight="1">
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Arsenal do Alfeite, S.A. while looking at companies working in shipbuilding and marine fabrication, and your work as a state naval shipyard caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="230" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
         <is>
           <t>West Sea - Viana Shipyard</t>
@@ -4704,8 +7334,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="167" ht="44" customHeight="1">
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across West Sea - Viana Shipyard while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding/repair yard on Portugal's Atlantic coast caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="230" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
         <is>
           <t>ENVC S.A.</t>
@@ -4729,8 +7375,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="168" ht="44" customHeight="1">
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ENVC S.A. while looking at companies working in shipbuilding and marine fabrication, and your work as a public shipbuilding/repair company, Atlantic coast caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="230" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Naval Rocha</t>
@@ -4754,8 +7416,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="169" ht="44" customHeight="1">
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Naval Rocha while looking at companies working in shipbuilding and marine fabrication, and your work as a vessel repair/maintenance yard in Lisbon caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="230" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Odisseia Teórica LDA</t>
@@ -4779,8 +7457,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="170" ht="44" customHeight="1">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Odisseia Teórica LDA while looking at companies working in shipbuilding and marine fabrication, and your work as a repair, maintenance and shipbuilding company, onshore and offshore caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="230" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Metalúrgica Fonseca &amp; Flora</t>
@@ -4804,8 +7498,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="171" ht="44" customHeight="1">
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Metalúrgica Fonseca &amp; Flora while looking at companies working in shipbuilding and marine fabrication, and I noticed that Metalúrgica Fonseca &amp; Flora produces zinc/aluminium sacrificial anodes and machined parts for shipbuilding, repair and maintenance, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="230" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
         <is>
           <t>TF Metals (Tribunas &amp; Figueiredo, Lda)</t>
@@ -4829,8 +7539,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="172" ht="44" customHeight="1">
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across TF Metals (Tribunas &amp; Figueiredo, Lda) while looking at companies working in marine and offshore engineering, and your work as a metalworking company established 1997 caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="230" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Iberomecânica, Lda.</t>
@@ -4854,8 +7580,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="173" ht="44" customHeight="1">
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Iberomecânica, Lda. while looking at companies working in marine and offshore engineering, and your work as a precision metalworking company caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="230" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Neorion</t>
@@ -4879,8 +7621,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="174" ht="44" customHeight="1">
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Neorion while looking at companies working in shipbuilding and marine fabrication, and your position as one of the oldest Greek heavy industries, historic shipyard on Syros caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="230" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
         <is>
           <t>Skaramangas Shipyards</t>
@@ -4904,8 +7662,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="175" ht="44" customHeight="1">
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Skaramangas Shipyards while looking at companies working in shipbuilding and marine fabrication, and your work as a large shipyard caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="230" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
         <is>
           <t>Elefsis Shipyards</t>
@@ -4929,8 +7703,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="176" ht="44" customHeight="1">
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Elefsis Shipyards while looking at companies working in shipbuilding and marine fabrication, and your work as a Greek shipbuilding company founded 1968 caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="230" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
         <is>
           <t>Chalkis Shipyards S.A.</t>
@@ -4954,8 +7744,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="177" ht="44" customHeight="1">
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Chalkis Shipyards S.A. while looking at companies working in shipbuilding and marine fabrication, and your work as a large shipyard founded 1971 caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="230" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
         <is>
           <t>Motomarine S.A.</t>
@@ -4979,8 +7785,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="178" ht="44" customHeight="1">
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Motomarine S.A. while looking at companies working in shipbuilding and marine fabrication, and your work as a Greek shipbuilder founded 1962 caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="230" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Technava</t>
@@ -5004,8 +7826,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="179" ht="44" customHeight="1">
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Technava while looking at companies working in marine and offshore engineering, and your work as a supply, installation and service of shipboard equipment for all vessel types caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="230" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
         <is>
           <t>Spanopoulos Group</t>
@@ -5029,8 +7867,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="180" ht="44" customHeight="1">
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Spanopoulos Group while looking at companies working in marine construction and offshore engineering, and your work as a leading marine construction contractor across the Mediterranean, North Africa and Red Sea caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="230" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Group Navale</t>
@@ -5054,8 +7908,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="181" ht="44" customHeight="1">
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Group Navale while looking at companies working in naval architecture and marine engineering, and your work as a naval architecture and marine engineering services provider caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="230" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
         <is>
           <t>3. Maj (Treći Maj Brodogradilište d.d.)</t>
@@ -5079,8 +7949,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="182" ht="44" customHeight="1">
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across 3. Maj (Treći Maj Brodogradilište d.d.) while looking at companies working in shipbuilding and marine fabrication, and your work as a largest shipyard in Croatia caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="230" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
         <is>
           <t>Brodosplit d.d.</t>
@@ -5104,8 +7990,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="183" ht="44" customHeight="1">
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Brodosplit d.d. while looking at companies working in shipbuilding and marine fabrication, and your work as a largest shipyard in Croatia by some measures, located on the Split peninsula caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="230" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
         <is>
           <t>Viktor Lenac Shipyard</t>
@@ -5129,8 +8031,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="184" ht="44" customHeight="1">
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Viktor Lenac Shipyard while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard founded 1896 on the northern Adriatic coast caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="230" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
         <is>
           <t>Kraljevica Shipyard</t>
@@ -5154,8 +8072,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="185" ht="44" customHeight="1">
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Kraljevica Shipyard while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilder on Croatia's Adriatic coast caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="230" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
         <is>
           <t>IHC Engineering Croatia (IEC)</t>
@@ -5179,8 +8113,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="186" ht="44" customHeight="1">
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across IHC Engineering Croatia (IEC) while looking at companies working in marine and offshore engineering, and your work as a subsidiary of Royal IHC caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="230" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
         <is>
           <t>Brodoplan Ltd.</t>
@@ -5204,8 +8154,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="187" ht="44" customHeight="1">
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Brodoplan Ltd. while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilder known for patrol boats and specialised maritime vessels caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="230" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
         <is>
           <t>Brodarski Institut</t>
@@ -5229,8 +8195,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="188" ht="44" customHeight="1">
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Brodarski Institut while looking at companies working in marine equipment and propulsion systems, and your work as a marine engineering and research institute caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="230" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
         <is>
           <t>Damen Shipyards Galati</t>
@@ -5254,8 +8236,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="189" ht="44" customHeight="1">
+      <c r="H188" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Damen Shipyards Galati while looking at companies working in shipbuilding and marine fabrication, and your work as a major shipyard, part of the Damen Group caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="230" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
         <is>
           <t>Vard Braila</t>
@@ -5279,8 +8277,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="190" ht="44" customHeight="1">
+      <c r="H189" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Vard Braila while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard part of the Vard group caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="230" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
         <is>
           <t>Santierul Naval Constanta</t>
@@ -5304,8 +8318,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="191" ht="44" customHeight="1">
+      <c r="H190" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Santierul Naval Constanta while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard on the Black Sea coast caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="230" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
         <is>
           <t>Vard Tulcea</t>
@@ -5329,8 +8359,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="192" ht="44" customHeight="1">
+      <c r="H191" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Vard Tulcea while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard, top-revenue Romanian shipbuilder in 2019 caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="230" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
         <is>
           <t>Damen Shiprepair Mangalia</t>
@@ -5354,8 +8400,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="193" ht="44" customHeight="1">
+      <c r="H192" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Damen Shiprepair Mangalia while looking at companies working in shipbuilding and marine fabrication, and your work as a ship repair yard, part of the Damen Group caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="230" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
         <is>
           <t>Marine Engineering Galati (MEGA)</t>
@@ -5379,8 +8441,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="194" ht="44" customHeight="1">
+      <c r="H193" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Marine Engineering Galati (MEGA) while looking at companies working in shipbuilding and marine fabrication, and your work as a damen Schelde Naval Shipbuilding engineering company providing detailed engineering for hulls, piping and outfitting caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="230" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
         <is>
           <t>NAVALINK Srl.</t>
@@ -5404,8 +8482,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="195" ht="44" customHeight="1">
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across NAVALINK Srl. while looking at companies working in marine and offshore engineering, and your 20+ years in marine newbuilds across Europe and vessel dry-docking services around Constanța caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="230" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
         <is>
           <t>BLRT Grupp AS</t>
@@ -5429,8 +8523,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="196" ht="44" customHeight="1">
+      <c r="H195" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BLRT Grupp AS while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding group headquartered in Tallinn, active across the Baltic/Nordic region caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="230" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
         <is>
           <t>Baltic Workboats AS</t>
@@ -5454,8 +8564,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="197" ht="44" customHeight="1">
+      <c r="H196" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Baltic Workboats AS while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilder specialising in aluminium/steel workboats, patrol vessels, pilot boats, ferries caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="230" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
         <is>
           <t>Riga Shipyard (JSC)</t>
@@ -5479,8 +8605,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="198" ht="44" customHeight="1">
+      <c r="H197" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Riga Shipyard (JSC) while looking at companies working in shipbuilding and marine fabrication, and your position as one of the largest shipyards in the Baltic region caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="230" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
         <is>
           <t>BLRT Western Shipyard</t>
@@ -5504,8 +8646,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="199" ht="44" customHeight="1">
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BLRT Western Shipyard while looking at companies working in shipbuilding and marine fabrication, and your work as a shipyard in Klaipėda, part of the BLRT Grupp caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="230" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
         <is>
           <t>Navalis Group</t>
@@ -5529,8 +8687,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="200" ht="44" customHeight="1">
+      <c r="H199" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Navalis Group while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding/offshore construction services operating across Estonia, Latvia, Lithuania, Netherlands, Germany and Finland caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="230" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
         <is>
           <t>Bourgas Shipyards JSC</t>
@@ -5554,8 +8728,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="201" ht="44" customHeight="1">
+      <c r="H200" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Bourgas Shipyards JSC while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding and ship repair company caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="230" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
         <is>
           <t>Rousse Shipyard West JSC</t>
@@ -5579,8 +8769,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="202" ht="44" customHeight="1">
+      <c r="H201" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Rousse Shipyard West JSC while looking at companies working in marine and offshore engineering, and I noticed that Rousse Shipyard West JSC specialises in construction of new river and sea-going vessels, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="230" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
         <is>
           <t>NOVAGLASS LTD</t>
@@ -5604,8 +8810,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="203" ht="44" customHeight="1">
+      <c r="H202" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across NOVAGLASS LTD while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding and ship repair services provider caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="230" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
         <is>
           <t>PBM Bulgaria</t>
@@ -5629,8 +8851,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="204" ht="44" customHeight="1">
+      <c r="H203" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across PBM Bulgaria while looking at companies working in shipbuilding and marine fabrication, and I noticed that PBM Bulgaria operates a workshop at Odessos Shipyard, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="230" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
         <is>
           <t>Baier Marine CME Ltd.</t>
@@ -5654,8 +8892,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="205" ht="44" customHeight="1">
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Baier Marine CME Ltd. while looking at companies working in shipbuilding and marine fabrication, and your work as a marine/shipbuilding services company caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="230" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
         <is>
           <t>Shipyard Famagusta Ltd.</t>
@@ -5679,8 +8933,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="206" ht="44" customHeight="1">
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Shipyard Famagusta Ltd. while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding/repair yard caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="230" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
         <is>
           <t>Nexans</t>
@@ -5704,8 +8974,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="207" ht="44" customHeight="1">
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Nexans while looking at companies working in offshore wind structural engineering, and your work as a designs/manufactures high-voltage inter-array and export cables for offshore wind caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="230" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
         <is>
           <t>Hellenic Cables</t>
@@ -5729,8 +9015,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="208" ht="44" customHeight="1">
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Hellenic Cables while looking at companies working in offshore wind structural engineering, and I noticed that Hellenic Cables provides export and inter-array cable packages for offshore wind farms, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="230" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
         <is>
           <t>Ali &amp; Sons Marine Engineering Factory (ASMEF) / Emarat Aloula Industries</t>
@@ -5754,8 +9056,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="209" ht="44" customHeight="1">
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ali &amp; Sons Marine Engineering Factory (ASMEF) / Emarat Aloula Industries while looking at companies working in marine equipment and propulsion systems, and your position as one of the largest marine engineering/fabrication facilities in the UAE caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="230" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi Ship Building (ADSB)</t>
@@ -5779,8 +9097,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="210" ht="44" customHeight="1">
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Abu Dhabi Ship Building (ADSB) while looking at companies working in marine and offshore engineering, and your work as a construction, repair and refit of naval and commercial vessels caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="230" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi MAR (ADM)</t>
@@ -5804,8 +9138,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="211" ht="44" customHeight="1">
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Abu Dhabi MAR (ADM) while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding group, one of the leading shipbuilders in the Persian Gulf caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="230" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
         <is>
           <t>ADSO Group of Companies</t>
@@ -5829,8 +9179,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="212" ht="44" customHeight="1">
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ADSO Group of Companies while looking at companies working in marine construction and offshore engineering, and your work as a marine contracting company providing comprehensive marine contracting services caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="230" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
         <is>
           <t>OceanSi</t>
@@ -5854,8 +9220,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="213" ht="44" customHeight="1">
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across OceanSi while looking at companies working in heavy lift and marine transport engineering, and I noticed that OceanSi delivers industrial heavy machinery, which caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="230" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
         <is>
           <t>Drilltech UAE</t>
@@ -5879,8 +9261,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="214" ht="44" customHeight="1">
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Drilltech UAE while looking at companies working in marine and offshore engineering, and your work as a designs/manufactures offshore contracted items and aluminum work caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="230" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
         <is>
           <t>Al Bawardi Marine Services (ABMS)</t>
@@ -5904,8 +9302,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="215" ht="44" customHeight="1">
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Al Bawardi Marine Services (ABMS) while looking at companies working in marine and offshore engineering, and your work as a maritime company providing marine services supporting oil &amp; gas and other maritime sectors caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="230" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
         <is>
           <t>Latest Mechanical Equipment LLC</t>
@@ -5929,8 +9343,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="216" ht="44" customHeight="1">
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Latest Mechanical Equipment LLC while looking at companies working in marine and offshore engineering, and your work as a mechanical equipment/fabrication services provider caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="230" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
         <is>
           <t>Front Line Mechanical Equipment Maintenance LLC</t>
@@ -5954,8 +9384,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="217" ht="44" customHeight="1">
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Front Line Mechanical Equipment Maintenance LLC while looking at companies working in marine and offshore engineering, and your work as a mechanical equipment maintenance/fabrication provider caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="230" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
         <is>
           <t>APT Global Marine and Offshore Engineering</t>
@@ -5991,8 +9437,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="218" ht="44" customHeight="1">
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Beau,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across APT Global Marine and Offshore Engineering while looking at companies working in marine equipment and propulsion systems, and your work as a marine engineering/steel-structure fabrication company with facilities in UAE, India, Qatar, Belgium, Netherlands, Taiwan and USA caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="230" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
         <is>
           <t>Grandweld Shipyards (Stanford Marine Group)</t>
@@ -6028,8 +9490,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="219" ht="44" customHeight="1">
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Cameron,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Grandweld Shipyards (Stanford Marine Group) while looking at companies working in shipbuilding and marine fabrication, and your work as a fully integrated shipyard in Dubai Maritime City, shipbuilding, ship repair and marine engineering solutions caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="230" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
         <is>
           <t>McDermott Dubai (McDermott International)</t>
@@ -6053,8 +9531,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="220" ht="44" customHeight="1">
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across McDermott Dubai (McDermott International) while looking at companies working in marine and offshore engineering, and your work as a global offshore oil &amp; gas EPC major with a Jebel Ali facility caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="230" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
         <is>
           <t>SAS International Marine Services LLC</t>
@@ -6078,8 +9572,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="221" ht="44" customHeight="1">
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across SAS International Marine Services LLC while looking at companies working in marine and offshore engineering, and your work as a marine services company based in Jebel Ali Free Zone caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="230" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
         <is>
           <t>Schottel Middle East FZE</t>
@@ -6103,8 +9613,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="222" ht="44" customHeight="1">
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Schottel Middle East FZE while looking at companies working in marine equipment and propulsion systems, and your work as a middle East arm of Schottel, supplier of marine propulsion systems caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="230" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
         <is>
           <t>Seaworks ME</t>
@@ -6128,8 +9654,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="223" ht="44" customHeight="1">
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Seaworks ME while looking at companies working in marine and offshore engineering, and your work as a marine services company in Jebel Ali Free Zone caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="230" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
         <is>
           <t>Van Oord Gulf FZE</t>
@@ -6153,8 +9695,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="224" ht="44" customHeight="1">
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Van Oord Gulf FZE while looking at companies working in marine construction and offshore engineering, and your work as a gulf arm of Dutch marine contractor Van Oord, dredging and marine construction caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="230" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
         <is>
           <t>Valbruna Gulf FZE</t>
@@ -6178,8 +9736,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="225" ht="44" customHeight="1">
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Valbruna Gulf FZE while looking at companies working in marine and offshore engineering, and your work as a steel distribution company in Jebel Ali Free Zone caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="230" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
         <is>
           <t>Union Dredgers &amp; Marine Contracting (UDMC)</t>
@@ -6203,8 +9777,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="226" ht="44" customHeight="1">
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Union Dredgers &amp; Marine Contracting (UDMC) while looking at companies working in marine construction and offshore engineering, and your work as a marine construction contractor, construction, dredging and offshore pipeline installation caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="230" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
         <is>
           <t>Tecmark Contracting LLC</t>
@@ -6228,8 +9818,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="227" ht="44" customHeight="1">
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Tecmark Contracting LLC while looking at companies working in marine and offshore engineering, and your work as a construction contractor active in JAFZA projects caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="230" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
         <is>
           <t>Albwardy Damen</t>
@@ -6253,8 +9859,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="228" ht="44" customHeight="1">
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Albwardy Damen while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding/ship-repair yards in Dubai, Sharjah and Fujairah, building Damen and non-Damen designs up to 120m caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="230" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
         <is>
           <t>VU Marine</t>
@@ -6278,8 +9900,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="229" ht="44" customHeight="1">
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across VU Marine while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding company operating across UAE and the Gulf, including boat building in Dubai caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="230" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
         <is>
           <t>Ocean Connect FZE</t>
@@ -6303,8 +9941,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="230" ht="44" customHeight="1">
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ocean Connect FZE while looking at companies working in shipbuilding and marine fabrication, and your work as a marine services company, ship repair, dry docking and vessel support across UAE ports caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="230" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
         <is>
           <t>Inventure Metal Products Industries LLC</t>
@@ -6328,8 +9982,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="231" ht="44" customHeight="1">
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Inventure Metal Products Industries LLC while looking at companies working in marine and offshore engineering, and your work as an automated cutting and fabrication capabilities, Dubai Silicon Oasis caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="231" ht="230" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
         <is>
           <t>Laser Beam Industry LLC</t>
@@ -6353,8 +10023,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="232" ht="44" customHeight="1">
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Laser Beam Industry LLC while looking at companies working in marine and offshore engineering, and your work as an automated cutting/fabrication company in Al Quoz caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="230" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
         <is>
           <t>Al Baraq Steel</t>
@@ -6378,8 +10064,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="233" ht="44" customHeight="1">
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Al Baraq Steel while looking at companies working in structural steel fabrication, and your work as a steel erection company respected for structural steel contracting across the UAE caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="230" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
         <is>
           <t>Standard Steel Fabrication Co LLC</t>
@@ -6403,8 +10105,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="234" ht="44" customHeight="1">
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Standard Steel Fabrication Co LLC while looking at companies working in marine and offshore engineering, and your work as a fabrication assistance to various industrial sectors in the UAE caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="230" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
         <is>
           <t>Kingston (Middle East Metals)</t>
@@ -6428,8 +10146,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="235" ht="44" customHeight="1">
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Kingston (Middle East Metals) while looking at companies working in marine equipment and propulsion systems, and your work as an engineering, fabrication and construction across a wide spectrum of industries caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="230" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
         <is>
           <t>Yarmouk Steel</t>
@@ -6453,8 +10187,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="236" ht="44" customHeight="1">
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Yarmouk Steel while looking at companies working in structural steel fabrication, and your 40+ years in steel fabrication, recognized among Dubai's top steel companies caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="230" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
         <is>
           <t>Middle East Metals</t>
@@ -6478,8 +10228,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="237" ht="44" customHeight="1">
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Middle East Metals while looking at companies working in structural steel fabrication, and your work as a custom industrial steel fabrication and heavy steel structures specialist caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="230" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
         <is>
           <t>Rukn Al Mizan Metal</t>
@@ -6503,8 +10269,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="238" ht="44" customHeight="1">
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Rukn Al Mizan Metal while looking at companies working in structural steel fabrication, and your work as a fabrication and structural steelwork company caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="230" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
         <is>
           <t>Al Nawras Steel Middle East FZC</t>
@@ -6528,8 +10310,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="239" ht="44" customHeight="1">
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Al Nawras Steel Middle East FZC while looking at companies working in structural steel fabrication, and your work as a steel structure fabrication specialist operating from Hamriya Free Zone caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="230" customHeight="1">
       <c r="A239" s="2" t="inlineStr">
         <is>
           <t>Ghosh Metal Industries LLC</t>
@@ -6553,8 +10351,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="240" ht="44" customHeight="1">
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ghosh Metal Industries LLC while looking at companies working in marine and offshore engineering, and your work as a fabrication facility with in-house production support caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="230" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
         <is>
           <t>SABER-1</t>
@@ -6578,8 +10392,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="241" ht="44" customHeight="1">
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across SABER-1 while looking at companies working in heavy lift and marine transport engineering, and your work as a completed load-out and float-off operation for jack-up barge Vahana Arjun caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="230" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
         <is>
           <t>Phoenix Engineering &amp; Marine Co. LLC (Phoenix Engineering Group)</t>
@@ -6603,8 +10433,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="242" ht="44" customHeight="1">
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Phoenix Engineering &amp; Marine Co. LLC (Phoenix Engineering Group) while looking at companies working in shipbuilding and marine fabrication, and your work as an onshore/offshore contractor, ship repair/new construction, structural steel work, insulation &amp; cladding, refractory linings caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="230" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
         <is>
           <t>OSA Engineering Works Est LLC</t>
@@ -6628,8 +10474,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="243" ht="44" customHeight="1">
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across OSA Engineering Works Est LLC while looking at companies working in structural steel fabrication, and your work as a structural steel fabrication company based in Al Sajaa caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="230" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
         <is>
           <t>Techno Marine Ship Repairing LLC</t>
@@ -6653,8 +10515,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="244" ht="44" customHeight="1">
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Techno Marine Ship Repairing LLC while looking at companies working in marine equipment and propulsion systems, and your work as an iSO-certified marine repair company, marine repairs, maintenance, fabrication, engine reconditioning, Class survey prep caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="230" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
         <is>
           <t>NICO International</t>
@@ -6678,8 +10556,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="245" ht="44" customHeight="1">
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across NICO International while looking at companies working in marine equipment and propulsion systems, and your work as a marine and industrial repair services across UAE/Middle East, repair, maintenance, refurbishment, fabrication, engineering caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="230" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
         <is>
           <t>AIMAR Marine Services</t>
@@ -6703,8 +10597,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="246" ht="44" customHeight="1">
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across AIMAR Marine Services while looking at companies working in marine and offshore engineering, and your work as a marine services operating across multiple UAE ports including Ajman Port and Umm Al Quwain Port caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="230" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
         <is>
           <t>BMT</t>
@@ -6728,8 +10638,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="247" ht="44" customHeight="1">
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BMT while looking at companies working in naval architecture and marine engineering, and your work as a marine and offshore engineering consultancy providing naval architecture, structural and specialist design services caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="230" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
         <is>
           <t>Ramboll UK (Offshore Wind)</t>
@@ -6753,8 +10679,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="248" ht="44" customHeight="1">
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ramboll UK (Offshore Wind) while looking at companies working in offshore wind structural engineering, and your work as an engineering consultancy with a major offshore wind foundation/structural design practice caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="230" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
         <is>
           <t>Xodus Group</t>
@@ -6778,8 +10720,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="249" ht="44" customHeight="1">
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Xodus Group while looking at companies working in offshore wind structural engineering, and your work as an energy consultancy providing engineering, subsea and offshore wind advisory services caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="230" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
         <is>
           <t>Genesis (TechnipFMC)</t>
@@ -6803,8 +10761,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="250" ht="44" customHeight="1">
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Genesis (TechnipFMC) while looking at companies working in offshore and structural engineering consultancy, and your work as an oil &amp; gas and offshore engineering consultancy caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="230" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
         <is>
           <t>Wood Group (Wood plc)</t>
@@ -6828,8 +10802,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="251" ht="44" customHeight="1">
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Wood Group (Wood plc) while looking at companies working in offshore and structural engineering consultancy, and your work as a global engineering and consultancy company serving energy, including offshore oil &amp; gas and renewables caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="230" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
         <is>
           <t>Global Maritime</t>
@@ -6853,8 +10843,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="252" ht="44" customHeight="1">
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Global Maritime while looking at companies working in offshore and structural engineering consultancy, and your work as a marine warranty surveying and offshore engineering consultancy for marine operations caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="230" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
         <is>
           <t>ODE Offshore Design Engineering</t>
@@ -6878,8 +10884,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="253" ht="44" customHeight="1">
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ODE Offshore Design Engineering while looking at companies working in offshore and structural engineering consultancy, and your work as an independent offshore engineering consultancy for oil &amp; gas and renewables projects caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="230" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
         <is>
           <t>JDR Cable Systems</t>
@@ -6903,8 +10925,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="254" ht="44" customHeight="1">
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across JDR Cable Systems while looking at companies working in offshore wind structural engineering, and your work as a manufacturer of subsea power and umbilical cables for offshore wind and oil &amp; gas caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="230" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
         <is>
           <t>Houlder</t>
@@ -6928,8 +10966,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="255" ht="44" customHeight="1">
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Houlder while looking at companies working in offshore and structural engineering consultancy, and your work as a marine and offshore engineering consultancy specialising in ship design and offshore renewables caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="230" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
         <is>
           <t>Frazer-Nash Consultancy</t>
@@ -6953,8 +11007,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="256" ht="44" customHeight="1">
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Frazer-Nash Consultancy while looking at companies working in offshore and structural engineering consultancy, and your work as a systems and engineering consultancy with a marine/offshore structural engineering practice caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="230" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
         <is>
           <t>Aker Solutions</t>
@@ -6978,8 +11048,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="257" ht="44" customHeight="1">
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Aker Solutions while looking at companies working in marine equipment and propulsion systems, and your work as an engineering and construction services provider for offshore oil &amp; gas and renewable energy projects caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="230" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
         <is>
           <t>Kvaerner</t>
@@ -7003,8 +11089,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="258" ht="44" customHeight="1">
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Kvaerner while looking at companies working in marine and offshore engineering, and your work as an EPC contractor for offshore platforms, substructures and onshore facilities caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="230" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
         <is>
           <t>TechnipFMC Norway</t>
@@ -7028,8 +11130,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="259" ht="44" customHeight="1">
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across TechnipFMC Norway while looking at companies working in subsea structural engineering, and your work as a Norwegian arm of the global subsea/offshore engineering and technology group caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="230" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
         <is>
           <t>DNV</t>
@@ -7053,8 +11171,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="260" ht="44" customHeight="1">
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across DNV while looking at companies working in naval architecture and marine engineering, and your work as a classification society and technical advisor providing naval architecture, structural engineering and standards for offshore/marine structures caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="230" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
         <is>
           <t>Reinertsen</t>
@@ -7078,8 +11212,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="261" ht="44" customHeight="1">
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Reinertsen while looking at companies working in offshore and structural engineering consultancy, and your work as a Norwegian engineering company delivering structural, mechanical and offshore engineering services caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="230" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
         <is>
           <t>Multiconsult</t>
@@ -7103,8 +11253,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="262" ht="44" customHeight="1">
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Multiconsult while looking at companies working in offshore and structural engineering consultancy, and your work as a Norwegian multidisciplinary consultancy with marine/offshore structural engineering capability caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="230" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
         <is>
           <t>Ørsted A/S</t>
@@ -7128,8 +11294,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="263" ht="44" customHeight="1">
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ørsted A/S while looking at companies working in offshore wind structural engineering, and your position as World's largest offshore wind developer/operator, headquartered in Denmark caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="230" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
         <is>
           <t>RWE Offshore Wind GmbH</t>
@@ -7153,8 +11335,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="264" ht="44" customHeight="1">
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across RWE Offshore Wind GmbH while looking at companies working in offshore wind structural engineering, and your work as a major German utility's offshore wind development/operations arm caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="230" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
         <is>
           <t>Vattenfall Offshore Wind</t>
@@ -7178,8 +11376,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="265" ht="44" customHeight="1">
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Vattenfall Offshore Wind while looking at companies working in offshore wind structural engineering, and your work as a Swedish state-owned utility's offshore wind development/operations arm caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="230" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
         <is>
           <t>Iberdrola (Offshore Wind)</t>
@@ -7203,8 +11417,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="266" ht="44" customHeight="1">
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Iberdrola (Offshore Wind) while looking at companies working in offshore wind structural engineering, and your work as a major Spanish utility with a large offshore wind development portfolio caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="230" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
         <is>
           <t>EDF Renewables (Offshore Wind)</t>
@@ -7228,8 +11458,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="267" ht="44" customHeight="1">
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across EDF Renewables (Offshore Wind) while looking at companies working in offshore wind structural engineering, and your work as a French utility's renewable energy arm, active in offshore wind caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="230" customHeight="1">
       <c r="A267" s="2" t="inlineStr">
         <is>
           <t>SSE Renewables</t>
@@ -7253,8 +11499,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="268" ht="44" customHeight="1">
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across SSE Renewables while looking at companies working in offshore wind structural engineering, and your work as a UK/Irish utility's renewable energy arm with a large offshore wind portfolio caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="230" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
         <is>
           <t>ScottishPower Renewables</t>
@@ -7278,8 +11540,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="269" ht="44" customHeight="1">
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ScottishPower Renewables while looking at companies working in offshore wind structural engineering, and your work as a UK renewable energy developer active in offshore wind caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="230" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
         <is>
           <t>Ocean Winds</t>
@@ -7303,8 +11581,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="270" ht="44" customHeight="1">
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ocean Winds while looking at companies working in offshore wind structural engineering, and your work as a joint venture offshore wind developer active across Europe caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="230" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
           <t>Equinor</t>
@@ -7328,8 +11622,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="271" ht="44" customHeight="1">
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Equinor while looking at companies working in offshore wind structural engineering, and your work as a Norwegian energy major with a significant offshore wind portfolio caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="230" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
           <t>EnBW</t>
@@ -7353,8 +11663,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="272" ht="44" customHeight="1">
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across EnBW while looking at companies working in offshore wind structural engineering, and your work as a German utility with an offshore wind development/operations portfolio caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="230" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
         <is>
           <t>Shell (Offshore Wind)</t>
@@ -7378,8 +11704,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="273" ht="44" customHeight="1">
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Shell (Offshore Wind) while looking at companies working in offshore wind structural engineering, and your work as a global energy major with a growing offshore wind development portfolio caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="230" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
         <is>
           <t>TotalEnergies (Offshore Wind)</t>
@@ -7403,8 +11745,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="274" ht="44" customHeight="1">
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across TotalEnergies (Offshore Wind) while looking at companies working in offshore wind structural engineering, and your work as a French energy major with an offshore wind development portfolio caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="230" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
         <is>
           <t>BP (Offshore Wind)</t>
@@ -7428,8 +11786,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="275" ht="44" customHeight="1">
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BP (Offshore Wind) while looking at companies working in offshore wind structural engineering, and your work as a UK-based energy major with an offshore wind development portfolio caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="275" ht="230" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
         <is>
           <t>Northland Power (Europe)</t>
@@ -7453,8 +11827,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="276" ht="44" customHeight="1">
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Northland Power (Europe) while looking at companies working in offshore wind structural engineering, and your work as a canadian-headquartered developer with major European offshore wind assets caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="230" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
         <is>
           <t>Eneco</t>
@@ -7478,8 +11868,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="277" ht="44" customHeight="1">
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Eneco while looking at companies working in offshore wind structural engineering, and your work as a Dutch energy company active in offshore wind development caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="230" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
         <is>
           <t>Van Oord</t>
@@ -7503,8 +11909,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="278" ht="44" customHeight="1">
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Van Oord while looking at companies working in offshore wind structural engineering, and your 150-year-old Dutch marine contractor designing/building offshore wind farms in Europe, Asia and the USA caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="230" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
         <is>
           <t>Boskalis</t>
@@ -7528,8 +11950,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="279" ht="44" customHeight="1">
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Boskalis while looking at companies working in marine construction and offshore engineering, and your work as a Dutch dredging and marine services group active in offshore energy installation caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="230" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
         <is>
           <t>Seaway7 (Subsea7)</t>
@@ -7553,8 +11991,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="280" ht="44" customHeight="1">
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Seaway7 (Subsea7) while looking at companies working in offshore wind structural engineering, and your work as an offshore wind installation specialist, delivering foundations and cable installation caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="230" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
         <is>
           <t>GVA Consultants</t>
@@ -7578,8 +12032,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="281" ht="44" customHeight="1">
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GVA Consultants while looking at companies working in offshore and structural engineering consultancy, and your work as a Swedish/Norwegian structural and marine engineering/design consultancy caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="230" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
         <is>
           <t>Semco Maritime (Germany operations)</t>
@@ -7603,8 +12073,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="282" ht="44" customHeight="1">
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Semco Maritime (Germany operations) while looking at companies working in offshore wind structural engineering, and your work as a German arm of the Danish offshore wind EPC firm Semco Maritime caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="230" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
         <is>
           <t>Gmmostech</t>
@@ -7628,8 +12114,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="283" ht="44" customHeight="1">
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Gmmostech while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding and repair services provider in the Dubai/Sharjah/Ajman/Umm Al Quwain area caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="230" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
         <is>
           <t>Adams Marine</t>
@@ -7653,8 +12155,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="284" ht="44" customHeight="1">
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Adams Marine while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding and repair services provider in the UAE caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="230" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
         <is>
           <t>Triangle Marine Services</t>
@@ -7678,8 +12196,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="285" ht="44" customHeight="1">
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Triangle Marine Services while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding and repair services provider in the UAE caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="230" customHeight="1">
       <c r="A285" s="2" t="inlineStr">
         <is>
           <t>Hamriyah Free Zone Fabrication Cluster (general)</t>
@@ -7703,8 +12237,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="286" ht="44" customHeight="1">
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Hamriyah Free Zone Fabrication Cluster (general) while looking at companies working in marine and offshore engineering, and your work as a cluster of steel and marine fabrication companies operating from Hamriyah Free Zone, Sharjah caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="286" ht="230" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
         <is>
           <t>Emirates Technical Associates (ETA)</t>
@@ -7728,8 +12278,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="287" ht="44" customHeight="1">
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Emirates Technical Associates (ETA) while looking at companies working in marine equipment and propulsion systems, and your work as an engineering and industrial fabrication services provider in the UAE caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="230" customHeight="1">
       <c r="A287" s="2" t="inlineStr">
         <is>
           <t>Malta Shipyards (Palumbo Malta)</t>
@@ -7753,8 +12319,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="288" ht="44" customHeight="1">
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Malta Shipyards (Palumbo Malta) while looking at companies working in shipbuilding and marine fabrication, and your work as a ship repair and conversion yard, a major Mediterranean drydock facility caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="230" customHeight="1">
       <c r="A288" s="2" t="inlineStr">
         <is>
           <t>Slovenia marine/steel fabrication sector (no single dominant firm identified)</t>
@@ -7778,8 +12360,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="289" ht="44" customHeight="1">
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Slovenia marine/steel fabrication sector (no single dominant firm identified) while looking at companies working in shipbuilding and marine fabrication, and your position as Slovenia's registered shipbuilders are mostly small workshops caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="230" customHeight="1">
       <c r="A289" s="2" t="inlineStr">
         <is>
           <t>Siemens Gamesa Renewable Energy</t>
@@ -7803,8 +12401,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="290" ht="44" customHeight="1">
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Siemens Gamesa Renewable Energy while looking at companies working in offshore wind structural engineering, and your work as a major wind turbine OEM with offshore turbine, tower and foundation-adjacent manufacturing across Europe caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="230" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
         <is>
           <t>GE Renewable Energy (Offshore Wind)</t>
@@ -7828,8 +12442,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="291" ht="44" customHeight="1">
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GE Renewable Energy (Offshore Wind) while looking at companies working in offshore wind structural engineering, and your work as a global turbine OEM with European offshore wind manufacturing operations caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="230" customHeight="1">
       <c r="A291" s="2" t="inlineStr">
         <is>
           <t>GRI Renewable Industries</t>
@@ -7853,8 +12483,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="292" ht="44" customHeight="1">
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GRI Renewable Industries while looking at companies working in offshore wind structural engineering, and your work as a Spanish manufacturer of steel and concrete wind towers, 22 facilities across nine countries caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="230" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
         <is>
           <t>CS Wind Corporation (Portugal facility)</t>
@@ -7878,8 +12524,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="293" ht="44" customHeight="1">
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across CS Wind Corporation (Portugal facility) while looking at companies working in offshore wind structural engineering, and your work as a global wind tower manufacturer with a production facility in Portugal caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="230" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
         <is>
           <t>LM Wind Power</t>
@@ -7903,8 +12565,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="294" ht="44" customHeight="1">
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across LM Wind Power while looking at companies working in offshore wind structural engineering, and your work as a rotor blade manufacturer for onshore/offshore wind turbines caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="230" customHeight="1">
       <c r="A294" s="2" t="inlineStr">
         <is>
           <t>Flender International GmbH</t>
@@ -7928,8 +12606,24 @@
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="295" ht="44" customHeight="1">
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Flender International GmbH while looking at companies working in offshore wind structural engineering, and your work as a manufacturer of gearboxes/drivetrain components for wind turbines caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="230" customHeight="1">
       <c r="A295" s="2" t="inlineStr">
         <is>
           <t>Wood Thilsted</t>
@@ -7953,8 +12647,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="296" ht="44" customHeight="1">
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Wood Thilsted while looking at companies working in offshore wind structural engineering, and your work as a specialist offshore wind foundation design and structural engineering consultancy caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="230" customHeight="1">
       <c r="A296" s="2" t="inlineStr">
         <is>
           <t>Atkins (Offshore Wind, part of SNC-Lavalin)</t>
@@ -7978,8 +12688,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="297" ht="44" customHeight="1">
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Atkins (Offshore Wind, part of SNC-Lavalin) while looking at companies working in offshore wind structural engineering, and your work as a major engineering consultancy with an offshore wind structural design practice caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="297" ht="230" customHeight="1">
       <c r="A297" s="2" t="inlineStr">
         <is>
           <t>Xerxes Offshore Engineering</t>
@@ -8003,8 +12729,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="298" ht="44" customHeight="1">
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Xerxes Offshore Engineering while looking at companies working in offshore and structural engineering consultancy, and your work as an offshore engineering consultancy supporting fixed and floating structure design caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="230" customHeight="1">
       <c r="A298" s="2" t="inlineStr">
         <is>
           <t>K2 Management</t>
@@ -8028,8 +12770,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="299" ht="44" customHeight="1">
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across K2 Management while looking at companies working in offshore and structural engineering consultancy, and your work as an independent offshore/onshore wind engineering and consultancy firm caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="230" customHeight="1">
       <c r="A299" s="2" t="inlineStr">
         <is>
           <t>Natural Power</t>
@@ -8053,8 +12811,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="300" ht="44" customHeight="1">
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Natural Power while looking at companies working in offshore wind structural engineering, and your work as a renewable energy engineering and consultancy firm active in offshore wind caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="230" customHeight="1">
       <c r="A300" s="2" t="inlineStr">
         <is>
           <t>Longitude Engineering</t>
@@ -8078,8 +12852,24 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="301" ht="44" customHeight="1">
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Longitude Engineering while looking at companies working in offshore wind structural engineering, and your work as an independent engineering consultancy specialising in offshore wind foundation design caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="230" customHeight="1">
       <c r="A301" s="2" t="inlineStr">
         <is>
           <t>Temporary Works Design BV</t>
@@ -8103,8 +12893,24 @@
           <t>B</t>
         </is>
       </c>
-    </row>
-    <row r="302" ht="44" customHeight="1">
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Temporary Works Design BV while looking at companies working in offshore and structural engineering consultancy, and your work as a Dutch engineering firm specialising in temporary works and installation engineering for offshore projects caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="230" customHeight="1">
       <c r="A302" s="2" t="inlineStr">
         <is>
           <t>GustoMSC (part of NOV)</t>
@@ -8126,6 +12932,22 @@
       <c r="G302" s="2" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GustoMSC (part of NOV) while looking at companies working in heavy lift and marine transport engineering, and your work as a Dutch designer of offshore vessels and jack-up rigs for wind installation and oil &amp; gas caught my attention.
+I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
+I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
+If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
+You can see some examples of my work and capabilities at ahstructures.com.
+Best regards,
+Ahmad Hussain
+Structural / Mechanical Engineer
+AH Structures
+ahstructures.com</t>
         </is>
       </c>
     </row>

--- a/UAE_EU_Outreach AH Structures.xlsx
+++ b/UAE_EU_Outreach AH Structures.xlsx
@@ -10,7 +10,7 @@
     <sheet name="UAE &amp; EU Outreach" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'UAE &amp; EU Outreach'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'UAE &amp; EU Outreach'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,17 +451,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H302"/>
+  <dimension ref="A1:I302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="100" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="100" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -492,15 +493,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Email Draft</t>
         </is>
@@ -514,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Multidisciplinary steel construction contractor fabricating modules, platforms, drilling packages, substructures and derricks for offshore/onshore oil &amp; gas and renewables, yards at Gorinchem and Kinderdijk.</t>
+          <t>Multidisciplinary steel construction contractor fabricating modules, platforms, drilling packages, substructures and derricks for offshore and onshore oil &amp; gas and renewables clients, with yards at Gorinchem and Kinderdijk. Krinkelwinkel 6, Gorinchem (KVK 23039342).</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -527,18 +533,23 @@
           <t>General Director</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>+31 183 668822</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>Gorinchem, Netherlands</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -563,27 +574,32 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Major offshore construction contractor operating some of the largest heavy-lift and pipelay crane vessels in the industry; active in oil &amp; gas and offshore wind installation/decommissioning.</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr"/>
+          <t>Offshore construction contractor operating some of the largest heavy-lift and pipelay crane vessels in the industry, delivering transport, installation and decommissioning of offshore structures for oil &amp; gas and offshore wind. Netherlands headquarters at Vondellaan 47, Leiden.</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>+31 (0)71 579 9000</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Leiden, Netherlands</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Heerema Marine Contractors (HMC) while looking at companies working in offshore wind structural engineering, and your work as a major offshore construction contractor operating some of the largest heavy-lift and pipelay crane vessels caught my attention.
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Heerema Marine Contractors (HMC) while looking at companies working in offshore wind structural engineering, and your work as an offshore construction contractor operating some of the largest heavy-lift and pipelay crane vessels caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -604,27 +620,32 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Yard specially equipped for EPC(I) of offshore structures and construction of jackets of all sizes, part of the Heerema group.</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
+          <t>Yard equipped for EPC(I) of offshore structures and construction of jackets of all sizes, part of the Heerema group. Belgieweg-Oost 1, Harbor no. 8401, Nieuwdorp (Vlissingen).</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>+31 (0)113 618 000</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>Vlissingen, Netherlands</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Heerema Fabrication Group - Vlissingen Yard while looking at companies working in marine and offshore engineering, and your work as a yard specially equipped for EPC of offshore structures and construction of jackets of all sizes caught my attention.
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Heerema Fabrication Group - Vlissingen Yard while looking at companies working in marine and offshore engineering, and your work as a yard equipped for EPC of offshore structures and construction of jackets of all sizes caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -645,27 +666,44 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Leading position in fabrication/integration of high-voltage substations and offshore wind foundation structures; track record of 3.6+ GW connected across Europe.</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
+          <t>Integrated EPCIC (engineering, procurement, construction, installation and commissioning) supplier for offshore energy projects, specialising in offshore high-voltage substations and wind foundation structures, with a track record of connecting over 3.6 GW of offshore wind in Europe. Westfrankelandsedijk 9, Haven 528, Schiedam. Acquired by Smulders.</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Hans Leerdam</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>sales@smulders-hsm.com</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>+31 (0)10 427 92 00</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Smulders HSM (HSM Offshore Energy) while looking at companies working in offshore wind structural engineering, and your work as a leading position in fabrication/integration of high-voltage substations and offshore wind foundation structures caught my attention.
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Hans,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Smulders HSM (HSM Offshore Energy) while looking at companies working in offshore wind structural engineering, and your work as an integrated EPCIC supplier for offshore energy projects caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -686,27 +724,32 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>75-year-old pioneer in offshore foundations based in Maasvlakte, Rotterdam; monopiles are its flagship product for offshore wind turbine installation.</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
+          <t>Market leader with 75+ years of experience specialising in monopile foundations for offshore wind, plus transition pieces and related logistics. Production facility at Maasvlakte 2, Port of Rotterdam (Pieter van Vollenhovenweg 101); head office in Roermond.</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>+31 475 385 777</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across SIF Netherlands B.V. while looking at companies working in offshore wind structural engineering, and your 75-year-old pioneer in offshore foundations based in Maasvlakte, Rotterdam caught my attention.
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across SIF Netherlands B.V. while looking at companies working in offshore wind structural engineering, and your work as a market leader with 75+ years of experience specialising in monopile foundations for offshore wind caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -730,20 +773,21 @@
           <t>Offers conversions, ship repair, port/voyage maintenance, heavy-lift floating cranes, and steel construction work for offshore wind mobilization/demobilization.</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -771,20 +815,21 @@
           <t>Extensive experience in offshore fabrication across various countries and seas worldwide.</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -812,20 +857,21 @@
           <t>Marine and offshore supply company serving the Rotterdam port area.</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -853,20 +899,21 @@
           <t>Global Dutch shipbuilding/engineering conglomerate producing warships, yachts, fishing vessels, barges, merchant vessels and dredgers (mixed commercial/naval).</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Gorinchem, Netherlands</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -894,20 +941,21 @@
           <t>Multinational shipbuilder and equipment manufacturer for dredging and offshore vessels/equipment.</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Kinderdijk, Netherlands</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -935,20 +983,21 @@
           <t>Shipbuilder specializing in newbuild sailing and unique motor superyachts.</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr"/>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Vollenhove, Netherlands</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -973,27 +1022,36 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Worldwide supplier of heavy-lift cranes and step-changing offshore equipment for oil &amp; gas, renewable energy and civil markets.</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr"/>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>Worldwide supplier of heavy construction equipment and step-changing technical solutions for offshore oil and gas, renewable energy, entertainment and civil markets, including heavy-lift cranes, pipelay systems, drilling equipment and vessel designs. Admiraal Trompstraat 2, Schiedam.</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>info@huisman-nl.com</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>+31 (0)88 070 22 22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>Schiedam, Netherlands</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Huisman Equipment while looking at companies working in heavy lift and marine transport engineering, and your work as a worldwide supplier of heavy-lift cranes and step-changing offshore equipment for oil &amp; gas caught my attention.
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Huisman Equipment while looking at companies working in heavy lift and marine transport engineering, and your work as a worldwide supplier of heavy construction equipment and step-changing technical solutions for offshore oil and gas caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -1017,20 +1075,21 @@
           <t>Developer of motion-compensated gangway and offshore access systems (with Bosch Rexroth) for offshore wind and marine operations.</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1058,20 +1117,21 @@
           <t>Repair shipyard in the port of Rotterdam.</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr"/>
-      <c r="D15" s="2" t="inlineStr"/>
-      <c r="E15" s="2" t="inlineStr"/>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1096,27 +1156,44 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Offshore engineering and naval architecture firm covering ship design &amp; conversion, maritime engineering and on-site services.</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
-      <c r="D16" s="2" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
+          <t>Customised marine engineering and naval architecture solutions for the maritime and offshore industries. Founded in 2007 by naval engineers, now 20+ specialists working across yachting, offshore, repair, heavy lift and commercial shipping. Leerparkpromenade 40, Dordrecht.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Sander Broekmeulen</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Group CEO</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>info@saltwater.nl</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>+31 78 205 15 00</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Saltwater while looking at companies working in naval architecture and marine engineering, and your work as an offshore engineering and naval architecture firm covering ship design &amp; conversion caught my attention.
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Sander,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Saltwater while looking at companies working in naval architecture and marine engineering, and your work as a customised marine engineering and naval architecture solutions for the maritime and offshore industries caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -1137,27 +1214,36 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Dutch engineering company specialised in transportation, installation and removal engineering for offshore oil, gas and wind farm projects.</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="2" t="inlineStr"/>
+          <t>Engineering company specialised in transportation, installation and removal engineering for global offshore oil, gas and wind farm projects, including offshore substation transport and offshore structural engineering. Westplein 7, Rotterdam.</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>info@h2offshore-eng.com</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>+31 (0)10 442 57 27</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across H2Offshore Engineering B.V. while looking at companies working in offshore and structural engineering consultancy, and your work as a Dutch engineering company specialised in transportation caught my attention.
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across H2Offshore Engineering B.V. while looking at companies working in offshore and structural engineering consultancy, and your work as an engineering company specialised in transportation caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -1181,20 +1267,21 @@
           <t>Rigging and lifting equipment supplier for marine/offshore, with operations in Netherlands, Norway, UK and Poland.</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1219,27 +1306,28 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Offshore wind structures specialist; engineers experienced in monopile, transition piece and secondary steel design.</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr">
+          <t>Offshore wind, hydrogen and mission equipment engineering specialist whose engineers design monopiles, transition pieces and secondary steel. Delivered secondary steel design for 50+ WTG monopile foundations at OranjeWind and a reusable monopile cover for Vattenfall's Hollandse Kust Zuid. Jan Evertsenweg 12, Schiedam.</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Enersea while looking at companies working in offshore wind structural engineering, and your work as an offshore wind structures specialist caught my attention.
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Enersea while looking at companies working in offshore wind structural engineering, and your work as an offshore wind, hydrogen and mission equipment engineering specialist whose engineers design monopiles, transition pieces caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -1278,17 +1366,18 @@
           <t>info@eew-group.com</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Erndtebrück / Rostock, Germany</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Frank,
@@ -1326,18 +1415,19 @@
           <t>Managing Director</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Cuxhaven, Germany</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Bertram,
@@ -1365,20 +1455,21 @@
           <t>Marine engineering/dredging contractor active in Germany for ~50 years, involved in installation of multiple German offshore wind farms.</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Bremen, Germany</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1406,20 +1497,21 @@
           <t>Leading independent technical maintenance/service provider for offshore wind turbines.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr"/>
-      <c r="E23" s="2" t="inlineStr"/>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Bremen, Germany</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1447,20 +1539,21 @@
           <t>Major shipbuilder (founded 1795) constructing large cruise ships and specialised vessels.</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Papenburg, Germany</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1488,20 +1581,21 @@
           <t>World's largest yacht builder with some naval-adjacent work; multiple shipbuilding sites in northern Germany.</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="2" t="inlineStr"/>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Bremen-Vegesack, Germany</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1529,20 +1623,21 @@
           <t>Shipbuilder of custom special-purpose vessels, lifeboats and deck equipment.</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Berne, Germany</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1570,20 +1665,21 @@
           <t>Shipyard (formerly Wismar shipyard) producing specialised vessels; owned by Genting Hong Kong.</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr"/>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Wismar, Germany</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1611,20 +1707,21 @@
           <t>Shipyard founded 1850, delivered 1,500+ new ships, now part of Meyer group producing river cruise vessels.</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr"/>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="2" t="inlineStr"/>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Rostock-Warnemünde, Germany</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1652,20 +1749,21 @@
           <t>Shipbuilder specialising in design/construction of naval vessels (frigates, corvettes) - defense-primary.</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="2" t="inlineStr"/>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Kiel, Germany</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1693,20 +1791,21 @@
           <t>Provides offshore wind energy services from Bremen.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Bremen, Germany</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1734,20 +1833,21 @@
           <t>Offshore wind developer/operator with offices in Hamburg, Bremen, Rostock and Leer.</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr"/>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Hamburg, Germany</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1775,20 +1875,21 @@
           <t>Former offshore wind turbine/service company headquartered in Bremerhaven, now part of Siemens Gamesa.</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Bremerhaven, Germany</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1813,27 +1914,32 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Designs and manufactures heavy-duty steel offshore foundation structures in Bremerhaven.</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr"/>
-      <c r="E33" s="2" t="inlineStr"/>
+          <t>Designs and manufactures heavy-duty steel foundation structures, including tripods, for offshore wind turbines from its Bremerhaven facility. Am Lunedeich 158, Bremerhaven.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
+      <c r="E33" s="2" t="n"/>
       <c r="F33" s="2" t="inlineStr">
         <is>
+          <t>+49 471 902628-10</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
           <t>Bremerhaven, Germany</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across WeserWind Offshore Construction (Georgsmarienhütte) while looking at companies working in offshore foundation fabrication, and I noticed that WeserWind Offshore Construction (Georgsmarienhütte) designs and manufactures heavy-duty steel offshore foundation structures in Bremerhaven, which caught my attention.
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across WeserWind Offshore Construction (Georgsmarienhütte) while looking at companies working in offshore wind structural engineering, and I noticed that WeserWind Offshore Construction (Georgsmarienhütte) designs and manufactures heavy-duty steel foundation structures, which caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -1857,20 +1963,21 @@
           <t>Operates a wind-tunnel test centre in Bremerhaven offering aerodynamic testing for rotor blades.</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr"/>
-      <c r="D34" s="2" t="inlineStr"/>
-      <c r="E34" s="2" t="inlineStr"/>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Bremerhaven, Germany</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1895,7 +2002,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Steel fabricator specialising in offshore wind foundations (monopiles, jackets); offshore-structure joint ventures with EEW Group.</t>
+          <t>International steel contractor specialising in large-scale, highly complex steel structures across three business areas: wind and renewable energy, oil and gas, and infrastructure. HQ at Nørredybet 1, Aalborg Øst, with offices in Copenhagen and Poland and production at Lindø Industry Park, Funen.</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1908,22 +2015,31 @@
           <t>CEO</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>office@bladt.dk</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
+          <t>+45 9635 3700</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
           <t>Aalborg, Denmark</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Anders,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Bladt Industries A/S while looking at companies working in offshore wind structural engineering, and your work as a steel fabricator specialising in offshore wind foundations caught my attention.
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Bladt Industries A/S while looking at companies working in structural steel fabrication, and your work as an international steel contractor specialising in large-scale caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -1947,20 +2063,21 @@
           <t>Construction/civil engineering group active in bridges, buildings and offshore wind turbine foundation installation.</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
+      <c r="E36" s="2" t="n"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Søborg, Denmark</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1988,20 +2105,21 @@
           <t>Naval architecture and ship-design advisory firm with heritage from the former Odense Steel Shipyard (est. 1917).</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="2" t="inlineStr"/>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Odense, Denmark</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2029,20 +2147,21 @@
           <t>Shipyard (founded 1916) specialising in shipbuilding and repair.</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
-      <c r="E38" s="2" t="inlineStr"/>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Munkebo, Denmark</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2070,20 +2189,21 @@
           <t>Shipbuilder founded 1958.</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Frederikshavn, Denmark</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2108,27 +2228,36 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Offshore wind EPC firm offering full-scope engineering from FEED to detailed design; designed/built 20+ offshore substations.</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr"/>
+          <t>Project engineering company established in 1888, focused on offshore substation services, electrical installations and rig services for the global energy market. Offers full-scope engineering from conceptual studies through FEED to detailed design. 1,000-5,000 staff across 13 locations. Esbjerg Brygge 30, Esbjerg.</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Semco@semcomaritime.com</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
+          <t>+45 79 16 66 66</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
           <t>Esbjerg, Denmark</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Semco Maritime while looking at companies working in offshore wind structural engineering, and your work as an offshore wind EPC firm offering full-scope engineering from FEED to detailed design caught my attention.
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Semco Maritime while looking at companies working in offshore and structural engineering consultancy, and your work as a project engineering company established in 1888 caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -2152,20 +2281,21 @@
           <t>Offshore support vessel operator serving offshore wind and oil &amp; gas (standby, emergency response, rescue).</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr"/>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="n"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Esbjerg, Denmark</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2190,27 +2320,36 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>450,000 m2 offshore wind tower manufacturing facility with workshops for painting, blasting, rolling and welding.</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>Leading producer of premium offshore wind foundations, with a portfolio covering transition pieces, monopiles, jackets and floating foundations. Nørredybet 1, Aalborg Øst, with 450,000 m2 of facilities including painting, blasting, rolling and welding workshops.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>CSWO_office@cswind.com</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
+          <t>+45 9635 3700</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
           <t>Aalborg, Denmark</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across CS Wind Offshore A/S while looking at companies working in offshore wind structural engineering, and your 450,000 m2 offshore wind tower manufacturing facility with workshops for painting, blasting, rolling and welding caught my attention.
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across CS Wind Offshore A/S while looking at companies working in offshore wind structural engineering, and your work as a leading producer of premium offshore wind foundations caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -2231,27 +2370,36 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Wind turbine tower manufacturer with production facilities in Denmark and Germany.</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr"/>
+          <t>Wind turbine tower manufacturer and steel processing/surface treatment specialist serving the wind industry, with European production in Denmark and Germany. Engdraget 20, Varde.</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>titan@titan-wind.com</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t>+45 70 70 71 50</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Titan Wind Energy (Europe) A/S while looking at companies working in offshore wind structural engineering, and your work as a wind turbine tower manufacturer with production facilities in Denmark and Germany caught my attention.
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Titan Wind Energy (Europe) A/S while looking at companies working in offshore wind structural engineering, and your work as a wind turbine tower manufacturer and steel processing/surface treatment specialist serving the wind industry caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -2272,27 +2420,36 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Steel tower manufacturer for offshore wind, known for engineering quality; partnered with Marmen (Canada) on offshore tower fabrication.</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
+          <t>World's leading manufacturer of offshore wind towers, holding worldwide production rights for the Stiesdal floating and bottom-fixed offshore foundations. Recent deliveries include towers for Hollandse Kust West VI. Based in Give, Denmark.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>welcon@welcon.dk</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>+45 30 18 61 00</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Welcon A/S while looking at companies working in offshore wind structural engineering, and your work as a steel tower manufacturer for offshore wind, known for engineering quality caught my attention.
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Welcon A/S while looking at companies working in offshore wind structural engineering, and your position as World's leading manufacturer of offshore wind towers caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -2316,20 +2473,21 @@
           <t>Historic offshore wind farm installation/service vessel operator based in Fredericia.</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr"/>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Fredericia, Denmark</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2357,20 +2515,21 @@
           <t>Major wind turbine OEM designing/manufacturing/installing/servicing offshore turbines, towers and blades.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr"/>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Aarhus, Denmark</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2395,7 +2554,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Steel construction specialist (Eiffage Group) with 50 years of sea-based structure experience; major fabricator of jackets/foundations for fixed offshore wind, expanding into floating wind.</t>
+          <t>Steel construction specialist within the Eiffage Group with over 20 years of offshore wind experience, having completed or begun more than 3,000 foundations and 30 electrical substations for the European market. HQ at 3-7 place de l'Europe, Vélizy-Villacoublay; fabrication at Cuincy/Lauwin-Planque.</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2408,22 +2567,27 @@
           <t>Director Energy &amp; Industry</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="n"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t>+33 1 34 65 89 89</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>Vélizy-Villacoublay, France</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Arnaud,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Eiffage Métal while looking at companies working in offshore wind structural engineering, and your work as a steel construction specialist with 50 years of sea-based structure experience caught my attention.
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Eiffage Métal while looking at companies working in offshore wind structural engineering, and your work as a steel construction specialist within the Eiffage Group with over 20 years of offshore wind experience caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -2462,17 +2626,18 @@
           <t>offshorewind@setec.com</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Pascal,
@@ -2500,20 +2665,21 @@
           <t>Europe's largest shipyard, building commercial, naval and passenger ships; sites also in Brest, Toulon, La Réunion, La Martinique.</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr"/>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n"/>
+      <c r="E49" s="2" t="n"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Saint-Nazaire, France</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2541,20 +2707,21 @@
           <t>Repair yard with three dry docks (largest 420x80m); large workshops for steelwork, mechanical work, LNG equipment and pipefitting.</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Brest, France</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2579,27 +2746,28 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Floating offshore wind foundation designer/developer, partnering with NGE on a floating-foundation manufacturing facility in southern France.</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
-      <c r="D51" s="2" t="inlineStr"/>
-      <c r="E51" s="2" t="inlineStr"/>
-      <c r="F51" s="2" t="inlineStr">
+          <t>Fully integrated developer of large-scale floating offshore wind projects and provider of its patented Damping Pool floating foundation technology. Subsidiary of BW Offshore. Zone Athelia IV, 147 avenue du Jujubier, La Ciotat.</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BW Ideol while looking at companies working in offshore wind structural engineering, and your work as a floating offshore wind foundation designer/developer caught my attention.
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BW Ideol while looking at companies working in offshore wind structural engineering, and your work as a fully integrated developer of large-scale floating offshore wind projects and provider of its patented Damping caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -2623,20 +2791,21 @@
           <t>French construction group entering floating offshore wind via a 50% stake in BW Ideol's Fos-sur-Mer serial production line.</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="n"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2664,20 +2833,21 @@
           <t>Offshore wind developer active since 2014, with an engineering office and O&amp;M subsidiary (VALEMO).</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr"/>
-      <c r="D53" s="2" t="inlineStr"/>
-      <c r="E53" s="2" t="inlineStr"/>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2702,27 +2872,36 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Global offshore engineering/construction major with an offshore competency centre in France; designs/builds fixed and mobile platforms, subsea pipelines.</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr"/>
+          <t>Global leader in engineering and construction of major offshore and onshore energy and infrastructure projects, present in 50+ countries with eight fabrication yards and a fleet of 15+ construction vessels. Founded 1957. The vendor.management address is the route for supplier and subcontractor registration.</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>vendor.management@saipem.com</t>
+        </is>
+      </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
+          <t>+39 02 44231</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
           <t>Saint-Quentin-en-Yvelines, France</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Saipem (France) while looking at companies working in subsea structural engineering, and your work as a global offshore engineering/construction major with an offshore competency centre in France caught my attention.
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Saipem (France) while looking at companies working in marine equipment and propulsion systems, and your work as a global leader in engineering and construction of major offshore and onshore energy and infrastructure projects caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -2761,17 +2940,18 @@
           <t>info@haizeawindgroup.com</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Zierbena / Bilbao, Spain</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Borja,
@@ -2814,17 +2994,18 @@
           <t>comunicacion@windwaves.com</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Ferrol, Spain</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Diego,
@@ -2849,27 +3030,36 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Manufacturer of offshore wind foundations, strategic partnership with Navantia for a one-stop offshore service.</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr"/>
-      <c r="D57" s="2" t="inlineStr"/>
-      <c r="E57" s="2" t="inlineStr"/>
+          <t>Manufacturer of wind towers and offshore foundations with proven experience in complex tubular steel structures. Expanded its Avilés capability since 2012 and holds a strategic partnership with Navantia providing one-stop service for offshore projects. Avenida de la Siderurgia 28, Avilés, Asturias.</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>windar@windar-renovables.com</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
+          <t>+34 985 560 090</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
           <t>Avilés, Spain</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Windar Renovables while looking at companies working in offshore wind structural engineering, and your work as a manufacturer of offshore wind foundations, strategic partnership with Navantia for a one-stop offshore service caught my attention.
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Windar Renovables while looking at companies working in offshore wind structural engineering, and your work as a manufacturer of wind towers and offshore foundations with proven experience in complex tubular steel structures caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -2893,20 +3083,21 @@
           <t>State-owned shipbuilder for civil and military naval construction, also producing structures for offshore wind/hydrogen; sites in Ferrol, Cádiz, Cartagena, Madrid.</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr"/>
-      <c r="D58" s="2" t="inlineStr"/>
-      <c r="E58" s="2" t="inlineStr"/>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n"/>
+      <c r="E58" s="2" t="n"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Ferrol / Cádiz / Cartagena, Spain</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2931,27 +3122,28 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Engineering provider with fixed-bottom offshore wind experience, including foundation and monopile design.</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr"/>
-      <c r="D59" s="2" t="inlineStr"/>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr">
+          <t>Marine and offshore structural engineering and consultancy firm founded in 2015, specialising in the fixed-bottom offshore wind industry including foundation and monopile design. Acquired by Global Maritime in January 2024. C/ Marcenado 25, Madrid.</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Iberian Offshore while looking at companies working in offshore wind structural engineering, and your work as an engineering provider with fixed-bottom offshore wind experience, including foundation and monopile design caught my attention.
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Iberian Offshore while looking at companies working in offshore wind structural engineering, and your work as a marine and offshore structural engineering and consultancy firm founded in 2015 caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -2972,27 +3164,32 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Joint venture (Simply Blue Group, Proes Consultores/Grupo Amper, FF New Energy Venture) for floating offshore wind farm design/development.</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
-      <c r="D60" s="2" t="inlineStr"/>
-      <c r="E60" s="2" t="inlineStr"/>
-      <c r="F60" s="2" t="inlineStr">
+          <t>Joint venture of Simply Blue Group (Ireland), Proes Consultores (Amper Group) and FF New Energy Venture, specialising in the design, development and management of floating offshore wind farms across Spain and Portugal, including the first cross-border Spanish-Portuguese project. C/ Serrano 8, Madrid.</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>info@iberbluewind.com</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across IberBlue Wind while looking at companies working in offshore wind structural engineering, and your work as a joint venture for floating offshore wind farm design/development caught my attention.
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across IberBlue Wind while looking at companies working in offshore wind structural engineering, and your work as a joint venture of Simply Blue Group caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -3013,27 +3210,28 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Engineering division of Grupo Amper providing offshore wind structural/foundation design services.</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr"/>
-      <c r="D61" s="2" t="inlineStr"/>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr">
+          <t>Multidisciplinary international engineering and architecture consultancy within the Amper Group, with 50 years delivering projects, technical assistance and advisory work in transport and energy. HQ in Madrid with offices in Bogotá, Lima and La Paz. Co-founder of the IberBlue Wind floating offshore wind JV.</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n"/>
+      <c r="E61" s="2" t="n"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Proes Consultores (Grupo Amper) while looking at companies working in offshore wind structural engineering, and your work as an engineering division of Grupo Amper providing offshore wind structural/foundation design services caught my attention.
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Proes Consultores (Grupo Amper) while looking at companies working in offshore wind structural engineering, and your work as a multidisciplinary international engineering and architecture consultancy within the Amper Group caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -3057,20 +3255,21 @@
           <t>Manufacturer of mechanically welded foundation components for offshore wind power.</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr"/>
-      <c r="D62" s="2" t="inlineStr"/>
-      <c r="E62" s="2" t="inlineStr"/>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n"/>
+      <c r="E62" s="2" t="n"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3098,20 +3297,21 @@
           <t>Supplies and provides technical assistance for shaft and rudder line equipment; Vigo is a major European Atlantic ship-repair hub.</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr"/>
-      <c r="D63" s="2" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+      <c r="E63" s="2" t="n"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>Vigo, Spain</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3136,27 +3336,36 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Designs/manufactures critical handling, lifting, anchoring and launch/recovery systems for offshore oil &amp; gas, offshore/floating wind and subsea sectors.</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr"/>
-      <c r="E64" s="2" t="inlineStr"/>
+          <t>Designs and manufactures critical equipment for offshore oil &amp; gas, offshore and floating wind, subsea and underwater sectors, including handling, lifting, anchoring and launch and recovery systems, plus hot-section components for gas turbines. Via Portici Manarini 41/A, Chiuduno (BG).</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>info@remazel.com</t>
+        </is>
+      </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
+          <t>+39 035 0693111</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
           <t>Chiuduno, Italy</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Remazel Engineering S.p.A. (Fincantieri subsidiary) while looking at companies working in subsea structural engineering, and your work as a designs/manufactures critical handling, lifting, anchoring and launch/recovery systems for offshore oil &amp; gas, offshore/floating wind caught my attention.
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Remazel Engineering S.p.A. (Fincantieri subsidiary) while looking at companies working in subsea structural engineering, and I noticed that Remazel Engineering S.p.A. (Fincantieri subsidiary) designs and manufactures critical equipment for offshore oil &amp; gas, which caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -3180,20 +3389,21 @@
           <t>40+ years of heavy steel structures construction, supplying wind turbine components and offshore/onshore energy supply-chain elements.</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr"/>
-      <c r="D65" s="2" t="inlineStr"/>
-      <c r="E65" s="2" t="inlineStr"/>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>Ravenna, Italy</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3221,20 +3431,21 @@
           <t>Major shipbuilder (7,000+ vessels over 230 years) expanding into offshore engineering via acquisitions.</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr"/>
-      <c r="D66" s="2" t="inlineStr"/>
-      <c r="E66" s="2" t="inlineStr"/>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n"/>
+      <c r="E66" s="2" t="n"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Trieste, Italy</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3262,20 +3473,21 @@
           <t>Joint venture between Genoa shipbuilder T. Mariotti and steel manufacturer Cimolai.</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr"/>
-      <c r="D67" s="2" t="inlineStr"/>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="C67" s="2" t="n"/>
+      <c r="D67" s="2" t="n"/>
+      <c r="E67" s="2" t="n"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>San Giorgio di Nogaro, Italy</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3303,20 +3515,21 @@
           <t>Group uniting two historic Genoa shipyards - ultra-luxury cruise ship construction and ship repair/conversion.</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr"/>
-      <c r="E68" s="2" t="inlineStr"/>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n"/>
+      <c r="E68" s="2" t="n"/>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3341,27 +3554,36 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Global leader in design/construction of offshore plants (fixed/mobile platforms, subsea pipelines); Sardinia (Arbatax) facility fabricates HVAC offshore substations.</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr"/>
-      <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="2" t="inlineStr"/>
+          <t>Global leader in engineering and construction of major offshore and onshore energy and infrastructure projects, present in 50+ countries with eight fabrication yards and a fleet of 15+ construction vessels plus 15 drilling vessels. Founded 1957. HQ Via Luigi Russolo 5, Milan. The vendor.management address is the route for supplier and subcontractor registration.</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>vendor.management@saipem.com</t>
+        </is>
+      </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
+          <t>+39 02 44231</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
           <t>San Donato Milanese, Italy</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Saipem S.p.A. while looking at companies working in subsea structural engineering, and your work as a global leader in design/construction of offshore plants caught my attention.
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Saipem S.p.A. while looking at companies working in marine equipment and propulsion systems, and your work as a global leader in engineering and construction of major offshore and onshore energy and infrastructure projects caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -3385,20 +3607,21 @@
           <t>Naval architects and marine engineers designing/building offshore and other vessel types since 1994.</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr"/>
-      <c r="D70" s="2" t="inlineStr"/>
-      <c r="E70" s="2" t="inlineStr"/>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="C70" s="2" t="n"/>
+      <c r="D70" s="2" t="n"/>
+      <c r="E70" s="2" t="n"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3426,20 +3649,21 @@
           <t>Shipbuilder (founded 1970) specialising in fibre-reinforced plastic hull vessels.</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr"/>
-      <c r="D71" s="2" t="inlineStr"/>
-      <c r="E71" s="2" t="inlineStr"/>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3467,20 +3691,21 @@
           <t>Shipyard-area operator/workshop in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr"/>
-      <c r="D72" s="2" t="inlineStr"/>
-      <c r="E72" s="2" t="inlineStr"/>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3508,20 +3733,21 @@
           <t>Shipyard-area operator/workshop in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr"/>
-      <c r="D73" s="2" t="inlineStr"/>
-      <c r="E73" s="2" t="inlineStr"/>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="C73" s="2" t="n"/>
+      <c r="D73" s="2" t="n"/>
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3549,20 +3775,21 @@
           <t>Shipyard operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr"/>
-      <c r="E74" s="2" t="inlineStr"/>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3590,20 +3817,21 @@
           <t>Marine/ship service workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr"/>
-      <c r="D75" s="2" t="inlineStr"/>
-      <c r="E75" s="2" t="inlineStr"/>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n"/>
+      <c r="E75" s="2" t="n"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3631,20 +3859,21 @@
           <t>Dry-dock/ship repair operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr"/>
-      <c r="D76" s="2" t="inlineStr"/>
-      <c r="E76" s="2" t="inlineStr"/>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3672,20 +3901,21 @@
           <t>Shipyard operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr"/>
-      <c r="D77" s="2" t="inlineStr"/>
-      <c r="E77" s="2" t="inlineStr"/>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="C77" s="2" t="n"/>
+      <c r="D77" s="2" t="n"/>
+      <c r="E77" s="2" t="n"/>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3713,20 +3943,21 @@
           <t>Marine services operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr"/>
-      <c r="D78" s="2" t="inlineStr"/>
-      <c r="E78" s="2" t="inlineStr"/>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3754,20 +3985,21 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr"/>
-      <c r="D79" s="2" t="inlineStr"/>
-      <c r="E79" s="2" t="inlineStr"/>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+      <c r="E79" s="2" t="n"/>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3795,20 +4027,21 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr"/>
-      <c r="D80" s="2" t="inlineStr"/>
-      <c r="E80" s="2" t="inlineStr"/>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3836,20 +4069,21 @@
           <t>Marine engine/diesel repair workshop in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr"/>
-      <c r="D81" s="2" t="inlineStr"/>
-      <c r="E81" s="2" t="inlineStr"/>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="C81" s="2" t="n"/>
+      <c r="D81" s="2" t="n"/>
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3877,20 +4111,21 @@
           <t>Steel/ship repair workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr"/>
-      <c r="D82" s="2" t="inlineStr"/>
-      <c r="E82" s="2" t="inlineStr"/>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="C82" s="2" t="n"/>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3918,20 +4153,21 @@
           <t>Marine engine workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+      <c r="E83" s="2" t="n"/>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3959,20 +4195,21 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr"/>
-      <c r="D84" s="2" t="inlineStr"/>
-      <c r="E84" s="2" t="inlineStr"/>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4000,20 +4237,21 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr"/>
-      <c r="D85" s="2" t="inlineStr"/>
-      <c r="E85" s="2" t="inlineStr"/>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="C85" s="2" t="n"/>
+      <c r="D85" s="2" t="n"/>
+      <c r="E85" s="2" t="n"/>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4041,20 +4279,21 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr"/>
-      <c r="D86" s="2" t="inlineStr"/>
-      <c r="E86" s="2" t="inlineStr"/>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4082,20 +4321,21 @@
           <t>Ship repair/workshop operator in the Port of Genoa.</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr"/>
-      <c r="D87" s="2" t="inlineStr"/>
-      <c r="E87" s="2" t="inlineStr"/>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="C87" s="2" t="n"/>
+      <c r="D87" s="2" t="n"/>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4123,20 +4363,21 @@
           <t>Largest ship repair facility in Tuzla Bay, offering repair and conversion services.</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr"/>
-      <c r="D88" s="2" t="inlineStr"/>
-      <c r="E88" s="2" t="inlineStr"/>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4164,20 +4405,21 @@
           <t>65+ year shipbuilding/repair yard, 85+ delivered vessel projects (chemical tankers, ferries, heavy-duty barges, specialised marine vessels).</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr"/>
-      <c r="D89" s="2" t="inlineStr"/>
-      <c r="E89" s="2" t="inlineStr"/>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n"/>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4205,20 +4447,21 @@
           <t>Group of shipyards (Tuzla, TGE, Neta, Altinova) covering shipbuilding and steel/pipe fabrication.</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr"/>
-      <c r="D90" s="2" t="inlineStr"/>
-      <c r="E90" s="2" t="inlineStr"/>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>Tuzla / Altınova, Turkey</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4246,20 +4489,21 @@
           <t>Shipyard located in Tuzla, Istanbul.</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr"/>
-      <c r="D91" s="2" t="inlineStr"/>
-      <c r="E91" s="2" t="inlineStr"/>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="C91" s="2" t="n"/>
+      <c r="D91" s="2" t="n"/>
+      <c r="E91" s="2" t="n"/>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4287,20 +4531,21 @@
           <t>Shipyard established 1990 in Tuzla, Istanbul.</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr"/>
-      <c r="D92" s="2" t="inlineStr"/>
-      <c r="E92" s="2" t="inlineStr"/>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4328,20 +4573,21 @@
           <t>Shipyard established 1999 in Tuzla, Istanbul.</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr"/>
-      <c r="D93" s="2" t="inlineStr"/>
-      <c r="E93" s="2" t="inlineStr"/>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n"/>
+      <c r="E93" s="2" t="n"/>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4369,20 +4615,21 @@
           <t>Shipyard established 1975 in Tuzla, Istanbul.</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr"/>
-      <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="2" t="inlineStr"/>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4407,27 +4654,32 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>UK corporation (est. Feb 2021) building the world's largest monopile manufacturing plant in Teesside.</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr"/>
-      <c r="D95" s="2" t="inlineStr"/>
-      <c r="E95" s="2" t="inlineStr"/>
+          <t>Operator of the world's largest monopile manufacturing facility at Teesworks: 800 m long, 40 m tall, 115,000 m2, designed to produce 100-150 monopiles a year up to 120 m long, 15.5 m diameter and over 3,000 tonnes, creating 750 direct jobs. South Tees Way, Middlesbrough.</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n"/>
+      <c r="E95" s="2" t="n"/>
       <c r="F95" s="2" t="inlineStr">
         <is>
+          <t>+44 1642 130060</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
           <t>Teesside, UK</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across SeAh Wind while looking at companies working in offshore wind structural engineering, and your work as a UK corporation building the world's largest monopile manufacturing plant in Teesside caught my attention.
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across SeAh Wind while looking at companies working in offshore wind structural engineering, and your work as an operator of the world's largest monopile manufacturing facility at Teesworks: 800 m long caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -4448,27 +4700,36 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Fabricates jacket foundations and transition pieces for offshore wind turbines from its Wallsend yard, North East England.</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr"/>
-      <c r="D96" s="2" t="inlineStr"/>
-      <c r="E96" s="2" t="inlineStr"/>
+          <t>Produces and finally assembles steel foundations for offshore wind turbines and offshore substations (topsides and foundations). Wallsend yard covers 325,000 m2 with 40,000 m2 production area, 1,200 tonne lifting capacity and 170 staff, on the Tyne with direct North Sea access. Hadrian Way, Wallsend.</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>info@smulders.com</t>
+        </is>
+      </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
+          <t>+44 191 295 8700</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
           <t>Wallsend, UK</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Smulders Group (Wallsend yard) while looking at companies working in offshore wind structural engineering, and I noticed that Smulders Group (Wallsend yard) fabricates jacket foundations and transition pieces for offshore wind turbines from its Wallsend yard, which caught my attention.
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Smulders Group (Wallsend yard) while looking at companies working in offshore wind structural engineering, and I noticed that Smulders Group (Wallsend yard) produces and finally assembles steel foundations for offshore wind turbines and offshore substations, which caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -4492,20 +4753,21 @@
           <t>Produces fabricated products for offshore wind farms - material prep, fabrication, welding and assembly for carbon/stainless/duplex steel.</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr"/>
-      <c r="D97" s="2" t="inlineStr"/>
-      <c r="E97" s="2" t="inlineStr"/>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4530,27 +4792,36 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Specialises in heavy offshore structure fabrication for general marine, offshore renewables and oil &amp; gas industries.</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr"/>
-      <c r="D98" s="2" t="inlineStr"/>
-      <c r="E98" s="2" t="inlineStr"/>
+          <t>Specialist in heavy offshore structure fabrication for general marine, offshore renewables and oil &amp; gas, covering offshore vessels, drilling platforms, ro-ro ramps and subsea structures. Part of the global ESC Group (note: group operations are headquartered in Asia rather than the UK).</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>info@escsteelstructures.com</t>
+        </is>
+      </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
+          <t>+852 8198 0239</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ESC Steel Structures while looking at companies working in marine and offshore engineering, and I noticed that ESC Steel Structures specialises in heavy offshore structure fabrication for general marine, which caught my attention.
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ESC Steel Structures while looking at companies working in subsea structural engineering, and your work as a specialist in heavy offshore structure fabrication for general marine caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -4574,20 +4845,21 @@
           <t>45+ years delivering fabrication/construction services to Offshore, Oil &amp; Gas and Renewable Energy sectors.</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr"/>
-      <c r="D99" s="2" t="inlineStr"/>
-      <c r="E99" s="2" t="inlineStr"/>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n"/>
+      <c r="E99" s="2" t="n"/>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4615,20 +4887,21 @@
           <t>UK manufacturer qualified to produce aluminium handrails/ladders for offshore wind turbine transition pieces.</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr"/>
-      <c r="D100" s="2" t="inlineStr"/>
-      <c r="E100" s="2" t="inlineStr"/>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4656,20 +4929,21 @@
           <t>Shipbuilding/fabrication company (HQ London) with sites in Belfast, Arnish, Appledore and Methil; ship repair, shipbuilding and offshore construction (mixed commercial/defense).</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr"/>
-      <c r="D101" s="2" t="inlineStr"/>
-      <c r="E101" s="2" t="inlineStr"/>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n"/>
+      <c r="E101" s="2" t="n"/>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>Belfast, UK</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4697,20 +4971,21 @@
           <t>Storied British shipbuilder; built RRS Sir David Attenborough, holds ongoing Royal Navy/RFA dry-dock and refit work (defense-heavy).</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr"/>
-      <c r="D102" s="2" t="inlineStr"/>
-      <c r="E102" s="2" t="inlineStr"/>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>Birkenhead, UK</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4738,20 +5013,21 @@
           <t>Refit/maintenance yards (Falmouth, Tyne) serving Royal Fleet Auxiliary and offshore energy/defence fabrication work (mixed).</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr"/>
-      <c r="D103" s="2" t="inlineStr"/>
-      <c r="E103" s="2" t="inlineStr"/>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="C103" s="2" t="n"/>
+      <c r="D103" s="2" t="n"/>
+      <c r="E103" s="2" t="n"/>
+      <c r="F103" s="2" t="inlineStr"/>
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>Falmouth / Tyne, UK</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4776,27 +5052,36 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Major offshore engineering, construction and project management services provider.</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr"/>
-      <c r="D104" s="2" t="inlineStr"/>
-      <c r="E104" s="2" t="inlineStr"/>
+          <t>Multinational subsea engineering, construction and project management services company for the offshore energy industry, with around 13,000 staff of 80+ nationalities across 36 countries. Registered HQ at 412F Route d'Esch, Luxembourg, with major UK operations in Aberdeen.</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>communications@subsea7.com</t>
+        </is>
+      </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
+          <t>+44 1224 344300</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
           <t>Sutton, Greater London, UK</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Subsea 7 S.A. while looking at companies working in marine equipment and propulsion systems, and your work as a major offshore engineering, construction and project management services provider caught my attention.
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Subsea 7 S.A. while looking at companies working in subsea structural engineering, and your work as a multinational subsea engineering, construction and project management services company for the offshore energy industry, caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -4817,27 +5102,32 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Global services organisation focused on seabed-to-surface subsea services and structural integrity.</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr"/>
-      <c r="D105" s="2" t="inlineStr"/>
-      <c r="E105" s="2" t="inlineStr"/>
+          <t>Specialist subsea services group founded in 2004 with around 1,538 staff, bringing together life-of-field services from exploration to decommissioning for oil, gas and renewables. Focus areas include foundations and moorings, risers, conductors and flowlines, and marine electronics and surveys. Group companies include 2H Offshore, InterMoor, Claxton, MENCK and Seatronics. Head office in Norwich.</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n"/>
+      <c r="E105" s="2" t="n"/>
       <c r="F105" s="2" t="inlineStr">
         <is>
+          <t>+44 1603 227019</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Acteon Group Ltd while looking at companies working in subsea structural engineering, and your work as a global services organisation focused on seabed-to-surface subsea services and structural integrity caught my attention.
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Acteon Group Ltd while looking at companies working in subsea structural engineering, and your work as a specialist subsea services group founded in 2004 with around 1 caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -4858,27 +5148,44 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Structural and hydrodynamic consultancy for the offshore oil &amp; gas sector, established 1986.</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr"/>
-      <c r="D106" s="2" t="inlineStr"/>
-      <c r="E106" s="2" t="inlineStr"/>
+          <t>Developer of OrcaFlex, the market-leading numerical simulation package for dynamic analysis of offshore marine systems including risers, moorings, cable and pipe lay, towed arrays and installation analysis. Based in Ulverston since 1986, serving oil &amp; gas, offshore renewables, oceanographic, seismic, defence and aquaculture. Daltongate, Ulverston, Cumbria.</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>David Heffernan</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>enquiry@orcina.com</t>
+        </is>
+      </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
+          <t>+44 (0)1229 584 742</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Orcina Ltd while looking at companies working in offshore and structural engineering consultancy, and your work as a structural and hydrodynamic consultancy for the offshore oil &amp; gas sector, established 1986 caught my attention.
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi David,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Orcina Ltd while looking at companies working in offshore cable and subsea infrastructure, and your work as a developer of OrcaFlex, the market-leading numerical simulation package for dynamic analysis of offshore marine systems caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -4902,20 +5209,21 @@
           <t>30+ years offshore experience providing long-term operations &amp; maintenance (O&amp;M) packages for offshore wind.</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr"/>
-      <c r="D107" s="2" t="inlineStr"/>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n"/>
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4943,20 +5251,21 @@
           <t>Supports 12+ GW of power generation across UK/European wind farms with maintenance and repair solutions.</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr"/>
-      <c r="D108" s="2" t="inlineStr"/>
-      <c r="E108" s="2" t="inlineStr"/>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4984,20 +5293,21 @@
           <t>Supports all phases of UK offshore wind farms from planning/development through O&amp;M.</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr"/>
-      <c r="D109" s="2" t="inlineStr"/>
-      <c r="E109" s="2" t="inlineStr"/>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n"/>
+      <c r="E109" s="2" t="n"/>
+      <c r="F109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>Burntisland, UK</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5025,20 +5335,21 @@
           <t>Steel fabrication for renewable, oil &amp; gas (and defense-adjacent) sectors; yards at Methil and Arnish.</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr"/>
-      <c r="D110" s="2" t="inlineStr"/>
-      <c r="E110" s="2" t="inlineStr"/>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>Methil / Arnish, UK</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5063,27 +5374,32 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Manufacture, assembly and factory acceptance testing services; assembles turbines and manufactures offshore wind infrastructure products.</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr"/>
-      <c r="D111" s="2" t="inlineStr"/>
-      <c r="E111" s="2" t="inlineStr"/>
+          <t>Service and contracting company founded in 2005 with bases in Inverness (HQ), Aberdeen and Edinburgh, and owner-operator of the Port of Nigg with direct North Sea access. Works across renewables, oil &amp; gas, water treatment and hydro, and nuclear, including offshore wind infrastructure manufacture, assembly and factory acceptance testing. 13 Henderson Road, Inverness.</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n"/>
+      <c r="E111" s="2" t="n"/>
       <c r="F111" s="2" t="inlineStr">
         <is>
+          <t>+44 (0)1463 725460</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
           <t>Inverness, UK</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Global Energy Group while looking at companies working in offshore wind structural engineering, and your work as a manufacture, assembly and factory acceptance testing services caught my attention.
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Global Energy Group while looking at companies working in offshore wind structural engineering, and your work as a service and contracting company founded in 2005 with bases in Inverness caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -5107,20 +5423,21 @@
           <t>Steel fabrication company covering Cardiff, Newport, Bridgend, Swansea and surrounding South Wales.</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr"/>
-      <c r="D112" s="2" t="inlineStr"/>
-      <c r="E112" s="2" t="inlineStr"/>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>Barry, UK</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5148,20 +5465,21 @@
           <t>Steel supplier serving Cardiff, Swansea, Newport and Bristol.</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr"/>
-      <c r="D113" s="2" t="inlineStr"/>
-      <c r="E113" s="2" t="inlineStr"/>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="C113" s="2" t="n"/>
+      <c r="D113" s="2" t="n"/>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>Cardiff, UK</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5189,20 +5507,21 @@
           <t>Steel fabricator providing services in Cardiff, Newport and South Wales.</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr"/>
-      <c r="D114" s="2" t="inlineStr"/>
-      <c r="E114" s="2" t="inlineStr"/>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>Caerphilly, UK</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5230,20 +5549,21 @@
           <t>Fabrication in mild steel, stainless steel and aluminium - design through installation, based in Newport.</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr"/>
-      <c r="D115" s="2" t="inlineStr"/>
-      <c r="E115" s="2" t="inlineStr"/>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n"/>
+      <c r="E115" s="2" t="n"/>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>Newport, UK</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5271,20 +5591,21 @@
           <t>Bespoke steelwork fabricator in Newport, Gwent.</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr"/>
-      <c r="D116" s="2" t="inlineStr"/>
-      <c r="E116" s="2" t="inlineStr"/>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>Newport, UK</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5312,20 +5633,21 @@
           <t>Manufacturer of bespoke stainless steel/sheet metal products and structural steel supply/fabrication for South Wales.</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr"/>
-      <c r="D117" s="2" t="inlineStr"/>
-      <c r="E117" s="2" t="inlineStr"/>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n"/>
+      <c r="E117" s="2" t="n"/>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>South Wales, UK</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5353,20 +5675,21 @@
           <t>Group of ~30 companies covering shipbuilding, ship design, diesel engines, propulsion and hydraulic deck machinery; founded 1917.</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr"/>
-      <c r="D118" s="2" t="inlineStr"/>
-      <c r="E118" s="2" t="inlineStr"/>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>Ulsteinvik, Norway</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5394,20 +5717,21 @@
           <t>Shipbuilder specialising in high-speed naval vessels, mine countermeasure vessels and fast patrol boats (defense-primary).</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr"/>
-      <c r="D119" s="2" t="inlineStr"/>
-      <c r="E119" s="2" t="inlineStr"/>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n"/>
+      <c r="E119" s="2" t="n"/>
+      <c r="F119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>Mandal, Norway</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5432,27 +5756,28 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Design/engineering company for oil &amp; gas, marine and process industries.</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr"/>
-      <c r="D120" s="2" t="inlineStr"/>
-      <c r="E120" s="2" t="inlineStr"/>
-      <c r="F120" s="2" t="inlineStr">
+          <t>Design and engineering company serving the oil and gas, marine and process industries, headquartered in Sandefjord with operations in Stavanger.</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>Sandefjord / Stavanger, Norway</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Grenland Framnæs (formerly Hitec Framnæs) while looking at companies working in offshore and structural engineering consultancy, and your work as a design/engineering company for oil &amp; gas, marine and process industries caught my attention.
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Grenland Framnæs (formerly Hitec Framnæs) while looking at companies working in offshore and structural engineering consultancy, and your work as a design and engineering company serving the oil and gas caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -5476,20 +5801,21 @@
           <t>Naval architecture/marine engineering firm supplying complete design/construction/drawing packages for newbuilds.</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr"/>
-      <c r="D121" s="2" t="inlineStr"/>
-      <c r="E121" s="2" t="inlineStr"/>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n"/>
+      <c r="E121" s="2" t="n"/>
+      <c r="F121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>Florø, Norway</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5517,20 +5843,21 @@
           <t>Shipyard building modern live fish carriers (aquaculture-focused marine fabrication).</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr"/>
-      <c r="D122" s="2" t="inlineStr"/>
-      <c r="E122" s="2" t="inlineStr"/>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n"/>
+      <c r="E122" s="2" t="n"/>
+      <c r="F122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5555,27 +5882,28 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Structural engineering, design, fabrication and construction company (~250 employees, multiple Norwegian facilities).</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr"/>
-      <c r="D123" s="2" t="inlineStr"/>
-      <c r="E123" s="2" t="inlineStr"/>
-      <c r="F123" s="2" t="inlineStr">
+          <t>Group of fabrication and engineering companies supplying engineering and fabrication services to the oil &amp; gas market and general industry, with around 250 employees. Headquarters at Helsfyr in Oslo, with further locations in Fredrikstad and Halden.</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n"/>
+      <c r="E123" s="2" t="n"/>
+      <c r="F123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>Oslo, Norway</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Jotne Group while looking at companies working in marine equipment and propulsion systems, and your work as a structural engineering, design, fabrication and construction company caught my attention.
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Jotne Group while looking at companies working in marine equipment and propulsion systems, and your work as a group of fabrication and engineering companies supplying engineering and fabrication services to the oil &amp; caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -5596,27 +5924,28 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Subsea engineering specialist - structural, piping and finite element analysis (FEA) design and consultancy.</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr"/>
-      <c r="D124" s="2" t="inlineStr"/>
-      <c r="E124" s="2" t="inlineStr"/>
-      <c r="F124" s="2" t="inlineStr">
+          <t>Subsea niche company established in 2007, based just north of Oslo and Gardermoen airport, specialising in subsea products, consultancy, engineering and design with a core focus on structural, piping and finite element analysis. Delivers EPC including 3D modelling and drawings, structural and piping analysis, and FEA of subsea protection structures, plus 24/7 subsea engineering support.</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n"/>
+      <c r="E124" s="2" t="n"/>
+      <c r="F124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>Norway (near Oslo)</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across eSubsea AS while looking at companies working in subsea structural engineering, and your work as a subsea engineering specialist, structural, piping and finite element analysis design and consultancy caught my attention.
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across eSubsea AS while looking at companies working in subsea structural engineering, and your work as a subsea niche company established in 2007 caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -5637,27 +5966,28 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Engineering firm specialising in naval architecture, offshore structural engineering and subsea solutions for maritime/oil &amp; gas.</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr"/>
-      <c r="D125" s="2" t="inlineStr"/>
-      <c r="E125" s="2" t="inlineStr"/>
-      <c r="F125" s="2" t="inlineStr">
+          <t>Independent offshore engineering consultancy supporting operators, developers and engineering contractors on technically demanding marine and subsea projects. Specialises in naval architecture, offshore structural engineering and subsea solutions, covering floating systems (FPSOs, semi-submersibles, TLPs, SPAR platforms, offshore service vessels), jack-up units and wellhead platforms, mooring and anchoring design, offloading systems and installation engineering for SURF and subsea structures.</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="2" t="n"/>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Havport AS while looking at companies working in subsea structural engineering, and your work as an engineering firm specialising in naval architecture caught my attention.
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Havport AS while looking at companies working in subsea structural engineering, and your work as an independent offshore engineering consultancy supporting operators caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -5681,20 +6011,21 @@
           <t>Independent marine engineering company for offshore and shipping industry concept development.</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr"/>
-      <c r="D126" s="2" t="inlineStr"/>
-      <c r="E126" s="2" t="inlineStr"/>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5722,20 +6053,21 @@
           <t>Marine geoscience/geotechnics consultancy for offshore wind, E&amp;P and seabed minerals site surveys.</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr"/>
-      <c r="D127" s="2" t="inlineStr"/>
-      <c r="E127" s="2" t="inlineStr"/>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n"/>
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5763,20 +6095,21 @@
           <t>Independent engineering company providing engineering services to shipyards, ship-owners and offshore yards.</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr"/>
-      <c r="D128" s="2" t="inlineStr"/>
-      <c r="E128" s="2" t="inlineStr"/>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="C128" s="2" t="n"/>
+      <c r="D128" s="2" t="n"/>
+      <c r="E128" s="2" t="n"/>
+      <c r="F128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>Rogaland, Norway</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5801,27 +6134,32 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Offshore substations/topsides EPC provider.</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr"/>
-      <c r="D129" s="2" t="inlineStr"/>
-      <c r="E129" s="2" t="inlineStr"/>
+          <t>Norwegian EPC contractor whose Haugesund yard processes and outfits offshore wind platforms, including HVDC converter platforms for Dogger Bank, the world's largest offshore wind farm, and the DolWin 5 converter platform for TenneT (with Seatrium). Jens Risøensgt. 72, Haugesund.</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" s="2" t="n"/>
       <c r="F129" s="2" t="inlineStr">
         <is>
+          <t>+47 85 27 00 00</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
           <t>Haugesund, Norway</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Aibel while looking at companies working in offshore substation fabrication, and your work as an offshore substations/topsides EPC provider caught my attention.
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Aibel while looking at companies working in offshore wind structural engineering, and your work as a Norwegian EPC contractor whose Haugesund yard processes and outfits offshore wind platforms caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -5842,27 +6180,36 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>International steel construction company (1,000+ employees across BE/NL/UK/PL), member of the Offshore Wind Foundations Alliance.</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr"/>
-      <c r="D130" s="2" t="inlineStr"/>
-      <c r="E130" s="2" t="inlineStr"/>
+          <t>Manufactures foundations and towers for the onshore and offshore sectors and is a member of the Offshore Wind Foundations Alliance. Part of the international Smulders group with 1,000+ employees across Belgium, the Netherlands, the UK and Poland, offering engineering, construction, supply and assembly plus turnkey EPCI of substations and foundations. Leo Bosschartlaan 20, Hoboken.</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n"/>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>info@smulders.com</t>
+        </is>
+      </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
+          <t>+32 3 8300 999</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
           <t>Hoboken, Belgium</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Smulders Projects Belgium while looking at companies working in offshore wind structural engineering, and your work as an international steel construction company, member of the Offshore Wind Foundations Alliance caught my attention.
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Smulders Projects Belgium while looking at companies working in offshore wind structural engineering, and I noticed that Smulders Projects Belgium manufactures foundations and towers for the onshore and offshore sectors and is a member, which caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -5883,27 +6230,32 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Part of a consortium for EPC of offshore substations in Belgian wind farms; design coordination/integration at Hoboken yard.</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr"/>
-      <c r="D131" s="2" t="inlineStr"/>
-      <c r="E131" s="2" t="inlineStr"/>
+          <t>Builds and assembles offshore high-voltage stations (OHVS) for North Sea offshore wind farms at its Hoboken yard, having delivered more than 22 offshore substations. Part of consortia with ENGIE Tractebel, Smulders and DEME Offshore on projects including SeaMade and Hollandse Kust Noord.</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n"/>
+      <c r="E131" s="2" t="n"/>
       <c r="F131" s="2" t="inlineStr">
         <is>
+          <t>+32 3 740 44 50</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
           <t>Hoboken, Belgium</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ENGIE Fabricom (Equans) while looking at companies working in offshore substation fabrication, and your work as a part of a consortium for EPC of offshore substations in Belgian wind farms caught my attention.
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ENGIE Fabricom (Equans) while looking at companies working in offshore wind structural engineering, and I noticed that ENGIE Fabricom (Equans) builds and assembles offshore high-voltage stations for North Sea offshore wind farms at its Hoboken, which caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -5927,20 +6279,21 @@
           <t>Belgian marine construction/dredging company active in offshore renewable energy since 2012.</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr"/>
-      <c r="D132" s="2" t="inlineStr"/>
-      <c r="E132" s="2" t="inlineStr"/>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n"/>
+      <c r="E132" s="2" t="n"/>
+      <c r="F132" s="2" t="inlineStr"/>
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>Hofstade-Aalst, Belgium</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5968,20 +6321,21 @@
           <t>Major dredging/marine engineering group, involved in offshore installation across Europe.</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr"/>
-      <c r="D133" s="2" t="inlineStr"/>
-      <c r="E133" s="2" t="inlineStr"/>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" s="2" t="n"/>
+      <c r="F133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>Zwijndrecht, Belgium</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6009,20 +6363,21 @@
           <t>Develops steel solutions for wind turbines (up to 285 tons of steel per turbine); primarily a raw-material producer.</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr"/>
-      <c r="D134" s="2" t="inlineStr"/>
-      <c r="E134" s="2" t="inlineStr"/>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" s="2" t="n"/>
+      <c r="F134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>Ghent, Belgium</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6050,20 +6405,21 @@
           <t>Large historic shipyard in northern Poland.</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr"/>
-      <c r="D135" s="2" t="inlineStr"/>
-      <c r="E135" s="2" t="inlineStr"/>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n"/>
+      <c r="E135" s="2" t="n"/>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>Gdańsk, Poland</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6088,27 +6444,36 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Shipyard (Port of Gdynia, founded 1990) producing offshore-industry ships including wind turbine installation vessels.</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr"/>
-      <c r="D136" s="2" t="inlineStr"/>
-      <c r="E136" s="2" t="inlineStr"/>
+          <t>One of the leaders in the offshore sector, founded 1990, covering shipbuilding, offshore constructions, steel structures and marine, land and civil engineering, and known for building wind turbine installation vessels. Ul. Kadłubowców 11, Gdynia. Offshore division (CRIST Offshore) can also be reached at office@cristoffshore.com.pl.</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n"/>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>biurogdynia@crist.com.pl</t>
+        </is>
+      </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
+          <t>+48 58 778 68 90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
           <t>Gdynia, Poland</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across CRIST S.A. while looking at companies working in offshore wind structural engineering, and your work as a shipyard producing offshore-industry ships including wind turbine installation vessels caught my attention.
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across CRIST S.A. while looking at companies working in offshore wind structural engineering, and your position as one of the leaders in the offshore sector caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -6132,20 +6497,21 @@
           <t>Shipyard specialising in container ships, chemical tankers, multi-purpose vessels and ConRo ships.</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr"/>
-      <c r="D137" s="2" t="inlineStr"/>
-      <c r="E137" s="2" t="inlineStr"/>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n"/>
+      <c r="E137" s="2" t="n"/>
+      <c r="F137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>Szczecin, Poland</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6173,20 +6539,21 @@
           <t>Established 1989; complete ship construction plus technical/engineering documentation for the shipbuilding industry.</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr"/>
-      <c r="D138" s="2" t="inlineStr"/>
-      <c r="E138" s="2" t="inlineStr"/>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n"/>
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6214,20 +6581,21 @@
           <t>Competence centre (est. 2013) for engineering-to-order, one-offs and prototype vessels.</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr"/>
-      <c r="D139" s="2" t="inlineStr"/>
-      <c r="E139" s="2" t="inlineStr"/>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n"/>
+      <c r="E139" s="2" t="n"/>
+      <c r="F139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>Gdańsk, Poland</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6255,20 +6623,21 @@
           <t>Construction of new floating units, ship modernization and repair of offshore/land structures.</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr"/>
-      <c r="D140" s="2" t="inlineStr"/>
-      <c r="E140" s="2" t="inlineStr"/>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" s="2" t="n"/>
+      <c r="F140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6296,20 +6665,21 @@
           <t>One of the largest shipbuilding-sector companies in Poland.</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr"/>
-      <c r="D141" s="2" t="inlineStr"/>
-      <c r="E141" s="2" t="inlineStr"/>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" s="2" t="n"/>
+      <c r="F141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>Gdańsk, Poland</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6337,20 +6707,21 @@
           <t>Shipbuilding operation developing in Pomerania as part of the Vard group.</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr"/>
-      <c r="D142" s="2" t="inlineStr"/>
-      <c r="E142" s="2" t="inlineStr"/>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" s="2" t="n"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6378,20 +6749,21 @@
           <t>Polish subsidiary of Kongsberg Maritime equipment/systems supplier.</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr"/>
-      <c r="D143" s="2" t="inlineStr"/>
-      <c r="E143" s="2" t="inlineStr"/>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" s="2" t="n"/>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6419,20 +6791,21 @@
           <t>Precision fabrication and emergency repairs, custom metal structures/components for marine vessels.</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr"/>
-      <c r="D144" s="2" t="inlineStr"/>
-      <c r="E144" s="2" t="inlineStr"/>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n"/>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>Cork, Ireland</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6457,27 +6830,28 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Multi-disciplinary engineering services, project management, procurement and fabrication for marine/offshore clients.</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr"/>
-      <c r="D145" s="2" t="inlineStr"/>
-      <c r="E145" s="2" t="inlineStr"/>
-      <c r="F145" s="2" t="inlineStr">
-        <is>
-          <t>Ireland</t>
-        </is>
-      </c>
+          <t>Integrated maritime and industrial solutions provider covering dry bulk shipping, industrial logistics, chemical transportation, shipyard services, marine and offshore engineering and consumer logistics. NOTE: the group is headquartered in Singapore, not Ireland as originally recorded.</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n"/>
+      <c r="E145" s="2" t="n"/>
+      <c r="F145" s="2" t="inlineStr"/>
       <c r="G145" s="2" t="inlineStr">
         <is>
+          <t>Singapore (not Ireland)</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across IMC Marine and Offshore Engineering (IMC Industrial Group) while looking at companies working in offshore and structural engineering consultancy, and your work as a multi-disciplinary engineering services, project management, procurement and fabrication for marine/offshore clients caught my attention.
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across IMC Marine and Offshore Engineering (IMC Industrial Group) while looking at companies working in shipbuilding and marine fabrication, and your work as an integrated maritime and industrial solutions provider covering dry bulk shipping caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -6501,20 +6875,21 @@
           <t>Nearshore fibre-optic/power cable installation, marine civil engineering and diving services.</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr"/>
-      <c r="D146" s="2" t="inlineStr"/>
-      <c r="E146" s="2" t="inlineStr"/>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="C146" s="2" t="n"/>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" s="2" t="n"/>
+      <c r="F146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6542,20 +6917,21 @@
           <t>Design and manufacture services including high-precision fabrication and prototype development.</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr"/>
-      <c r="D147" s="2" t="inlineStr"/>
-      <c r="E147" s="2" t="inlineStr"/>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="C147" s="2" t="n"/>
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" s="2" t="n"/>
+      <c r="F147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6583,20 +6959,21 @@
           <t>Marine and river engineering consultancy active since 1993.</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr"/>
-      <c r="D148" s="2" t="inlineStr"/>
-      <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n"/>
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6624,20 +7001,21 @@
           <t>Swedish shipbuilder of fast craft/patrol boats.</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr"/>
-      <c r="D149" s="2" t="inlineStr"/>
-      <c r="E149" s="2" t="inlineStr"/>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" s="2" t="n"/>
+      <c r="F149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6665,20 +7043,21 @@
           <t>Ship design house.</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr"/>
-      <c r="D150" s="2" t="inlineStr"/>
-      <c r="E150" s="2" t="inlineStr"/>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6706,20 +7085,21 @@
           <t>Naval shipbuilder (submarines/surface combatants) - defense-primary.</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr"/>
-      <c r="D151" s="2" t="inlineStr"/>
-      <c r="E151" s="2" t="inlineStr"/>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n"/>
+      <c r="E151" s="2" t="n"/>
+      <c r="F151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>Malmö, Sweden</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6747,20 +7127,21 @@
           <t>Ship design and shipowning group.</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr"/>
-      <c r="D152" s="2" t="inlineStr"/>
-      <c r="E152" s="2" t="inlineStr"/>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n"/>
+      <c r="E152" s="2" t="n"/>
+      <c r="F152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>Stockholm, Sweden</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6788,20 +7169,21 @@
           <t>Specialized shipyard group (Djupvik, Swede Ship Composite, Swede Ship Yachtservice) on Sweden's west coast; building ships since the 1890s.</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr"/>
-      <c r="D153" s="2" t="inlineStr"/>
-      <c r="E153" s="2" t="inlineStr"/>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n"/>
+      <c r="E153" s="2" t="n"/>
+      <c r="F153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6829,20 +7211,21 @@
           <t>Constructs customized steel/aluminium port vessels; prefabricates ship parts.</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr"/>
-      <c r="D154" s="2" t="inlineStr"/>
-      <c r="E154" s="2" t="inlineStr"/>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n"/>
+      <c r="E154" s="2" t="n"/>
+      <c r="F154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6870,20 +7253,21 @@
           <t>Leisure boat manufacturer.</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr"/>
-      <c r="D155" s="2" t="inlineStr"/>
-      <c r="E155" s="2" t="inlineStr"/>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" s="2" t="n"/>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6911,20 +7295,21 @@
           <t>Marine tank-cleaning equipment manufacturer, Gothenburg.</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr"/>
-      <c r="D156" s="2" t="inlineStr"/>
-      <c r="E156" s="2" t="inlineStr"/>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="C156" s="2" t="n"/>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" s="2" t="n"/>
+      <c r="F156" s="2" t="inlineStr"/>
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>Gothenburg, Sweden</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6952,20 +7337,21 @@
           <t>Primary Swedish supplier of high-strength steel plate/coil for marine hulls and offshore platforms; raw-material producer.</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr"/>
-      <c r="D157" s="2" t="inlineStr"/>
-      <c r="E157" s="2" t="inlineStr"/>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="C157" s="2" t="n"/>
+      <c r="D157" s="2" t="n"/>
+      <c r="E157" s="2" t="n"/>
+      <c r="F157" s="2" t="inlineStr"/>
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6993,20 +7379,21 @@
           <t>Shipbuilder specialising in cruise ships and cruiseferries.</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr"/>
-      <c r="D158" s="2" t="inlineStr"/>
-      <c r="E158" s="2" t="inlineStr"/>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n"/>
+      <c r="E158" s="2" t="n"/>
+      <c r="F158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>Turku, Finland</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7034,20 +7421,21 @@
           <t>Major marine engine, propulsion systems and lifecycle solutions provider.</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr"/>
-      <c r="D159" s="2" t="inlineStr"/>
-      <c r="E159" s="2" t="inlineStr"/>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="C159" s="2" t="n"/>
+      <c r="D159" s="2" t="n"/>
+      <c r="E159" s="2" t="n"/>
+      <c r="F159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>Helsinki, Finland</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7072,27 +7460,36 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Arctic/ice-class ship and structure engineering specialist.</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr"/>
-      <c r="D160" s="2" t="inlineStr"/>
-      <c r="E160" s="2" t="inlineStr"/>
+          <t>Independent company specialising in development, design, engineering, consulting and testing for ice-going vessels, icebreakers, offshore marine structures, marine transport solutions and ports. Operates the world's only privately owned ice model testing facility, in Helsinki. Founded 2004, offices in Finland, Canada and Russia.</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="n"/>
+      <c r="D160" s="2" t="n"/>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>info@akerarctic.fi</t>
+        </is>
+      </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
+          <t>+358 10 323 6300</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
           <t>Helsinki, Finland</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Aker Arctic Technology while looking at companies working in marine equipment and propulsion systems, and your work as an arctic/ice-class ship and structure engineering specialist caught my attention.
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Aker Arctic Technology while looking at companies working in marine equipment and propulsion systems, and your work as an independent company specialising in development caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -7116,20 +7513,21 @@
           <t>Designer/manufacturer of aluminium and composite boats (5-27m) for navies, coast guards, government agencies and ports.</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr"/>
-      <c r="D161" s="2" t="inlineStr"/>
-      <c r="E161" s="2" t="inlineStr"/>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n"/>
+      <c r="E161" s="2" t="n"/>
+      <c r="F161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7157,20 +7555,21 @@
           <t>Marine electrical systems and ports equipment supplier.</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr"/>
-      <c r="D162" s="2" t="inlineStr"/>
-      <c r="E162" s="2" t="inlineStr"/>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n"/>
+      <c r="E162" s="2" t="n"/>
+      <c r="F162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7198,20 +7597,21 @@
           <t>Finnish subsidiary of Kongsberg Maritime equipment/systems supplier.</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr"/>
-      <c r="D163" s="2" t="inlineStr"/>
-      <c r="E163" s="2" t="inlineStr"/>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n"/>
+      <c r="E163" s="2" t="n"/>
+      <c r="F163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7239,20 +7639,21 @@
           <t>Major ship repair yard.</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr"/>
-      <c r="D164" s="2" t="inlineStr"/>
-      <c r="E164" s="2" t="inlineStr"/>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="C164" s="2" t="n"/>
+      <c r="D164" s="2" t="n"/>
+      <c r="E164" s="2" t="n"/>
+      <c r="F164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>Setúbal, Portugal</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7280,20 +7681,21 @@
           <t>State naval shipyard - defense-primary.</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr"/>
-      <c r="D165" s="2" t="inlineStr"/>
-      <c r="E165" s="2" t="inlineStr"/>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n"/>
+      <c r="E165" s="2" t="n"/>
+      <c r="F165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>Almada, Portugal</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7321,20 +7723,21 @@
           <t>Shipbuilding/repair yard on Portugal's Atlantic coast.</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr"/>
-      <c r="D166" s="2" t="inlineStr"/>
-      <c r="E166" s="2" t="inlineStr"/>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="C166" s="2" t="n"/>
+      <c r="D166" s="2" t="n"/>
+      <c r="E166" s="2" t="n"/>
+      <c r="F166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>Viana do Castelo, Portugal</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7362,20 +7765,21 @@
           <t>Public shipbuilding/repair company (since 1944), Atlantic coast; has faced financial difficulty.</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr"/>
-      <c r="D167" s="2" t="inlineStr"/>
-      <c r="E167" s="2" t="inlineStr"/>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="C167" s="2" t="n"/>
+      <c r="D167" s="2" t="n"/>
+      <c r="E167" s="2" t="n"/>
+      <c r="F167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>Viana do Castelo, Portugal</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7403,20 +7807,21 @@
           <t>Vessel repair/maintenance yard in Lisbon.</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr"/>
-      <c r="D168" s="2" t="inlineStr"/>
-      <c r="E168" s="2" t="inlineStr"/>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="C168" s="2" t="n"/>
+      <c r="D168" s="2" t="n"/>
+      <c r="E168" s="2" t="n"/>
+      <c r="F168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>Lisbon, Portugal</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7444,20 +7849,21 @@
           <t>Repair, maintenance and shipbuilding company (founded 2017), onshore and offshore.</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr"/>
-      <c r="D169" s="2" t="inlineStr"/>
-      <c r="E169" s="2" t="inlineStr"/>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="n"/>
+      <c r="D169" s="2" t="n"/>
+      <c r="E169" s="2" t="n"/>
+      <c r="F169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7485,20 +7891,21 @@
           <t>Produces zinc/aluminium sacrificial anodes and machined parts for shipbuilding, repair and maintenance.</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr"/>
-      <c r="D170" s="2" t="inlineStr"/>
-      <c r="E170" s="2" t="inlineStr"/>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n"/>
+      <c r="E170" s="2" t="n"/>
+      <c r="F170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7526,20 +7933,21 @@
           <t>Metalworking company established 1997.</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr"/>
-      <c r="D171" s="2" t="inlineStr"/>
-      <c r="E171" s="2" t="inlineStr"/>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="n"/>
+      <c r="D171" s="2" t="n"/>
+      <c r="E171" s="2" t="n"/>
+      <c r="F171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>Águeda, Portugal</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7567,20 +7975,21 @@
           <t>Precision metalworking company.</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr"/>
-      <c r="D172" s="2" t="inlineStr"/>
-      <c r="E172" s="2" t="inlineStr"/>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="C172" s="2" t="n"/>
+      <c r="D172" s="2" t="n"/>
+      <c r="E172" s="2" t="n"/>
+      <c r="F172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>Santo Tirso, Portugal</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7608,20 +8017,21 @@
           <t>One of the oldest Greek heavy industries (founded 1861), historic shipyard on Syros.</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr"/>
-      <c r="D173" s="2" t="inlineStr"/>
-      <c r="E173" s="2" t="inlineStr"/>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="n"/>
+      <c r="D173" s="2" t="n"/>
+      <c r="E173" s="2" t="n"/>
+      <c r="F173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>Ermoupolis, Greece</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7649,20 +8059,21 @@
           <t>Large shipyard (founded 1937), historically linked to Greek Navy work (mixed).</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr"/>
-      <c r="D174" s="2" t="inlineStr"/>
-      <c r="E174" s="2" t="inlineStr"/>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n"/>
+      <c r="E174" s="2" t="n"/>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>Skaramagas, Greece</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7690,20 +8101,21 @@
           <t>Greek shipbuilding company founded 1968.</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr"/>
-      <c r="D175" s="2" t="inlineStr"/>
-      <c r="E175" s="2" t="inlineStr"/>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="C175" s="2" t="n"/>
+      <c r="D175" s="2" t="n"/>
+      <c r="E175" s="2" t="n"/>
+      <c r="F175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>Athens, Greece</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7731,20 +8143,21 @@
           <t>Large shipyard founded 1971.</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr"/>
-      <c r="D176" s="2" t="inlineStr"/>
-      <c r="E176" s="2" t="inlineStr"/>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="C176" s="2" t="n"/>
+      <c r="D176" s="2" t="n"/>
+      <c r="E176" s="2" t="n"/>
+      <c r="F176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>Aulis, Evia, Greece</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7772,20 +8185,21 @@
           <t>Greek shipbuilder founded 1962.</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr"/>
-      <c r="D177" s="2" t="inlineStr"/>
-      <c r="E177" s="2" t="inlineStr"/>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="C177" s="2" t="n"/>
+      <c r="D177" s="2" t="n"/>
+      <c r="E177" s="2" t="n"/>
+      <c r="F177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>Koropi, Greece</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7813,20 +8227,21 @@
           <t>Founded 1968; supply, installation and service of shipboard equipment for all vessel types.</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr"/>
-      <c r="D178" s="2" t="inlineStr"/>
-      <c r="E178" s="2" t="inlineStr"/>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="C178" s="2" t="n"/>
+      <c r="D178" s="2" t="n"/>
+      <c r="E178" s="2" t="n"/>
+      <c r="F178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7851,27 +8266,36 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Leading marine construction contractor across the Mediterranean, North Africa and Red Sea.</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr"/>
-      <c r="D179" s="2" t="inlineStr"/>
-      <c r="E179" s="2" t="inlineStr"/>
+          <t>Leading marine construction contractor across the Mediterranean, North Africa and the Red Sea, with over 50 years of experience and more than 400 completed projects covering marine and offshore works and harbour construction. Offices in Salamina, Perama, Kavala, Chania and Thessaloniki.</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n"/>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>info@spanopoulos-group.com</t>
+        </is>
+      </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
+          <t>+30 210 4095 000</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Spanopoulos Group while looking at companies working in marine construction and offshore engineering, and your work as a leading marine construction contractor across the Mediterranean, North Africa and Red Sea caught my attention.
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Spanopoulos Group while looking at companies working in marine construction and offshore engineering, and your work as a leading marine construction contractor across the Mediterranean caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -7892,27 +8316,36 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Naval architecture and marine engineering services provider.</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr"/>
-      <c r="D180" s="2" t="inlineStr"/>
-      <c r="E180" s="2" t="inlineStr"/>
-      <c r="F180" s="2" t="inlineStr">
+          <t>Naval architecture and marine engineering services firm based in Piraeus with over 12 years of operation, advising on ship construction and modification and on improving vessel energy efficiency index and carbon intensity. Co-founded by Dimitris Panagos (30 years as Head of New Building at Greek Flag Authorities) and Theoharis K. Stavrou (NTUA, 20 years in ship construction and modification).</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Dimitris Panagos</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder, Naval Architect and Marine Engineer</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n"/>
+      <c r="F180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Group Navale while looking at companies working in naval architecture and marine engineering, and your work as a naval architecture and marine engineering services provider caught my attention.
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Dimitris,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Group Navale while looking at companies working in naval architecture and marine engineering, and your work as a naval architecture and marine engineering services firm based in Piraeus with over 12 years caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -7936,20 +8369,21 @@
           <t>Largest shipyard in Croatia (Rijeka); builds oil tankers, bulk carriers, container ships.</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr"/>
-      <c r="D181" s="2" t="inlineStr"/>
-      <c r="E181" s="2" t="inlineStr"/>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n"/>
+      <c r="E181" s="2" t="n"/>
+      <c r="F181" s="2" t="inlineStr"/>
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>Rijeka, Croatia</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7977,20 +8411,21 @@
           <t>Largest shipyard in Croatia by some measures, located on the Split peninsula.</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr"/>
-      <c r="D182" s="2" t="inlineStr"/>
-      <c r="E182" s="2" t="inlineStr"/>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="C182" s="2" t="n"/>
+      <c r="D182" s="2" t="n"/>
+      <c r="E182" s="2" t="n"/>
+      <c r="F182" s="2" t="inlineStr"/>
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>Split, Croatia</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8018,20 +8453,21 @@
           <t>Shipyard founded 1896 on the northern Adriatic coast.</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr"/>
-      <c r="D183" s="2" t="inlineStr"/>
-      <c r="E183" s="2" t="inlineStr"/>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="C183" s="2" t="n"/>
+      <c r="D183" s="2" t="n"/>
+      <c r="E183" s="2" t="n"/>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>Rijeka, Croatia</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8059,20 +8495,21 @@
           <t>Shipbuilder on Croatia's Adriatic coast.</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr"/>
-      <c r="D184" s="2" t="inlineStr"/>
-      <c r="E184" s="2" t="inlineStr"/>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="C184" s="2" t="n"/>
+      <c r="D184" s="2" t="n"/>
+      <c r="E184" s="2" t="n"/>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>Kraljevica, Croatia</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8100,20 +8537,21 @@
           <t>Subsidiary of Royal IHC.</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr"/>
-      <c r="D185" s="2" t="inlineStr"/>
-      <c r="E185" s="2" t="inlineStr"/>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="C185" s="2" t="n"/>
+      <c r="D185" s="2" t="n"/>
+      <c r="E185" s="2" t="n"/>
+      <c r="F185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8141,20 +8579,21 @@
           <t>Shipbuilder (est. 1995) known for patrol boats and specialised maritime vessels (defense-leaning).</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr"/>
-      <c r="D186" s="2" t="inlineStr"/>
-      <c r="E186" s="2" t="inlineStr"/>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="C186" s="2" t="n"/>
+      <c r="D186" s="2" t="n"/>
+      <c r="E186" s="2" t="n"/>
+      <c r="F186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8179,27 +8618,36 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Marine engineering and research institute (established 1948).</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr"/>
-      <c r="D187" s="2" t="inlineStr"/>
-      <c r="E187" s="2" t="inlineStr"/>
+          <t>Croatian institute for maritime and green technologies, established 1948, providing marine engineering, shipbuilding and consultancy services across a wide range of maritime engineering and environmental issues. Ave. V. Holjevca 20, Zagreb.</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="n"/>
+      <c r="D187" s="2" t="n"/>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>nina.subasic@hrbi.hr</t>
+        </is>
+      </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
+          <t>+385 1 6504 269</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Brodarski Institut while looking at companies working in marine equipment and propulsion systems, and your work as a marine engineering and research institute caught my attention.
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Brodarski Institut while looking at companies working in shipbuilding and marine fabrication, and your work as a Croatian institute for maritime and green technologies caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -8223,20 +8671,21 @@
           <t>Major shipyard, part of the Damen Group.</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr"/>
-      <c r="D188" s="2" t="inlineStr"/>
-      <c r="E188" s="2" t="inlineStr"/>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="C188" s="2" t="n"/>
+      <c r="D188" s="2" t="n"/>
+      <c r="E188" s="2" t="n"/>
+      <c r="F188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>Galați, Romania</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8264,20 +8713,21 @@
           <t>Shipyard part of the Vard group.</t>
         </is>
       </c>
-      <c r="C189" s="2" t="inlineStr"/>
-      <c r="D189" s="2" t="inlineStr"/>
-      <c r="E189" s="2" t="inlineStr"/>
-      <c r="F189" s="2" t="inlineStr">
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="2" t="n"/>
+      <c r="E189" s="2" t="n"/>
+      <c r="F189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
         <is>
           <t>Brăila, Romania</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8305,20 +8755,21 @@
           <t>Shipyard on the Black Sea coast.</t>
         </is>
       </c>
-      <c r="C190" s="2" t="inlineStr"/>
-      <c r="D190" s="2" t="inlineStr"/>
-      <c r="E190" s="2" t="inlineStr"/>
-      <c r="F190" s="2" t="inlineStr">
+      <c r="C190" s="2" t="n"/>
+      <c r="D190" s="2" t="n"/>
+      <c r="E190" s="2" t="n"/>
+      <c r="F190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
         <is>
           <t>Constanța, Romania</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8346,20 +8797,21 @@
           <t>Shipyard, top-revenue Romanian shipbuilder in 2019.</t>
         </is>
       </c>
-      <c r="C191" s="2" t="inlineStr"/>
-      <c r="D191" s="2" t="inlineStr"/>
-      <c r="E191" s="2" t="inlineStr"/>
-      <c r="F191" s="2" t="inlineStr">
+      <c r="C191" s="2" t="n"/>
+      <c r="D191" s="2" t="n"/>
+      <c r="E191" s="2" t="n"/>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
         <is>
           <t>Tulcea, Romania</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8387,20 +8839,21 @@
           <t>Ship repair yard, part of the Damen Group.</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr"/>
-      <c r="D192" s="2" t="inlineStr"/>
-      <c r="E192" s="2" t="inlineStr"/>
-      <c r="F192" s="2" t="inlineStr">
+      <c r="C192" s="2" t="n"/>
+      <c r="D192" s="2" t="n"/>
+      <c r="E192" s="2" t="n"/>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>Mangalia, Romania</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8425,27 +8878,32 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Damen Schelde Naval Shipbuilding engineering company (100+ employees) providing detailed engineering for hulls, piping and outfitting.</t>
-        </is>
-      </c>
-      <c r="C193" s="2" t="inlineStr"/>
-      <c r="D193" s="2" t="inlineStr"/>
-      <c r="E193" s="2" t="inlineStr"/>
+          <t>Engineering company set up by Damen Schelde Naval Shipbuilding, employing more than 100 people and specialising in shipbuilding, mainly providing detailed engineering packages for hulls, piping and outfitting. 132 Moruzzi, Galati.</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="n"/>
+      <c r="D193" s="2" t="n"/>
+      <c r="E193" s="2" t="n"/>
       <c r="F193" s="2" t="inlineStr">
         <is>
+          <t>+40 (0)236 44 85 15</t>
+        </is>
+      </c>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
           <t>Galați, Romania</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Marine Engineering Galati (MEGA) while looking at companies working in shipbuilding and marine fabrication, and your work as a damen Schelde Naval Shipbuilding engineering company providing detailed engineering for hulls, piping and outfitting caught my attention.
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Marine Engineering Galati (MEGA) while looking at companies working in shipbuilding and marine fabrication, and your work as an engineering company set up by Damen Schelde Naval Shipbuilding caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -8469,20 +8927,21 @@
           <t>20+ years in marine newbuilds across Europe and vessel dry-docking services around Constanța.</t>
         </is>
       </c>
-      <c r="C194" s="2" t="inlineStr"/>
-      <c r="D194" s="2" t="inlineStr"/>
-      <c r="E194" s="2" t="inlineStr"/>
-      <c r="F194" s="2" t="inlineStr">
+      <c r="C194" s="2" t="n"/>
+      <c r="D194" s="2" t="n"/>
+      <c r="E194" s="2" t="n"/>
+      <c r="F194" s="2" t="inlineStr"/>
+      <c r="G194" s="2" t="inlineStr">
         <is>
           <t>Constanța, Romania</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8510,20 +8969,21 @@
           <t>Shipbuilding group (50+ companies) headquartered in Tallinn, active across the Baltic/Nordic region.</t>
         </is>
       </c>
-      <c r="C195" s="2" t="inlineStr"/>
-      <c r="D195" s="2" t="inlineStr"/>
-      <c r="E195" s="2" t="inlineStr"/>
-      <c r="F195" s="2" t="inlineStr">
+      <c r="C195" s="2" t="n"/>
+      <c r="D195" s="2" t="n"/>
+      <c r="E195" s="2" t="n"/>
+      <c r="F195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
         <is>
           <t>Tallinn, Estonia</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8551,20 +9011,21 @@
           <t>Shipbuilder specialising in aluminium/steel workboats - patrol vessels, pilot boats, ferries.</t>
         </is>
       </c>
-      <c r="C196" s="2" t="inlineStr"/>
-      <c r="D196" s="2" t="inlineStr"/>
-      <c r="E196" s="2" t="inlineStr"/>
-      <c r="F196" s="2" t="inlineStr">
+      <c r="C196" s="2" t="n"/>
+      <c r="D196" s="2" t="n"/>
+      <c r="E196" s="2" t="n"/>
+      <c r="F196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr">
         <is>
           <t>Estonia</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8592,20 +9053,21 @@
           <t>One of the largest shipyards in the Baltic region.</t>
         </is>
       </c>
-      <c r="C197" s="2" t="inlineStr"/>
-      <c r="D197" s="2" t="inlineStr"/>
-      <c r="E197" s="2" t="inlineStr"/>
-      <c r="F197" s="2" t="inlineStr">
+      <c r="C197" s="2" t="n"/>
+      <c r="D197" s="2" t="n"/>
+      <c r="E197" s="2" t="n"/>
+      <c r="F197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr">
         <is>
           <t>Riga, Latvia</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="I197" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8633,20 +9095,21 @@
           <t>Shipyard in Klaipėda, part of the BLRT Grupp.</t>
         </is>
       </c>
-      <c r="C198" s="2" t="inlineStr"/>
-      <c r="D198" s="2" t="inlineStr"/>
-      <c r="E198" s="2" t="inlineStr"/>
-      <c r="F198" s="2" t="inlineStr">
+      <c r="C198" s="2" t="n"/>
+      <c r="D198" s="2" t="n"/>
+      <c r="E198" s="2" t="n"/>
+      <c r="F198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr">
         <is>
           <t>Klaipėda, Lithuania</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8674,20 +9137,21 @@
           <t>Shipbuilding/offshore construction services operating across Estonia, Latvia, Lithuania, Netherlands, Germany and Finland.</t>
         </is>
       </c>
-      <c r="C199" s="2" t="inlineStr"/>
-      <c r="D199" s="2" t="inlineStr"/>
-      <c r="E199" s="2" t="inlineStr"/>
-      <c r="F199" s="2" t="inlineStr">
+      <c r="C199" s="2" t="n"/>
+      <c r="D199" s="2" t="n"/>
+      <c r="E199" s="2" t="n"/>
+      <c r="F199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr">
         <is>
           <t>Baltic region</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8715,20 +9179,21 @@
           <t>Shipbuilding and ship repair company.</t>
         </is>
       </c>
-      <c r="C200" s="2" t="inlineStr"/>
-      <c r="D200" s="2" t="inlineStr"/>
-      <c r="E200" s="2" t="inlineStr"/>
-      <c r="F200" s="2" t="inlineStr">
+      <c r="C200" s="2" t="n"/>
+      <c r="D200" s="2" t="n"/>
+      <c r="E200" s="2" t="n"/>
+      <c r="F200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr">
         <is>
           <t>Burgas, Bulgaria</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8756,20 +9221,21 @@
           <t>Specialises in construction of new river and sea-going vessels.</t>
         </is>
       </c>
-      <c r="C201" s="2" t="inlineStr"/>
-      <c r="D201" s="2" t="inlineStr"/>
-      <c r="E201" s="2" t="inlineStr"/>
-      <c r="F201" s="2" t="inlineStr">
+      <c r="C201" s="2" t="n"/>
+      <c r="D201" s="2" t="n"/>
+      <c r="E201" s="2" t="n"/>
+      <c r="F201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr">
         <is>
           <t>Ruse, Bulgaria</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8797,20 +9263,21 @@
           <t>Shipbuilding and ship repair services provider.</t>
         </is>
       </c>
-      <c r="C202" s="2" t="inlineStr"/>
-      <c r="D202" s="2" t="inlineStr"/>
-      <c r="E202" s="2" t="inlineStr"/>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="C202" s="2" t="n"/>
+      <c r="D202" s="2" t="n"/>
+      <c r="E202" s="2" t="n"/>
+      <c r="F202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr">
         <is>
           <t>Sofia, Bulgaria</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8838,20 +9305,21 @@
           <t>Operates a workshop at Odessos Shipyard.</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr"/>
-      <c r="D203" s="2" t="inlineStr"/>
-      <c r="E203" s="2" t="inlineStr"/>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="C203" s="2" t="n"/>
+      <c r="D203" s="2" t="n"/>
+      <c r="E203" s="2" t="n"/>
+      <c r="F203" s="2" t="inlineStr"/>
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>Varna, Bulgaria</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8879,20 +9347,21 @@
           <t>Marine/shipbuilding services company.</t>
         </is>
       </c>
-      <c r="C204" s="2" t="inlineStr"/>
-      <c r="D204" s="2" t="inlineStr"/>
-      <c r="E204" s="2" t="inlineStr"/>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="C204" s="2" t="n"/>
+      <c r="D204" s="2" t="n"/>
+      <c r="E204" s="2" t="n"/>
+      <c r="F204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr">
         <is>
           <t>Cyprus</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8920,20 +9389,21 @@
           <t>Shipbuilding/repair yard.</t>
         </is>
       </c>
-      <c r="C205" s="2" t="inlineStr"/>
-      <c r="D205" s="2" t="inlineStr"/>
-      <c r="E205" s="2" t="inlineStr"/>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="C205" s="2" t="n"/>
+      <c r="D205" s="2" t="n"/>
+      <c r="E205" s="2" t="n"/>
+      <c r="F205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr">
         <is>
           <t>Famagusta, Cyprus</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="I205" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8961,20 +9431,21 @@
           <t>Designs/manufactures high-voltage inter-array and export cables for offshore wind.</t>
         </is>
       </c>
-      <c r="C206" s="2" t="inlineStr"/>
-      <c r="D206" s="2" t="inlineStr"/>
-      <c r="E206" s="2" t="inlineStr"/>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="C206" s="2" t="n"/>
+      <c r="D206" s="2" t="n"/>
+      <c r="E206" s="2" t="n"/>
+      <c r="F206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr">
         <is>
           <t>Courbevoie, France</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="I206" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9002,20 +9473,21 @@
           <t>Provides export and inter-array cable packages for offshore wind farms.</t>
         </is>
       </c>
-      <c r="C207" s="2" t="inlineStr"/>
-      <c r="D207" s="2" t="inlineStr"/>
-      <c r="E207" s="2" t="inlineStr"/>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="C207" s="2" t="n"/>
+      <c r="D207" s="2" t="n"/>
+      <c r="E207" s="2" t="n"/>
+      <c r="F207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="I207" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9040,27 +9512,28 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>One of the largest marine engineering/fabrication facilities in the UAE - 280,000 m2 yard, 545m unrestricted waterfront.</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr"/>
-      <c r="D208" s="2" t="inlineStr"/>
-      <c r="E208" s="2" t="inlineStr"/>
-      <c r="F208" s="2" t="inlineStr">
+          <t>Established 2009 to support the marine and oil &amp; gas industries in the UAE, operating one of the largest marine engineering and fabrication facilities in the country with a 280,000 m2 yard and 545 m unrestricted waterfront. Plot 354-MR2, Industrial City of Abu Dhabi ICAD II, Mussafah.</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="n"/>
+      <c r="D208" s="2" t="n"/>
+      <c r="E208" s="2" t="n"/>
+      <c r="F208" s="2" t="inlineStr"/>
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>Mussafah, Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ali &amp; Sons Marine Engineering Factory (ASMEF) / Emarat Aloula Industries while looking at companies working in marine equipment and propulsion systems, and your position as one of the largest marine engineering/fabrication facilities in the UAE caught my attention.
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ali &amp; Sons Marine Engineering Factory (ASMEF) / Emarat Aloula Industries while looking at companies working in marine equipment and propulsion systems, and your work as an established 2009 to support the marine and oil &amp; gas industries in the UAE caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -9084,20 +9557,21 @@
           <t>Established 1996; construction, repair and refit of naval and commercial vessels (mixed defense/commercial).</t>
         </is>
       </c>
-      <c r="C209" s="2" t="inlineStr"/>
-      <c r="D209" s="2" t="inlineStr"/>
-      <c r="E209" s="2" t="inlineStr"/>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="C209" s="2" t="n"/>
+      <c r="D209" s="2" t="n"/>
+      <c r="E209" s="2" t="n"/>
+      <c r="F209" s="2" t="inlineStr"/>
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="I209" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9125,20 +9599,21 @@
           <t>Shipbuilding group, one of the leading shipbuilders in the Persian Gulf.</t>
         </is>
       </c>
-      <c r="C210" s="2" t="inlineStr"/>
-      <c r="D210" s="2" t="inlineStr"/>
-      <c r="E210" s="2" t="inlineStr"/>
-      <c r="F210" s="2" t="inlineStr">
+      <c r="C210" s="2" t="n"/>
+      <c r="D210" s="2" t="n"/>
+      <c r="E210" s="2" t="n"/>
+      <c r="F210" s="2" t="inlineStr"/>
+      <c r="G210" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="I210" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9166,20 +9641,21 @@
           <t>Marine contracting company providing comprehensive marine contracting services.</t>
         </is>
       </c>
-      <c r="C211" s="2" t="inlineStr"/>
-      <c r="D211" s="2" t="inlineStr"/>
-      <c r="E211" s="2" t="inlineStr"/>
-      <c r="F211" s="2" t="inlineStr">
+      <c r="C211" s="2" t="n"/>
+      <c r="D211" s="2" t="n"/>
+      <c r="E211" s="2" t="n"/>
+      <c r="F211" s="2" t="inlineStr"/>
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="I211" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9207,20 +9683,21 @@
           <t>Delivers industrial heavy machinery, offshore marine cranes, ROV launch &amp; recovery systems and custom industrial fabrication.</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr"/>
-      <c r="D212" s="2" t="inlineStr"/>
-      <c r="E212" s="2" t="inlineStr"/>
-      <c r="F212" s="2" t="inlineStr">
+      <c r="C212" s="2" t="n"/>
+      <c r="D212" s="2" t="n"/>
+      <c r="E212" s="2" t="n"/>
+      <c r="F212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="I212" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9248,20 +9725,21 @@
           <t>Designs/manufactures offshore contracted items and aluminum work (oil &amp; gas-leaning).</t>
         </is>
       </c>
-      <c r="C213" s="2" t="inlineStr"/>
-      <c r="D213" s="2" t="inlineStr"/>
-      <c r="E213" s="2" t="inlineStr"/>
-      <c r="F213" s="2" t="inlineStr">
+      <c r="C213" s="2" t="n"/>
+      <c r="D213" s="2" t="n"/>
+      <c r="E213" s="2" t="n"/>
+      <c r="F213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="I213" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9289,20 +9767,21 @@
           <t>Maritime company providing marine services supporting oil &amp; gas and other maritime sectors.</t>
         </is>
       </c>
-      <c r="C214" s="2" t="inlineStr"/>
-      <c r="D214" s="2" t="inlineStr"/>
-      <c r="E214" s="2" t="inlineStr"/>
-      <c r="F214" s="2" t="inlineStr">
+      <c r="C214" s="2" t="n"/>
+      <c r="D214" s="2" t="n"/>
+      <c r="E214" s="2" t="n"/>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="I214" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9330,20 +9809,21 @@
           <t>Mechanical equipment/fabrication services provider.</t>
         </is>
       </c>
-      <c r="C215" s="2" t="inlineStr"/>
-      <c r="D215" s="2" t="inlineStr"/>
-      <c r="E215" s="2" t="inlineStr"/>
-      <c r="F215" s="2" t="inlineStr">
+      <c r="C215" s="2" t="n"/>
+      <c r="D215" s="2" t="n"/>
+      <c r="E215" s="2" t="n"/>
+      <c r="F215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="I215" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9371,20 +9851,21 @@
           <t>Mechanical equipment maintenance/fabrication provider.</t>
         </is>
       </c>
-      <c r="C216" s="2" t="inlineStr"/>
-      <c r="D216" s="2" t="inlineStr"/>
-      <c r="E216" s="2" t="inlineStr"/>
-      <c r="F216" s="2" t="inlineStr">
+      <c r="C216" s="2" t="n"/>
+      <c r="D216" s="2" t="n"/>
+      <c r="E216" s="2" t="n"/>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="I216" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9427,17 +9908,18 @@
           <t>info@aptglobalmarine.com</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr">
         <is>
           <t>Dubai / Ras Al Khaimah, UAE</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="I217" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Beau,
@@ -9480,17 +9962,18 @@
           <t>Cameron@grandweld.com; marawan.f@grandweld.com</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="I218" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Cameron,
@@ -9518,20 +10001,21 @@
           <t>Global offshore oil &amp; gas EPC major with a Jebel Ali facility (oil &amp; gas-primary).</t>
         </is>
       </c>
-      <c r="C219" s="2" t="inlineStr"/>
-      <c r="D219" s="2" t="inlineStr"/>
-      <c r="E219" s="2" t="inlineStr"/>
-      <c r="F219" s="2" t="inlineStr">
+      <c r="C219" s="2" t="n"/>
+      <c r="D219" s="2" t="n"/>
+      <c r="E219" s="2" t="n"/>
+      <c r="F219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr">
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="I219" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9559,20 +10043,21 @@
           <t>Marine services company based in Jebel Ali Free Zone.</t>
         </is>
       </c>
-      <c r="C220" s="2" t="inlineStr"/>
-      <c r="D220" s="2" t="inlineStr"/>
-      <c r="E220" s="2" t="inlineStr"/>
-      <c r="F220" s="2" t="inlineStr">
+      <c r="C220" s="2" t="n"/>
+      <c r="D220" s="2" t="n"/>
+      <c r="E220" s="2" t="n"/>
+      <c r="F220" s="2" t="inlineStr"/>
+      <c r="G220" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="I220" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9600,20 +10085,21 @@
           <t>Middle East arm of Schottel, supplier of marine propulsion systems.</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr"/>
-      <c r="D221" s="2" t="inlineStr"/>
-      <c r="E221" s="2" t="inlineStr"/>
-      <c r="F221" s="2" t="inlineStr">
+      <c r="C221" s="2" t="n"/>
+      <c r="D221" s="2" t="n"/>
+      <c r="E221" s="2" t="n"/>
+      <c r="F221" s="2" t="inlineStr"/>
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="I221" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9641,20 +10127,21 @@
           <t>Marine services company in Jebel Ali Free Zone.</t>
         </is>
       </c>
-      <c r="C222" s="2" t="inlineStr"/>
-      <c r="D222" s="2" t="inlineStr"/>
-      <c r="E222" s="2" t="inlineStr"/>
-      <c r="F222" s="2" t="inlineStr">
+      <c r="C222" s="2" t="n"/>
+      <c r="D222" s="2" t="n"/>
+      <c r="E222" s="2" t="n"/>
+      <c r="F222" s="2" t="inlineStr"/>
+      <c r="G222" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr">
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="I222" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9682,20 +10169,21 @@
           <t>Gulf arm of Dutch marine contractor Van Oord - dredging and marine construction.</t>
         </is>
       </c>
-      <c r="C223" s="2" t="inlineStr"/>
-      <c r="D223" s="2" t="inlineStr"/>
-      <c r="E223" s="2" t="inlineStr"/>
-      <c r="F223" s="2" t="inlineStr">
+      <c r="C223" s="2" t="n"/>
+      <c r="D223" s="2" t="n"/>
+      <c r="E223" s="2" t="n"/>
+      <c r="F223" s="2" t="inlineStr"/>
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr">
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="I223" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9723,20 +10211,21 @@
           <t>Steel distribution company in Jebel Ali Free Zone (raw-material supplier).</t>
         </is>
       </c>
-      <c r="C224" s="2" t="inlineStr"/>
-      <c r="D224" s="2" t="inlineStr"/>
-      <c r="E224" s="2" t="inlineStr"/>
-      <c r="F224" s="2" t="inlineStr">
+      <c r="C224" s="2" t="n"/>
+      <c r="D224" s="2" t="n"/>
+      <c r="E224" s="2" t="n"/>
+      <c r="F224" s="2" t="inlineStr"/>
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr">
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="I224" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9764,20 +10253,21 @@
           <t>Marine construction contractor (since 2007) - construction, dredging and offshore pipeline installation.</t>
         </is>
       </c>
-      <c r="C225" s="2" t="inlineStr"/>
-      <c r="D225" s="2" t="inlineStr"/>
-      <c r="E225" s="2" t="inlineStr"/>
-      <c r="F225" s="2" t="inlineStr">
+      <c r="C225" s="2" t="n"/>
+      <c r="D225" s="2" t="n"/>
+      <c r="E225" s="2" t="n"/>
+      <c r="F225" s="2" t="inlineStr"/>
+      <c r="G225" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr">
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="I225" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9805,20 +10295,21 @@
           <t>Construction contractor active in JAFZA projects.</t>
         </is>
       </c>
-      <c r="C226" s="2" t="inlineStr"/>
-      <c r="D226" s="2" t="inlineStr"/>
-      <c r="E226" s="2" t="inlineStr"/>
-      <c r="F226" s="2" t="inlineStr">
+      <c r="C226" s="2" t="n"/>
+      <c r="D226" s="2" t="n"/>
+      <c r="E226" s="2" t="n"/>
+      <c r="F226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="I226" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9843,27 +10334,32 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Shipbuilding/ship-repair yards in Dubai, Sharjah and Fujairah, building Damen and non-Damen designs up to 120m.</t>
-        </is>
-      </c>
-      <c r="C227" s="2" t="inlineStr"/>
-      <c r="D227" s="2" t="inlineStr"/>
-      <c r="E227" s="2" t="inlineStr"/>
-      <c r="F227" s="2" t="inlineStr">
+          <t>Joint venture between Albwardy Investment (Dubai) and Damen Shipyards Group (Netherlands), providing shipbuilding and ship repair to the marine and oil &amp; gas industries in the Middle East. Around 2,500 staff of 26 nationalities across three UAE yards in Dubai, Sharjah and Fujairah, including a new office and workshop facility in Dubai Maritime City.</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="n"/>
+      <c r="D227" s="2" t="n"/>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>sales@albwardydamen.com</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr">
         <is>
           <t>Dubai / Sharjah / Fujairah, UAE</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Albwardy Damen while looking at companies working in shipbuilding and marine fabrication, and your work as a shipbuilding/ship-repair yards in Dubai, Sharjah and Fujairah, building Damen and non-Damen designs up to 120m caught my attention.
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Albwardy Damen while looking at companies working in shipbuilding and marine fabrication, and your work as a joint venture between Albwardy Investment and Damen Shipyards Group caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -9887,20 +10383,21 @@
           <t>Shipbuilding company operating across UAE and the Gulf, including boat building in Dubai.</t>
         </is>
       </c>
-      <c r="C228" s="2" t="inlineStr"/>
-      <c r="D228" s="2" t="inlineStr"/>
-      <c r="E228" s="2" t="inlineStr"/>
-      <c r="F228" s="2" t="inlineStr">
+      <c r="C228" s="2" t="n"/>
+      <c r="D228" s="2" t="n"/>
+      <c r="E228" s="2" t="n"/>
+      <c r="F228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="I228" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9928,20 +10425,21 @@
           <t>Marine services company - ship repair, dry docking and vessel support across UAE ports.</t>
         </is>
       </c>
-      <c r="C229" s="2" t="inlineStr"/>
-      <c r="D229" s="2" t="inlineStr"/>
-      <c r="E229" s="2" t="inlineStr"/>
-      <c r="F229" s="2" t="inlineStr">
+      <c r="C229" s="2" t="n"/>
+      <c r="D229" s="2" t="n"/>
+      <c r="E229" s="2" t="n"/>
+      <c r="F229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="I229" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9969,20 +10467,21 @@
           <t>Automated cutting and fabrication capabilities, Dubai Silicon Oasis.</t>
         </is>
       </c>
-      <c r="C230" s="2" t="inlineStr"/>
-      <c r="D230" s="2" t="inlineStr"/>
-      <c r="E230" s="2" t="inlineStr"/>
-      <c r="F230" s="2" t="inlineStr">
+      <c r="C230" s="2" t="n"/>
+      <c r="D230" s="2" t="n"/>
+      <c r="E230" s="2" t="n"/>
+      <c r="F230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr">
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="I230" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10010,20 +10509,21 @@
           <t>Automated cutting/fabrication company in Al Quoz.</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr"/>
-      <c r="D231" s="2" t="inlineStr"/>
-      <c r="E231" s="2" t="inlineStr"/>
-      <c r="F231" s="2" t="inlineStr">
+      <c r="C231" s="2" t="n"/>
+      <c r="D231" s="2" t="n"/>
+      <c r="E231" s="2" t="n"/>
+      <c r="F231" s="2" t="inlineStr"/>
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr">
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="I231" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10051,20 +10551,21 @@
           <t>Steel erection company respected for structural steel contracting across the UAE.</t>
         </is>
       </c>
-      <c r="C232" s="2" t="inlineStr"/>
-      <c r="D232" s="2" t="inlineStr"/>
-      <c r="E232" s="2" t="inlineStr"/>
-      <c r="F232" s="2" t="inlineStr">
+      <c r="C232" s="2" t="n"/>
+      <c r="D232" s="2" t="n"/>
+      <c r="E232" s="2" t="n"/>
+      <c r="F232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr">
         <is>
           <t>Ajman / Dubai, UAE</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="I232" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10092,20 +10593,21 @@
           <t>Established 2009; fabrication assistance to various industrial sectors in the UAE.</t>
         </is>
       </c>
-      <c r="C233" s="2" t="inlineStr"/>
-      <c r="D233" s="2" t="inlineStr"/>
-      <c r="E233" s="2" t="inlineStr"/>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="C233" s="2" t="n"/>
+      <c r="D233" s="2" t="n"/>
+      <c r="E233" s="2" t="n"/>
+      <c r="F233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="I233" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10133,20 +10635,21 @@
           <t>Engineering, fabrication and construction across a wide spectrum of industries; sites in Sharjah, Dubai and Abu Dhabi.</t>
         </is>
       </c>
-      <c r="C234" s="2" t="inlineStr"/>
-      <c r="D234" s="2" t="inlineStr"/>
-      <c r="E234" s="2" t="inlineStr"/>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="C234" s="2" t="n"/>
+      <c r="D234" s="2" t="n"/>
+      <c r="E234" s="2" t="n"/>
+      <c r="F234" s="2" t="inlineStr"/>
+      <c r="G234" s="2" t="inlineStr">
         <is>
           <t>Sharjah / Dubai / Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="I234" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10174,20 +10677,21 @@
           <t>40+ years in steel fabrication, recognized among Dubai's top steel companies.</t>
         </is>
       </c>
-      <c r="C235" s="2" t="inlineStr"/>
-      <c r="D235" s="2" t="inlineStr"/>
-      <c r="E235" s="2" t="inlineStr"/>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="C235" s="2" t="n"/>
+      <c r="D235" s="2" t="n"/>
+      <c r="E235" s="2" t="n"/>
+      <c r="F235" s="2" t="inlineStr"/>
+      <c r="G235" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr">
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="I235" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10215,20 +10719,21 @@
           <t>Custom industrial steel fabrication and heavy steel structures specialist.</t>
         </is>
       </c>
-      <c r="C236" s="2" t="inlineStr"/>
-      <c r="D236" s="2" t="inlineStr"/>
-      <c r="E236" s="2" t="inlineStr"/>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="C236" s="2" t="n"/>
+      <c r="D236" s="2" t="n"/>
+      <c r="E236" s="2" t="n"/>
+      <c r="F236" s="2" t="inlineStr"/>
+      <c r="G236" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr">
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="I236" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10256,20 +10761,21 @@
           <t>Fabrication and structural steelwork company.</t>
         </is>
       </c>
-      <c r="C237" s="2" t="inlineStr"/>
-      <c r="D237" s="2" t="inlineStr"/>
-      <c r="E237" s="2" t="inlineStr"/>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="C237" s="2" t="n"/>
+      <c r="D237" s="2" t="n"/>
+      <c r="E237" s="2" t="n"/>
+      <c r="F237" s="2" t="inlineStr"/>
+      <c r="G237" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr">
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="I237" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10297,20 +10803,21 @@
           <t>Steel structure fabrication specialist operating from Hamriya Free Zone.</t>
         </is>
       </c>
-      <c r="C238" s="2" t="inlineStr"/>
-      <c r="D238" s="2" t="inlineStr"/>
-      <c r="E238" s="2" t="inlineStr"/>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="C238" s="2" t="n"/>
+      <c r="D238" s="2" t="n"/>
+      <c r="E238" s="2" t="n"/>
+      <c r="F238" s="2" t="inlineStr"/>
+      <c r="G238" s="2" t="inlineStr">
         <is>
           <t>Sharjah, UAE</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr">
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="I238" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10338,20 +10845,21 @@
           <t>Fabrication facility with in-house production support.</t>
         </is>
       </c>
-      <c r="C239" s="2" t="inlineStr"/>
-      <c r="D239" s="2" t="inlineStr"/>
-      <c r="E239" s="2" t="inlineStr"/>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="C239" s="2" t="n"/>
+      <c r="D239" s="2" t="n"/>
+      <c r="E239" s="2" t="n"/>
+      <c r="F239" s="2" t="inlineStr"/>
+      <c r="G239" s="2" t="inlineStr">
         <is>
           <t>Ras Al Khaimah, UAE</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr">
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="I239" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10379,20 +10887,21 @@
           <t>Heavy-lift specialist; completed load-out and float-off operation for jack-up barge Vahana Arjun.</t>
         </is>
       </c>
-      <c r="C240" s="2" t="inlineStr"/>
-      <c r="D240" s="2" t="inlineStr"/>
-      <c r="E240" s="2" t="inlineStr"/>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="C240" s="2" t="n"/>
+      <c r="D240" s="2" t="n"/>
+      <c r="E240" s="2" t="n"/>
+      <c r="F240" s="2" t="inlineStr"/>
+      <c r="G240" s="2" t="inlineStr">
         <is>
           <t>Ras Al Khaimah, UAE</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr">
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="I240" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10420,20 +10929,21 @@
           <t>Onshore/offshore contractor - ship repair/new construction, structural steel work, insulation &amp; cladding, refractory linings.</t>
         </is>
       </c>
-      <c r="C241" s="2" t="inlineStr"/>
-      <c r="D241" s="2" t="inlineStr"/>
-      <c r="E241" s="2" t="inlineStr"/>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="C241" s="2" t="n"/>
+      <c r="D241" s="2" t="n"/>
+      <c r="E241" s="2" t="n"/>
+      <c r="F241" s="2" t="inlineStr"/>
+      <c r="G241" s="2" t="inlineStr">
         <is>
           <t>Sharjah, UAE</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr">
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="I241" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10461,20 +10971,21 @@
           <t>Structural steel fabrication company based in Al Sajaa.</t>
         </is>
       </c>
-      <c r="C242" s="2" t="inlineStr"/>
-      <c r="D242" s="2" t="inlineStr"/>
-      <c r="E242" s="2" t="inlineStr"/>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="C242" s="2" t="n"/>
+      <c r="D242" s="2" t="n"/>
+      <c r="E242" s="2" t="n"/>
+      <c r="F242" s="2" t="inlineStr"/>
+      <c r="G242" s="2" t="inlineStr">
         <is>
           <t>Sharjah, UAE</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="I242" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10502,20 +11013,21 @@
           <t>ISO-certified marine repair company - marine repairs, maintenance, fabrication, engine reconditioning, Class survey prep.</t>
         </is>
       </c>
-      <c r="C243" s="2" t="inlineStr"/>
-      <c r="D243" s="2" t="inlineStr"/>
-      <c r="E243" s="2" t="inlineStr"/>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="C243" s="2" t="n"/>
+      <c r="D243" s="2" t="n"/>
+      <c r="E243" s="2" t="n"/>
+      <c r="F243" s="2" t="inlineStr"/>
+      <c r="G243" s="2" t="inlineStr">
         <is>
           <t>Fujairah, UAE</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr">
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="I243" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10543,20 +11055,21 @@
           <t>Marine and industrial repair services across UAE/Middle East - repair, maintenance, refurbishment, fabrication, engineering.</t>
         </is>
       </c>
-      <c r="C244" s="2" t="inlineStr"/>
-      <c r="D244" s="2" t="inlineStr"/>
-      <c r="E244" s="2" t="inlineStr"/>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="C244" s="2" t="n"/>
+      <c r="D244" s="2" t="n"/>
+      <c r="E244" s="2" t="n"/>
+      <c r="F244" s="2" t="inlineStr"/>
+      <c r="G244" s="2" t="inlineStr">
         <is>
           <t>Dubai / Fujairah / Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr">
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="I244" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10584,20 +11097,21 @@
           <t>Marine services operating across multiple UAE ports including Ajman Port and Umm Al Quwain Port.</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr"/>
-      <c r="D245" s="2" t="inlineStr"/>
-      <c r="E245" s="2" t="inlineStr"/>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="C245" s="2" t="n"/>
+      <c r="D245" s="2" t="n"/>
+      <c r="E245" s="2" t="n"/>
+      <c r="F245" s="2" t="inlineStr"/>
+      <c r="G245" s="2" t="inlineStr">
         <is>
           <t>Ajman / Umm Al Quwain, UAE</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr">
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="I245" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10622,27 +11136,36 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Marine and offshore engineering consultancy providing naval architecture, structural and specialist design services.</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr"/>
-      <c r="D246" s="2" t="inlineStr"/>
-      <c r="E246" s="2" t="inlineStr"/>
+          <t>International multidisciplinary engineering, science and technology consultancy established in 1985 (formerly British Maritime Technology), with around 1,500 professionals in 60 offices across Europe, Asia and the Americas. Specialises in maritime engineering design, design support, risk and contract management. Head office in London.</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="n"/>
+      <c r="D246" s="2" t="n"/>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@bmtglobal.com</t>
+        </is>
+      </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
+          <t>+44 (0)20 8943 5544</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr">
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H246" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BMT while looking at companies working in naval architecture and marine engineering, and your work as a marine and offshore engineering consultancy providing naval architecture, structural and specialist design services caught my attention.
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across BMT while looking at companies working in offshore and structural engineering consultancy, and your work as an international multidisciplinary engineering, science and technology consultancy established in 1985, with around 1,500 professionals caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -10663,27 +11186,40 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Engineering consultancy with a major offshore wind foundation/structural design practice.</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr"/>
-      <c r="D247" s="2" t="inlineStr"/>
-      <c r="E247" s="2" t="inlineStr"/>
-      <c r="F247" s="2" t="inlineStr">
+          <t>World-leading engineering consultancy for offshore wind and global market leader in detailed design of foundation structures, involved in over 70% of all operating offshore wind projects globally. 1,800 experts across the UK and Ireland. Other published wind contacts include Kirsty McGuinness (Global Renewable Energy Sector Leader) and Denis Matha (Global Head of Floating Wind).</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Raya Peterson</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Global Lead, Offshore Wind Development</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>raya.peterson@ramboll.com</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr"/>
+      <c r="G247" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr">
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H247" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ramboll UK (Offshore Wind) while looking at companies working in offshore wind structural engineering, and your work as an engineering consultancy with a major offshore wind foundation/structural design practice caught my attention.
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Raya,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Ramboll UK (Offshore Wind) while looking at companies working in offshore wind structural engineering, and your work as a world-leading engineering consultancy for offshore wind and global market leader in detailed design of foundation caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -10704,27 +11240,36 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Energy consultancy providing engineering, subsea and offshore wind advisory services.</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr"/>
-      <c r="D248" s="2" t="inlineStr"/>
-      <c r="E248" s="2" t="inlineStr"/>
+          <t>Global energy consultancy formed in 2005 delivering integrated engineering, covering energy production, technology development, environmental and technical safety, compliance and business risk. Head office Xodus House, 50 Huntly Street, Aberdeen, with offices in London, Glasgow, Edinburgh and Orkney.</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="n"/>
+      <c r="D248" s="2" t="n"/>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>info@xodusgroup.com</t>
+        </is>
+      </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
+          <t>+44 1224 628300</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
           <t>Aberdeen, UK</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr">
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H248" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Xodus Group while looking at companies working in offshore wind structural engineering, and your work as an energy consultancy providing engineering, subsea and offshore wind advisory services caught my attention.
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Xodus Group while looking at companies working in offshore and structural engineering consultancy, and your work as a global energy consultancy formed in 2005 delivering integrated engineering caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -10748,20 +11293,21 @@
           <t>Oil &amp; gas and offshore engineering consultancy (part of TechnipFMC).</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr"/>
-      <c r="D249" s="2" t="inlineStr"/>
-      <c r="E249" s="2" t="inlineStr"/>
-      <c r="F249" s="2" t="inlineStr">
+      <c r="C249" s="2" t="n"/>
+      <c r="D249" s="2" t="n"/>
+      <c r="E249" s="2" t="n"/>
+      <c r="F249" s="2" t="inlineStr"/>
+      <c r="G249" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr">
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="I249" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10789,20 +11335,21 @@
           <t>Global engineering and consultancy company serving energy, including offshore oil &amp; gas and renewables.</t>
         </is>
       </c>
-      <c r="C250" s="2" t="inlineStr"/>
-      <c r="D250" s="2" t="inlineStr"/>
-      <c r="E250" s="2" t="inlineStr"/>
-      <c r="F250" s="2" t="inlineStr">
+      <c r="C250" s="2" t="n"/>
+      <c r="D250" s="2" t="n"/>
+      <c r="E250" s="2" t="n"/>
+      <c r="F250" s="2" t="inlineStr"/>
+      <c r="G250" s="2" t="inlineStr">
         <is>
           <t>Aberdeen, UK</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr">
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="I250" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10827,27 +11374,28 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Marine warranty surveying and offshore engineering consultancy for marine operations.</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr"/>
-      <c r="D251" s="2" t="inlineStr"/>
-      <c r="E251" s="2" t="inlineStr"/>
-      <c r="F251" s="2" t="inlineStr">
-        <is>
-          <t>London, UK</t>
-        </is>
-      </c>
+          <t>Marine, offshore and engineering consultancy founded in 1979 specialising in marine warranty surveying, dynamic positioning and engineering services, spanning the full offshore project lifecycle from engineering and design and third-party verification through installation, risk management and decommissioning. Main HQ at Kanalsletta 8, Stavanger, Norway.</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="n"/>
+      <c r="D251" s="2" t="n"/>
+      <c r="E251" s="2" t="n"/>
+      <c r="F251" s="2" t="inlineStr"/>
       <c r="G251" s="2" t="inlineStr">
         <is>
+          <t>Stavanger, Norway</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H251" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Global Maritime while looking at companies working in offshore and structural engineering consultancy, and your work as a marine warranty surveying and offshore engineering consultancy for marine operations caught my attention.
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Global Maritime while looking at companies working in offshore and structural engineering consultancy, and your work as a marine, offshore and engineering consultancy founded in 1979 specialising in marine warranty surveying, dynamic positioning caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -10868,27 +11416,36 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Independent offshore engineering consultancy for oil &amp; gas and renewables projects.</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr"/>
-      <c r="D252" s="2" t="inlineStr"/>
-      <c r="E252" s="2" t="inlineStr"/>
+          <t>International technical service provider to the oil, gas and renewable energy markets, established in 1978 as the design wing of a major offshore fabricator and now part of the DORIS Group with 50+ years of experience. Provides consulting, engineering, procurement, project management and operations support. Great Yarmouth and Wimbledon, London.</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="n"/>
+      <c r="D252" s="2" t="n"/>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>info@ode-ltd.co.uk</t>
+        </is>
+      </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
+          <t>+44 (0)1493 845100</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
           <t>Aberdeen, UK</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H252" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ODE Offshore Design Engineering while looking at companies working in offshore and structural engineering consultancy, and your work as an independent offshore engineering consultancy for oil &amp; gas and renewables projects caught my attention.
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across ODE Offshore Design Engineering while looking at companies working in marine equipment and propulsion systems, and your work as an international technical service provider to the oil caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -10912,20 +11469,21 @@
           <t>Manufacturer of subsea power and umbilical cables for offshore wind and oil &amp; gas.</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr"/>
-      <c r="D253" s="2" t="inlineStr"/>
-      <c r="E253" s="2" t="inlineStr"/>
-      <c r="F253" s="2" t="inlineStr">
+      <c r="C253" s="2" t="n"/>
+      <c r="D253" s="2" t="n"/>
+      <c r="E253" s="2" t="n"/>
+      <c r="F253" s="2" t="inlineStr"/>
+      <c r="G253" s="2" t="inlineStr">
         <is>
           <t>Hartlepool, UK</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr">
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="I253" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10950,27 +11508,36 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Marine and offshore engineering consultancy specialising in ship design and offshore renewables.</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr"/>
-      <c r="D254" s="2" t="inlineStr"/>
-      <c r="E254" s="2" t="inlineStr"/>
+          <t>Independent consultancy specialising in engineering design, clean technology and technical consultancy for marine and offshore environments, spanning vessel design, vessel analysis, marine equipment, project management and offshore engineering, with a focus on maritime decarbonisation and renewable energy infrastructure. 3-7 Temple Avenue, London EC4Y 0DA.</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="n"/>
+      <c r="D254" s="2" t="n"/>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@houlderltd.com</t>
+        </is>
+      </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
+          <t>+44 345 262 9940</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H254" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Houlder while looking at companies working in offshore and structural engineering consultancy, and your work as a marine and offshore engineering consultancy specialising in ship design and offshore renewables caught my attention.
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Houlder while looking at companies working in offshore and structural engineering consultancy, and your work as an independent consultancy specialising in engineering design caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -10994,20 +11561,21 @@
           <t>Systems and engineering consultancy with a marine/offshore structural engineering practice.</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr"/>
-      <c r="D255" s="2" t="inlineStr"/>
-      <c r="E255" s="2" t="inlineStr"/>
-      <c r="F255" s="2" t="inlineStr">
+      <c r="C255" s="2" t="n"/>
+      <c r="D255" s="2" t="n"/>
+      <c r="E255" s="2" t="n"/>
+      <c r="F255" s="2" t="inlineStr"/>
+      <c r="G255" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr">
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11035,20 +11603,21 @@
           <t>Engineering and construction services provider for offshore oil &amp; gas and renewable energy projects.</t>
         </is>
       </c>
-      <c r="C256" s="2" t="inlineStr"/>
-      <c r="D256" s="2" t="inlineStr"/>
-      <c r="E256" s="2" t="inlineStr"/>
-      <c r="F256" s="2" t="inlineStr">
+      <c r="C256" s="2" t="n"/>
+      <c r="D256" s="2" t="n"/>
+      <c r="E256" s="2" t="n"/>
+      <c r="F256" s="2" t="inlineStr"/>
+      <c r="G256" s="2" t="inlineStr">
         <is>
           <t>Oslo, Norway</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr">
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="I256" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11076,20 +11645,21 @@
           <t>EPC contractor for offshore platforms, substructures and onshore facilities.</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr"/>
-      <c r="D257" s="2" t="inlineStr"/>
-      <c r="E257" s="2" t="inlineStr"/>
-      <c r="F257" s="2" t="inlineStr">
+      <c r="C257" s="2" t="n"/>
+      <c r="D257" s="2" t="n"/>
+      <c r="E257" s="2" t="n"/>
+      <c r="F257" s="2" t="inlineStr"/>
+      <c r="G257" s="2" t="inlineStr">
         <is>
           <t>Oslo, Norway</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr">
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="I257" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11117,20 +11687,21 @@
           <t>Norwegian arm of the global subsea/offshore engineering and technology group.</t>
         </is>
       </c>
-      <c r="C258" s="2" t="inlineStr"/>
-      <c r="D258" s="2" t="inlineStr"/>
-      <c r="E258" s="2" t="inlineStr"/>
-      <c r="F258" s="2" t="inlineStr">
+      <c r="C258" s="2" t="n"/>
+      <c r="D258" s="2" t="n"/>
+      <c r="E258" s="2" t="n"/>
+      <c r="F258" s="2" t="inlineStr"/>
+      <c r="G258" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr">
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="I258" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11155,27 +11726,36 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Classification society and technical advisor providing naval architecture, structural engineering and standards for offshore/marine structures.</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr"/>
-      <c r="D259" s="2" t="inlineStr"/>
-      <c r="E259" s="2" t="inlineStr"/>
+          <t>International classification society and technical advisor headquartered in Høvik, Norway, serving maritime, oil and gas, renewable energy, electrification and healthcare. Provides naval architecture and structural engineering consultancy, structural analysis and the DNV standards widely used for offshore and marine structures. Veritasveien 1, Høvik.</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="n"/>
+      <c r="D259" s="2" t="n"/>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>dnvgl.certification.norway@dnv.com</t>
+        </is>
+      </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
+          <t>+47 6757 9900</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
           <t>Høvik, Norway</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr">
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H259" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across DNV while looking at companies working in naval architecture and marine engineering, and your work as a classification society and technical advisor providing naval architecture, structural engineering and standards for offshore/marine structures caught my attention.
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across DNV while looking at companies working in naval architecture and marine engineering, and your work as an international classification society and technical advisor headquartered in Høvik caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -11199,20 +11779,21 @@
           <t>Norwegian engineering company delivering structural, mechanical and offshore engineering services.</t>
         </is>
       </c>
-      <c r="C260" s="2" t="inlineStr"/>
-      <c r="D260" s="2" t="inlineStr"/>
-      <c r="E260" s="2" t="inlineStr"/>
-      <c r="F260" s="2" t="inlineStr">
+      <c r="C260" s="2" t="n"/>
+      <c r="D260" s="2" t="n"/>
+      <c r="E260" s="2" t="n"/>
+      <c r="F260" s="2" t="inlineStr"/>
+      <c r="G260" s="2" t="inlineStr">
         <is>
           <t>Trondheim, Norway</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr">
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="I260" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11240,20 +11821,21 @@
           <t>Norwegian multidisciplinary consultancy with marine/offshore structural engineering capability.</t>
         </is>
       </c>
-      <c r="C261" s="2" t="inlineStr"/>
-      <c r="D261" s="2" t="inlineStr"/>
-      <c r="E261" s="2" t="inlineStr"/>
-      <c r="F261" s="2" t="inlineStr">
+      <c r="C261" s="2" t="n"/>
+      <c r="D261" s="2" t="n"/>
+      <c r="E261" s="2" t="n"/>
+      <c r="F261" s="2" t="inlineStr"/>
+      <c r="G261" s="2" t="inlineStr">
         <is>
           <t>Oslo, Norway</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr">
+      <c r="H261" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="I261" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11281,20 +11863,21 @@
           <t>World's largest offshore wind developer/operator, headquartered in Denmark.</t>
         </is>
       </c>
-      <c r="C262" s="2" t="inlineStr"/>
-      <c r="D262" s="2" t="inlineStr"/>
-      <c r="E262" s="2" t="inlineStr"/>
-      <c r="F262" s="2" t="inlineStr">
+      <c r="C262" s="2" t="n"/>
+      <c r="D262" s="2" t="n"/>
+      <c r="E262" s="2" t="n"/>
+      <c r="F262" s="2" t="inlineStr"/>
+      <c r="G262" s="2" t="inlineStr">
         <is>
           <t>Fredericia, Denmark</t>
         </is>
       </c>
-      <c r="G262" s="2" t="inlineStr">
+      <c r="H262" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="I262" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11322,20 +11905,21 @@
           <t>Major German utility's offshore wind development/operations arm.</t>
         </is>
       </c>
-      <c r="C263" s="2" t="inlineStr"/>
-      <c r="D263" s="2" t="inlineStr"/>
-      <c r="E263" s="2" t="inlineStr"/>
-      <c r="F263" s="2" t="inlineStr">
+      <c r="C263" s="2" t="n"/>
+      <c r="D263" s="2" t="n"/>
+      <c r="E263" s="2" t="n"/>
+      <c r="F263" s="2" t="inlineStr"/>
+      <c r="G263" s="2" t="inlineStr">
         <is>
           <t>Hamburg, Germany</t>
         </is>
       </c>
-      <c r="G263" s="2" t="inlineStr">
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="I263" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11363,20 +11947,21 @@
           <t>Swedish state-owned utility's offshore wind development/operations arm.</t>
         </is>
       </c>
-      <c r="C264" s="2" t="inlineStr"/>
-      <c r="D264" s="2" t="inlineStr"/>
-      <c r="E264" s="2" t="inlineStr"/>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="C264" s="2" t="n"/>
+      <c r="D264" s="2" t="n"/>
+      <c r="E264" s="2" t="n"/>
+      <c r="F264" s="2" t="inlineStr"/>
+      <c r="G264" s="2" t="inlineStr">
         <is>
           <t>Stockholm, Sweden</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr">
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="I264" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11404,20 +11989,21 @@
           <t>Major Spanish utility with a large offshore wind development portfolio.</t>
         </is>
       </c>
-      <c r="C265" s="2" t="inlineStr"/>
-      <c r="D265" s="2" t="inlineStr"/>
-      <c r="E265" s="2" t="inlineStr"/>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="C265" s="2" t="n"/>
+      <c r="D265" s="2" t="n"/>
+      <c r="E265" s="2" t="n"/>
+      <c r="F265" s="2" t="inlineStr"/>
+      <c r="G265" s="2" t="inlineStr">
         <is>
           <t>Bilbao, Spain</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr">
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="I265" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11445,20 +12031,21 @@
           <t>French utility's renewable energy arm, active in offshore wind.</t>
         </is>
       </c>
-      <c r="C266" s="2" t="inlineStr"/>
-      <c r="D266" s="2" t="inlineStr"/>
-      <c r="E266" s="2" t="inlineStr"/>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="C266" s="2" t="n"/>
+      <c r="D266" s="2" t="n"/>
+      <c r="E266" s="2" t="n"/>
+      <c r="F266" s="2" t="inlineStr"/>
+      <c r="G266" s="2" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr">
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H266" s="2" t="inlineStr">
+      <c r="I266" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11486,20 +12073,21 @@
           <t>UK/Irish utility's renewable energy arm with a large offshore wind portfolio.</t>
         </is>
       </c>
-      <c r="C267" s="2" t="inlineStr"/>
-      <c r="D267" s="2" t="inlineStr"/>
-      <c r="E267" s="2" t="inlineStr"/>
-      <c r="F267" s="2" t="inlineStr">
+      <c r="C267" s="2" t="n"/>
+      <c r="D267" s="2" t="n"/>
+      <c r="E267" s="2" t="n"/>
+      <c r="F267" s="2" t="inlineStr"/>
+      <c r="G267" s="2" t="inlineStr">
         <is>
           <t>Glasgow, UK</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr">
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H267" s="2" t="inlineStr">
+      <c r="I267" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11527,20 +12115,21 @@
           <t>UK renewable energy developer (Iberdrola subsidiary) active in offshore wind.</t>
         </is>
       </c>
-      <c r="C268" s="2" t="inlineStr"/>
-      <c r="D268" s="2" t="inlineStr"/>
-      <c r="E268" s="2" t="inlineStr"/>
-      <c r="F268" s="2" t="inlineStr">
+      <c r="C268" s="2" t="n"/>
+      <c r="D268" s="2" t="n"/>
+      <c r="E268" s="2" t="n"/>
+      <c r="F268" s="2" t="inlineStr"/>
+      <c r="G268" s="2" t="inlineStr">
         <is>
           <t>Glasgow, UK</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr">
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H268" s="2" t="inlineStr">
+      <c r="I268" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11568,20 +12157,21 @@
           <t>Joint venture (EDP Renewables/Engie) offshore wind developer active across Europe.</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr"/>
-      <c r="D269" s="2" t="inlineStr"/>
-      <c r="E269" s="2" t="inlineStr"/>
-      <c r="F269" s="2" t="inlineStr">
+      <c r="C269" s="2" t="n"/>
+      <c r="D269" s="2" t="n"/>
+      <c r="E269" s="2" t="n"/>
+      <c r="F269" s="2" t="inlineStr"/>
+      <c r="G269" s="2" t="inlineStr">
         <is>
           <t>Madrid, Spain</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr">
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H269" s="2" t="inlineStr">
+      <c r="I269" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11609,20 +12199,21 @@
           <t>Norwegian energy major with a significant offshore wind (and oil &amp; gas) portfolio.</t>
         </is>
       </c>
-      <c r="C270" s="2" t="inlineStr"/>
-      <c r="D270" s="2" t="inlineStr"/>
-      <c r="E270" s="2" t="inlineStr"/>
-      <c r="F270" s="2" t="inlineStr">
+      <c r="C270" s="2" t="n"/>
+      <c r="D270" s="2" t="n"/>
+      <c r="E270" s="2" t="n"/>
+      <c r="F270" s="2" t="inlineStr"/>
+      <c r="G270" s="2" t="inlineStr">
         <is>
           <t>Stavanger, Norway</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr">
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H270" s="2" t="inlineStr">
+      <c r="I270" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11650,20 +12241,21 @@
           <t>German utility with an offshore wind development/operations portfolio.</t>
         </is>
       </c>
-      <c r="C271" s="2" t="inlineStr"/>
-      <c r="D271" s="2" t="inlineStr"/>
-      <c r="E271" s="2" t="inlineStr"/>
-      <c r="F271" s="2" t="inlineStr">
+      <c r="C271" s="2" t="n"/>
+      <c r="D271" s="2" t="n"/>
+      <c r="E271" s="2" t="n"/>
+      <c r="F271" s="2" t="inlineStr"/>
+      <c r="G271" s="2" t="inlineStr">
         <is>
           <t>Karlsruhe, Germany</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr">
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H271" s="2" t="inlineStr">
+      <c r="I271" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11691,20 +12283,21 @@
           <t>Global energy major with a growing offshore wind development portfolio.</t>
         </is>
       </c>
-      <c r="C272" s="2" t="inlineStr"/>
-      <c r="D272" s="2" t="inlineStr"/>
-      <c r="E272" s="2" t="inlineStr"/>
-      <c r="F272" s="2" t="inlineStr">
+      <c r="C272" s="2" t="n"/>
+      <c r="D272" s="2" t="n"/>
+      <c r="E272" s="2" t="n"/>
+      <c r="F272" s="2" t="inlineStr"/>
+      <c r="G272" s="2" t="inlineStr">
         <is>
           <t>The Hague, Netherlands</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr">
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H272" s="2" t="inlineStr">
+      <c r="I272" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11732,20 +12325,21 @@
           <t>French energy major with an offshore wind development portfolio.</t>
         </is>
       </c>
-      <c r="C273" s="2" t="inlineStr"/>
-      <c r="D273" s="2" t="inlineStr"/>
-      <c r="E273" s="2" t="inlineStr"/>
-      <c r="F273" s="2" t="inlineStr">
+      <c r="C273" s="2" t="n"/>
+      <c r="D273" s="2" t="n"/>
+      <c r="E273" s="2" t="n"/>
+      <c r="F273" s="2" t="inlineStr"/>
+      <c r="G273" s="2" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr">
+      <c r="H273" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H273" s="2" t="inlineStr">
+      <c r="I273" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11773,20 +12367,21 @@
           <t>UK-based energy major with an offshore wind development portfolio.</t>
         </is>
       </c>
-      <c r="C274" s="2" t="inlineStr"/>
-      <c r="D274" s="2" t="inlineStr"/>
-      <c r="E274" s="2" t="inlineStr"/>
-      <c r="F274" s="2" t="inlineStr">
+      <c r="C274" s="2" t="n"/>
+      <c r="D274" s="2" t="n"/>
+      <c r="E274" s="2" t="n"/>
+      <c r="F274" s="2" t="inlineStr"/>
+      <c r="G274" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr">
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="I274" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11814,20 +12409,21 @@
           <t>Canadian-headquartered developer with major European offshore wind assets.</t>
         </is>
       </c>
-      <c r="C275" s="2" t="inlineStr"/>
-      <c r="D275" s="2" t="inlineStr"/>
-      <c r="E275" s="2" t="inlineStr"/>
-      <c r="F275" s="2" t="inlineStr">
+      <c r="C275" s="2" t="n"/>
+      <c r="D275" s="2" t="n"/>
+      <c r="E275" s="2" t="n"/>
+      <c r="F275" s="2" t="inlineStr"/>
+      <c r="G275" s="2" t="inlineStr">
         <is>
           <t>Netherlands/Germany</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr">
+      <c r="H275" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H275" s="2" t="inlineStr">
+      <c r="I275" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11855,20 +12451,21 @@
           <t>Dutch energy company active in offshore wind development.</t>
         </is>
       </c>
-      <c r="C276" s="2" t="inlineStr"/>
-      <c r="D276" s="2" t="inlineStr"/>
-      <c r="E276" s="2" t="inlineStr"/>
-      <c r="F276" s="2" t="inlineStr">
+      <c r="C276" s="2" t="n"/>
+      <c r="D276" s="2" t="n"/>
+      <c r="E276" s="2" t="n"/>
+      <c r="F276" s="2" t="inlineStr"/>
+      <c r="G276" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr">
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H276" s="2" t="inlineStr">
+      <c r="I276" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11896,20 +12493,21 @@
           <t>150-year-old Dutch marine contractor designing/building offshore wind farms in Europe, Asia and the USA.</t>
         </is>
       </c>
-      <c r="C277" s="2" t="inlineStr"/>
-      <c r="D277" s="2" t="inlineStr"/>
-      <c r="E277" s="2" t="inlineStr"/>
-      <c r="F277" s="2" t="inlineStr">
+      <c r="C277" s="2" t="n"/>
+      <c r="D277" s="2" t="n"/>
+      <c r="E277" s="2" t="n"/>
+      <c r="F277" s="2" t="inlineStr"/>
+      <c r="G277" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="G277" s="2" t="inlineStr">
+      <c r="H277" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H277" s="2" t="inlineStr">
+      <c r="I277" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11937,20 +12535,21 @@
           <t>Dutch dredging and marine services group active in offshore energy installation.</t>
         </is>
       </c>
-      <c r="C278" s="2" t="inlineStr"/>
-      <c r="D278" s="2" t="inlineStr"/>
-      <c r="E278" s="2" t="inlineStr"/>
-      <c r="F278" s="2" t="inlineStr">
+      <c r="C278" s="2" t="n"/>
+      <c r="D278" s="2" t="n"/>
+      <c r="E278" s="2" t="n"/>
+      <c r="F278" s="2" t="inlineStr"/>
+      <c r="G278" s="2" t="inlineStr">
         <is>
           <t>Papendrecht, Netherlands</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr">
+      <c r="H278" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H278" s="2" t="inlineStr">
+      <c r="I278" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11975,27 +12574,36 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Offshore wind installation specialist (part of Subsea7), delivering foundations and cable installation.</t>
-        </is>
-      </c>
-      <c r="C279" s="2" t="inlineStr"/>
-      <c r="D279" s="2" t="inlineStr"/>
-      <c r="E279" s="2" t="inlineStr"/>
+          <t>Part of the Subsea7 Group and a global leader in delivering offshore wind projects, offering specialist foundation, offshore substation, submarine cable, floating system and wind turbine installation services plus heavy transportation for the renewables sector. Offices in Aberdeen, Leer, Taipei, Zoetermeer, Bois-Colombes, Oslo, Vejle and Gdynia.</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="n"/>
+      <c r="D279" s="2" t="n"/>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>client.enquiry@seaway7.com</t>
+        </is>
+      </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
+          <t>+31 79 363 77 00</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
           <t>Oslo, Norway</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr">
+      <c r="H279" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H279" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Seaway7 (Subsea7) while looking at companies working in offshore wind structural engineering, and your work as an offshore wind installation specialist, delivering foundations and cable installation caught my attention.
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Seaway7 (Subsea7) while looking at companies working in offshore wind structural engineering, and your work as a part of the Subsea7 Group and a global leader in delivering offshore wind projects caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -12016,27 +12624,28 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Swedish/Norwegian structural and marine engineering/design consultancy.</t>
-        </is>
-      </c>
-      <c r="C280" s="2" t="inlineStr"/>
-      <c r="D280" s="2" t="inlineStr"/>
-      <c r="E280" s="2" t="inlineStr"/>
-      <c r="F280" s="2" t="inlineStr">
+          <t>NOTE - APPEARS DEFUNCT: GVA was a world-leading designer and licensor of technology for large floating marine platforms within offshore oil &amp; gas and renewable power, headquartered in Gothenburg. Owner KBR shut down GVA Consultants in 2016. Verify current status before any outreach.</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="n"/>
+      <c r="D280" s="2" t="n"/>
+      <c r="E280" s="2" t="n"/>
+      <c r="F280" s="2" t="inlineStr"/>
+      <c r="G280" s="2" t="inlineStr">
         <is>
           <t>Gothenburg, Sweden</t>
         </is>
       </c>
-      <c r="G280" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GVA Consultants while looking at companies working in offshore and structural engineering consultancy, and your work as a Swedish/Norwegian structural and marine engineering/design consultancy caught my attention.
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GVA Consultants while looking at companies working in marine and offshore engineering, and your work as an NOTE, APPEARS DEFUNCT: GVA was a world-leading designer and licensor of technology for large floating caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -12060,20 +12669,21 @@
           <t>German arm of the Danish offshore wind EPC firm Semco Maritime.</t>
         </is>
       </c>
-      <c r="C281" s="2" t="inlineStr"/>
-      <c r="D281" s="2" t="inlineStr"/>
-      <c r="E281" s="2" t="inlineStr"/>
-      <c r="F281" s="2" t="inlineStr">
+      <c r="C281" s="2" t="n"/>
+      <c r="D281" s="2" t="n"/>
+      <c r="E281" s="2" t="n"/>
+      <c r="F281" s="2" t="inlineStr"/>
+      <c r="G281" s="2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="G281" s="2" t="inlineStr">
+      <c r="H281" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H281" s="2" t="inlineStr">
+      <c r="I281" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12101,20 +12711,21 @@
           <t>Shipbuilding and repair services provider in the Dubai/Sharjah/Ajman/Umm Al Quwain area.</t>
         </is>
       </c>
-      <c r="C282" s="2" t="inlineStr"/>
-      <c r="D282" s="2" t="inlineStr"/>
-      <c r="E282" s="2" t="inlineStr"/>
-      <c r="F282" s="2" t="inlineStr">
+      <c r="C282" s="2" t="n"/>
+      <c r="D282" s="2" t="n"/>
+      <c r="E282" s="2" t="n"/>
+      <c r="F282" s="2" t="inlineStr"/>
+      <c r="G282" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr">
+      <c r="H282" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H282" s="2" t="inlineStr">
+      <c r="I282" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12142,20 +12753,21 @@
           <t>Shipbuilding and repair services provider in the UAE.</t>
         </is>
       </c>
-      <c r="C283" s="2" t="inlineStr"/>
-      <c r="D283" s="2" t="inlineStr"/>
-      <c r="E283" s="2" t="inlineStr"/>
-      <c r="F283" s="2" t="inlineStr">
+      <c r="C283" s="2" t="n"/>
+      <c r="D283" s="2" t="n"/>
+      <c r="E283" s="2" t="n"/>
+      <c r="F283" s="2" t="inlineStr"/>
+      <c r="G283" s="2" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr">
+      <c r="H283" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H283" s="2" t="inlineStr">
+      <c r="I283" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12183,20 +12795,21 @@
           <t>Shipbuilding and repair services provider in the UAE.</t>
         </is>
       </c>
-      <c r="C284" s="2" t="inlineStr"/>
-      <c r="D284" s="2" t="inlineStr"/>
-      <c r="E284" s="2" t="inlineStr"/>
-      <c r="F284" s="2" t="inlineStr">
+      <c r="C284" s="2" t="n"/>
+      <c r="D284" s="2" t="n"/>
+      <c r="E284" s="2" t="n"/>
+      <c r="F284" s="2" t="inlineStr"/>
+      <c r="G284" s="2" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr">
+      <c r="H284" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H284" s="2" t="inlineStr">
+      <c r="I284" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12224,20 +12837,21 @@
           <t>Cluster of steel and marine fabrication companies operating from Hamriyah Free Zone, Sharjah.</t>
         </is>
       </c>
-      <c r="C285" s="2" t="inlineStr"/>
-      <c r="D285" s="2" t="inlineStr"/>
-      <c r="E285" s="2" t="inlineStr"/>
-      <c r="F285" s="2" t="inlineStr">
+      <c r="C285" s="2" t="n"/>
+      <c r="D285" s="2" t="n"/>
+      <c r="E285" s="2" t="n"/>
+      <c r="F285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr">
         <is>
           <t>Sharjah, UAE</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr">
+      <c r="H285" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H285" s="2" t="inlineStr">
+      <c r="I285" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12265,20 +12879,21 @@
           <t>Engineering and industrial fabrication services provider in the UAE.</t>
         </is>
       </c>
-      <c r="C286" s="2" t="inlineStr"/>
-      <c r="D286" s="2" t="inlineStr"/>
-      <c r="E286" s="2" t="inlineStr"/>
-      <c r="F286" s="2" t="inlineStr">
+      <c r="C286" s="2" t="n"/>
+      <c r="D286" s="2" t="n"/>
+      <c r="E286" s="2" t="n"/>
+      <c r="F286" s="2" t="inlineStr"/>
+      <c r="G286" s="2" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr">
+      <c r="H286" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H286" s="2" t="inlineStr">
+      <c r="I286" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12306,20 +12921,21 @@
           <t>Ship repair and conversion yard (part of the Palumbo Group), a major Mediterranean drydock facility.</t>
         </is>
       </c>
-      <c r="C287" s="2" t="inlineStr"/>
-      <c r="D287" s="2" t="inlineStr"/>
-      <c r="E287" s="2" t="inlineStr"/>
-      <c r="F287" s="2" t="inlineStr">
+      <c r="C287" s="2" t="n"/>
+      <c r="D287" s="2" t="n"/>
+      <c r="E287" s="2" t="n"/>
+      <c r="F287" s="2" t="inlineStr"/>
+      <c r="G287" s="2" t="inlineStr">
         <is>
           <t>Marsa, Malta</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr">
+      <c r="H287" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H287" s="2" t="inlineStr">
+      <c r="I287" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12347,20 +12963,21 @@
           <t>Slovenia's registered shipbuilders are mostly small workshops; no single dominant marine structural fabricator was confirmed in this pass - flagged for a deeper follow-up search if needed.</t>
         </is>
       </c>
-      <c r="C288" s="2" t="inlineStr"/>
-      <c r="D288" s="2" t="inlineStr"/>
-      <c r="E288" s="2" t="inlineStr"/>
-      <c r="F288" s="2" t="inlineStr">
+      <c r="C288" s="2" t="n"/>
+      <c r="D288" s="2" t="n"/>
+      <c r="E288" s="2" t="n"/>
+      <c r="F288" s="2" t="inlineStr"/>
+      <c r="G288" s="2" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr">
+      <c r="H288" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H288" s="2" t="inlineStr">
+      <c r="I288" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12388,20 +13005,21 @@
           <t>Major wind turbine OEM with offshore turbine, tower and foundation-adjacent manufacturing across Europe.</t>
         </is>
       </c>
-      <c r="C289" s="2" t="inlineStr"/>
-      <c r="D289" s="2" t="inlineStr"/>
-      <c r="E289" s="2" t="inlineStr"/>
-      <c r="F289" s="2" t="inlineStr">
+      <c r="C289" s="2" t="n"/>
+      <c r="D289" s="2" t="n"/>
+      <c r="E289" s="2" t="n"/>
+      <c r="F289" s="2" t="inlineStr"/>
+      <c r="G289" s="2" t="inlineStr">
         <is>
           <t>Zamudio, Spain</t>
         </is>
       </c>
-      <c r="G289" s="2" t="inlineStr">
+      <c r="H289" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H289" s="2" t="inlineStr">
+      <c r="I289" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12429,20 +13047,21 @@
           <t>Global turbine OEM with European offshore wind manufacturing operations (Haliade-X).</t>
         </is>
       </c>
-      <c r="C290" s="2" t="inlineStr"/>
-      <c r="D290" s="2" t="inlineStr"/>
-      <c r="E290" s="2" t="inlineStr"/>
-      <c r="F290" s="2" t="inlineStr">
+      <c r="C290" s="2" t="n"/>
+      <c r="D290" s="2" t="n"/>
+      <c r="E290" s="2" t="n"/>
+      <c r="F290" s="2" t="inlineStr"/>
+      <c r="G290" s="2" t="inlineStr">
         <is>
           <t>Saint-Nazaire, France</t>
         </is>
       </c>
-      <c r="G290" s="2" t="inlineStr">
+      <c r="H290" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H290" s="2" t="inlineStr">
+      <c r="I290" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12467,27 +13086,28 @@
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Spanish manufacturer of steel and concrete wind towers, 22 facilities across nine countries.</t>
-        </is>
-      </c>
-      <c r="C291" s="2" t="inlineStr"/>
-      <c r="D291" s="2" t="inlineStr"/>
-      <c r="E291" s="2" t="inlineStr"/>
-      <c r="F291" s="2" t="inlineStr">
+          <t>Founded 2008 and devoted to manufacturing towers and flanges for the wind energy sector, with 25 factories across 9 countries (Spain, Argentina, Brazil, China, USA, India, Poland, South Africa, Turkey). Supplies onshore and offshore towers, plus hybrid steel/concrete towers up to 200 m through Windtechnic. Part of ACEK Corporation.</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="n"/>
+      <c r="D291" s="2" t="n"/>
+      <c r="E291" s="2" t="n"/>
+      <c r="F291" s="2" t="inlineStr"/>
+      <c r="G291" s="2" t="inlineStr">
         <is>
           <t>Bilbao, Spain</t>
         </is>
       </c>
-      <c r="G291" s="2" t="inlineStr">
+      <c r="H291" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H291" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GRI Renewable Industries while looking at companies working in offshore wind structural engineering, and your work as a Spanish manufacturer of steel and concrete wind towers, 22 facilities across nine countries caught my attention.
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GRI Renewable Industries while looking at companies working in marine and offshore engineering, and your work as a founded 2008 and devoted to manufacturing towers and flanges for the wind energy sector caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -12511,20 +13131,21 @@
           <t>Global wind tower manufacturer with a production facility in Portugal.</t>
         </is>
       </c>
-      <c r="C292" s="2" t="inlineStr"/>
-      <c r="D292" s="2" t="inlineStr"/>
-      <c r="E292" s="2" t="inlineStr"/>
-      <c r="F292" s="2" t="inlineStr">
+      <c r="C292" s="2" t="n"/>
+      <c r="D292" s="2" t="n"/>
+      <c r="E292" s="2" t="n"/>
+      <c r="F292" s="2" t="inlineStr"/>
+      <c r="G292" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="G292" s="2" t="inlineStr">
+      <c r="H292" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H292" s="2" t="inlineStr">
+      <c r="I292" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12552,20 +13173,21 @@
           <t>Rotor blade manufacturer for onshore/offshore wind turbines.</t>
         </is>
       </c>
-      <c r="C293" s="2" t="inlineStr"/>
-      <c r="D293" s="2" t="inlineStr"/>
-      <c r="E293" s="2" t="inlineStr"/>
-      <c r="F293" s="2" t="inlineStr">
+      <c r="C293" s="2" t="n"/>
+      <c r="D293" s="2" t="n"/>
+      <c r="E293" s="2" t="n"/>
+      <c r="F293" s="2" t="inlineStr"/>
+      <c r="G293" s="2" t="inlineStr">
         <is>
           <t>Kolding, Denmark</t>
         </is>
       </c>
-      <c r="G293" s="2" t="inlineStr">
+      <c r="H293" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H293" s="2" t="inlineStr">
+      <c r="I293" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12593,20 +13215,21 @@
           <t>Manufacturer of gearboxes/drivetrain components for wind turbines.</t>
         </is>
       </c>
-      <c r="C294" s="2" t="inlineStr"/>
-      <c r="D294" s="2" t="inlineStr"/>
-      <c r="E294" s="2" t="inlineStr"/>
-      <c r="F294" s="2" t="inlineStr">
+      <c r="C294" s="2" t="n"/>
+      <c r="D294" s="2" t="n"/>
+      <c r="E294" s="2" t="n"/>
+      <c r="F294" s="2" t="inlineStr"/>
+      <c r="G294" s="2" t="inlineStr">
         <is>
           <t>Bocholt, Germany</t>
         </is>
       </c>
-      <c r="G294" s="2" t="inlineStr">
+      <c r="H294" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H294" s="2" t="inlineStr">
+      <c r="I294" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12631,27 +13254,44 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Specialist offshore wind foundation design and structural engineering consultancy.</t>
-        </is>
-      </c>
-      <c r="C295" s="2" t="inlineStr"/>
-      <c r="D295" s="2" t="inlineStr"/>
-      <c r="E295" s="2" t="inlineStr"/>
+          <t>Engineering consultancy leading the industry in offshore wind monopile design, with extensive jacket expertise and a pivotal role in floating foundation solutions. Has delivered over 13 GW of detailed design projects worldwide, including Vineyard Wind 1 (first commercial-scale US offshore wind farm), Outer Dowsing and Caledonia. 1st Floor, Friars Yard, 160 Blackfriars Road, London SE1 8EZ.</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>Christian Thilsted</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>CTO and Co-Founder</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>info@woodthilsted.com</t>
+        </is>
+      </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
+          <t>+44 303 123 1113</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G295" s="2" t="inlineStr">
+      <c r="H295" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H295" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Wood Thilsted while looking at companies working in offshore wind structural engineering, and your work as a specialist offshore wind foundation design and structural engineering consultancy caught my attention.
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Christian,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Wood Thilsted while looking at companies working in offshore wind structural engineering, and your work as an engineering consultancy leading the industry in offshore wind monopile design caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -12672,27 +13312,28 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Major engineering consultancy with an offshore wind structural design practice.</t>
-        </is>
-      </c>
-      <c r="C296" s="2" t="inlineStr"/>
-      <c r="D296" s="2" t="inlineStr"/>
-      <c r="E296" s="2" t="inlineStr"/>
-      <c r="F296" s="2" t="inlineStr">
+          <t>Now trading as AtkinsRéalis, a world-leading professional services and project management company with roots dating to 1911, providing end-to-end engineering and design services to the offshore wind sector as the UK targets 50 GW of offshore wind by 2030.</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="n"/>
+      <c r="D296" s="2" t="n"/>
+      <c r="E296" s="2" t="n"/>
+      <c r="F296" s="2" t="inlineStr"/>
+      <c r="G296" s="2" t="inlineStr">
         <is>
           <t>Epsom, UK</t>
         </is>
       </c>
-      <c r="G296" s="2" t="inlineStr">
+      <c r="H296" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H296" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Atkins (Offshore Wind, part of SNC-Lavalin) while looking at companies working in offshore wind structural engineering, and your work as a major engineering consultancy with an offshore wind structural design practice caught my attention.
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Atkins (Offshore Wind, part of SNC-Lavalin) while looking at companies working in offshore wind structural engineering, and your work as a now trading as AtkinsRéalis caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -12716,20 +13357,21 @@
           <t>Offshore engineering consultancy supporting fixed and floating structure design.</t>
         </is>
       </c>
-      <c r="C297" s="2" t="inlineStr"/>
-      <c r="D297" s="2" t="inlineStr"/>
-      <c r="E297" s="2" t="inlineStr"/>
-      <c r="F297" s="2" t="inlineStr">
+      <c r="C297" s="2" t="n"/>
+      <c r="D297" s="2" t="n"/>
+      <c r="E297" s="2" t="n"/>
+      <c r="F297" s="2" t="inlineStr"/>
+      <c r="G297" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="G297" s="2" t="inlineStr">
+      <c r="H297" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H297" s="2" t="inlineStr">
+      <c r="I297" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12754,27 +13396,28 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Independent offshore/onshore wind engineering and consultancy firm.</t>
-        </is>
-      </c>
-      <c r="C298" s="2" t="inlineStr"/>
-      <c r="D298" s="2" t="inlineStr"/>
-      <c r="E298" s="2" t="inlineStr"/>
-      <c r="F298" s="2" t="inlineStr">
+          <t>Wind project consultancy covering the entire value chain from early planning and development through construction and maintenance, involved in more than 1,000 onshore and offshore wind projects in over 30 countries. Headquartered in Denmark with 10 global offices; now part of Ramboll's Wind Division. UK offices in Glasgow (133 Finnieston Street) and Bristol.</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="n"/>
+      <c r="D298" s="2" t="n"/>
+      <c r="E298" s="2" t="n"/>
+      <c r="F298" s="2" t="inlineStr"/>
+      <c r="G298" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G298" s="2" t="inlineStr">
+      <c r="H298" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H298" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across K2 Management while looking at companies working in offshore and structural engineering consultancy, and your work as an independent offshore/onshore wind engineering and consultancy firm caught my attention.
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across K2 Management while looking at companies working in offshore wind structural engineering, and your work as a wind project consultancy covering the entire value chain from early planning and development through construction caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -12798,20 +13441,21 @@
           <t>Renewable energy engineering and consultancy firm active in offshore wind.</t>
         </is>
       </c>
-      <c r="C299" s="2" t="inlineStr"/>
-      <c r="D299" s="2" t="inlineStr"/>
-      <c r="E299" s="2" t="inlineStr"/>
-      <c r="F299" s="2" t="inlineStr">
+      <c r="C299" s="2" t="n"/>
+      <c r="D299" s="2" t="n"/>
+      <c r="E299" s="2" t="n"/>
+      <c r="F299" s="2" t="inlineStr"/>
+      <c r="G299" s="2" t="inlineStr">
         <is>
           <t>Scotland, UK</t>
         </is>
       </c>
-      <c r="G299" s="2" t="inlineStr">
+      <c r="H299" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H299" s="2" t="inlineStr">
+      <c r="I299" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12836,27 +13480,36 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Independent engineering consultancy specialising in offshore wind foundation design (part of Xodus/Baker Hughes group).</t>
-        </is>
-      </c>
-      <c r="C300" s="2" t="inlineStr"/>
-      <c r="D300" s="2" t="inlineStr"/>
-      <c r="E300" s="2" t="inlineStr"/>
-      <c r="F300" s="2" t="inlineStr">
+          <t>Design and engineering arm of ABL Group providing concept design, FEED and detailed design for fixed-bottom and floating wind turbine foundations, offshore substation foundations, cables and cable routing, OSS topsides and landfall. Division leadership recruited from COWI; Michael Sienko serves as business development director. Part of ABL Group, which operates across 43 countries.</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Jan Erik Berg</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>Head of Offshore Wind Foundation Design (division launched 2025)</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="n"/>
+      <c r="F300" s="2" t="inlineStr"/>
+      <c r="G300" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="G300" s="2" t="inlineStr">
+      <c r="H300" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H300" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Longitude Engineering while looking at companies working in offshore wind structural engineering, and your work as an independent engineering consultancy specialising in offshore wind foundation design caught my attention.
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi Jan,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across Longitude Engineering while looking at companies working in offshore wind structural engineering, and your work as a design and engineering arm of ABL Group providing concept design caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -12880,20 +13533,21 @@
           <t>Dutch engineering firm specialising in temporary works and installation engineering for offshore projects.</t>
         </is>
       </c>
-      <c r="C301" s="2" t="inlineStr"/>
-      <c r="D301" s="2" t="inlineStr"/>
-      <c r="E301" s="2" t="inlineStr"/>
-      <c r="F301" s="2" t="inlineStr">
+      <c r="C301" s="2" t="n"/>
+      <c r="D301" s="2" t="n"/>
+      <c r="E301" s="2" t="n"/>
+      <c r="F301" s="2" t="inlineStr"/>
+      <c r="G301" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="G301" s="2" t="inlineStr">
+      <c r="H301" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H301" s="2" t="inlineStr">
+      <c r="I301" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12918,27 +13572,36 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Dutch designer of offshore vessels and jack-up rigs for wind installation and oil &amp; gas.</t>
-        </is>
-      </c>
-      <c r="C302" s="2" t="inlineStr"/>
-      <c r="D302" s="2" t="inlineStr"/>
-      <c r="E302" s="2" t="inlineStr"/>
+          <t>World market leader in mobile offshore unit designs and equipment, part of NOV. The vast majority of offshore wind jack-ups and installation vessels operating today were designed by GustoMSC. Provides offshore designs, equipment and engineering consultancy. Karel Doormanweg 35, Schiedam.</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="n"/>
+      <c r="D302" s="2" t="n"/>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>info.gustomsc@nov.com</t>
+        </is>
+      </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
+          <t>+31 (0)10 2883 000</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
           <t>Schiedam, Netherlands</t>
         </is>
       </c>
-      <c r="G302" s="2" t="inlineStr">
+      <c r="H302" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H302" s="2" t="inlineStr">
-        <is>
-          <t>Subject: Overflow FEA &amp; Structural Engineering Support
-Hi there,
-I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GustoMSC (part of NOV) while looking at companies working in heavy lift and marine transport engineering, and your work as a Dutch designer of offshore vessels and jack-up rigs for wind installation and oil &amp; gas caught my attention.
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>Subject: Overflow FEA &amp; Structural Engineering Support
+Hi there,
+I'm Ahmad, a structural and mechanical engineer based in Vancouver. I came across GustoMSC (part of NOV) while looking at companies working in offshore wind structural engineering, and your work as a world market leader in mobile offshore unit designs and equipment, part of NOV caught my attention.
 I have 8+ years of experience in structural analysis and FEA, primarily across heavy lift, transport, marine and industrial projects. My work has included lifting and rigging analysis, SPMT transport, sea fastening, lifting structures and detailed FEA using FEMAP/Simcenter Nastran.
 I recently started AH Structures to provide specialized engineering support to consultancies and project teams that need additional capacity, whether for overflow work or a self-contained analysis and verification scope.
 If your team ever has more analysis work than internal capacity, or a project requiring specialized FEA or heavy-lift/transport support, I'd be interested in discussing whether I could help.
@@ -12952,7 +13615,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/UAE_EU_Outreach AH Structures.xlsx
+++ b/UAE_EU_Outreach AH Structures.xlsx
@@ -10,7 +10,7 @@
     <sheet name="UAE &amp; EU Outreach" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'UAE &amp; EU Outreach'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'UAE &amp; EU Outreach'!$A$1:$J$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -49,6 +49,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
         <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,12 +84,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -451,18 +460,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I302"/>
+  <dimension ref="A1:J302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="100" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="100" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -493,20 +503,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Email Source</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Email Draft</t>
         </is>
@@ -534,22 +549,23 @@
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>+31 183 668822</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Gorinchem, Netherlands</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -580,22 +596,23 @@
       <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>+31 (0)71 579 9000</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Leiden, Netherlands</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -626,22 +643,23 @@
       <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>+31 (0)113 618 000</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Vlissingen, Netherlands</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -686,20 +704,25 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>+31 (0)10 427 92 00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Hans,
@@ -730,22 +753,23 @@
       <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>+31 475 385 777</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -777,17 +801,18 @@
       <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -819,17 +844,18 @@
       <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -861,17 +887,18 @@
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n"/>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -903,17 +930,18 @@
       <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Gorinchem, Netherlands</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -945,17 +973,18 @@
       <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Kinderdijk, Netherlands</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -987,17 +1016,18 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Vollenhove, Netherlands</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1034,20 +1064,25 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>+31 (0)88 070 22 22</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Schiedam, Netherlands</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1079,17 +1114,18 @@
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="n"/>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1121,17 +1157,18 @@
       <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="n"/>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1171,25 +1208,30 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>info@saltwater.nl</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+          <t>s.broekmeulen@saltwater.nl</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Directory listing - verify before sending</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>+31 78 205 15 00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Sander,
@@ -1226,20 +1268,25 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>+31 (0)10 442 57 27</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1271,17 +1318,18 @@
       <c r="D18" s="2" t="n"/>
       <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1313,17 +1361,18 @@
       <c r="D19" s="2" t="n"/>
       <c r="E19" s="2" t="n"/>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1366,18 +1415,23 @@
           <t>info@eew-group.com</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Erndtebrück / Rostock, Germany</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Frank,
@@ -1417,17 +1471,18 @@
       </c>
       <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Cuxhaven, Germany</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Bertram,
@@ -1459,17 +1514,18 @@
       <c r="D22" s="2" t="n"/>
       <c r="E22" s="2" t="n"/>
       <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Bremen, Germany</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1501,17 +1557,18 @@
       <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="n"/>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Bremen, Germany</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1543,17 +1600,18 @@
       <c r="D24" s="2" t="n"/>
       <c r="E24" s="2" t="n"/>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Papenburg, Germany</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1585,17 +1643,18 @@
       <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="n"/>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Bremen-Vegesack, Germany</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1627,17 +1686,18 @@
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Berne, Germany</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1669,17 +1729,18 @@
       <c r="D27" s="2" t="n"/>
       <c r="E27" s="2" t="n"/>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Wismar, Germany</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1711,17 +1772,18 @@
       <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="n"/>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Rostock-Warnemünde, Germany</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1753,17 +1815,18 @@
       <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Kiel, Germany</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1795,17 +1858,18 @@
       <c r="D30" s="2" t="n"/>
       <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Bremen, Germany</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="I30" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1837,17 +1901,18 @@
       <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="n"/>
       <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Hamburg, Germany</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1879,17 +1944,18 @@
       <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="n"/>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Bremerhaven, Germany</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1920,22 +1986,23 @@
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="n"/>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>+49 471 902628-10</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Bremerhaven, Germany</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -1967,17 +2034,18 @@
       <c r="D34" s="2" t="n"/>
       <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Bremerhaven, Germany</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2002,19 +2070,11 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>International steel contractor specialising in large-scale, highly complex steel structures across three business areas: wind and renewable energy, oil and gas, and infrastructure. HQ at Nørredybet 1, Aalborg Øst, with offices in Copenhagen and Poland and production at Lindø Industry Park, Funen.</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Anders Søe-Jensen</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>International steel contractor specialising in large-scale, highly complex steel structures across three business areas: wind and renewable energy, oil and gas, and infrastructure. HQ at Nørredybet 1, Aalborg Øst, with offices in Copenhagen and Poland and production at Lindø Industry Park, Funen. NOTE: Anders Soe-Jensen has stepped down as CEO; confirm the current chief executive before addressing outreach to a named person.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
           <t>office@bladt.dk</t>
@@ -2022,20 +2082,25 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
           <t>+45 9635 3700</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Aalborg, Denmark</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Anders,
@@ -2067,17 +2132,18 @@
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Søborg, Denmark</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2109,17 +2175,18 @@
       <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="n"/>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Odense, Denmark</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2151,17 +2218,18 @@
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="n"/>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Munkebo, Denmark</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2193,17 +2261,18 @@
       <c r="D39" s="2" t="n"/>
       <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Frederikshavn, Denmark</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="I39" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2240,20 +2309,25 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
           <t>+45 79 16 66 66</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Esbjerg, Denmark</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="I40" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2285,17 +2359,18 @@
       <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="n"/>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Esbjerg, Denmark</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2332,20 +2407,25 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
           <t>+45 9635 3700</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>Aalborg, Denmark</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2382,20 +2462,25 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
           <t>+45 70 70 71 50</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2432,20 +2517,25 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
           <t>+45 30 18 61 00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2477,17 +2567,18 @@
       <c r="D45" s="2" t="n"/>
       <c r="E45" s="2" t="n"/>
       <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Fredericia, Denmark</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2519,17 +2610,18 @@
       <c r="D46" s="2" t="n"/>
       <c r="E46" s="2" t="n"/>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Aarhus, Denmark</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2568,22 +2660,23 @@
         </is>
       </c>
       <c r="E47" s="2" t="n"/>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>+33 1 34 65 89 89</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Vélizy-Villacoublay, France</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Arnaud,
@@ -2626,18 +2719,23 @@
           <t>offshorewind@setec.com</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Company website / official listing</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Pascal,
@@ -2669,17 +2767,18 @@
       <c r="D49" s="2" t="n"/>
       <c r="E49" s="2" t="n"/>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Saint-Nazaire, France</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2711,17 +2810,18 @@
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="n"/>
       <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Brest, France</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2753,17 +2853,18 @@
       <c r="D51" s="2" t="n"/>
       <c r="E51" s="2" t="n"/>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2795,17 +2896,18 @@
       <c r="D52" s="2" t="n"/>
       <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2837,17 +2939,18 @@
       <c r="D53" s="2" t="n"/>
       <c r="E53" s="2" t="n"/>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2884,20 +2987,25 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
           <t>+39 02 44231</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Saint-Quentin-en-Yvelines, France</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="I54" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -2940,18 +3048,23 @@
           <t>info@haizeawindgroup.com</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Zierbena / Bilbao, Spain</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Borja,
@@ -2994,18 +3107,23 @@
           <t>comunicacion@windwaves.com</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Company website / official listing</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Ferrol, Spain</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="I56" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Diego,
@@ -3042,20 +3160,25 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
           <t>+34 985 560 090</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Avilés, Spain</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3087,17 +3210,18 @@
       <c r="D58" s="2" t="n"/>
       <c r="E58" s="2" t="n"/>
       <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Ferrol / Cádiz / Cartagena, Spain</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3129,17 +3253,18 @@
       <c r="D59" s="2" t="n"/>
       <c r="E59" s="2" t="n"/>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3174,18 +3299,23 @@
           <t>info@iberbluewind.com</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3217,17 +3347,18 @@
       <c r="D61" s="2" t="n"/>
       <c r="E61" s="2" t="n"/>
       <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="n"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3259,17 +3390,18 @@
       <c r="D62" s="2" t="n"/>
       <c r="E62" s="2" t="n"/>
       <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="n"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Spain</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3301,17 +3433,18 @@
       <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="n"/>
       <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="n"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Vigo, Spain</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3348,20 +3481,25 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
           <t>+39 035 0693111</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>Chiuduno, Italy</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3393,17 +3531,18 @@
       <c r="D65" s="2" t="n"/>
       <c r="E65" s="2" t="n"/>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>Ravenna, Italy</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3435,17 +3574,18 @@
       <c r="D66" s="2" t="n"/>
       <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="n"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Trieste, Italy</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3477,17 +3617,18 @@
       <c r="D67" s="2" t="n"/>
       <c r="E67" s="2" t="n"/>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="n"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>San Giorgio di Nogaro, Italy</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3519,17 +3660,18 @@
       <c r="D68" s="2" t="n"/>
       <c r="E68" s="2" t="n"/>
       <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="n"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3566,20 +3708,25 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
           <t>+39 02 44231</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>San Donato Milanese, Italy</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3611,17 +3758,18 @@
       <c r="D70" s="2" t="n"/>
       <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="n"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3653,17 +3801,18 @@
       <c r="D71" s="2" t="n"/>
       <c r="E71" s="2" t="n"/>
       <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>Italy</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3695,17 +3844,18 @@
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
       <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3737,17 +3887,18 @@
       <c r="D73" s="2" t="n"/>
       <c r="E73" s="2" t="n"/>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="n"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3779,17 +3930,18 @@
       <c r="D74" s="2" t="n"/>
       <c r="E74" s="2" t="n"/>
       <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3821,17 +3973,18 @@
       <c r="D75" s="2" t="n"/>
       <c r="E75" s="2" t="n"/>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="n"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3863,17 +4016,18 @@
       <c r="D76" s="2" t="n"/>
       <c r="E76" s="2" t="n"/>
       <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3905,17 +4059,18 @@
       <c r="D77" s="2" t="n"/>
       <c r="E77" s="2" t="n"/>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="n"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3947,17 +4102,18 @@
       <c r="D78" s="2" t="n"/>
       <c r="E78" s="2" t="n"/>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -3989,17 +4145,18 @@
       <c r="D79" s="2" t="n"/>
       <c r="E79" s="2" t="n"/>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="n"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4031,17 +4188,18 @@
       <c r="D80" s="2" t="n"/>
       <c r="E80" s="2" t="n"/>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4073,17 +4231,18 @@
       <c r="D81" s="2" t="n"/>
       <c r="E81" s="2" t="n"/>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4115,17 +4274,18 @@
       <c r="D82" s="2" t="n"/>
       <c r="E82" s="2" t="n"/>
       <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4157,17 +4317,18 @@
       <c r="D83" s="2" t="n"/>
       <c r="E83" s="2" t="n"/>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="n"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4199,17 +4360,18 @@
       <c r="D84" s="2" t="n"/>
       <c r="E84" s="2" t="n"/>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4241,17 +4403,18 @@
       <c r="D85" s="2" t="n"/>
       <c r="E85" s="2" t="n"/>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="n"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4283,17 +4446,18 @@
       <c r="D86" s="2" t="n"/>
       <c r="E86" s="2" t="n"/>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4325,17 +4489,18 @@
       <c r="D87" s="2" t="n"/>
       <c r="E87" s="2" t="n"/>
       <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Genoa, Italy</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr">
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4367,17 +4532,18 @@
       <c r="D88" s="2" t="n"/>
       <c r="E88" s="2" t="n"/>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4409,17 +4575,18 @@
       <c r="D89" s="2" t="n"/>
       <c r="E89" s="2" t="n"/>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4451,17 +4618,18 @@
       <c r="D90" s="2" t="n"/>
       <c r="E90" s="2" t="n"/>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="n"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Tuzla / Altınova, Turkey</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4493,17 +4661,18 @@
       <c r="D91" s="2" t="n"/>
       <c r="E91" s="2" t="n"/>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="n"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4535,17 +4704,18 @@
       <c r="D92" s="2" t="n"/>
       <c r="E92" s="2" t="n"/>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4577,17 +4747,18 @@
       <c r="D93" s="2" t="n"/>
       <c r="E93" s="2" t="n"/>
       <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="n"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4619,17 +4790,18 @@
       <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="n"/>
       <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Tuzla, Turkey</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
+      <c r="J94" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4660,22 +4832,23 @@
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n"/>
       <c r="E95" s="2" t="n"/>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>+44 1642 130060</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Teesside, UK</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
+      <c r="J95" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4712,20 +4885,25 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
           <t>+44 191 295 8700</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Wallsend, UK</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
+      <c r="J96" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4757,17 +4935,18 @@
       <c r="D97" s="2" t="n"/>
       <c r="E97" s="2" t="n"/>
       <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="n"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4804,20 +4983,25 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
           <t>+852 8198 0239</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4849,17 +5033,18 @@
       <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="n"/>
       <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="n"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4891,17 +5076,18 @@
       <c r="D100" s="2" t="n"/>
       <c r="E100" s="2" t="n"/>
       <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr">
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4933,17 +5119,18 @@
       <c r="D101" s="2" t="n"/>
       <c r="E101" s="2" t="n"/>
       <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="n"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Belfast, UK</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="J101" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -4975,17 +5162,18 @@
       <c r="D102" s="2" t="n"/>
       <c r="E102" s="2" t="n"/>
       <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="n"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Birkenhead, UK</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr">
+      <c r="J102" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5017,17 +5205,18 @@
       <c r="D103" s="2" t="n"/>
       <c r="E103" s="2" t="n"/>
       <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="n"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Falmouth / Tyne, UK</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5064,20 +5253,25 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
           <t>+44 1224 344300</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Sutton, Greater London, UK</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="J104" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5108,22 +5302,23 @@
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n"/>
       <c r="E105" s="2" t="n"/>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr"/>
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>+44 1603 227019</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
+      <c r="J105" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5163,25 +5358,30 @@
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>enquiry@orcina.com</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="inlineStr">
+          <t>david.heffernan@orcina.com</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>Directory listing - verify before sending</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>+44 (0)1229 584 742</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="J106" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi David,
@@ -5213,17 +5413,18 @@
       <c r="D107" s="2" t="n"/>
       <c r="E107" s="2" t="n"/>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="n"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
+      <c r="J107" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5255,17 +5456,18 @@
       <c r="D108" s="2" t="n"/>
       <c r="E108" s="2" t="n"/>
       <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="n"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="J108" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5297,17 +5499,18 @@
       <c r="D109" s="2" t="n"/>
       <c r="E109" s="2" t="n"/>
       <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="n"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Burntisland, UK</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
+      <c r="J109" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5339,17 +5542,18 @@
       <c r="D110" s="2" t="n"/>
       <c r="E110" s="2" t="n"/>
       <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Methil / Arnish, UK</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
+      <c r="J110" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5380,22 +5584,23 @@
       <c r="C111" s="2" t="n"/>
       <c r="D111" s="2" t="n"/>
       <c r="E111" s="2" t="n"/>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>+44 (0)1463 725460</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Inverness, UK</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
+      <c r="J111" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5427,17 +5632,18 @@
       <c r="D112" s="2" t="n"/>
       <c r="E112" s="2" t="n"/>
       <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Barry, UK</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
+      <c r="J112" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5469,17 +5675,18 @@
       <c r="D113" s="2" t="n"/>
       <c r="E113" s="2" t="n"/>
       <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Cardiff, UK</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
+      <c r="J113" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5511,17 +5718,18 @@
       <c r="D114" s="2" t="n"/>
       <c r="E114" s="2" t="n"/>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Caerphilly, UK</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
+      <c r="J114" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5553,17 +5761,18 @@
       <c r="D115" s="2" t="n"/>
       <c r="E115" s="2" t="n"/>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G115" s="2" t="n"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Newport, UK</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
+      <c r="J115" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5595,17 +5804,18 @@
       <c r="D116" s="2" t="n"/>
       <c r="E116" s="2" t="n"/>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G116" s="2" t="n"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Newport, UK</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr">
+      <c r="J116" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5637,17 +5847,18 @@
       <c r="D117" s="2" t="n"/>
       <c r="E117" s="2" t="n"/>
       <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="n"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>South Wales, UK</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr">
+      <c r="J117" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5679,17 +5890,18 @@
       <c r="D118" s="2" t="n"/>
       <c r="E118" s="2" t="n"/>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Ulsteinvik, Norway</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr">
+      <c r="J118" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5721,17 +5933,18 @@
       <c r="D119" s="2" t="n"/>
       <c r="E119" s="2" t="n"/>
       <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="n"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Mandal, Norway</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
+      <c r="J119" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5763,17 +5976,18 @@
       <c r="D120" s="2" t="n"/>
       <c r="E120" s="2" t="n"/>
       <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="n"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Sandefjord / Stavanger, Norway</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr">
+      <c r="J120" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5805,17 +6019,18 @@
       <c r="D121" s="2" t="n"/>
       <c r="E121" s="2" t="n"/>
       <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="n"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Florø, Norway</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
+      <c r="J121" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5847,17 +6062,18 @@
       <c r="D122" s="2" t="n"/>
       <c r="E122" s="2" t="n"/>
       <c r="F122" s="2" t="inlineStr"/>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="n"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr">
+      <c r="J122" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5889,17 +6105,18 @@
       <c r="D123" s="2" t="n"/>
       <c r="E123" s="2" t="n"/>
       <c r="F123" s="2" t="inlineStr"/>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="n"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Oslo, Norway</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
+      <c r="J123" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5931,17 +6148,18 @@
       <c r="D124" s="2" t="n"/>
       <c r="E124" s="2" t="n"/>
       <c r="F124" s="2" t="inlineStr"/>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="n"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Norway (near Oslo)</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr">
+      <c r="J124" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -5973,17 +6191,18 @@
       <c r="D125" s="2" t="n"/>
       <c r="E125" s="2" t="n"/>
       <c r="F125" s="2" t="inlineStr"/>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G125" s="2" t="n"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr">
+      <c r="J125" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6015,17 +6234,18 @@
       <c r="D126" s="2" t="n"/>
       <c r="E126" s="2" t="n"/>
       <c r="F126" s="2" t="inlineStr"/>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr">
+      <c r="J126" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6057,17 +6277,18 @@
       <c r="D127" s="2" t="n"/>
       <c r="E127" s="2" t="n"/>
       <c r="F127" s="2" t="inlineStr"/>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G127" s="2" t="n"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6099,17 +6320,18 @@
       <c r="D128" s="2" t="n"/>
       <c r="E128" s="2" t="n"/>
       <c r="F128" s="2" t="inlineStr"/>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G128" s="2" t="n"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Rogaland, Norway</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr">
+      <c r="J128" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6140,22 +6362,23 @@
       <c r="C129" s="2" t="n"/>
       <c r="D129" s="2" t="n"/>
       <c r="E129" s="2" t="n"/>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>+47 85 27 00 00</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Haugesund, Norway</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr">
+      <c r="J129" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6192,20 +6415,25 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
           <t>+32 3 8300 999</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Hoboken, Belgium</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr">
+      <c r="J130" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6236,22 +6464,23 @@
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n"/>
       <c r="E131" s="2" t="n"/>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>+32 3 740 44 50</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Hoboken, Belgium</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr">
+      <c r="J131" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6283,17 +6512,18 @@
       <c r="D132" s="2" t="n"/>
       <c r="E132" s="2" t="n"/>
       <c r="F132" s="2" t="inlineStr"/>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="n"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Hofstade-Aalst, Belgium</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
+      <c r="J132" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6325,17 +6555,18 @@
       <c r="D133" s="2" t="n"/>
       <c r="E133" s="2" t="n"/>
       <c r="F133" s="2" t="inlineStr"/>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="n"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Zwijndrecht, Belgium</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr">
+      <c r="J133" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6367,17 +6598,18 @@
       <c r="D134" s="2" t="n"/>
       <c r="E134" s="2" t="n"/>
       <c r="F134" s="2" t="inlineStr"/>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="n"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>Ghent, Belgium</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr">
+      <c r="J134" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6409,17 +6641,18 @@
       <c r="D135" s="2" t="n"/>
       <c r="E135" s="2" t="n"/>
       <c r="F135" s="2" t="inlineStr"/>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G135" s="2" t="n"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>Gdańsk, Poland</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr">
+      <c r="J135" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6456,20 +6689,25 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
           <t>+48 58 778 68 90</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>Gdynia, Poland</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr">
+      <c r="J136" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6501,17 +6739,18 @@
       <c r="D137" s="2" t="n"/>
       <c r="E137" s="2" t="n"/>
       <c r="F137" s="2" t="inlineStr"/>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G137" s="2" t="n"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>Szczecin, Poland</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr">
+      <c r="J137" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6543,17 +6782,18 @@
       <c r="D138" s="2" t="n"/>
       <c r="E138" s="2" t="n"/>
       <c r="F138" s="2" t="inlineStr"/>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G138" s="2" t="n"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
+      <c r="J138" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6585,17 +6825,18 @@
       <c r="D139" s="2" t="n"/>
       <c r="E139" s="2" t="n"/>
       <c r="F139" s="2" t="inlineStr"/>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G139" s="2" t="n"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>Gdańsk, Poland</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="J139" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6627,17 +6868,18 @@
       <c r="D140" s="2" t="n"/>
       <c r="E140" s="2" t="n"/>
       <c r="F140" s="2" t="inlineStr"/>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G140" s="2" t="n"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
+      <c r="J140" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6669,17 +6911,18 @@
       <c r="D141" s="2" t="n"/>
       <c r="E141" s="2" t="n"/>
       <c r="F141" s="2" t="inlineStr"/>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G141" s="2" t="n"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>Gdańsk, Poland</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr">
+      <c r="J141" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6711,17 +6954,18 @@
       <c r="D142" s="2" t="n"/>
       <c r="E142" s="2" t="n"/>
       <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G142" s="2" t="n"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr">
+      <c r="J142" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6753,17 +6997,18 @@
       <c r="D143" s="2" t="n"/>
       <c r="E143" s="2" t="n"/>
       <c r="F143" s="2" t="inlineStr"/>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G143" s="2" t="n"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr">
+      <c r="J143" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6795,17 +7040,18 @@
       <c r="D144" s="2" t="n"/>
       <c r="E144" s="2" t="n"/>
       <c r="F144" s="2" t="inlineStr"/>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G144" s="2" t="n"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Cork, Ireland</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
+      <c r="J144" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6837,17 +7083,18 @@
       <c r="D145" s="2" t="n"/>
       <c r="E145" s="2" t="n"/>
       <c r="F145" s="2" t="inlineStr"/>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G145" s="2" t="n"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>Singapore (not Ireland)</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
+      <c r="J145" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6879,17 +7126,18 @@
       <c r="D146" s="2" t="n"/>
       <c r="E146" s="2" t="n"/>
       <c r="F146" s="2" t="inlineStr"/>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G146" s="2" t="n"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
+      <c r="J146" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6921,17 +7169,18 @@
       <c r="D147" s="2" t="n"/>
       <c r="E147" s="2" t="n"/>
       <c r="F147" s="2" t="inlineStr"/>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G147" s="2" t="n"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
+      <c r="J147" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -6963,17 +7212,18 @@
       <c r="D148" s="2" t="n"/>
       <c r="E148" s="2" t="n"/>
       <c r="F148" s="2" t="inlineStr"/>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G148" s="2" t="n"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
+      <c r="J148" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7005,17 +7255,18 @@
       <c r="D149" s="2" t="n"/>
       <c r="E149" s="2" t="n"/>
       <c r="F149" s="2" t="inlineStr"/>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G149" s="2" t="n"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
+      <c r="J149" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7047,17 +7298,18 @@
       <c r="D150" s="2" t="n"/>
       <c r="E150" s="2" t="n"/>
       <c r="F150" s="2" t="inlineStr"/>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G150" s="2" t="n"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="J150" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7089,17 +7341,18 @@
       <c r="D151" s="2" t="n"/>
       <c r="E151" s="2" t="n"/>
       <c r="F151" s="2" t="inlineStr"/>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G151" s="2" t="n"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Malmö, Sweden</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr">
+      <c r="J151" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7131,17 +7384,18 @@
       <c r="D152" s="2" t="n"/>
       <c r="E152" s="2" t="n"/>
       <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G152" s="2" t="n"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Stockholm, Sweden</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
+      <c r="J152" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7173,17 +7427,18 @@
       <c r="D153" s="2" t="n"/>
       <c r="E153" s="2" t="n"/>
       <c r="F153" s="2" t="inlineStr"/>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G153" s="2" t="n"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
+      <c r="J153" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7215,17 +7470,18 @@
       <c r="D154" s="2" t="n"/>
       <c r="E154" s="2" t="n"/>
       <c r="F154" s="2" t="inlineStr"/>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G154" s="2" t="n"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
+      <c r="J154" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7257,17 +7513,18 @@
       <c r="D155" s="2" t="n"/>
       <c r="E155" s="2" t="n"/>
       <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G155" s="2" t="n"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
+      <c r="J155" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7299,17 +7556,18 @@
       <c r="D156" s="2" t="n"/>
       <c r="E156" s="2" t="n"/>
       <c r="F156" s="2" t="inlineStr"/>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G156" s="2" t="n"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>Gothenburg, Sweden</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr">
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7341,17 +7599,18 @@
       <c r="D157" s="2" t="n"/>
       <c r="E157" s="2" t="n"/>
       <c r="F157" s="2" t="inlineStr"/>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G157" s="2" t="n"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
+      <c r="J157" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7383,17 +7642,18 @@
       <c r="D158" s="2" t="n"/>
       <c r="E158" s="2" t="n"/>
       <c r="F158" s="2" t="inlineStr"/>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G158" s="2" t="n"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>Turku, Finland</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr">
+      <c r="J158" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7425,17 +7685,18 @@
       <c r="D159" s="2" t="n"/>
       <c r="E159" s="2" t="n"/>
       <c r="F159" s="2" t="inlineStr"/>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G159" s="2" t="n"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>Helsinki, Finland</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr">
+      <c r="J159" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7472,20 +7733,25 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
           <t>+358 10 323 6300</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>Helsinki, Finland</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr">
+      <c r="J160" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7517,17 +7783,18 @@
       <c r="D161" s="2" t="n"/>
       <c r="E161" s="2" t="n"/>
       <c r="F161" s="2" t="inlineStr"/>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G161" s="2" t="n"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr">
+      <c r="J161" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7559,17 +7826,18 @@
       <c r="D162" s="2" t="n"/>
       <c r="E162" s="2" t="n"/>
       <c r="F162" s="2" t="inlineStr"/>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G162" s="2" t="n"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr">
+      <c r="J162" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7601,17 +7869,18 @@
       <c r="D163" s="2" t="n"/>
       <c r="E163" s="2" t="n"/>
       <c r="F163" s="2" t="inlineStr"/>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G163" s="2" t="n"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr">
+      <c r="J163" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7643,17 +7912,18 @@
       <c r="D164" s="2" t="n"/>
       <c r="E164" s="2" t="n"/>
       <c r="F164" s="2" t="inlineStr"/>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G164" s="2" t="n"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>Setúbal, Portugal</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr">
+      <c r="J164" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7685,17 +7955,18 @@
       <c r="D165" s="2" t="n"/>
       <c r="E165" s="2" t="n"/>
       <c r="F165" s="2" t="inlineStr"/>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G165" s="2" t="n"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>Almada, Portugal</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr">
+      <c r="J165" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7727,17 +7998,18 @@
       <c r="D166" s="2" t="n"/>
       <c r="E166" s="2" t="n"/>
       <c r="F166" s="2" t="inlineStr"/>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G166" s="2" t="n"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>Viana do Castelo, Portugal</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr">
+      <c r="J166" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7769,17 +8041,18 @@
       <c r="D167" s="2" t="n"/>
       <c r="E167" s="2" t="n"/>
       <c r="F167" s="2" t="inlineStr"/>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G167" s="2" t="n"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>Viana do Castelo, Portugal</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr">
+      <c r="J167" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7811,17 +8084,18 @@
       <c r="D168" s="2" t="n"/>
       <c r="E168" s="2" t="n"/>
       <c r="F168" s="2" t="inlineStr"/>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G168" s="2" t="n"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>Lisbon, Portugal</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr">
+      <c r="J168" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7853,17 +8127,18 @@
       <c r="D169" s="2" t="n"/>
       <c r="E169" s="2" t="n"/>
       <c r="F169" s="2" t="inlineStr"/>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G169" s="2" t="n"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7895,17 +8170,18 @@
       <c r="D170" s="2" t="n"/>
       <c r="E170" s="2" t="n"/>
       <c r="F170" s="2" t="inlineStr"/>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G170" s="2" t="n"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr">
+      <c r="J170" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7937,17 +8213,18 @@
       <c r="D171" s="2" t="n"/>
       <c r="E171" s="2" t="n"/>
       <c r="F171" s="2" t="inlineStr"/>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G171" s="2" t="n"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>Águeda, Portugal</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr">
+      <c r="J171" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -7979,17 +8256,18 @@
       <c r="D172" s="2" t="n"/>
       <c r="E172" s="2" t="n"/>
       <c r="F172" s="2" t="inlineStr"/>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G172" s="2" t="n"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>Santo Tirso, Portugal</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr">
+      <c r="J172" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8021,17 +8299,18 @@
       <c r="D173" s="2" t="n"/>
       <c r="E173" s="2" t="n"/>
       <c r="F173" s="2" t="inlineStr"/>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G173" s="2" t="n"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>Ermoupolis, Greece</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr">
+      <c r="J173" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8063,17 +8342,18 @@
       <c r="D174" s="2" t="n"/>
       <c r="E174" s="2" t="n"/>
       <c r="F174" s="2" t="inlineStr"/>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G174" s="2" t="n"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>Skaramagas, Greece</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr">
+      <c r="J174" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8105,17 +8385,18 @@
       <c r="D175" s="2" t="n"/>
       <c r="E175" s="2" t="n"/>
       <c r="F175" s="2" t="inlineStr"/>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G175" s="2" t="n"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>Athens, Greece</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr">
+      <c r="J175" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8147,17 +8428,18 @@
       <c r="D176" s="2" t="n"/>
       <c r="E176" s="2" t="n"/>
       <c r="F176" s="2" t="inlineStr"/>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G176" s="2" t="n"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>Aulis, Evia, Greece</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr">
+      <c r="J176" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8189,17 +8471,18 @@
       <c r="D177" s="2" t="n"/>
       <c r="E177" s="2" t="n"/>
       <c r="F177" s="2" t="inlineStr"/>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G177" s="2" t="n"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>Koropi, Greece</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr">
+      <c r="J177" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8231,17 +8514,18 @@
       <c r="D178" s="2" t="n"/>
       <c r="E178" s="2" t="n"/>
       <c r="F178" s="2" t="inlineStr"/>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G178" s="2" t="n"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr">
+      <c r="J178" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8278,20 +8562,25 @@
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
           <t>+30 210 4095 000</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr">
+      <c r="J179" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8331,17 +8620,18 @@
       </c>
       <c r="E180" s="2" t="n"/>
       <c r="F180" s="2" t="inlineStr"/>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G180" s="2" t="n"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr">
+      <c r="J180" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Dimitris,
@@ -8373,17 +8663,18 @@
       <c r="D181" s="2" t="n"/>
       <c r="E181" s="2" t="n"/>
       <c r="F181" s="2" t="inlineStr"/>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G181" s="2" t="n"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>Rijeka, Croatia</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr">
+      <c r="J181" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8415,17 +8706,18 @@
       <c r="D182" s="2" t="n"/>
       <c r="E182" s="2" t="n"/>
       <c r="F182" s="2" t="inlineStr"/>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G182" s="2" t="n"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>Split, Croatia</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr">
+      <c r="J182" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8457,17 +8749,18 @@
       <c r="D183" s="2" t="n"/>
       <c r="E183" s="2" t="n"/>
       <c r="F183" s="2" t="inlineStr"/>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G183" s="2" t="n"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>Rijeka, Croatia</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8499,17 +8792,18 @@
       <c r="D184" s="2" t="n"/>
       <c r="E184" s="2" t="n"/>
       <c r="F184" s="2" t="inlineStr"/>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G184" s="2" t="n"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>Kraljevica, Croatia</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr">
+      <c r="J184" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8541,17 +8835,18 @@
       <c r="D185" s="2" t="n"/>
       <c r="E185" s="2" t="n"/>
       <c r="F185" s="2" t="inlineStr"/>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G185" s="2" t="n"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr">
+      <c r="J185" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8583,17 +8878,18 @@
       <c r="D186" s="2" t="n"/>
       <c r="E186" s="2" t="n"/>
       <c r="F186" s="2" t="inlineStr"/>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G186" s="2" t="n"/>
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr">
+      <c r="J186" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8630,20 +8926,25 @@
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
+          <t>Company website / official listing</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
           <t>+385 1 6504 269</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr">
+      <c r="J187" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8675,17 +8976,18 @@
       <c r="D188" s="2" t="n"/>
       <c r="E188" s="2" t="n"/>
       <c r="F188" s="2" t="inlineStr"/>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G188" s="2" t="n"/>
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>Galați, Romania</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="I188" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr">
+      <c r="J188" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8717,17 +9019,18 @@
       <c r="D189" s="2" t="n"/>
       <c r="E189" s="2" t="n"/>
       <c r="F189" s="2" t="inlineStr"/>
-      <c r="G189" s="2" t="inlineStr">
+      <c r="G189" s="2" t="n"/>
+      <c r="H189" s="2" t="inlineStr">
         <is>
           <t>Brăila, Romania</t>
         </is>
       </c>
-      <c r="H189" s="2" t="inlineStr">
+      <c r="I189" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I189" s="2" t="inlineStr">
+      <c r="J189" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8759,17 +9062,18 @@
       <c r="D190" s="2" t="n"/>
       <c r="E190" s="2" t="n"/>
       <c r="F190" s="2" t="inlineStr"/>
-      <c r="G190" s="2" t="inlineStr">
+      <c r="G190" s="2" t="n"/>
+      <c r="H190" s="2" t="inlineStr">
         <is>
           <t>Constanța, Romania</t>
         </is>
       </c>
-      <c r="H190" s="2" t="inlineStr">
+      <c r="I190" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I190" s="2" t="inlineStr">
+      <c r="J190" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8801,17 +9105,18 @@
       <c r="D191" s="2" t="n"/>
       <c r="E191" s="2" t="n"/>
       <c r="F191" s="2" t="inlineStr"/>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G191" s="2" t="n"/>
+      <c r="H191" s="2" t="inlineStr">
         <is>
           <t>Tulcea, Romania</t>
         </is>
       </c>
-      <c r="H191" s="2" t="inlineStr">
+      <c r="I191" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr">
+      <c r="J191" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8843,17 +9148,18 @@
       <c r="D192" s="2" t="n"/>
       <c r="E192" s="2" t="n"/>
       <c r="F192" s="2" t="inlineStr"/>
-      <c r="G192" s="2" t="inlineStr">
+      <c r="G192" s="2" t="n"/>
+      <c r="H192" s="2" t="inlineStr">
         <is>
           <t>Mangalia, Romania</t>
         </is>
       </c>
-      <c r="H192" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I192" s="2" t="inlineStr">
+      <c r="J192" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8884,22 +9190,23 @@
       <c r="C193" s="2" t="n"/>
       <c r="D193" s="2" t="n"/>
       <c r="E193" s="2" t="n"/>
-      <c r="F193" s="2" t="inlineStr">
+      <c r="F193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr">
         <is>
           <t>+40 (0)236 44 85 15</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
+      <c r="H193" s="2" t="inlineStr">
         <is>
           <t>Galați, Romania</t>
         </is>
       </c>
-      <c r="H193" s="2" t="inlineStr">
+      <c r="I193" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I193" s="2" t="inlineStr">
+      <c r="J193" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8931,17 +9238,18 @@
       <c r="D194" s="2" t="n"/>
       <c r="E194" s="2" t="n"/>
       <c r="F194" s="2" t="inlineStr"/>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G194" s="2" t="n"/>
+      <c r="H194" s="2" t="inlineStr">
         <is>
           <t>Constanța, Romania</t>
         </is>
       </c>
-      <c r="H194" s="2" t="inlineStr">
+      <c r="I194" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I194" s="2" t="inlineStr">
+      <c r="J194" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -8973,17 +9281,18 @@
       <c r="D195" s="2" t="n"/>
       <c r="E195" s="2" t="n"/>
       <c r="F195" s="2" t="inlineStr"/>
-      <c r="G195" s="2" t="inlineStr">
+      <c r="G195" s="2" t="n"/>
+      <c r="H195" s="2" t="inlineStr">
         <is>
           <t>Tallinn, Estonia</t>
         </is>
       </c>
-      <c r="H195" s="2" t="inlineStr">
+      <c r="I195" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I195" s="2" t="inlineStr">
+      <c r="J195" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9015,17 +9324,18 @@
       <c r="D196" s="2" t="n"/>
       <c r="E196" s="2" t="n"/>
       <c r="F196" s="2" t="inlineStr"/>
-      <c r="G196" s="2" t="inlineStr">
+      <c r="G196" s="2" t="n"/>
+      <c r="H196" s="2" t="inlineStr">
         <is>
           <t>Estonia</t>
         </is>
       </c>
-      <c r="H196" s="2" t="inlineStr">
+      <c r="I196" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I196" s="2" t="inlineStr">
+      <c r="J196" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9057,17 +9367,18 @@
       <c r="D197" s="2" t="n"/>
       <c r="E197" s="2" t="n"/>
       <c r="F197" s="2" t="inlineStr"/>
-      <c r="G197" s="2" t="inlineStr">
+      <c r="G197" s="2" t="n"/>
+      <c r="H197" s="2" t="inlineStr">
         <is>
           <t>Riga, Latvia</t>
         </is>
       </c>
-      <c r="H197" s="2" t="inlineStr">
+      <c r="I197" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I197" s="2" t="inlineStr">
+      <c r="J197" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9099,17 +9410,18 @@
       <c r="D198" s="2" t="n"/>
       <c r="E198" s="2" t="n"/>
       <c r="F198" s="2" t="inlineStr"/>
-      <c r="G198" s="2" t="inlineStr">
+      <c r="G198" s="2" t="n"/>
+      <c r="H198" s="2" t="inlineStr">
         <is>
           <t>Klaipėda, Lithuania</t>
         </is>
       </c>
-      <c r="H198" s="2" t="inlineStr">
+      <c r="I198" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I198" s="2" t="inlineStr">
+      <c r="J198" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9141,17 +9453,18 @@
       <c r="D199" s="2" t="n"/>
       <c r="E199" s="2" t="n"/>
       <c r="F199" s="2" t="inlineStr"/>
-      <c r="G199" s="2" t="inlineStr">
+      <c r="G199" s="2" t="n"/>
+      <c r="H199" s="2" t="inlineStr">
         <is>
           <t>Baltic region</t>
         </is>
       </c>
-      <c r="H199" s="2" t="inlineStr">
+      <c r="I199" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I199" s="2" t="inlineStr">
+      <c r="J199" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9183,17 +9496,18 @@
       <c r="D200" s="2" t="n"/>
       <c r="E200" s="2" t="n"/>
       <c r="F200" s="2" t="inlineStr"/>
-      <c r="G200" s="2" t="inlineStr">
+      <c r="G200" s="2" t="n"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>Burgas, Bulgaria</t>
         </is>
       </c>
-      <c r="H200" s="2" t="inlineStr">
+      <c r="I200" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I200" s="2" t="inlineStr">
+      <c r="J200" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9225,17 +9539,18 @@
       <c r="D201" s="2" t="n"/>
       <c r="E201" s="2" t="n"/>
       <c r="F201" s="2" t="inlineStr"/>
-      <c r="G201" s="2" t="inlineStr">
+      <c r="G201" s="2" t="n"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>Ruse, Bulgaria</t>
         </is>
       </c>
-      <c r="H201" s="2" t="inlineStr">
+      <c r="I201" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I201" s="2" t="inlineStr">
+      <c r="J201" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9267,17 +9582,18 @@
       <c r="D202" s="2" t="n"/>
       <c r="E202" s="2" t="n"/>
       <c r="F202" s="2" t="inlineStr"/>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G202" s="2" t="n"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>Sofia, Bulgaria</t>
         </is>
       </c>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="I202" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr">
+      <c r="J202" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9309,17 +9625,18 @@
       <c r="D203" s="2" t="n"/>
       <c r="E203" s="2" t="n"/>
       <c r="F203" s="2" t="inlineStr"/>
-      <c r="G203" s="2" t="inlineStr">
+      <c r="G203" s="2" t="n"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>Varna, Bulgaria</t>
         </is>
       </c>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I203" s="2" t="inlineStr">
+      <c r="J203" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9351,17 +9668,18 @@
       <c r="D204" s="2" t="n"/>
       <c r="E204" s="2" t="n"/>
       <c r="F204" s="2" t="inlineStr"/>
-      <c r="G204" s="2" t="inlineStr">
+      <c r="G204" s="2" t="n"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>Cyprus</t>
         </is>
       </c>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="I204" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I204" s="2" t="inlineStr">
+      <c r="J204" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9393,17 +9711,18 @@
       <c r="D205" s="2" t="n"/>
       <c r="E205" s="2" t="n"/>
       <c r="F205" s="2" t="inlineStr"/>
-      <c r="G205" s="2" t="inlineStr">
+      <c r="G205" s="2" t="n"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>Famagusta, Cyprus</t>
         </is>
       </c>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="I205" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I205" s="2" t="inlineStr">
+      <c r="J205" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9435,17 +9754,18 @@
       <c r="D206" s="2" t="n"/>
       <c r="E206" s="2" t="n"/>
       <c r="F206" s="2" t="inlineStr"/>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G206" s="2" t="n"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Courbevoie, France</t>
         </is>
       </c>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="I206" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I206" s="2" t="inlineStr">
+      <c r="J206" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9477,17 +9797,18 @@
       <c r="D207" s="2" t="n"/>
       <c r="E207" s="2" t="n"/>
       <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" s="2" t="inlineStr">
+      <c r="G207" s="2" t="n"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t>Greece</t>
         </is>
       </c>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="I207" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I207" s="2" t="inlineStr">
+      <c r="J207" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9519,17 +9840,18 @@
       <c r="D208" s="2" t="n"/>
       <c r="E208" s="2" t="n"/>
       <c r="F208" s="2" t="inlineStr"/>
-      <c r="G208" s="2" t="inlineStr">
+      <c r="G208" s="2" t="n"/>
+      <c r="H208" s="2" t="inlineStr">
         <is>
           <t>Mussafah, Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="I208" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I208" s="2" t="inlineStr">
+      <c r="J208" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9561,17 +9883,18 @@
       <c r="D209" s="2" t="n"/>
       <c r="E209" s="2" t="n"/>
       <c r="F209" s="2" t="inlineStr"/>
-      <c r="G209" s="2" t="inlineStr">
+      <c r="G209" s="2" t="n"/>
+      <c r="H209" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="I209" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I209" s="2" t="inlineStr">
+      <c r="J209" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9603,17 +9926,18 @@
       <c r="D210" s="2" t="n"/>
       <c r="E210" s="2" t="n"/>
       <c r="F210" s="2" t="inlineStr"/>
-      <c r="G210" s="2" t="inlineStr">
+      <c r="G210" s="2" t="n"/>
+      <c r="H210" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H210" s="2" t="inlineStr">
+      <c r="I210" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I210" s="2" t="inlineStr">
+      <c r="J210" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9645,17 +9969,18 @@
       <c r="D211" s="2" t="n"/>
       <c r="E211" s="2" t="n"/>
       <c r="F211" s="2" t="inlineStr"/>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="G211" s="2" t="n"/>
+      <c r="H211" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H211" s="2" t="inlineStr">
+      <c r="I211" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I211" s="2" t="inlineStr">
+      <c r="J211" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9687,17 +10012,18 @@
       <c r="D212" s="2" t="n"/>
       <c r="E212" s="2" t="n"/>
       <c r="F212" s="2" t="inlineStr"/>
-      <c r="G212" s="2" t="inlineStr">
+      <c r="G212" s="2" t="n"/>
+      <c r="H212" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H212" s="2" t="inlineStr">
+      <c r="I212" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I212" s="2" t="inlineStr">
+      <c r="J212" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9729,17 +10055,18 @@
       <c r="D213" s="2" t="n"/>
       <c r="E213" s="2" t="n"/>
       <c r="F213" s="2" t="inlineStr"/>
-      <c r="G213" s="2" t="inlineStr">
+      <c r="G213" s="2" t="n"/>
+      <c r="H213" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H213" s="2" t="inlineStr">
+      <c r="I213" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I213" s="2" t="inlineStr">
+      <c r="J213" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9771,17 +10098,18 @@
       <c r="D214" s="2" t="n"/>
       <c r="E214" s="2" t="n"/>
       <c r="F214" s="2" t="inlineStr"/>
-      <c r="G214" s="2" t="inlineStr">
+      <c r="G214" s="2" t="n"/>
+      <c r="H214" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H214" s="2" t="inlineStr">
+      <c r="I214" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I214" s="2" t="inlineStr">
+      <c r="J214" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9813,17 +10141,18 @@
       <c r="D215" s="2" t="n"/>
       <c r="E215" s="2" t="n"/>
       <c r="F215" s="2" t="inlineStr"/>
-      <c r="G215" s="2" t="inlineStr">
+      <c r="G215" s="2" t="n"/>
+      <c r="H215" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H215" s="2" t="inlineStr">
+      <c r="I215" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I215" s="2" t="inlineStr">
+      <c r="J215" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9855,17 +10184,18 @@
       <c r="D216" s="2" t="n"/>
       <c r="E216" s="2" t="n"/>
       <c r="F216" s="2" t="inlineStr"/>
-      <c r="G216" s="2" t="inlineStr">
+      <c r="G216" s="2" t="n"/>
+      <c r="H216" s="2" t="inlineStr">
         <is>
           <t>Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H216" s="2" t="inlineStr">
+      <c r="I216" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I216" s="2" t="inlineStr">
+      <c r="J216" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -9908,18 +10238,23 @@
           <t>info@aptglobalmarine.com</t>
         </is>
       </c>
-      <c r="F217" s="2" t="inlineStr"/>
-      <c r="G217" s="2" t="inlineStr">
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="n"/>
+      <c r="H217" s="2" t="inlineStr">
         <is>
           <t>Dubai / Ras Al Khaimah, UAE</t>
         </is>
       </c>
-      <c r="H217" s="2" t="inlineStr">
+      <c r="I217" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I217" s="2" t="inlineStr">
+      <c r="J217" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Beau,
@@ -9962,18 +10297,23 @@
           <t>Cameron@grandweld.com; marawan.f@grandweld.com</t>
         </is>
       </c>
-      <c r="F218" s="2" t="inlineStr"/>
-      <c r="G218" s="2" t="inlineStr">
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Company website / official listing</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="n"/>
+      <c r="H218" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H218" s="2" t="inlineStr">
+      <c r="I218" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I218" s="2" t="inlineStr">
+      <c r="J218" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Cameron,
@@ -10005,17 +10345,18 @@
       <c r="D219" s="2" t="n"/>
       <c r="E219" s="2" t="n"/>
       <c r="F219" s="2" t="inlineStr"/>
-      <c r="G219" s="2" t="inlineStr">
+      <c r="G219" s="2" t="n"/>
+      <c r="H219" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="H219" s="2" t="inlineStr">
+      <c r="I219" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I219" s="2" t="inlineStr">
+      <c r="J219" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10047,17 +10388,18 @@
       <c r="D220" s="2" t="n"/>
       <c r="E220" s="2" t="n"/>
       <c r="F220" s="2" t="inlineStr"/>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="G220" s="2" t="n"/>
+      <c r="H220" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="H220" s="2" t="inlineStr">
+      <c r="I220" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I220" s="2" t="inlineStr">
+      <c r="J220" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10089,17 +10431,18 @@
       <c r="D221" s="2" t="n"/>
       <c r="E221" s="2" t="n"/>
       <c r="F221" s="2" t="inlineStr"/>
-      <c r="G221" s="2" t="inlineStr">
+      <c r="G221" s="2" t="n"/>
+      <c r="H221" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="H221" s="2" t="inlineStr">
+      <c r="I221" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I221" s="2" t="inlineStr">
+      <c r="J221" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10131,17 +10474,18 @@
       <c r="D222" s="2" t="n"/>
       <c r="E222" s="2" t="n"/>
       <c r="F222" s="2" t="inlineStr"/>
-      <c r="G222" s="2" t="inlineStr">
+      <c r="G222" s="2" t="n"/>
+      <c r="H222" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="H222" s="2" t="inlineStr">
+      <c r="I222" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I222" s="2" t="inlineStr">
+      <c r="J222" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10173,17 +10517,18 @@
       <c r="D223" s="2" t="n"/>
       <c r="E223" s="2" t="n"/>
       <c r="F223" s="2" t="inlineStr"/>
-      <c r="G223" s="2" t="inlineStr">
+      <c r="G223" s="2" t="n"/>
+      <c r="H223" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="H223" s="2" t="inlineStr">
+      <c r="I223" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I223" s="2" t="inlineStr">
+      <c r="J223" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10215,17 +10560,18 @@
       <c r="D224" s="2" t="n"/>
       <c r="E224" s="2" t="n"/>
       <c r="F224" s="2" t="inlineStr"/>
-      <c r="G224" s="2" t="inlineStr">
+      <c r="G224" s="2" t="n"/>
+      <c r="H224" s="2" t="inlineStr">
         <is>
           <t>Jebel Ali, Dubai, UAE</t>
         </is>
       </c>
-      <c r="H224" s="2" t="inlineStr">
+      <c r="I224" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I224" s="2" t="inlineStr">
+      <c r="J224" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10257,17 +10603,18 @@
       <c r="D225" s="2" t="n"/>
       <c r="E225" s="2" t="n"/>
       <c r="F225" s="2" t="inlineStr"/>
-      <c r="G225" s="2" t="inlineStr">
+      <c r="G225" s="2" t="n"/>
+      <c r="H225" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H225" s="2" t="inlineStr">
+      <c r="I225" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I225" s="2" t="inlineStr">
+      <c r="J225" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10299,17 +10646,18 @@
       <c r="D226" s="2" t="n"/>
       <c r="E226" s="2" t="n"/>
       <c r="F226" s="2" t="inlineStr"/>
-      <c r="G226" s="2" t="inlineStr">
+      <c r="G226" s="2" t="n"/>
+      <c r="H226" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H226" s="2" t="inlineStr">
+      <c r="I226" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I226" s="2" t="inlineStr">
+      <c r="J226" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10344,18 +10692,23 @@
           <t>sales@albwardydamen.com</t>
         </is>
       </c>
-      <c r="F227" s="2" t="inlineStr"/>
-      <c r="G227" s="2" t="inlineStr">
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="n"/>
+      <c r="H227" s="2" t="inlineStr">
         <is>
           <t>Dubai / Sharjah / Fujairah, UAE</t>
         </is>
       </c>
-      <c r="H227" s="2" t="inlineStr">
+      <c r="I227" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I227" s="2" t="inlineStr">
+      <c r="J227" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10387,17 +10740,18 @@
       <c r="D228" s="2" t="n"/>
       <c r="E228" s="2" t="n"/>
       <c r="F228" s="2" t="inlineStr"/>
-      <c r="G228" s="2" t="inlineStr">
+      <c r="G228" s="2" t="n"/>
+      <c r="H228" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H228" s="2" t="inlineStr">
+      <c r="I228" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I228" s="2" t="inlineStr">
+      <c r="J228" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10429,17 +10783,18 @@
       <c r="D229" s="2" t="n"/>
       <c r="E229" s="2" t="n"/>
       <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" s="2" t="inlineStr">
+      <c r="G229" s="2" t="n"/>
+      <c r="H229" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H229" s="2" t="inlineStr">
+      <c r="I229" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I229" s="2" t="inlineStr">
+      <c r="J229" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10471,17 +10826,18 @@
       <c r="D230" s="2" t="n"/>
       <c r="E230" s="2" t="n"/>
       <c r="F230" s="2" t="inlineStr"/>
-      <c r="G230" s="2" t="inlineStr">
+      <c r="G230" s="2" t="n"/>
+      <c r="H230" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H230" s="2" t="inlineStr">
+      <c r="I230" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I230" s="2" t="inlineStr">
+      <c r="J230" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10513,17 +10869,18 @@
       <c r="D231" s="2" t="n"/>
       <c r="E231" s="2" t="n"/>
       <c r="F231" s="2" t="inlineStr"/>
-      <c r="G231" s="2" t="inlineStr">
+      <c r="G231" s="2" t="n"/>
+      <c r="H231" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H231" s="2" t="inlineStr">
+      <c r="I231" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I231" s="2" t="inlineStr">
+      <c r="J231" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10555,17 +10912,18 @@
       <c r="D232" s="2" t="n"/>
       <c r="E232" s="2" t="n"/>
       <c r="F232" s="2" t="inlineStr"/>
-      <c r="G232" s="2" t="inlineStr">
+      <c r="G232" s="2" t="n"/>
+      <c r="H232" s="2" t="inlineStr">
         <is>
           <t>Ajman / Dubai, UAE</t>
         </is>
       </c>
-      <c r="H232" s="2" t="inlineStr">
+      <c r="I232" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I232" s="2" t="inlineStr">
+      <c r="J232" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10597,17 +10955,18 @@
       <c r="D233" s="2" t="n"/>
       <c r="E233" s="2" t="n"/>
       <c r="F233" s="2" t="inlineStr"/>
-      <c r="G233" s="2" t="inlineStr">
+      <c r="G233" s="2" t="n"/>
+      <c r="H233" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="I233" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I233" s="2" t="inlineStr">
+      <c r="J233" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10639,17 +10998,18 @@
       <c r="D234" s="2" t="n"/>
       <c r="E234" s="2" t="n"/>
       <c r="F234" s="2" t="inlineStr"/>
-      <c r="G234" s="2" t="inlineStr">
+      <c r="G234" s="2" t="n"/>
+      <c r="H234" s="2" t="inlineStr">
         <is>
           <t>Sharjah / Dubai / Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="I234" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I234" s="2" t="inlineStr">
+      <c r="J234" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10681,17 +11041,18 @@
       <c r="D235" s="2" t="n"/>
       <c r="E235" s="2" t="n"/>
       <c r="F235" s="2" t="inlineStr"/>
-      <c r="G235" s="2" t="inlineStr">
+      <c r="G235" s="2" t="n"/>
+      <c r="H235" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="I235" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I235" s="2" t="inlineStr">
+      <c r="J235" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10723,17 +11084,18 @@
       <c r="D236" s="2" t="n"/>
       <c r="E236" s="2" t="n"/>
       <c r="F236" s="2" t="inlineStr"/>
-      <c r="G236" s="2" t="inlineStr">
+      <c r="G236" s="2" t="n"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="I236" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I236" s="2" t="inlineStr">
+      <c r="J236" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10765,17 +11127,18 @@
       <c r="D237" s="2" t="n"/>
       <c r="E237" s="2" t="n"/>
       <c r="F237" s="2" t="inlineStr"/>
-      <c r="G237" s="2" t="inlineStr">
+      <c r="G237" s="2" t="n"/>
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="I237" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I237" s="2" t="inlineStr">
+      <c r="J237" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10807,17 +11170,18 @@
       <c r="D238" s="2" t="n"/>
       <c r="E238" s="2" t="n"/>
       <c r="F238" s="2" t="inlineStr"/>
-      <c r="G238" s="2" t="inlineStr">
+      <c r="G238" s="2" t="n"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>Sharjah, UAE</t>
         </is>
       </c>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="I238" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I238" s="2" t="inlineStr">
+      <c r="J238" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10849,17 +11213,18 @@
       <c r="D239" s="2" t="n"/>
       <c r="E239" s="2" t="n"/>
       <c r="F239" s="2" t="inlineStr"/>
-      <c r="G239" s="2" t="inlineStr">
+      <c r="G239" s="2" t="n"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>Ras Al Khaimah, UAE</t>
         </is>
       </c>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="I239" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I239" s="2" t="inlineStr">
+      <c r="J239" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10891,17 +11256,18 @@
       <c r="D240" s="2" t="n"/>
       <c r="E240" s="2" t="n"/>
       <c r="F240" s="2" t="inlineStr"/>
-      <c r="G240" s="2" t="inlineStr">
+      <c r="G240" s="2" t="n"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>Ras Al Khaimah, UAE</t>
         </is>
       </c>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="I240" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I240" s="2" t="inlineStr">
+      <c r="J240" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10933,17 +11299,18 @@
       <c r="D241" s="2" t="n"/>
       <c r="E241" s="2" t="n"/>
       <c r="F241" s="2" t="inlineStr"/>
-      <c r="G241" s="2" t="inlineStr">
+      <c r="G241" s="2" t="n"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>Sharjah, UAE</t>
         </is>
       </c>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="I241" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I241" s="2" t="inlineStr">
+      <c r="J241" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -10975,17 +11342,18 @@
       <c r="D242" s="2" t="n"/>
       <c r="E242" s="2" t="n"/>
       <c r="F242" s="2" t="inlineStr"/>
-      <c r="G242" s="2" t="inlineStr">
+      <c r="G242" s="2" t="n"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>Sharjah, UAE</t>
         </is>
       </c>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="I242" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I242" s="2" t="inlineStr">
+      <c r="J242" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11017,17 +11385,18 @@
       <c r="D243" s="2" t="n"/>
       <c r="E243" s="2" t="n"/>
       <c r="F243" s="2" t="inlineStr"/>
-      <c r="G243" s="2" t="inlineStr">
+      <c r="G243" s="2" t="n"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>Fujairah, UAE</t>
         </is>
       </c>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="I243" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I243" s="2" t="inlineStr">
+      <c r="J243" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11059,17 +11428,18 @@
       <c r="D244" s="2" t="n"/>
       <c r="E244" s="2" t="n"/>
       <c r="F244" s="2" t="inlineStr"/>
-      <c r="G244" s="2" t="inlineStr">
+      <c r="G244" s="2" t="n"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t>Dubai / Fujairah / Abu Dhabi, UAE</t>
         </is>
       </c>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="I244" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I244" s="2" t="inlineStr">
+      <c r="J244" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11101,17 +11471,18 @@
       <c r="D245" s="2" t="n"/>
       <c r="E245" s="2" t="n"/>
       <c r="F245" s="2" t="inlineStr"/>
-      <c r="G245" s="2" t="inlineStr">
+      <c r="G245" s="2" t="n"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>Ajman / Umm Al Quwain, UAE</t>
         </is>
       </c>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="I245" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I245" s="2" t="inlineStr">
+      <c r="J245" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11148,20 +11519,25 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
           <t>+44 (0)20 8943 5544</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr">
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="I246" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I246" s="2" t="inlineStr">
+      <c r="J246" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11204,18 +11580,23 @@
           <t>raya.peterson@ramboll.com</t>
         </is>
       </c>
-      <c r="F247" s="2" t="inlineStr"/>
-      <c r="G247" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Company website / official listing</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="n"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H247" s="2" t="inlineStr">
+      <c r="I247" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I247" s="2" t="inlineStr">
+      <c r="J247" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Raya,
@@ -11252,20 +11633,25 @@
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
           <t>+44 1224 628300</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr">
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>Aberdeen, UK</t>
         </is>
       </c>
-      <c r="H248" s="2" t="inlineStr">
+      <c r="I248" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I248" s="2" t="inlineStr">
+      <c r="J248" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11297,17 +11683,18 @@
       <c r="D249" s="2" t="n"/>
       <c r="E249" s="2" t="n"/>
       <c r="F249" s="2" t="inlineStr"/>
-      <c r="G249" s="2" t="inlineStr">
+      <c r="G249" s="2" t="n"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="H249" s="2" t="inlineStr">
+      <c r="I249" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I249" s="2" t="inlineStr">
+      <c r="J249" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11339,17 +11726,18 @@
       <c r="D250" s="2" t="n"/>
       <c r="E250" s="2" t="n"/>
       <c r="F250" s="2" t="inlineStr"/>
-      <c r="G250" s="2" t="inlineStr">
+      <c r="G250" s="2" t="n"/>
+      <c r="H250" s="2" t="inlineStr">
         <is>
           <t>Aberdeen, UK</t>
         </is>
       </c>
-      <c r="H250" s="2" t="inlineStr">
+      <c r="I250" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I250" s="2" t="inlineStr">
+      <c r="J250" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11381,17 +11769,18 @@
       <c r="D251" s="2" t="n"/>
       <c r="E251" s="2" t="n"/>
       <c r="F251" s="2" t="inlineStr"/>
-      <c r="G251" s="2" t="inlineStr">
+      <c r="G251" s="2" t="n"/>
+      <c r="H251" s="2" t="inlineStr">
         <is>
           <t>Stavanger, Norway</t>
         </is>
       </c>
-      <c r="H251" s="2" t="inlineStr">
+      <c r="I251" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I251" s="2" t="inlineStr">
+      <c r="J251" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11428,20 +11817,25 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
           <t>+44 (0)1493 845100</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
+      <c r="H252" s="2" t="inlineStr">
         <is>
           <t>Aberdeen, UK</t>
         </is>
       </c>
-      <c r="H252" s="2" t="inlineStr">
+      <c r="I252" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I252" s="2" t="inlineStr">
+      <c r="J252" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11473,17 +11867,18 @@
       <c r="D253" s="2" t="n"/>
       <c r="E253" s="2" t="n"/>
       <c r="F253" s="2" t="inlineStr"/>
-      <c r="G253" s="2" t="inlineStr">
+      <c r="G253" s="2" t="n"/>
+      <c r="H253" s="2" t="inlineStr">
         <is>
           <t>Hartlepool, UK</t>
         </is>
       </c>
-      <c r="H253" s="2" t="inlineStr">
+      <c r="I253" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I253" s="2" t="inlineStr">
+      <c r="J253" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11520,20 +11915,25 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
           <t>+44 345 262 9940</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
+      <c r="H254" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="H254" s="2" t="inlineStr">
+      <c r="I254" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I254" s="2" t="inlineStr">
+      <c r="J254" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11565,17 +11965,18 @@
       <c r="D255" s="2" t="n"/>
       <c r="E255" s="2" t="n"/>
       <c r="F255" s="2" t="inlineStr"/>
-      <c r="G255" s="2" t="inlineStr">
+      <c r="G255" s="2" t="n"/>
+      <c r="H255" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H255" s="2" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I255" s="2" t="inlineStr">
+      <c r="J255" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11607,17 +12008,18 @@
       <c r="D256" s="2" t="n"/>
       <c r="E256" s="2" t="n"/>
       <c r="F256" s="2" t="inlineStr"/>
-      <c r="G256" s="2" t="inlineStr">
+      <c r="G256" s="2" t="n"/>
+      <c r="H256" s="2" t="inlineStr">
         <is>
           <t>Oslo, Norway</t>
         </is>
       </c>
-      <c r="H256" s="2" t="inlineStr">
+      <c r="I256" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I256" s="2" t="inlineStr">
+      <c r="J256" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11649,17 +12051,18 @@
       <c r="D257" s="2" t="n"/>
       <c r="E257" s="2" t="n"/>
       <c r="F257" s="2" t="inlineStr"/>
-      <c r="G257" s="2" t="inlineStr">
+      <c r="G257" s="2" t="n"/>
+      <c r="H257" s="2" t="inlineStr">
         <is>
           <t>Oslo, Norway</t>
         </is>
       </c>
-      <c r="H257" s="2" t="inlineStr">
+      <c r="I257" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I257" s="2" t="inlineStr">
+      <c r="J257" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11691,17 +12094,18 @@
       <c r="D258" s="2" t="n"/>
       <c r="E258" s="2" t="n"/>
       <c r="F258" s="2" t="inlineStr"/>
-      <c r="G258" s="2" t="inlineStr">
+      <c r="G258" s="2" t="n"/>
+      <c r="H258" s="2" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H258" s="2" t="inlineStr">
+      <c r="I258" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I258" s="2" t="inlineStr">
+      <c r="J258" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11738,20 +12142,25 @@
       </c>
       <c r="F259" s="2" t="inlineStr">
         <is>
+          <t>Company website / official listing</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
           <t>+47 6757 9900</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr">
+      <c r="H259" s="2" t="inlineStr">
         <is>
           <t>Høvik, Norway</t>
         </is>
       </c>
-      <c r="H259" s="2" t="inlineStr">
+      <c r="I259" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I259" s="2" t="inlineStr">
+      <c r="J259" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11783,17 +12192,18 @@
       <c r="D260" s="2" t="n"/>
       <c r="E260" s="2" t="n"/>
       <c r="F260" s="2" t="inlineStr"/>
-      <c r="G260" s="2" t="inlineStr">
+      <c r="G260" s="2" t="n"/>
+      <c r="H260" s="2" t="inlineStr">
         <is>
           <t>Trondheim, Norway</t>
         </is>
       </c>
-      <c r="H260" s="2" t="inlineStr">
+      <c r="I260" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I260" s="2" t="inlineStr">
+      <c r="J260" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11825,17 +12235,18 @@
       <c r="D261" s="2" t="n"/>
       <c r="E261" s="2" t="n"/>
       <c r="F261" s="2" t="inlineStr"/>
-      <c r="G261" s="2" t="inlineStr">
+      <c r="G261" s="2" t="n"/>
+      <c r="H261" s="2" t="inlineStr">
         <is>
           <t>Oslo, Norway</t>
         </is>
       </c>
-      <c r="H261" s="2" t="inlineStr">
+      <c r="I261" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I261" s="2" t="inlineStr">
+      <c r="J261" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11867,17 +12278,18 @@
       <c r="D262" s="2" t="n"/>
       <c r="E262" s="2" t="n"/>
       <c r="F262" s="2" t="inlineStr"/>
-      <c r="G262" s="2" t="inlineStr">
+      <c r="G262" s="2" t="n"/>
+      <c r="H262" s="2" t="inlineStr">
         <is>
           <t>Fredericia, Denmark</t>
         </is>
       </c>
-      <c r="H262" s="2" t="inlineStr">
+      <c r="I262" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I262" s="2" t="inlineStr">
+      <c r="J262" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11909,17 +12321,18 @@
       <c r="D263" s="2" t="n"/>
       <c r="E263" s="2" t="n"/>
       <c r="F263" s="2" t="inlineStr"/>
-      <c r="G263" s="2" t="inlineStr">
+      <c r="G263" s="2" t="n"/>
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>Hamburg, Germany</t>
         </is>
       </c>
-      <c r="H263" s="2" t="inlineStr">
+      <c r="I263" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I263" s="2" t="inlineStr">
+      <c r="J263" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11951,17 +12364,18 @@
       <c r="D264" s="2" t="n"/>
       <c r="E264" s="2" t="n"/>
       <c r="F264" s="2" t="inlineStr"/>
-      <c r="G264" s="2" t="inlineStr">
+      <c r="G264" s="2" t="n"/>
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>Stockholm, Sweden</t>
         </is>
       </c>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="I264" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I264" s="2" t="inlineStr">
+      <c r="J264" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -11993,17 +12407,18 @@
       <c r="D265" s="2" t="n"/>
       <c r="E265" s="2" t="n"/>
       <c r="F265" s="2" t="inlineStr"/>
-      <c r="G265" s="2" t="inlineStr">
+      <c r="G265" s="2" t="n"/>
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>Bilbao, Spain</t>
         </is>
       </c>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="I265" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I265" s="2" t="inlineStr">
+      <c r="J265" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12035,17 +12450,18 @@
       <c r="D266" s="2" t="n"/>
       <c r="E266" s="2" t="n"/>
       <c r="F266" s="2" t="inlineStr"/>
-      <c r="G266" s="2" t="inlineStr">
+      <c r="G266" s="2" t="n"/>
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="H266" s="2" t="inlineStr">
+      <c r="I266" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I266" s="2" t="inlineStr">
+      <c r="J266" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12077,17 +12493,18 @@
       <c r="D267" s="2" t="n"/>
       <c r="E267" s="2" t="n"/>
       <c r="F267" s="2" t="inlineStr"/>
-      <c r="G267" s="2" t="inlineStr">
+      <c r="G267" s="2" t="n"/>
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>Glasgow, UK</t>
         </is>
       </c>
-      <c r="H267" s="2" t="inlineStr">
+      <c r="I267" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I267" s="2" t="inlineStr">
+      <c r="J267" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12119,17 +12536,18 @@
       <c r="D268" s="2" t="n"/>
       <c r="E268" s="2" t="n"/>
       <c r="F268" s="2" t="inlineStr"/>
-      <c r="G268" s="2" t="inlineStr">
+      <c r="G268" s="2" t="n"/>
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>Glasgow, UK</t>
         </is>
       </c>
-      <c r="H268" s="2" t="inlineStr">
+      <c r="I268" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I268" s="2" t="inlineStr">
+      <c r="J268" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12161,17 +12579,18 @@
       <c r="D269" s="2" t="n"/>
       <c r="E269" s="2" t="n"/>
       <c r="F269" s="2" t="inlineStr"/>
-      <c r="G269" s="2" t="inlineStr">
+      <c r="G269" s="2" t="n"/>
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>Madrid, Spain</t>
         </is>
       </c>
-      <c r="H269" s="2" t="inlineStr">
+      <c r="I269" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I269" s="2" t="inlineStr">
+      <c r="J269" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12203,17 +12622,18 @@
       <c r="D270" s="2" t="n"/>
       <c r="E270" s="2" t="n"/>
       <c r="F270" s="2" t="inlineStr"/>
-      <c r="G270" s="2" t="inlineStr">
+      <c r="G270" s="2" t="n"/>
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>Stavanger, Norway</t>
         </is>
       </c>
-      <c r="H270" s="2" t="inlineStr">
+      <c r="I270" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I270" s="2" t="inlineStr">
+      <c r="J270" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12245,17 +12665,18 @@
       <c r="D271" s="2" t="n"/>
       <c r="E271" s="2" t="n"/>
       <c r="F271" s="2" t="inlineStr"/>
-      <c r="G271" s="2" t="inlineStr">
+      <c r="G271" s="2" t="n"/>
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>Karlsruhe, Germany</t>
         </is>
       </c>
-      <c r="H271" s="2" t="inlineStr">
+      <c r="I271" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I271" s="2" t="inlineStr">
+      <c r="J271" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12287,17 +12708,18 @@
       <c r="D272" s="2" t="n"/>
       <c r="E272" s="2" t="n"/>
       <c r="F272" s="2" t="inlineStr"/>
-      <c r="G272" s="2" t="inlineStr">
+      <c r="G272" s="2" t="n"/>
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>The Hague, Netherlands</t>
         </is>
       </c>
-      <c r="H272" s="2" t="inlineStr">
+      <c r="I272" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I272" s="2" t="inlineStr">
+      <c r="J272" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12329,17 +12751,18 @@
       <c r="D273" s="2" t="n"/>
       <c r="E273" s="2" t="n"/>
       <c r="F273" s="2" t="inlineStr"/>
-      <c r="G273" s="2" t="inlineStr">
+      <c r="G273" s="2" t="n"/>
+      <c r="H273" s="2" t="inlineStr">
         <is>
           <t>Paris, France</t>
         </is>
       </c>
-      <c r="H273" s="2" t="inlineStr">
+      <c r="I273" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I273" s="2" t="inlineStr">
+      <c r="J273" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12371,17 +12794,18 @@
       <c r="D274" s="2" t="n"/>
       <c r="E274" s="2" t="n"/>
       <c r="F274" s="2" t="inlineStr"/>
-      <c r="G274" s="2" t="inlineStr">
+      <c r="G274" s="2" t="n"/>
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="I274" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I274" s="2" t="inlineStr">
+      <c r="J274" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12413,17 +12837,18 @@
       <c r="D275" s="2" t="n"/>
       <c r="E275" s="2" t="n"/>
       <c r="F275" s="2" t="inlineStr"/>
-      <c r="G275" s="2" t="inlineStr">
+      <c r="G275" s="2" t="n"/>
+      <c r="H275" s="2" t="inlineStr">
         <is>
           <t>Netherlands/Germany</t>
         </is>
       </c>
-      <c r="H275" s="2" t="inlineStr">
+      <c r="I275" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I275" s="2" t="inlineStr">
+      <c r="J275" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12455,17 +12880,18 @@
       <c r="D276" s="2" t="n"/>
       <c r="E276" s="2" t="n"/>
       <c r="F276" s="2" t="inlineStr"/>
-      <c r="G276" s="2" t="inlineStr">
+      <c r="G276" s="2" t="n"/>
+      <c r="H276" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H276" s="2" t="inlineStr">
+      <c r="I276" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I276" s="2" t="inlineStr">
+      <c r="J276" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12497,17 +12923,18 @@
       <c r="D277" s="2" t="n"/>
       <c r="E277" s="2" t="n"/>
       <c r="F277" s="2" t="inlineStr"/>
-      <c r="G277" s="2" t="inlineStr">
+      <c r="G277" s="2" t="n"/>
+      <c r="H277" s="2" t="inlineStr">
         <is>
           <t>Rotterdam, Netherlands</t>
         </is>
       </c>
-      <c r="H277" s="2" t="inlineStr">
+      <c r="I277" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I277" s="2" t="inlineStr">
+      <c r="J277" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12539,17 +12966,18 @@
       <c r="D278" s="2" t="n"/>
       <c r="E278" s="2" t="n"/>
       <c r="F278" s="2" t="inlineStr"/>
-      <c r="G278" s="2" t="inlineStr">
+      <c r="G278" s="2" t="n"/>
+      <c r="H278" s="2" t="inlineStr">
         <is>
           <t>Papendrecht, Netherlands</t>
         </is>
       </c>
-      <c r="H278" s="2" t="inlineStr">
+      <c r="I278" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I278" s="2" t="inlineStr">
+      <c r="J278" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12586,20 +13014,25 @@
       </c>
       <c r="F279" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
           <t>+31 79 363 77 00</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr">
+      <c r="H279" s="2" t="inlineStr">
         <is>
           <t>Oslo, Norway</t>
         </is>
       </c>
-      <c r="H279" s="2" t="inlineStr">
+      <c r="I279" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I279" s="2" t="inlineStr">
+      <c r="J279" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12631,17 +13064,18 @@
       <c r="D280" s="2" t="n"/>
       <c r="E280" s="2" t="n"/>
       <c r="F280" s="2" t="inlineStr"/>
-      <c r="G280" s="2" t="inlineStr">
+      <c r="G280" s="2" t="n"/>
+      <c r="H280" s="2" t="inlineStr">
         <is>
           <t>Gothenburg, Sweden</t>
         </is>
       </c>
-      <c r="H280" s="2" t="inlineStr">
+      <c r="I280" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I280" s="2" t="inlineStr">
+      <c r="J280" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12673,17 +13107,18 @@
       <c r="D281" s="2" t="n"/>
       <c r="E281" s="2" t="n"/>
       <c r="F281" s="2" t="inlineStr"/>
-      <c r="G281" s="2" t="inlineStr">
+      <c r="G281" s="2" t="n"/>
+      <c r="H281" s="2" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="H281" s="2" t="inlineStr">
+      <c r="I281" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I281" s="2" t="inlineStr">
+      <c r="J281" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12715,17 +13150,18 @@
       <c r="D282" s="2" t="n"/>
       <c r="E282" s="2" t="n"/>
       <c r="F282" s="2" t="inlineStr"/>
-      <c r="G282" s="2" t="inlineStr">
+      <c r="G282" s="2" t="n"/>
+      <c r="H282" s="2" t="inlineStr">
         <is>
           <t>Dubai, UAE</t>
         </is>
       </c>
-      <c r="H282" s="2" t="inlineStr">
+      <c r="I282" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I282" s="2" t="inlineStr">
+      <c r="J282" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12757,17 +13193,18 @@
       <c r="D283" s="2" t="n"/>
       <c r="E283" s="2" t="n"/>
       <c r="F283" s="2" t="inlineStr"/>
-      <c r="G283" s="2" t="inlineStr">
+      <c r="G283" s="2" t="n"/>
+      <c r="H283" s="2" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="H283" s="2" t="inlineStr">
+      <c r="I283" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I283" s="2" t="inlineStr">
+      <c r="J283" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12799,17 +13236,18 @@
       <c r="D284" s="2" t="n"/>
       <c r="E284" s="2" t="n"/>
       <c r="F284" s="2" t="inlineStr"/>
-      <c r="G284" s="2" t="inlineStr">
+      <c r="G284" s="2" t="n"/>
+      <c r="H284" s="2" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="H284" s="2" t="inlineStr">
+      <c r="I284" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I284" s="2" t="inlineStr">
+      <c r="J284" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12841,17 +13279,18 @@
       <c r="D285" s="2" t="n"/>
       <c r="E285" s="2" t="n"/>
       <c r="F285" s="2" t="inlineStr"/>
-      <c r="G285" s="2" t="inlineStr">
+      <c r="G285" s="2" t="n"/>
+      <c r="H285" s="2" t="inlineStr">
         <is>
           <t>Sharjah, UAE</t>
         </is>
       </c>
-      <c r="H285" s="2" t="inlineStr">
+      <c r="I285" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I285" s="2" t="inlineStr">
+      <c r="J285" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12883,17 +13322,18 @@
       <c r="D286" s="2" t="n"/>
       <c r="E286" s="2" t="n"/>
       <c r="F286" s="2" t="inlineStr"/>
-      <c r="G286" s="2" t="inlineStr">
+      <c r="G286" s="2" t="n"/>
+      <c r="H286" s="2" t="inlineStr">
         <is>
           <t>UAE</t>
         </is>
       </c>
-      <c r="H286" s="2" t="inlineStr">
+      <c r="I286" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I286" s="2" t="inlineStr">
+      <c r="J286" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12925,17 +13365,18 @@
       <c r="D287" s="2" t="n"/>
       <c r="E287" s="2" t="n"/>
       <c r="F287" s="2" t="inlineStr"/>
-      <c r="G287" s="2" t="inlineStr">
+      <c r="G287" s="2" t="n"/>
+      <c r="H287" s="2" t="inlineStr">
         <is>
           <t>Marsa, Malta</t>
         </is>
       </c>
-      <c r="H287" s="2" t="inlineStr">
+      <c r="I287" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I287" s="2" t="inlineStr">
+      <c r="J287" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -12967,17 +13408,18 @@
       <c r="D288" s="2" t="n"/>
       <c r="E288" s="2" t="n"/>
       <c r="F288" s="2" t="inlineStr"/>
-      <c r="G288" s="2" t="inlineStr">
+      <c r="G288" s="2" t="n"/>
+      <c r="H288" s="2" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="H288" s="2" t="inlineStr">
+      <c r="I288" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I288" s="2" t="inlineStr">
+      <c r="J288" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13009,17 +13451,18 @@
       <c r="D289" s="2" t="n"/>
       <c r="E289" s="2" t="n"/>
       <c r="F289" s="2" t="inlineStr"/>
-      <c r="G289" s="2" t="inlineStr">
+      <c r="G289" s="2" t="n"/>
+      <c r="H289" s="2" t="inlineStr">
         <is>
           <t>Zamudio, Spain</t>
         </is>
       </c>
-      <c r="H289" s="2" t="inlineStr">
+      <c r="I289" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I289" s="2" t="inlineStr">
+      <c r="J289" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13051,17 +13494,18 @@
       <c r="D290" s="2" t="n"/>
       <c r="E290" s="2" t="n"/>
       <c r="F290" s="2" t="inlineStr"/>
-      <c r="G290" s="2" t="inlineStr">
+      <c r="G290" s="2" t="n"/>
+      <c r="H290" s="2" t="inlineStr">
         <is>
           <t>Saint-Nazaire, France</t>
         </is>
       </c>
-      <c r="H290" s="2" t="inlineStr">
+      <c r="I290" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I290" s="2" t="inlineStr">
+      <c r="J290" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13093,17 +13537,18 @@
       <c r="D291" s="2" t="n"/>
       <c r="E291" s="2" t="n"/>
       <c r="F291" s="2" t="inlineStr"/>
-      <c r="G291" s="2" t="inlineStr">
+      <c r="G291" s="2" t="n"/>
+      <c r="H291" s="2" t="inlineStr">
         <is>
           <t>Bilbao, Spain</t>
         </is>
       </c>
-      <c r="H291" s="2" t="inlineStr">
+      <c r="I291" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I291" s="2" t="inlineStr">
+      <c r="J291" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13135,17 +13580,18 @@
       <c r="D292" s="2" t="n"/>
       <c r="E292" s="2" t="n"/>
       <c r="F292" s="2" t="inlineStr"/>
-      <c r="G292" s="2" t="inlineStr">
+      <c r="G292" s="2" t="n"/>
+      <c r="H292" s="2" t="inlineStr">
         <is>
           <t>Portugal</t>
         </is>
       </c>
-      <c r="H292" s="2" t="inlineStr">
+      <c r="I292" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I292" s="2" t="inlineStr">
+      <c r="J292" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13177,17 +13623,18 @@
       <c r="D293" s="2" t="n"/>
       <c r="E293" s="2" t="n"/>
       <c r="F293" s="2" t="inlineStr"/>
-      <c r="G293" s="2" t="inlineStr">
+      <c r="G293" s="2" t="n"/>
+      <c r="H293" s="2" t="inlineStr">
         <is>
           <t>Kolding, Denmark</t>
         </is>
       </c>
-      <c r="H293" s="2" t="inlineStr">
+      <c r="I293" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I293" s="2" t="inlineStr">
+      <c r="J293" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13219,17 +13666,18 @@
       <c r="D294" s="2" t="n"/>
       <c r="E294" s="2" t="n"/>
       <c r="F294" s="2" t="inlineStr"/>
-      <c r="G294" s="2" t="inlineStr">
+      <c r="G294" s="2" t="n"/>
+      <c r="H294" s="2" t="inlineStr">
         <is>
           <t>Bocholt, Germany</t>
         </is>
       </c>
-      <c r="H294" s="2" t="inlineStr">
+      <c r="I294" s="2" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="I294" s="2" t="inlineStr">
+      <c r="J294" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13269,25 +13717,30 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>info@woodthilsted.com</t>
-        </is>
-      </c>
-      <c r="F295" s="2" t="inlineStr">
+          <t>clt@woodthilsted.com</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="inlineStr">
+        <is>
+          <t>Directory listing - verify before sending</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
         <is>
           <t>+44 303 123 1113</t>
         </is>
       </c>
-      <c r="G295" s="2" t="inlineStr">
+      <c r="H295" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="H295" s="2" t="inlineStr">
+      <c r="I295" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I295" s="2" t="inlineStr">
+      <c r="J295" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Christian,
@@ -13319,17 +13772,18 @@
       <c r="D296" s="2" t="n"/>
       <c r="E296" s="2" t="n"/>
       <c r="F296" s="2" t="inlineStr"/>
-      <c r="G296" s="2" t="inlineStr">
+      <c r="G296" s="2" t="n"/>
+      <c r="H296" s="2" t="inlineStr">
         <is>
           <t>Epsom, UK</t>
         </is>
       </c>
-      <c r="H296" s="2" t="inlineStr">
+      <c r="I296" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I296" s="2" t="inlineStr">
+      <c r="J296" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13361,17 +13815,18 @@
       <c r="D297" s="2" t="n"/>
       <c r="E297" s="2" t="n"/>
       <c r="F297" s="2" t="inlineStr"/>
-      <c r="G297" s="2" t="inlineStr">
+      <c r="G297" s="2" t="n"/>
+      <c r="H297" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="H297" s="2" t="inlineStr">
+      <c r="I297" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I297" s="2" t="inlineStr">
+      <c r="J297" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13403,17 +13858,18 @@
       <c r="D298" s="2" t="n"/>
       <c r="E298" s="2" t="n"/>
       <c r="F298" s="2" t="inlineStr"/>
-      <c r="G298" s="2" t="inlineStr">
+      <c r="G298" s="2" t="n"/>
+      <c r="H298" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="H298" s="2" t="inlineStr">
+      <c r="I298" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I298" s="2" t="inlineStr">
+      <c r="J298" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13445,17 +13901,18 @@
       <c r="D299" s="2" t="n"/>
       <c r="E299" s="2" t="n"/>
       <c r="F299" s="2" t="inlineStr"/>
-      <c r="G299" s="2" t="inlineStr">
+      <c r="G299" s="2" t="n"/>
+      <c r="H299" s="2" t="inlineStr">
         <is>
           <t>Scotland, UK</t>
         </is>
       </c>
-      <c r="H299" s="2" t="inlineStr">
+      <c r="I299" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I299" s="2" t="inlineStr">
+      <c r="J299" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13490,22 +13947,23 @@
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Head of Offshore Wind Foundation Design (division launched 2025)</t>
+          <t>Head of Offshore Wind Foundation Design / global director for offshore wind design, based in Oslo</t>
         </is>
       </c>
       <c r="E300" s="2" t="n"/>
       <c r="F300" s="2" t="inlineStr"/>
-      <c r="G300" s="2" t="inlineStr">
+      <c r="G300" s="2" t="n"/>
+      <c r="H300" s="2" t="inlineStr">
         <is>
           <t>London, UK</t>
         </is>
       </c>
-      <c r="H300" s="2" t="inlineStr">
+      <c r="I300" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I300" s="2" t="inlineStr">
+      <c r="J300" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi Jan,
@@ -13537,17 +13995,18 @@
       <c r="D301" s="2" t="n"/>
       <c r="E301" s="2" t="n"/>
       <c r="F301" s="2" t="inlineStr"/>
-      <c r="G301" s="2" t="inlineStr">
+      <c r="G301" s="2" t="n"/>
+      <c r="H301" s="2" t="inlineStr">
         <is>
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="H301" s="2" t="inlineStr">
+      <c r="I301" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I301" s="2" t="inlineStr">
+      <c r="J301" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13584,20 +14043,25 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
+          <t>Company website (general inbox)</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
           <t>+31 (0)10 2883 000</t>
         </is>
       </c>
-      <c r="G302" s="2" t="inlineStr">
+      <c r="H302" s="2" t="inlineStr">
         <is>
           <t>Schiedam, Netherlands</t>
         </is>
       </c>
-      <c r="H302" s="2" t="inlineStr">
+      <c r="I302" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I302" s="2" t="inlineStr">
+      <c r="J302" s="2" t="inlineStr">
         <is>
           <t>Subject: Overflow FEA &amp; Structural Engineering Support
 Hi there,
@@ -13615,7 +14079,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>